--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -25,18 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">19/11/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/11/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/11/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/11/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">25/11/2024 12:00:00</t>
   </si>
   <si>
@@ -728,6 +716,9 @@
   </si>
   <si>
     <t xml:space="preserve">19/11/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/11/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -792,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
@@ -816,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>114800000</v>
+        <v>90000000</v>
       </c>
       <c r="C2" t="n">
-        <v>1002.1282</v>
+        <v>1006.3558</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -827,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>141160000</v>
+        <v>92330000</v>
       </c>
       <c r="C3" t="n">
-        <v>1002.85016</v>
+        <v>1007.11914</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -838,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>82280000</v>
+        <v>99270000</v>
       </c>
       <c r="C4" t="n">
-        <v>1004.0003</v>
+        <v>1008.05896</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -849,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>51500000</v>
+        <v>227840000</v>
       </c>
       <c r="C5" t="n">
-        <v>1003.9272</v>
+        <v>1009.5345</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -860,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>90000000</v>
+        <v>139630000</v>
       </c>
       <c r="C6" t="n">
-        <v>1006.3558</v>
+        <v>1011.75397</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -871,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>92330000</v>
+        <v>76610000</v>
       </c>
       <c r="C7" t="n">
-        <v>1007.11914</v>
+        <v>1012.0545</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -882,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>99270000</v>
+        <v>85800000</v>
       </c>
       <c r="C8" t="n">
-        <v>1008.05896</v>
+        <v>1012.7305</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -893,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>227840000</v>
+        <v>125840000</v>
       </c>
       <c r="C9" t="n">
-        <v>1009.5345</v>
+        <v>1013.0277</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -904,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>139630000</v>
+        <v>136540000</v>
       </c>
       <c r="C10" t="n">
-        <v>1011.75397</v>
+        <v>1012.78424</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -915,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>76610000</v>
+        <v>84630000</v>
       </c>
       <c r="C11" t="n">
-        <v>1012.0545</v>
+        <v>1015.8393</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -926,10 +917,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>85800000</v>
+        <v>53100000</v>
       </c>
       <c r="C12" t="n">
-        <v>1012.7305</v>
+        <v>1016.1278</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -937,10 +928,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>125840000</v>
+        <v>154600000</v>
       </c>
       <c r="C13" t="n">
-        <v>1013.0277</v>
+        <v>1016.7524</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -948,10 +939,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>136540000</v>
+        <v>166760000</v>
       </c>
       <c r="C14" t="n">
-        <v>1012.78424</v>
+        <v>1017.8712</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -959,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>84630000</v>
+        <v>120700000</v>
       </c>
       <c r="C15" t="n">
-        <v>1015.8393</v>
+        <v>1017.9877</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -970,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>53100000</v>
+        <v>136460000</v>
       </c>
       <c r="C16" t="n">
-        <v>1016.1278</v>
+        <v>1020.63074</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -981,10 +972,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>154600000</v>
+        <v>109500000</v>
       </c>
       <c r="C17" t="n">
-        <v>1016.7524</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -992,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>166760000</v>
+        <v>103710000</v>
       </c>
       <c r="C18" t="n">
-        <v>1017.8712</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -1003,10 +994,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>120700000</v>
+        <v>70020000</v>
       </c>
       <c r="C19" t="n">
-        <v>1017.9877</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1014,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>136460000</v>
+        <v>105600000</v>
       </c>
       <c r="C20" t="n">
-        <v>1020.63074</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1025,10 +1016,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>109500000</v>
+        <v>60970000</v>
       </c>
       <c r="C21" t="n">
-        <v>1020.69635</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1036,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>103710000</v>
+        <v>135210000</v>
       </c>
       <c r="C22" t="n">
-        <v>1021.90955</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1047,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>70020000</v>
+        <v>214050000</v>
       </c>
       <c r="C23" t="n">
-        <v>1022.2438</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1058,10 +1049,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>105600000</v>
+        <v>170650000</v>
       </c>
       <c r="C24" t="n">
-        <v>1022.24274</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1069,10 +1060,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>60970000</v>
+        <v>129920000</v>
       </c>
       <c r="C25" t="n">
-        <v>1025.3103</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1080,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>135210000</v>
+        <v>90600000</v>
       </c>
       <c r="C26" t="n">
-        <v>1028.5804</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1091,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>214050000</v>
+        <v>94620000</v>
       </c>
       <c r="C27" t="n">
-        <v>1028.1958</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1102,10 +1093,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>170650000</v>
+        <v>76740000</v>
       </c>
       <c r="C28" t="n">
-        <v>1030.4104</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1113,10 +1104,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>129920000</v>
+        <v>60220000</v>
       </c>
       <c r="C29" t="n">
-        <v>1031.7577</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1124,10 +1115,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>90600000</v>
+        <v>80100000</v>
       </c>
       <c r="C30" t="n">
-        <v>1032.4374</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1135,10 +1126,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>94620000</v>
+        <v>144200000</v>
       </c>
       <c r="C31" t="n">
-        <v>1034.7297</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1146,10 +1137,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>76740000</v>
+        <v>66560000</v>
       </c>
       <c r="C32" t="n">
-        <v>1035.4338</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1157,10 +1148,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>60220000</v>
+        <v>69770000</v>
       </c>
       <c r="C33" t="n">
-        <v>1035.8505</v>
+        <v>1040.3352</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1168,10 +1159,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>80100000</v>
+        <v>59000000</v>
       </c>
       <c r="C34" t="n">
-        <v>1036.7753</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1179,10 +1170,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>144200000</v>
+        <v>97600000</v>
       </c>
       <c r="C35" t="n">
-        <v>1036.8966</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1190,10 +1181,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>66560000</v>
+        <v>139000000</v>
       </c>
       <c r="C36" t="n">
-        <v>1039.2858</v>
+        <v>1041.9935</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1201,10 +1192,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>69770000</v>
+        <v>215030000</v>
       </c>
       <c r="C37" t="n">
-        <v>1040.3352</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1212,10 +1203,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>59000000</v>
+        <v>117720000</v>
       </c>
       <c r="C38" t="n">
-        <v>1040.7654</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1223,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>97600000</v>
+        <v>55800000</v>
       </c>
       <c r="C39" t="n">
-        <v>1041.2943</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1234,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>139000000</v>
+        <v>135550000</v>
       </c>
       <c r="C40" t="n">
-        <v>1041.9935</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1245,10 +1236,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>215030000</v>
+        <v>89000000</v>
       </c>
       <c r="C41" t="n">
-        <v>1045.5352</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1256,10 +1247,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>117720000</v>
+        <v>58100000</v>
       </c>
       <c r="C42" t="n">
-        <v>1046.7697</v>
+        <v>1050.2393</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1267,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>55800000</v>
+        <v>86600000</v>
       </c>
       <c r="C43" t="n">
-        <v>1046.9908</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1278,10 +1269,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>135550000</v>
+        <v>95150000</v>
       </c>
       <c r="C44" t="n">
-        <v>1046.9497</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1289,10 +1280,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>89000000</v>
+        <v>147140000</v>
       </c>
       <c r="C45" t="n">
-        <v>1049.7869</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1300,10 +1291,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>58100000</v>
+        <v>123760000</v>
       </c>
       <c r="C46" t="n">
-        <v>1050.2393</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1311,10 +1302,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>86600000</v>
+        <v>88880000</v>
       </c>
       <c r="C47" t="n">
-        <v>1051.1277</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1322,10 +1313,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>95150000</v>
+        <v>115600000</v>
       </c>
       <c r="C48" t="n">
-        <v>1051.69</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1333,10 +1324,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>147140000</v>
+        <v>93120000</v>
       </c>
       <c r="C49" t="n">
-        <v>1051.1226</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1344,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>123760000</v>
+        <v>162410000</v>
       </c>
       <c r="C50" t="n">
-        <v>1053.3625</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1355,10 +1346,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>88880000</v>
+        <v>191440000</v>
       </c>
       <c r="C51" t="n">
-        <v>1053.5273</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1366,10 +1357,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>115600000</v>
+        <v>98800000</v>
       </c>
       <c r="C52" t="n">
-        <v>1053.941</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1377,10 +1368,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>93120000</v>
+        <v>151830000</v>
       </c>
       <c r="C53" t="n">
-        <v>1054.1022</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1388,10 +1379,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>162410000</v>
+        <v>63730000</v>
       </c>
       <c r="C54" t="n">
-        <v>1053.6134</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1399,10 +1390,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>191440000</v>
+        <v>154380000</v>
       </c>
       <c r="C55" t="n">
-        <v>1055.6161</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1410,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>98800000</v>
+        <v>127430000</v>
       </c>
       <c r="C56" t="n">
-        <v>1055.6309</v>
+        <v>1058.3726</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1421,10 +1412,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>151830000</v>
+        <v>90150000</v>
       </c>
       <c r="C57" t="n">
-        <v>1056.2124</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1432,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>63730000</v>
+        <v>78400000</v>
       </c>
       <c r="C58" t="n">
-        <v>1056.7262</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1443,10 +1434,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>154380000</v>
+        <v>102390000</v>
       </c>
       <c r="C59" t="n">
-        <v>1056.4021</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1454,10 +1445,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>127430000</v>
+        <v>106130000</v>
       </c>
       <c r="C60" t="n">
-        <v>1058.3726</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1465,10 +1456,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>90150000</v>
+        <v>81520000</v>
       </c>
       <c r="C61" t="n">
-        <v>1058.5518</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1476,10 +1467,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>78400000</v>
+        <v>107290000</v>
       </c>
       <c r="C62" t="n">
-        <v>1059.0238</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1487,10 +1478,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>102390000</v>
+        <v>78500000</v>
       </c>
       <c r="C63" t="n">
-        <v>1058.5037</v>
+        <v>1061.6616</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1498,10 +1489,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>106130000</v>
+        <v>115700000</v>
       </c>
       <c r="C64" t="n">
-        <v>1060.2593</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1509,10 +1500,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>81520000</v>
+        <v>135350000</v>
       </c>
       <c r="C65" t="n">
-        <v>1060.7654</v>
+        <v>1063.4131</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1520,10 +1511,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>107290000</v>
+        <v>156190000</v>
       </c>
       <c r="C66" t="n">
-        <v>1061.1646</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1531,10 +1522,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>78500000</v>
+        <v>203700000</v>
       </c>
       <c r="C67" t="n">
-        <v>1061.6616</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1542,10 +1533,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>115700000</v>
+        <v>153120000</v>
       </c>
       <c r="C68" t="n">
-        <v>1062.0686</v>
+        <v>1065.5394</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1553,10 +1544,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>135350000</v>
+        <v>154930000</v>
       </c>
       <c r="C69" t="n">
-        <v>1063.4131</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1564,10 +1555,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>156190000</v>
+        <v>101660000</v>
       </c>
       <c r="C70" t="n">
-        <v>1063.8278</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1575,10 +1566,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>203700000</v>
+        <v>90000000</v>
       </c>
       <c r="C71" t="n">
-        <v>1064.3394</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1586,10 +1577,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>153120000</v>
+        <v>266600000</v>
       </c>
       <c r="C72" t="n">
-        <v>1065.5394</v>
+        <v>1066.7456</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1597,10 +1588,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>154930000</v>
+        <v>146970000</v>
       </c>
       <c r="C73" t="n">
-        <v>1065.7025</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1608,10 +1599,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>101660000</v>
+        <v>61200000</v>
       </c>
       <c r="C74" t="n">
-        <v>1066.0099</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1619,10 +1610,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>90000000</v>
+        <v>69170000</v>
       </c>
       <c r="C75" t="n">
-        <v>1066.2288</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1630,10 +1621,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>266600000</v>
+        <v>41240000</v>
       </c>
       <c r="C76" t="n">
-        <v>1066.7456</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1641,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>146970000</v>
+        <v>145230000</v>
       </c>
       <c r="C77" t="n">
-        <v>1068.2128</v>
+        <v>1068.3027</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1652,10 +1643,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>61200000</v>
+        <v>120040000</v>
       </c>
       <c r="C78" t="n">
-        <v>1068.3644</v>
+        <v>1070.8257</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1663,10 +1654,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>69170000</v>
+        <v>105520000</v>
       </c>
       <c r="C79" t="n">
-        <v>1069.0115</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1674,10 +1665,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>41240000</v>
+        <v>180350000</v>
       </c>
       <c r="C80" t="n">
-        <v>1069.0428</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1685,10 +1676,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>145230000</v>
+        <v>157240000</v>
       </c>
       <c r="C81" t="n">
-        <v>1068.3027</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1696,10 +1687,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>120040000</v>
+        <v>204650000</v>
       </c>
       <c r="C82" t="n">
-        <v>1070.8257</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1707,10 +1698,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>105520000</v>
+        <v>127150000</v>
       </c>
       <c r="C83" t="n">
-        <v>1071.3093</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1718,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>180350000</v>
+        <v>54310000</v>
       </c>
       <c r="C84" t="n">
-        <v>1071.5227</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1729,10 +1720,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>157240000</v>
+        <v>75470000</v>
       </c>
       <c r="C85" t="n">
-        <v>1070.9691</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1740,10 +1731,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>204650000</v>
+        <v>79680000</v>
       </c>
       <c r="C86" t="n">
-        <v>1073.0979</v>
+        <v>1075.5159</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1751,10 +1742,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>127150000</v>
+        <v>62750000</v>
       </c>
       <c r="C87" t="n">
-        <v>1072.918</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1762,10 +1753,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>54310000</v>
+        <v>75600000</v>
       </c>
       <c r="C88" t="n">
-        <v>1074.1038</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1773,10 +1764,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>75470000</v>
+        <v>63990000</v>
       </c>
       <c r="C89" t="n">
-        <v>1073.4634</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1784,10 +1775,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>79680000</v>
+        <v>225590000</v>
       </c>
       <c r="C90" t="n">
-        <v>1075.5159</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1795,10 +1786,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>62750000</v>
+        <v>415320000</v>
       </c>
       <c r="C91" t="n">
-        <v>1075.8248</v>
+        <v>1189.2566</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1806,10 +1797,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>75600000</v>
+        <v>230200000</v>
       </c>
       <c r="C92" t="n">
-        <v>1076.5104</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1817,10 +1808,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>63990000</v>
+        <v>347690000</v>
       </c>
       <c r="C93" t="n">
-        <v>1076.5854</v>
+        <v>1162.0159</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1828,10 +1819,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>225590000</v>
+        <v>339050000</v>
       </c>
       <c r="C94" t="n">
-        <v>1075.3297</v>
+        <v>1082.272</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1839,10 +1830,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>415320000</v>
+        <v>335470000</v>
       </c>
       <c r="C95" t="n">
-        <v>1189.2566</v>
+        <v>1092.0538</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1850,10 +1841,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>230200000</v>
+        <v>410800000</v>
       </c>
       <c r="C96" t="n">
-        <v>1199.1798</v>
+        <v>1135.2747</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1861,10 +1852,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>347690000</v>
+        <v>530219970</v>
       </c>
       <c r="C97" t="n">
-        <v>1162.0159</v>
+        <v>1176.6918</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1872,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>339050000</v>
+        <v>368410020</v>
       </c>
       <c r="C98" t="n">
-        <v>1082.272</v>
+        <v>1173.9497</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1883,10 +1874,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>335470000</v>
+        <v>359710000</v>
       </c>
       <c r="C99" t="n">
-        <v>1092.0538</v>
+        <v>1164.8855</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1894,10 +1885,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>410800000</v>
+        <v>327350000</v>
       </c>
       <c r="C100" t="n">
-        <v>1135.2747</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1905,10 +1896,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>530219970</v>
+        <v>451770000</v>
       </c>
       <c r="C101" t="n">
-        <v>1176.6918</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1916,10 +1907,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>368410020</v>
+        <v>373390000</v>
       </c>
       <c r="C102" t="n">
-        <v>1173.9497</v>
+        <v>1182.7354</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1927,10 +1918,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>359710000</v>
+        <v>267550000</v>
       </c>
       <c r="C103" t="n">
-        <v>1164.8855</v>
+        <v>1201.8551</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1938,10 +1929,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>327350000</v>
+        <v>298740000</v>
       </c>
       <c r="C104" t="n">
-        <v>1171.4315</v>
+        <v>1150.9364</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1949,10 +1940,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>451770000</v>
+        <v>263150000</v>
       </c>
       <c r="C105" t="n">
-        <v>1169.5444</v>
+        <v>1115.3589</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1960,10 +1951,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>373390000</v>
+        <v>200590000</v>
       </c>
       <c r="C106" t="n">
-        <v>1182.7354</v>
+        <v>1114.4547</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1971,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>267550000</v>
+        <v>279730000</v>
       </c>
       <c r="C107" t="n">
-        <v>1201.8551</v>
+        <v>1128.0269</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1982,10 +1973,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>298740000</v>
+        <v>395650020</v>
       </c>
       <c r="C108" t="n">
-        <v>1150.9364</v>
+        <v>1124.8623</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1993,10 +1984,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>263150000</v>
+        <v>331410020</v>
       </c>
       <c r="C109" t="n">
-        <v>1115.3589</v>
+        <v>1130.4915</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -2004,10 +1995,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>200590000</v>
+        <v>261090000</v>
       </c>
       <c r="C110" t="n">
-        <v>1114.4547</v>
+        <v>1135.9207</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2015,10 +2006,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>279730000</v>
+        <v>242790000</v>
       </c>
       <c r="C111" t="n">
-        <v>1128.0269</v>
+        <v>1144.8073</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2026,10 +2017,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>395650020</v>
+        <v>193430000</v>
       </c>
       <c r="C112" t="n">
-        <v>1124.8623</v>
+        <v>1134.3671</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2037,10 +2028,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>331410020</v>
+        <v>206570000</v>
       </c>
       <c r="C113" t="n">
-        <v>1130.4915</v>
+        <v>1143.0444</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2048,10 +2039,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>261090000</v>
+        <v>295490020</v>
       </c>
       <c r="C114" t="n">
-        <v>1135.9207</v>
+        <v>1144.6138</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2059,10 +2050,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>242790000</v>
+        <v>241590000</v>
       </c>
       <c r="C115" t="n">
-        <v>1144.8073</v>
+        <v>1142.3444</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2070,10 +2061,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>193430000</v>
+        <v>315600000</v>
       </c>
       <c r="C116" t="n">
-        <v>1134.3671</v>
+        <v>1136.4617</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2081,10 +2072,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>206570000</v>
+        <v>322010000</v>
       </c>
       <c r="C117" t="n">
-        <v>1143.0444</v>
+        <v>1148.4205</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2092,10 +2083,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>295490020</v>
+        <v>274060000</v>
       </c>
       <c r="C118" t="n">
-        <v>1144.6138</v>
+        <v>1162.3146</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2103,10 +2094,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>241590000</v>
+        <v>201240000</v>
       </c>
       <c r="C119" t="n">
-        <v>1142.3444</v>
+        <v>1175.8934</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2114,10 +2105,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>315600000</v>
+        <v>200400000</v>
       </c>
       <c r="C120" t="n">
-        <v>1136.4617</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2125,10 +2116,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>322010000</v>
+        <v>219350000</v>
       </c>
       <c r="C121" t="n">
-        <v>1148.4205</v>
+        <v>1182.2738</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2136,10 +2127,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>274060000</v>
+        <v>191080000</v>
       </c>
       <c r="C122" t="n">
-        <v>1162.3146</v>
+        <v>1185.7009</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2147,10 +2138,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>201240000</v>
+        <v>279980000</v>
       </c>
       <c r="C123" t="n">
-        <v>1175.8934</v>
+        <v>1184.3539</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2158,10 +2149,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>200400000</v>
+        <v>210400000</v>
       </c>
       <c r="C124" t="n">
-        <v>1196.2443</v>
+        <v>1190.1604</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2169,10 +2160,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>219350000</v>
+        <v>149050000</v>
       </c>
       <c r="C125" t="n">
-        <v>1182.2738</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2180,10 +2171,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>191080000</v>
+        <v>206060000</v>
       </c>
       <c r="C126" t="n">
-        <v>1185.7009</v>
+        <v>1187.3215</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2191,10 +2182,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>279980000</v>
+        <v>327800000</v>
       </c>
       <c r="C127" t="n">
-        <v>1184.3539</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2202,10 +2193,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>210400000</v>
+        <v>194900000</v>
       </c>
       <c r="C128" t="n">
-        <v>1190.1604</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2213,10 +2204,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>149050000</v>
+        <v>150070000</v>
       </c>
       <c r="C129" t="n">
-        <v>1189.0756</v>
+        <v>1186.3999</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2224,10 +2215,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>206060000</v>
+        <v>249730000</v>
       </c>
       <c r="C130" t="n">
-        <v>1187.3215</v>
+        <v>1184.7565</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2235,10 +2226,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>327800000</v>
+        <v>328930000</v>
       </c>
       <c r="C131" t="n">
-        <v>1187.3528</v>
+        <v>1177.4198</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2246,10 +2237,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>194900000</v>
+        <v>319130000</v>
       </c>
       <c r="C132" t="n">
-        <v>1183.6859</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2257,10 +2248,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>150070000</v>
+        <v>290900000</v>
       </c>
       <c r="C133" t="n">
-        <v>1186.3999</v>
+        <v>1168.4825</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2268,10 +2259,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>249730000</v>
+        <v>272000000</v>
       </c>
       <c r="C134" t="n">
-        <v>1184.7565</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2279,10 +2270,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>328930000</v>
+        <v>459869980</v>
       </c>
       <c r="C135" t="n">
-        <v>1177.4198</v>
+        <v>1176.724</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2290,10 +2281,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>319130000</v>
+        <v>250980000</v>
       </c>
       <c r="C136" t="n">
-        <v>1146.302</v>
+        <v>1192.3014</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2301,10 +2292,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>290900000</v>
+        <v>317930020</v>
       </c>
       <c r="C137" t="n">
-        <v>1168.4825</v>
+        <v>1187.0327</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2312,10 +2303,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>272000000</v>
+        <v>359550000</v>
       </c>
       <c r="C138" t="n">
-        <v>1178.1132</v>
+        <v>1193.3121</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2323,10 +2314,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>459869980</v>
+        <v>279650000</v>
       </c>
       <c r="C139" t="n">
-        <v>1176.724</v>
+        <v>1207.8153</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2334,10 +2325,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>250980000</v>
+        <v>286200000</v>
       </c>
       <c r="C140" t="n">
-        <v>1192.3014</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2345,10 +2336,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>317930020</v>
+        <v>343900000</v>
       </c>
       <c r="C141" t="n">
-        <v>1187.0327</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2356,10 +2347,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>359550000</v>
+        <v>310469980</v>
       </c>
       <c r="C142" t="n">
-        <v>1193.3121</v>
+        <v>1263.1807</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2367,10 +2358,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>279650000</v>
+        <v>324740000</v>
       </c>
       <c r="C143" t="n">
-        <v>1207.8153</v>
+        <v>1257.3591</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2378,10 +2369,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>286200000</v>
+        <v>301200000</v>
       </c>
       <c r="C144" t="n">
-        <v>1232.3434</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2389,10 +2380,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>343900000</v>
+        <v>298320000</v>
       </c>
       <c r="C145" t="n">
-        <v>1225.9089</v>
+        <v>1261.3674</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2400,10 +2391,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>310469980</v>
+        <v>393980000</v>
       </c>
       <c r="C146" t="n">
-        <v>1263.1807</v>
+        <v>1268.4539</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2411,10 +2402,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>324740000</v>
+        <v>398920000</v>
       </c>
       <c r="C147" t="n">
-        <v>1257.3591</v>
+        <v>1277.0442</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2422,10 +2413,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>301200000</v>
+        <v>323589980</v>
       </c>
       <c r="C148" t="n">
-        <v>1261.2496</v>
+        <v>1257.8407</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2433,10 +2424,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>298320000</v>
+        <v>307460000</v>
       </c>
       <c r="C149" t="n">
-        <v>1261.3674</v>
+        <v>1266.7705</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2444,10 +2435,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>393980000</v>
+        <v>297000000</v>
       </c>
       <c r="C150" t="n">
-        <v>1268.4539</v>
+        <v>1282.9014</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2455,10 +2446,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>398920000</v>
+        <v>291500000</v>
       </c>
       <c r="C151" t="n">
-        <v>1277.0442</v>
+        <v>1287.3074</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2466,10 +2457,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>323589980</v>
+        <v>242700000</v>
       </c>
       <c r="C152" t="n">
-        <v>1257.8407</v>
+        <v>1261.0431</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2477,10 +2468,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>307460000</v>
+        <v>183370000</v>
       </c>
       <c r="C153" t="n">
-        <v>1266.7705</v>
+        <v>1259.6431</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2488,10 +2479,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>297000000</v>
+        <v>241900000</v>
       </c>
       <c r="C154" t="n">
-        <v>1282.9014</v>
+        <v>1261.7827</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2499,10 +2490,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>291500000</v>
+        <v>273740000</v>
       </c>
       <c r="C155" t="n">
-        <v>1287.3074</v>
+        <v>1278.3439</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2510,10 +2501,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>242700000</v>
+        <v>212100000</v>
       </c>
       <c r="C156" t="n">
-        <v>1261.0431</v>
+        <v>1290.4368</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2521,10 +2512,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>183370000</v>
+        <v>308300000</v>
       </c>
       <c r="C157" t="n">
-        <v>1259.6431</v>
+        <v>1295.2062</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2532,10 +2523,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>241900000</v>
+        <v>165990000</v>
       </c>
       <c r="C158" t="n">
-        <v>1261.7827</v>
+        <v>1297.3245</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2543,10 +2534,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>273740000</v>
+        <v>328600000</v>
       </c>
       <c r="C159" t="n">
-        <v>1278.3439</v>
+        <v>1356.9905</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2554,10 +2545,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>212100000</v>
+        <v>213740000</v>
       </c>
       <c r="C160" t="n">
-        <v>1290.4368</v>
+        <v>1364.9016</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2565,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>308300000</v>
+        <v>220980000</v>
       </c>
       <c r="C161" t="n">
-        <v>1295.2062</v>
+        <v>1362.0563</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2576,10 +2567,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>165990000</v>
+        <v>311760000</v>
       </c>
       <c r="C162" t="n">
-        <v>1297.3245</v>
+        <v>1348.5603</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2587,10 +2578,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>328600000</v>
+        <v>324880000</v>
       </c>
       <c r="C163" t="n">
-        <v>1356.9905</v>
+        <v>1333.3021</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2598,10 +2589,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>213740000</v>
+        <v>194200000</v>
       </c>
       <c r="C164" t="n">
-        <v>1364.9016</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2609,10 +2600,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>220980000</v>
+        <v>219200000</v>
       </c>
       <c r="C165" t="n">
-        <v>1362.0563</v>
+        <v>1324.7318</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2620,10 +2611,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>311760000</v>
+        <v>265100000</v>
       </c>
       <c r="C166" t="n">
-        <v>1348.5603</v>
+        <v>1327.6051</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2631,10 +2622,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>324880000</v>
+        <v>318140000</v>
       </c>
       <c r="C167" t="n">
-        <v>1333.3021</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2642,10 +2633,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>194200000</v>
+        <v>323640000</v>
       </c>
       <c r="C168" t="n">
-        <v>1329.5576</v>
+        <v>1317.7236</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2653,10 +2644,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>219200000</v>
+        <v>258100000</v>
       </c>
       <c r="C169" t="n">
-        <v>1324.7318</v>
+        <v>1298.1354</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2664,10 +2655,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>265100000</v>
+        <v>245450000</v>
       </c>
       <c r="C170" t="n">
-        <v>1327.6051</v>
+        <v>1296.6604</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2675,10 +2666,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>318140000</v>
+        <v>388200000</v>
       </c>
       <c r="C171" t="n">
-        <v>1317.6909</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2686,10 +2677,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>323640000</v>
+        <v>218250000</v>
       </c>
       <c r="C172" t="n">
-        <v>1317.7236</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2697,10 +2688,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>258100000</v>
+        <v>135000000</v>
       </c>
       <c r="C173" t="n">
-        <v>1298.1354</v>
+        <v>1311.6772</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2708,10 +2699,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>245450000</v>
+        <v>230420000</v>
       </c>
       <c r="C174" t="n">
-        <v>1296.6604</v>
+        <v>1322.6124</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2719,10 +2710,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>388200000</v>
+        <v>186010000</v>
       </c>
       <c r="C175" t="n">
-        <v>1293.891</v>
+        <v>1349.7784</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2730,10 +2721,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>218250000</v>
+        <v>324380030</v>
       </c>
       <c r="C176" t="n">
-        <v>1299.0688</v>
+        <v>1353.8983</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2741,10 +2732,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>135000000</v>
+        <v>188250000</v>
       </c>
       <c r="C177" t="n">
-        <v>1311.6772</v>
+        <v>1360.0109</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2752,10 +2743,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>230420000</v>
+        <v>262170000</v>
       </c>
       <c r="C178" t="n">
-        <v>1322.6124</v>
+        <v>1338.8644</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2763,10 +2754,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>186010000</v>
+        <v>250290000</v>
       </c>
       <c r="C179" t="n">
-        <v>1349.7784</v>
+        <v>1330.1</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2774,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>324380030</v>
+        <v>396959970</v>
       </c>
       <c r="C180" t="n">
-        <v>1353.8983</v>
+        <v>1365.2227</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2785,10 +2776,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>188250000</v>
+        <v>181300000</v>
       </c>
       <c r="C181" t="n">
-        <v>1360.0109</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2796,10 +2787,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>262170000</v>
+        <v>349490020</v>
       </c>
       <c r="C182" t="n">
-        <v>1338.8644</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2807,10 +2798,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>250290000</v>
+        <v>354610000</v>
       </c>
       <c r="C183" t="n">
-        <v>1330.1</v>
+        <v>1366.1195</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2818,10 +2809,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>396959970</v>
+        <v>268370000</v>
       </c>
       <c r="C184" t="n">
-        <v>1365.2227</v>
+        <v>1424.0857</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2829,10 +2820,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>181300000</v>
+        <v>217230000</v>
       </c>
       <c r="C185" t="n">
-        <v>1361.4104</v>
+        <v>1419.2256</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2840,10 +2831,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>349490020</v>
+        <v>202800000</v>
       </c>
       <c r="C186" t="n">
-        <v>1362.602</v>
+        <v>1418.7972</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2851,10 +2842,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>354610000</v>
+        <v>182600000</v>
       </c>
       <c r="C187" t="n">
-        <v>1366.1195</v>
+        <v>1428.8694</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2862,10 +2853,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>268370000</v>
+        <v>186830000</v>
       </c>
       <c r="C188" t="n">
-        <v>1424.0857</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2873,10 +2864,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>217230000</v>
+        <v>256060000</v>
       </c>
       <c r="C189" t="n">
-        <v>1419.2256</v>
+        <v>1463.7825</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2884,10 +2875,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>202800000</v>
+        <v>181350000</v>
       </c>
       <c r="C190" t="n">
-        <v>1418.7972</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2895,10 +2886,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>182600000</v>
+        <v>175400000</v>
       </c>
       <c r="C191" t="n">
-        <v>1428.8694</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2906,10 +2897,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>186830000</v>
+        <v>231000000</v>
       </c>
       <c r="C192" t="n">
-        <v>1450.185</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2917,10 +2908,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>256060000</v>
+        <v>286250020</v>
       </c>
       <c r="C193" t="n">
-        <v>1463.7825</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2928,10 +2919,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>181350000</v>
+        <v>202930000</v>
       </c>
       <c r="C194" t="n">
-        <v>1464.3728</v>
+        <v>1432.339</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2939,10 +2930,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>175400000</v>
+        <v>275320000</v>
       </c>
       <c r="C195" t="n">
-        <v>1473.9847</v>
+        <v>1355.8496</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2950,10 +2941,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>231000000</v>
+        <v>480600000</v>
       </c>
       <c r="C196" t="n">
-        <v>1474.4945</v>
+        <v>1349.3229</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2961,10 +2952,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>286250020</v>
+        <v>589150000</v>
       </c>
       <c r="C197" t="n">
-        <v>1475.4567</v>
+        <v>1328.0879</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2972,10 +2963,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>202930000</v>
+        <v>392600000</v>
       </c>
       <c r="C198" t="n">
-        <v>1432.339</v>
+        <v>1331.5211</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2983,10 +2974,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>275320000</v>
+        <v>478160000</v>
       </c>
       <c r="C199" t="n">
-        <v>1355.8496</v>
+        <v>1341.6642</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2994,10 +2985,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>480600000</v>
+        <v>496829980</v>
       </c>
       <c r="C200" t="n">
-        <v>1349.3229</v>
+        <v>1374.023</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -3005,10 +2996,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>589150000</v>
+        <v>295170020</v>
       </c>
       <c r="C201" t="n">
-        <v>1328.0879</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3016,10 +3007,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>392600000</v>
+        <v>169440000</v>
       </c>
       <c r="C202" t="n">
-        <v>1331.5211</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3027,10 +3018,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>478160000</v>
+        <v>215520000</v>
       </c>
       <c r="C203" t="n">
-        <v>1341.6642</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3038,10 +3029,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>496829980</v>
+        <v>262840000</v>
       </c>
       <c r="C204" t="n">
-        <v>1374.023</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3049,10 +3040,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>295170020</v>
+        <v>315000000</v>
       </c>
       <c r="C205" t="n">
-        <v>1424.7794</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3060,10 +3051,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>169440000</v>
+        <v>338970020</v>
       </c>
       <c r="C206" t="n">
-        <v>1424.6221</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3071,10 +3062,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>215520000</v>
+        <v>260880000</v>
       </c>
       <c r="C207" t="n">
-        <v>1424.9015</v>
+        <v>1445.8335</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3082,10 +3073,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>262840000</v>
+        <v>346149980</v>
       </c>
       <c r="C208" t="n">
-        <v>1429.9982</v>
+        <v>1360.4852</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3093,10 +3084,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>315000000</v>
+        <v>431149980</v>
       </c>
       <c r="C209" t="n">
-        <v>1430.0143</v>
+        <v>1374.5894</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3104,10 +3095,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>338970020</v>
+        <v>279500000</v>
       </c>
       <c r="C210" t="n">
-        <v>1430.0298</v>
+        <v>1391.1584</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3115,10 +3106,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>260880000</v>
+        <v>357400000</v>
       </c>
       <c r="C211" t="n">
-        <v>1445.8335</v>
+        <v>1450.9777</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3126,10 +3117,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>346149980</v>
+        <v>254070000</v>
       </c>
       <c r="C212" t="n">
-        <v>1360.4852</v>
+        <v>1468.5831</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3137,10 +3128,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>431149980</v>
+        <v>405740000</v>
       </c>
       <c r="C213" t="n">
-        <v>1374.5894</v>
+        <v>1487.8324</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3148,10 +3139,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>279500000</v>
+        <v>521350000</v>
       </c>
       <c r="C214" t="n">
-        <v>1391.1584</v>
+        <v>1487.4933</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3159,10 +3150,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>357400000</v>
+        <v>393340030</v>
       </c>
       <c r="C215" t="n">
-        <v>1450.9777</v>
+        <v>1484.1245</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3170,10 +3161,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>254070000</v>
+        <v>423890020</v>
       </c>
       <c r="C216" t="n">
-        <v>1468.5831</v>
+        <v>1487.8551</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3181,10 +3172,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>405740000</v>
+        <v>176000000</v>
       </c>
       <c r="C217" t="n">
-        <v>1487.8324</v>
+        <v>1399.3765</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3192,10 +3183,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>521350000</v>
+        <v>334980000</v>
       </c>
       <c r="C218" t="n">
-        <v>1487.4933</v>
+        <v>1470.861</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3203,10 +3194,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>393340030</v>
+        <v>139200000</v>
       </c>
       <c r="C219" t="n">
-        <v>1484.1245</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3214,10 +3205,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>423890020</v>
+        <v>127040000</v>
       </c>
       <c r="C220" t="n">
-        <v>1487.8551</v>
+        <v>1434.8278</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3225,10 +3216,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>176000000</v>
+        <v>189260000</v>
       </c>
       <c r="C221" t="n">
-        <v>1399.3765</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3236,10 +3227,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>334980000</v>
+        <v>275010000</v>
       </c>
       <c r="C222" t="n">
-        <v>1470.861</v>
+        <v>1464.5471</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3247,10 +3238,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>139200000</v>
+        <v>194450000</v>
       </c>
       <c r="C223" t="n">
-        <v>1451.923</v>
+        <v>1471.4448</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3258,10 +3249,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>127040000</v>
+        <v>196250000</v>
       </c>
       <c r="C224" t="n">
-        <v>1434.8278</v>
+        <v>1447.554</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3269,10 +3260,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>189260000</v>
+        <v>208000000</v>
       </c>
       <c r="C225" t="n">
-        <v>1445.9563</v>
+        <v>1434.8108</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3280,10 +3271,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>275010000</v>
+        <v>209360000</v>
       </c>
       <c r="C226" t="n">
-        <v>1464.5471</v>
+        <v>1420.3701</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3291,10 +3282,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>194450000</v>
+        <v>212720000</v>
       </c>
       <c r="C227" t="n">
-        <v>1471.4448</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3302,10 +3293,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>196250000</v>
+        <v>241830000</v>
       </c>
       <c r="C228" t="n">
-        <v>1447.554</v>
+        <v>1407.7981</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3313,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>208000000</v>
+        <v>312580000</v>
       </c>
       <c r="C229" t="n">
-        <v>1434.8108</v>
+        <v>1404.9167</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3324,10 +3315,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>209360000</v>
+        <v>179500000</v>
       </c>
       <c r="C230" t="n">
-        <v>1420.3701</v>
+        <v>1401.7583</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3335,10 +3326,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>212720000</v>
+        <v>107500000</v>
       </c>
       <c r="C231" t="n">
-        <v>1403.0524</v>
+        <v>1392.0065</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3346,10 +3337,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>241830000</v>
+        <v>242990000</v>
       </c>
       <c r="C232" t="n">
-        <v>1407.7981</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3357,43 +3348,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>312580000</v>
+        <v>254470000</v>
       </c>
       <c r="C233" t="n">
-        <v>1404.9167</v>
-      </c>
-    </row>
-    <row r="234" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>235</v>
-      </c>
-      <c r="B234" t="n">
-        <v>179500000</v>
-      </c>
-      <c r="C234" t="n">
-        <v>1401.7583</v>
-      </c>
-    </row>
-    <row r="235" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>236</v>
-      </c>
-      <c r="B235" t="n">
-        <v>107500000</v>
-      </c>
-      <c r="C235" t="n">
-        <v>1392.0065</v>
-      </c>
-    </row>
-    <row r="236" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>237</v>
-      </c>
-      <c r="B236" t="n">
-        <v>242990000</v>
-      </c>
-      <c r="C236" t="n">
-        <v>1402.779</v>
+        <v>1418.5961</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -719,6 +719,9 @@
   </si>
   <si>
     <t xml:space="preserve">20/11/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/11/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -783,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C233"/>
+  <dimension ref="A1:C234"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
@@ -3354,6 +3357,17 @@
         <v>1418.5961</v>
       </c>
     </row>
+    <row r="234" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>235</v>
+      </c>
+      <c r="B234" t="n">
+        <v>76500000</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1448.0328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -25,9 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">25/11/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">26/11/2024 12:00:00</t>
   </si>
   <si>
@@ -722,6 +719,9 @@
   </si>
   <si>
     <t xml:space="preserve">25/11/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/11/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -810,10 +810,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>90000000</v>
+        <v>92330000</v>
       </c>
       <c r="C2" t="n">
-        <v>1006.3558</v>
+        <v>1007.11914</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>92330000</v>
+        <v>99270000</v>
       </c>
       <c r="C3" t="n">
-        <v>1007.11914</v>
+        <v>1008.05896</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -832,10 +832,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>99270000</v>
+        <v>227840000</v>
       </c>
       <c r="C4" t="n">
-        <v>1008.05896</v>
+        <v>1009.5345</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -843,10 +843,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>227840000</v>
+        <v>139630000</v>
       </c>
       <c r="C5" t="n">
-        <v>1009.5345</v>
+        <v>1011.75397</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -854,10 +854,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>139630000</v>
+        <v>76610000</v>
       </c>
       <c r="C6" t="n">
-        <v>1011.75397</v>
+        <v>1012.0545</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -865,10 +865,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>76610000</v>
+        <v>85800000</v>
       </c>
       <c r="C7" t="n">
-        <v>1012.0545</v>
+        <v>1012.7305</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -876,10 +876,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>85800000</v>
+        <v>125840000</v>
       </c>
       <c r="C8" t="n">
-        <v>1012.7305</v>
+        <v>1013.0277</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -887,10 +887,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>125840000</v>
+        <v>136540000</v>
       </c>
       <c r="C9" t="n">
-        <v>1013.0277</v>
+        <v>1012.78424</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -898,10 +898,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>136540000</v>
+        <v>84630000</v>
       </c>
       <c r="C10" t="n">
-        <v>1012.78424</v>
+        <v>1015.8393</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -909,10 +909,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>84630000</v>
+        <v>53100000</v>
       </c>
       <c r="C11" t="n">
-        <v>1015.8393</v>
+        <v>1016.1278</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -920,10 +920,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>53100000</v>
+        <v>154600000</v>
       </c>
       <c r="C12" t="n">
-        <v>1016.1278</v>
+        <v>1016.7524</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -931,10 +931,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>154600000</v>
+        <v>166760000</v>
       </c>
       <c r="C13" t="n">
-        <v>1016.7524</v>
+        <v>1017.8712</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -942,10 +942,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>166760000</v>
+        <v>120700000</v>
       </c>
       <c r="C14" t="n">
-        <v>1017.8712</v>
+        <v>1017.9877</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -953,10 +953,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>120700000</v>
+        <v>136460000</v>
       </c>
       <c r="C15" t="n">
-        <v>1017.9877</v>
+        <v>1020.63074</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -964,10 +964,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>136460000</v>
+        <v>109500000</v>
       </c>
       <c r="C16" t="n">
-        <v>1020.63074</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -975,10 +975,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>109500000</v>
+        <v>103710000</v>
       </c>
       <c r="C17" t="n">
-        <v>1020.69635</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -986,10 +986,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>103710000</v>
+        <v>70020000</v>
       </c>
       <c r="C18" t="n">
-        <v>1021.90955</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -997,10 +997,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>70020000</v>
+        <v>105600000</v>
       </c>
       <c r="C19" t="n">
-        <v>1022.2438</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1008,10 +1008,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>105600000</v>
+        <v>60970000</v>
       </c>
       <c r="C20" t="n">
-        <v>1022.24274</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1019,10 +1019,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>60970000</v>
+        <v>135210000</v>
       </c>
       <c r="C21" t="n">
-        <v>1025.3103</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1030,10 +1030,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>135210000</v>
+        <v>214050000</v>
       </c>
       <c r="C22" t="n">
-        <v>1028.5804</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1041,10 +1041,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>214050000</v>
+        <v>170650000</v>
       </c>
       <c r="C23" t="n">
-        <v>1028.1958</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1052,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>170650000</v>
+        <v>129920000</v>
       </c>
       <c r="C24" t="n">
-        <v>1030.4104</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1063,10 +1063,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>129920000</v>
+        <v>90600000</v>
       </c>
       <c r="C25" t="n">
-        <v>1031.7577</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>90600000</v>
+        <v>94620000</v>
       </c>
       <c r="C26" t="n">
-        <v>1032.4374</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1085,10 +1085,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>94620000</v>
+        <v>76740000</v>
       </c>
       <c r="C27" t="n">
-        <v>1034.7297</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1096,10 +1096,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>76740000</v>
+        <v>60220000</v>
       </c>
       <c r="C28" t="n">
-        <v>1035.4338</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>60220000</v>
+        <v>80100000</v>
       </c>
       <c r="C29" t="n">
-        <v>1035.8505</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1118,10 +1118,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>80100000</v>
+        <v>144200000</v>
       </c>
       <c r="C30" t="n">
-        <v>1036.7753</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1129,10 +1129,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>144200000</v>
+        <v>66560000</v>
       </c>
       <c r="C31" t="n">
-        <v>1036.8966</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1140,10 +1140,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>66560000</v>
+        <v>69770000</v>
       </c>
       <c r="C32" t="n">
-        <v>1039.2858</v>
+        <v>1040.3352</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1151,10 +1151,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>69770000</v>
+        <v>59000000</v>
       </c>
       <c r="C33" t="n">
-        <v>1040.3352</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>59000000</v>
+        <v>97600000</v>
       </c>
       <c r="C34" t="n">
-        <v>1040.7654</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1173,10 +1173,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>97600000</v>
+        <v>139000000</v>
       </c>
       <c r="C35" t="n">
-        <v>1041.2943</v>
+        <v>1041.9935</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1184,10 +1184,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>139000000</v>
+        <v>215030000</v>
       </c>
       <c r="C36" t="n">
-        <v>1041.9935</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1195,10 +1195,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>215030000</v>
+        <v>117720000</v>
       </c>
       <c r="C37" t="n">
-        <v>1045.5352</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1206,10 +1206,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>117720000</v>
+        <v>55800000</v>
       </c>
       <c r="C38" t="n">
-        <v>1046.7697</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1217,10 +1217,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>55800000</v>
+        <v>135550000</v>
       </c>
       <c r="C39" t="n">
-        <v>1046.9908</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1228,10 +1228,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>135550000</v>
+        <v>89000000</v>
       </c>
       <c r="C40" t="n">
-        <v>1046.9497</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1239,10 +1239,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>89000000</v>
+        <v>58100000</v>
       </c>
       <c r="C41" t="n">
-        <v>1049.7869</v>
+        <v>1050.2393</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1250,10 +1250,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>58100000</v>
+        <v>86600000</v>
       </c>
       <c r="C42" t="n">
-        <v>1050.2393</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1261,10 +1261,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>86600000</v>
+        <v>95150000</v>
       </c>
       <c r="C43" t="n">
-        <v>1051.1277</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1272,10 +1272,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>95150000</v>
+        <v>147140000</v>
       </c>
       <c r="C44" t="n">
-        <v>1051.69</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1283,10 +1283,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>147140000</v>
+        <v>123760000</v>
       </c>
       <c r="C45" t="n">
-        <v>1051.1226</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1294,10 +1294,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>123760000</v>
+        <v>88880000</v>
       </c>
       <c r="C46" t="n">
-        <v>1053.3625</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1305,10 +1305,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>88880000</v>
+        <v>115600000</v>
       </c>
       <c r="C47" t="n">
-        <v>1053.5273</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1316,10 +1316,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>115600000</v>
+        <v>93120000</v>
       </c>
       <c r="C48" t="n">
-        <v>1053.941</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1327,10 +1327,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>93120000</v>
+        <v>162410000</v>
       </c>
       <c r="C49" t="n">
-        <v>1054.1022</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1338,10 +1338,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>162410000</v>
+        <v>191440000</v>
       </c>
       <c r="C50" t="n">
-        <v>1053.6134</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1349,10 +1349,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>191440000</v>
+        <v>98800000</v>
       </c>
       <c r="C51" t="n">
-        <v>1055.6161</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1360,10 +1360,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>98800000</v>
+        <v>151830000</v>
       </c>
       <c r="C52" t="n">
-        <v>1055.6309</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1371,10 +1371,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>151830000</v>
+        <v>63730000</v>
       </c>
       <c r="C53" t="n">
-        <v>1056.2124</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>63730000</v>
+        <v>154380000</v>
       </c>
       <c r="C54" t="n">
-        <v>1056.7262</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>154380000</v>
+        <v>127430000</v>
       </c>
       <c r="C55" t="n">
-        <v>1056.4021</v>
+        <v>1058.3726</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1404,10 +1404,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>127430000</v>
+        <v>90150000</v>
       </c>
       <c r="C56" t="n">
-        <v>1058.3726</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1415,10 +1415,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>90150000</v>
+        <v>78400000</v>
       </c>
       <c r="C57" t="n">
-        <v>1058.5518</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1426,10 +1426,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>78400000</v>
+        <v>102390000</v>
       </c>
       <c r="C58" t="n">
-        <v>1059.0238</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1437,10 +1437,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>102390000</v>
+        <v>106130000</v>
       </c>
       <c r="C59" t="n">
-        <v>1058.5037</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1448,10 +1448,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>106130000</v>
+        <v>81520000</v>
       </c>
       <c r="C60" t="n">
-        <v>1060.2593</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1459,10 +1459,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>81520000</v>
+        <v>107290000</v>
       </c>
       <c r="C61" t="n">
-        <v>1060.7654</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1470,10 +1470,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>107290000</v>
+        <v>78500000</v>
       </c>
       <c r="C62" t="n">
-        <v>1061.1646</v>
+        <v>1061.6616</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1481,10 +1481,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>78500000</v>
+        <v>115700000</v>
       </c>
       <c r="C63" t="n">
-        <v>1061.6616</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1492,10 +1492,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>115700000</v>
+        <v>135350000</v>
       </c>
       <c r="C64" t="n">
-        <v>1062.0686</v>
+        <v>1063.4131</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1503,10 +1503,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>135350000</v>
+        <v>156190000</v>
       </c>
       <c r="C65" t="n">
-        <v>1063.4131</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1514,10 +1514,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>156190000</v>
+        <v>203700000</v>
       </c>
       <c r="C66" t="n">
-        <v>1063.8278</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1525,10 +1525,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>203700000</v>
+        <v>153120000</v>
       </c>
       <c r="C67" t="n">
-        <v>1064.3394</v>
+        <v>1065.5394</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1536,10 +1536,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>153120000</v>
+        <v>154930000</v>
       </c>
       <c r="C68" t="n">
-        <v>1065.5394</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1547,10 +1547,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>154930000</v>
+        <v>101660000</v>
       </c>
       <c r="C69" t="n">
-        <v>1065.7025</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1558,10 +1558,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>101660000</v>
+        <v>90000000</v>
       </c>
       <c r="C70" t="n">
-        <v>1066.0099</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1569,10 +1569,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>90000000</v>
+        <v>266600000</v>
       </c>
       <c r="C71" t="n">
-        <v>1066.2288</v>
+        <v>1066.7456</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1580,10 +1580,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>266600000</v>
+        <v>146970000</v>
       </c>
       <c r="C72" t="n">
-        <v>1066.7456</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1591,10 +1591,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>146970000</v>
+        <v>61200000</v>
       </c>
       <c r="C73" t="n">
-        <v>1068.2128</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1602,10 +1602,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>61200000</v>
+        <v>69170000</v>
       </c>
       <c r="C74" t="n">
-        <v>1068.3644</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1613,10 +1613,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>69170000</v>
+        <v>41240000</v>
       </c>
       <c r="C75" t="n">
-        <v>1069.0115</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1624,10 +1624,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>41240000</v>
+        <v>145230000</v>
       </c>
       <c r="C76" t="n">
-        <v>1069.0428</v>
+        <v>1068.3027</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1635,10 +1635,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>145230000</v>
+        <v>120040000</v>
       </c>
       <c r="C77" t="n">
-        <v>1068.3027</v>
+        <v>1070.8257</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1646,10 +1646,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>120040000</v>
+        <v>105520000</v>
       </c>
       <c r="C78" t="n">
-        <v>1070.8257</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1657,10 +1657,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>105520000</v>
+        <v>180350000</v>
       </c>
       <c r="C79" t="n">
-        <v>1071.3093</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1668,10 +1668,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>180350000</v>
+        <v>157240000</v>
       </c>
       <c r="C80" t="n">
-        <v>1071.5227</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1679,10 +1679,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>157240000</v>
+        <v>204650000</v>
       </c>
       <c r="C81" t="n">
-        <v>1070.9691</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1690,10 +1690,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>204650000</v>
+        <v>127150000</v>
       </c>
       <c r="C82" t="n">
-        <v>1073.0979</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1701,10 +1701,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>127150000</v>
+        <v>54310000</v>
       </c>
       <c r="C83" t="n">
-        <v>1072.918</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1712,10 +1712,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>54310000</v>
+        <v>75470000</v>
       </c>
       <c r="C84" t="n">
-        <v>1074.1038</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1723,10 +1723,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>75470000</v>
+        <v>79680000</v>
       </c>
       <c r="C85" t="n">
-        <v>1073.4634</v>
+        <v>1075.5159</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1734,10 +1734,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>79680000</v>
+        <v>62750000</v>
       </c>
       <c r="C86" t="n">
-        <v>1075.5159</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1745,10 +1745,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>62750000</v>
+        <v>75600000</v>
       </c>
       <c r="C87" t="n">
-        <v>1075.8248</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1756,10 +1756,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>75600000</v>
+        <v>63990000</v>
       </c>
       <c r="C88" t="n">
-        <v>1076.5104</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1767,10 +1767,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>63990000</v>
+        <v>225590000</v>
       </c>
       <c r="C89" t="n">
-        <v>1076.5854</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1778,10 +1778,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>225590000</v>
+        <v>415320000</v>
       </c>
       <c r="C90" t="n">
-        <v>1075.3297</v>
+        <v>1189.2566</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1789,10 +1789,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>415320000</v>
+        <v>230200000</v>
       </c>
       <c r="C91" t="n">
-        <v>1189.2566</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1800,10 +1800,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>230200000</v>
+        <v>347690000</v>
       </c>
       <c r="C92" t="n">
-        <v>1199.1798</v>
+        <v>1162.0159</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1811,10 +1811,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>347690000</v>
+        <v>339050000</v>
       </c>
       <c r="C93" t="n">
-        <v>1162.0159</v>
+        <v>1082.272</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1822,10 +1822,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>339050000</v>
+        <v>335470000</v>
       </c>
       <c r="C94" t="n">
-        <v>1082.272</v>
+        <v>1092.0538</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1833,10 +1833,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>335470000</v>
+        <v>410800000</v>
       </c>
       <c r="C95" t="n">
-        <v>1092.0538</v>
+        <v>1135.2747</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1844,10 +1844,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>410800000</v>
+        <v>530219970</v>
       </c>
       <c r="C96" t="n">
-        <v>1135.2747</v>
+        <v>1176.6918</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1855,10 +1855,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>530219970</v>
+        <v>368410020</v>
       </c>
       <c r="C97" t="n">
-        <v>1176.6918</v>
+        <v>1173.9497</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1866,10 +1866,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>368410020</v>
+        <v>359710000</v>
       </c>
       <c r="C98" t="n">
-        <v>1173.9497</v>
+        <v>1164.8855</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1877,10 +1877,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>359710000</v>
+        <v>327350000</v>
       </c>
       <c r="C99" t="n">
-        <v>1164.8855</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1888,10 +1888,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>327350000</v>
+        <v>451770000</v>
       </c>
       <c r="C100" t="n">
-        <v>1171.4315</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1899,10 +1899,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>451770000</v>
+        <v>373390000</v>
       </c>
       <c r="C101" t="n">
-        <v>1169.5444</v>
+        <v>1182.7354</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1910,10 +1910,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>373390000</v>
+        <v>267550000</v>
       </c>
       <c r="C102" t="n">
-        <v>1182.7354</v>
+        <v>1201.8551</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1921,10 +1921,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>267550000</v>
+        <v>298740000</v>
       </c>
       <c r="C103" t="n">
-        <v>1201.8551</v>
+        <v>1150.9364</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>298740000</v>
+        <v>263150000</v>
       </c>
       <c r="C104" t="n">
-        <v>1150.9364</v>
+        <v>1115.3589</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1943,10 +1943,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>263150000</v>
+        <v>200590000</v>
       </c>
       <c r="C105" t="n">
-        <v>1115.3589</v>
+        <v>1114.4547</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1954,10 +1954,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>200590000</v>
+        <v>279730000</v>
       </c>
       <c r="C106" t="n">
-        <v>1114.4547</v>
+        <v>1128.0269</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1965,10 +1965,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>279730000</v>
+        <v>395650020</v>
       </c>
       <c r="C107" t="n">
-        <v>1128.0269</v>
+        <v>1124.8623</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1976,10 +1976,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>395650020</v>
+        <v>331410020</v>
       </c>
       <c r="C108" t="n">
-        <v>1124.8623</v>
+        <v>1130.4915</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1987,10 +1987,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>331410020</v>
+        <v>261090000</v>
       </c>
       <c r="C109" t="n">
-        <v>1130.4915</v>
+        <v>1135.9207</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1998,10 +1998,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>261090000</v>
+        <v>242790000</v>
       </c>
       <c r="C110" t="n">
-        <v>1135.9207</v>
+        <v>1144.8073</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2009,10 +2009,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>242790000</v>
+        <v>193430000</v>
       </c>
       <c r="C111" t="n">
-        <v>1144.8073</v>
+        <v>1134.3671</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2020,10 +2020,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>193430000</v>
+        <v>206570000</v>
       </c>
       <c r="C112" t="n">
-        <v>1134.3671</v>
+        <v>1143.0444</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2031,10 +2031,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>206570000</v>
+        <v>295490020</v>
       </c>
       <c r="C113" t="n">
-        <v>1143.0444</v>
+        <v>1144.6138</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>295490020</v>
+        <v>241590000</v>
       </c>
       <c r="C114" t="n">
-        <v>1144.6138</v>
+        <v>1142.3444</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2053,10 +2053,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>241590000</v>
+        <v>315600000</v>
       </c>
       <c r="C115" t="n">
-        <v>1142.3444</v>
+        <v>1136.4617</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2064,10 +2064,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>315600000</v>
+        <v>322010000</v>
       </c>
       <c r="C116" t="n">
-        <v>1136.4617</v>
+        <v>1148.4205</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2075,10 +2075,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>322010000</v>
+        <v>274060000</v>
       </c>
       <c r="C117" t="n">
-        <v>1148.4205</v>
+        <v>1162.3146</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2086,10 +2086,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>274060000</v>
+        <v>201240000</v>
       </c>
       <c r="C118" t="n">
-        <v>1162.3146</v>
+        <v>1175.8934</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2097,10 +2097,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>201240000</v>
+        <v>200400000</v>
       </c>
       <c r="C119" t="n">
-        <v>1175.8934</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2108,10 +2108,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>200400000</v>
+        <v>219350000</v>
       </c>
       <c r="C120" t="n">
-        <v>1196.2443</v>
+        <v>1182.2738</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2119,10 +2119,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>219350000</v>
+        <v>191080000</v>
       </c>
       <c r="C121" t="n">
-        <v>1182.2738</v>
+        <v>1185.7009</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2130,10 +2130,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>191080000</v>
+        <v>279980000</v>
       </c>
       <c r="C122" t="n">
-        <v>1185.7009</v>
+        <v>1184.3539</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2141,10 +2141,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>279980000</v>
+        <v>210400000</v>
       </c>
       <c r="C123" t="n">
-        <v>1184.3539</v>
+        <v>1190.1604</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2152,10 +2152,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>210400000</v>
+        <v>149050000</v>
       </c>
       <c r="C124" t="n">
-        <v>1190.1604</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2163,10 +2163,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>149050000</v>
+        <v>206060000</v>
       </c>
       <c r="C125" t="n">
-        <v>1189.0756</v>
+        <v>1187.3215</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2174,10 +2174,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>206060000</v>
+        <v>327800000</v>
       </c>
       <c r="C126" t="n">
-        <v>1187.3215</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2185,10 +2185,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>327800000</v>
+        <v>194900000</v>
       </c>
       <c r="C127" t="n">
-        <v>1187.3528</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>194900000</v>
+        <v>150070000</v>
       </c>
       <c r="C128" t="n">
-        <v>1183.6859</v>
+        <v>1186.3999</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2207,10 +2207,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>150070000</v>
+        <v>249730000</v>
       </c>
       <c r="C129" t="n">
-        <v>1186.3999</v>
+        <v>1184.7565</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2218,10 +2218,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>249730000</v>
+        <v>328930000</v>
       </c>
       <c r="C130" t="n">
-        <v>1184.7565</v>
+        <v>1177.4198</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2229,10 +2229,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>328930000</v>
+        <v>319130000</v>
       </c>
       <c r="C131" t="n">
-        <v>1177.4198</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2240,10 +2240,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>319130000</v>
+        <v>290900000</v>
       </c>
       <c r="C132" t="n">
-        <v>1146.302</v>
+        <v>1168.4825</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2251,10 +2251,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>290900000</v>
+        <v>272000000</v>
       </c>
       <c r="C133" t="n">
-        <v>1168.4825</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2262,10 +2262,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>272000000</v>
+        <v>459869980</v>
       </c>
       <c r="C134" t="n">
-        <v>1178.1132</v>
+        <v>1176.724</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2273,10 +2273,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>459869980</v>
+        <v>250980000</v>
       </c>
       <c r="C135" t="n">
-        <v>1176.724</v>
+        <v>1192.3014</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2284,10 +2284,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>250980000</v>
+        <v>317930020</v>
       </c>
       <c r="C136" t="n">
-        <v>1192.3014</v>
+        <v>1187.0327</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2295,10 +2295,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>317930020</v>
+        <v>359550000</v>
       </c>
       <c r="C137" t="n">
-        <v>1187.0327</v>
+        <v>1193.3121</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2306,10 +2306,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>359550000</v>
+        <v>279650000</v>
       </c>
       <c r="C138" t="n">
-        <v>1193.3121</v>
+        <v>1207.8153</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2317,10 +2317,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>279650000</v>
+        <v>286200000</v>
       </c>
       <c r="C139" t="n">
-        <v>1207.8153</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2328,10 +2328,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>286200000</v>
+        <v>343900000</v>
       </c>
       <c r="C140" t="n">
-        <v>1232.3434</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2339,10 +2339,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>343900000</v>
+        <v>310469980</v>
       </c>
       <c r="C141" t="n">
-        <v>1225.9089</v>
+        <v>1263.1807</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2350,10 +2350,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>310469980</v>
+        <v>324740000</v>
       </c>
       <c r="C142" t="n">
-        <v>1263.1807</v>
+        <v>1257.3591</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2361,10 +2361,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>324740000</v>
+        <v>301200000</v>
       </c>
       <c r="C143" t="n">
-        <v>1257.3591</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2372,10 +2372,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>301200000</v>
+        <v>298320000</v>
       </c>
       <c r="C144" t="n">
-        <v>1261.2496</v>
+        <v>1261.3674</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2383,10 +2383,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>298320000</v>
+        <v>393980000</v>
       </c>
       <c r="C145" t="n">
-        <v>1261.3674</v>
+        <v>1268.4539</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2394,10 +2394,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>393980000</v>
+        <v>398920000</v>
       </c>
       <c r="C146" t="n">
-        <v>1268.4539</v>
+        <v>1277.0442</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2405,10 +2405,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>398920000</v>
+        <v>323589980</v>
       </c>
       <c r="C147" t="n">
-        <v>1277.0442</v>
+        <v>1257.8407</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2416,10 +2416,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>323589980</v>
+        <v>307460000</v>
       </c>
       <c r="C148" t="n">
-        <v>1257.8407</v>
+        <v>1266.7705</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2427,10 +2427,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>307460000</v>
+        <v>297000000</v>
       </c>
       <c r="C149" t="n">
-        <v>1266.7705</v>
+        <v>1282.9014</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2438,10 +2438,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>297000000</v>
+        <v>291500000</v>
       </c>
       <c r="C150" t="n">
-        <v>1282.9014</v>
+        <v>1287.3074</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2449,10 +2449,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>291500000</v>
+        <v>242700000</v>
       </c>
       <c r="C151" t="n">
-        <v>1287.3074</v>
+        <v>1261.0431</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2460,10 +2460,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>242700000</v>
+        <v>183370000</v>
       </c>
       <c r="C152" t="n">
-        <v>1261.0431</v>
+        <v>1259.6431</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2471,10 +2471,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>183370000</v>
+        <v>241900000</v>
       </c>
       <c r="C153" t="n">
-        <v>1259.6431</v>
+        <v>1261.7827</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2482,10 +2482,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>241900000</v>
+        <v>273740000</v>
       </c>
       <c r="C154" t="n">
-        <v>1261.7827</v>
+        <v>1278.3439</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2493,10 +2493,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>273740000</v>
+        <v>212100000</v>
       </c>
       <c r="C155" t="n">
-        <v>1278.3439</v>
+        <v>1290.4368</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2504,10 +2504,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>212100000</v>
+        <v>308300000</v>
       </c>
       <c r="C156" t="n">
-        <v>1290.4368</v>
+        <v>1295.2062</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2515,10 +2515,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>308300000</v>
+        <v>165990000</v>
       </c>
       <c r="C157" t="n">
-        <v>1295.2062</v>
+        <v>1297.3245</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2526,10 +2526,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>165990000</v>
+        <v>328600000</v>
       </c>
       <c r="C158" t="n">
-        <v>1297.3245</v>
+        <v>1356.9905</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2537,10 +2537,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>328600000</v>
+        <v>213740000</v>
       </c>
       <c r="C159" t="n">
-        <v>1356.9905</v>
+        <v>1364.9016</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2548,10 +2548,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>213740000</v>
+        <v>220980000</v>
       </c>
       <c r="C160" t="n">
-        <v>1364.9016</v>
+        <v>1362.0563</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2559,10 +2559,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>220980000</v>
+        <v>311760000</v>
       </c>
       <c r="C161" t="n">
-        <v>1362.0563</v>
+        <v>1348.5603</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2570,10 +2570,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>311760000</v>
+        <v>324880000</v>
       </c>
       <c r="C162" t="n">
-        <v>1348.5603</v>
+        <v>1333.3021</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2581,10 +2581,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>324880000</v>
+        <v>194200000</v>
       </c>
       <c r="C163" t="n">
-        <v>1333.3021</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2592,10 +2592,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>194200000</v>
+        <v>219200000</v>
       </c>
       <c r="C164" t="n">
-        <v>1329.5576</v>
+        <v>1324.7318</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2603,10 +2603,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>219200000</v>
+        <v>265100000</v>
       </c>
       <c r="C165" t="n">
-        <v>1324.7318</v>
+        <v>1327.6051</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2614,10 +2614,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>265100000</v>
+        <v>318140000</v>
       </c>
       <c r="C166" t="n">
-        <v>1327.6051</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2625,10 +2625,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>318140000</v>
+        <v>323640000</v>
       </c>
       <c r="C167" t="n">
-        <v>1317.6909</v>
+        <v>1317.7236</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2636,10 +2636,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>323640000</v>
+        <v>258100000</v>
       </c>
       <c r="C168" t="n">
-        <v>1317.7236</v>
+        <v>1298.1354</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2647,10 +2647,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>258100000</v>
+        <v>245450000</v>
       </c>
       <c r="C169" t="n">
-        <v>1298.1354</v>
+        <v>1296.6604</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2658,10 +2658,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>245450000</v>
+        <v>388200000</v>
       </c>
       <c r="C170" t="n">
-        <v>1296.6604</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2669,10 +2669,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>388200000</v>
+        <v>218250000</v>
       </c>
       <c r="C171" t="n">
-        <v>1293.891</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2680,10 +2680,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>218250000</v>
+        <v>135000000</v>
       </c>
       <c r="C172" t="n">
-        <v>1299.0688</v>
+        <v>1311.6772</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2691,10 +2691,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>135000000</v>
+        <v>230420000</v>
       </c>
       <c r="C173" t="n">
-        <v>1311.6772</v>
+        <v>1322.6124</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2702,10 +2702,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>230420000</v>
+        <v>186010000</v>
       </c>
       <c r="C174" t="n">
-        <v>1322.6124</v>
+        <v>1349.7784</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2713,10 +2713,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>186010000</v>
+        <v>324380030</v>
       </c>
       <c r="C175" t="n">
-        <v>1349.7784</v>
+        <v>1353.8983</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2724,10 +2724,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>324380030</v>
+        <v>188250000</v>
       </c>
       <c r="C176" t="n">
-        <v>1353.8983</v>
+        <v>1360.0109</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2735,10 +2735,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>188250000</v>
+        <v>262170000</v>
       </c>
       <c r="C177" t="n">
-        <v>1360.0109</v>
+        <v>1338.8644</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2746,10 +2746,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>262170000</v>
+        <v>250290000</v>
       </c>
       <c r="C178" t="n">
-        <v>1338.8644</v>
+        <v>1330.1</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2757,10 +2757,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>250290000</v>
+        <v>396959970</v>
       </c>
       <c r="C179" t="n">
-        <v>1330.1</v>
+        <v>1365.2227</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2768,10 +2768,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>396959970</v>
+        <v>181300000</v>
       </c>
       <c r="C180" t="n">
-        <v>1365.2227</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2779,10 +2779,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>181300000</v>
+        <v>349490020</v>
       </c>
       <c r="C181" t="n">
-        <v>1361.4104</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2790,10 +2790,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>349490020</v>
+        <v>354610000</v>
       </c>
       <c r="C182" t="n">
-        <v>1362.602</v>
+        <v>1366.1195</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2801,10 +2801,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>354610000</v>
+        <v>268370000</v>
       </c>
       <c r="C183" t="n">
-        <v>1366.1195</v>
+        <v>1424.0857</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2812,10 +2812,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>268370000</v>
+        <v>217230000</v>
       </c>
       <c r="C184" t="n">
-        <v>1424.0857</v>
+        <v>1419.2256</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2823,10 +2823,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>217230000</v>
+        <v>202800000</v>
       </c>
       <c r="C185" t="n">
-        <v>1419.2256</v>
+        <v>1418.7972</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2834,10 +2834,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>202800000</v>
+        <v>182600000</v>
       </c>
       <c r="C186" t="n">
-        <v>1418.7972</v>
+        <v>1428.8694</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2845,10 +2845,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>182600000</v>
+        <v>186830000</v>
       </c>
       <c r="C187" t="n">
-        <v>1428.8694</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2856,10 +2856,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>186830000</v>
+        <v>256060000</v>
       </c>
       <c r="C188" t="n">
-        <v>1450.185</v>
+        <v>1463.7825</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2867,10 +2867,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>256060000</v>
+        <v>181350000</v>
       </c>
       <c r="C189" t="n">
-        <v>1463.7825</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2878,10 +2878,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>181350000</v>
+        <v>175400000</v>
       </c>
       <c r="C190" t="n">
-        <v>1464.3728</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2889,10 +2889,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>175400000</v>
+        <v>231000000</v>
       </c>
       <c r="C191" t="n">
-        <v>1473.9847</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2900,10 +2900,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>231000000</v>
+        <v>286250020</v>
       </c>
       <c r="C192" t="n">
-        <v>1474.4945</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2911,10 +2911,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>286250020</v>
+        <v>202930000</v>
       </c>
       <c r="C193" t="n">
-        <v>1475.4567</v>
+        <v>1432.339</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2922,10 +2922,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>202930000</v>
+        <v>275320000</v>
       </c>
       <c r="C194" t="n">
-        <v>1432.339</v>
+        <v>1355.8496</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2933,10 +2933,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>275320000</v>
+        <v>480600000</v>
       </c>
       <c r="C195" t="n">
-        <v>1355.8496</v>
+        <v>1349.3229</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2944,10 +2944,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>480600000</v>
+        <v>589150000</v>
       </c>
       <c r="C196" t="n">
-        <v>1349.3229</v>
+        <v>1328.0879</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2955,10 +2955,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>589150000</v>
+        <v>392600000</v>
       </c>
       <c r="C197" t="n">
-        <v>1328.0879</v>
+        <v>1331.5211</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2966,10 +2966,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>392600000</v>
+        <v>478160000</v>
       </c>
       <c r="C198" t="n">
-        <v>1331.5211</v>
+        <v>1341.6642</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2977,10 +2977,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>478160000</v>
+        <v>496829980</v>
       </c>
       <c r="C199" t="n">
-        <v>1341.6642</v>
+        <v>1374.023</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2988,10 +2988,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>496829980</v>
+        <v>295170020</v>
       </c>
       <c r="C200" t="n">
-        <v>1374.023</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2999,10 +2999,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>295170020</v>
+        <v>169440000</v>
       </c>
       <c r="C201" t="n">
-        <v>1424.7794</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3010,10 +3010,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>169440000</v>
+        <v>215520000</v>
       </c>
       <c r="C202" t="n">
-        <v>1424.6221</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3021,10 +3021,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>215520000</v>
+        <v>262840000</v>
       </c>
       <c r="C203" t="n">
-        <v>1424.9015</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>262840000</v>
+        <v>315000000</v>
       </c>
       <c r="C204" t="n">
-        <v>1429.9982</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3043,10 +3043,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>315000000</v>
+        <v>338970020</v>
       </c>
       <c r="C205" t="n">
-        <v>1430.0143</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3054,10 +3054,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>338970020</v>
+        <v>260880000</v>
       </c>
       <c r="C206" t="n">
-        <v>1430.0298</v>
+        <v>1445.8335</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3065,10 +3065,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>260880000</v>
+        <v>346149980</v>
       </c>
       <c r="C207" t="n">
-        <v>1445.8335</v>
+        <v>1360.4852</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3076,10 +3076,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>346149980</v>
+        <v>431149980</v>
       </c>
       <c r="C208" t="n">
-        <v>1360.4852</v>
+        <v>1374.5894</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3087,10 +3087,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>431149980</v>
+        <v>279500000</v>
       </c>
       <c r="C209" t="n">
-        <v>1374.5894</v>
+        <v>1391.1584</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3098,10 +3098,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>279500000</v>
+        <v>357400000</v>
       </c>
       <c r="C210" t="n">
-        <v>1391.1584</v>
+        <v>1450.9777</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3109,10 +3109,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>357400000</v>
+        <v>254070000</v>
       </c>
       <c r="C211" t="n">
-        <v>1450.9777</v>
+        <v>1468.5831</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3120,10 +3120,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>254070000</v>
+        <v>405740000</v>
       </c>
       <c r="C212" t="n">
-        <v>1468.5831</v>
+        <v>1487.8324</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3131,10 +3131,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>405740000</v>
+        <v>521350000</v>
       </c>
       <c r="C213" t="n">
-        <v>1487.8324</v>
+        <v>1487.4933</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3142,10 +3142,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>521350000</v>
+        <v>393340030</v>
       </c>
       <c r="C214" t="n">
-        <v>1487.4933</v>
+        <v>1484.1245</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3153,10 +3153,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>393340030</v>
+        <v>423890020</v>
       </c>
       <c r="C215" t="n">
-        <v>1484.1245</v>
+        <v>1487.8551</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3164,10 +3164,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>423890020</v>
+        <v>176000000</v>
       </c>
       <c r="C216" t="n">
-        <v>1487.8551</v>
+        <v>1399.3765</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3175,10 +3175,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>176000000</v>
+        <v>334980000</v>
       </c>
       <c r="C217" t="n">
-        <v>1399.3765</v>
+        <v>1470.861</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3186,10 +3186,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>334980000</v>
+        <v>139200000</v>
       </c>
       <c r="C218" t="n">
-        <v>1470.861</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3197,10 +3197,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>139200000</v>
+        <v>127040000</v>
       </c>
       <c r="C219" t="n">
-        <v>1451.923</v>
+        <v>1434.8278</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3208,10 +3208,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>127040000</v>
+        <v>189260000</v>
       </c>
       <c r="C220" t="n">
-        <v>1434.8278</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3219,10 +3219,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>189260000</v>
+        <v>275010000</v>
       </c>
       <c r="C221" t="n">
-        <v>1445.9563</v>
+        <v>1464.5471</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3230,10 +3230,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>275010000</v>
+        <v>194450000</v>
       </c>
       <c r="C222" t="n">
-        <v>1464.5471</v>
+        <v>1471.4448</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3241,10 +3241,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>194450000</v>
+        <v>196250000</v>
       </c>
       <c r="C223" t="n">
-        <v>1471.4448</v>
+        <v>1447.554</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3252,10 +3252,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>196250000</v>
+        <v>208000000</v>
       </c>
       <c r="C224" t="n">
-        <v>1447.554</v>
+        <v>1434.8108</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3263,10 +3263,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>208000000</v>
+        <v>209360000</v>
       </c>
       <c r="C225" t="n">
-        <v>1434.8108</v>
+        <v>1420.3701</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3274,10 +3274,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>209360000</v>
+        <v>212720000</v>
       </c>
       <c r="C226" t="n">
-        <v>1420.3701</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3285,10 +3285,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>212720000</v>
+        <v>241830000</v>
       </c>
       <c r="C227" t="n">
-        <v>1403.0524</v>
+        <v>1407.7981</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3296,10 +3296,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>241830000</v>
+        <v>312580000</v>
       </c>
       <c r="C228" t="n">
-        <v>1407.7981</v>
+        <v>1404.9167</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3307,10 +3307,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>312580000</v>
+        <v>179500000</v>
       </c>
       <c r="C229" t="n">
-        <v>1404.9167</v>
+        <v>1401.7583</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3318,10 +3318,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>179500000</v>
+        <v>107500000</v>
       </c>
       <c r="C230" t="n">
-        <v>1401.7583</v>
+        <v>1392.0065</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3329,10 +3329,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>107500000</v>
+        <v>242990000</v>
       </c>
       <c r="C231" t="n">
-        <v>1392.0065</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3340,10 +3340,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>242990000</v>
+        <v>254470000</v>
       </c>
       <c r="C232" t="n">
-        <v>1402.779</v>
+        <v>1418.5961</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3351,10 +3351,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>254470000</v>
+        <v>331130000</v>
       </c>
       <c r="C233" t="n">
-        <v>1418.5961</v>
+        <v>1446.057</v>
       </c>
     </row>
     <row r="234" x14ac:dyDescent="0.25">
@@ -3362,10 +3362,10 @@
         <v>235</v>
       </c>
       <c r="B234" t="n">
-        <v>76500000</v>
+        <v>237200000</v>
       </c>
       <c r="C234" t="n">
-        <v>1448.0328</v>
+        <v>1450.5864</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -25,9 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">2/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">3/12/2024 12:00:00</t>
   </si>
   <si>
@@ -722,6 +719,9 @@
   </si>
   <si>
     <t xml:space="preserve">2/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -810,10 +810,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>139630000</v>
+        <v>76610000</v>
       </c>
       <c r="C2" t="n">
-        <v>1011.75397</v>
+        <v>1012.0545</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>76610000</v>
+        <v>85800000</v>
       </c>
       <c r="C3" t="n">
-        <v>1012.0545</v>
+        <v>1012.7305</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -832,10 +832,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>85800000</v>
+        <v>125840000</v>
       </c>
       <c r="C4" t="n">
-        <v>1012.7305</v>
+        <v>1013.0277</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -843,10 +843,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>125840000</v>
+        <v>136540000</v>
       </c>
       <c r="C5" t="n">
-        <v>1013.0277</v>
+        <v>1012.78424</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -854,10 +854,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>136540000</v>
+        <v>84630000</v>
       </c>
       <c r="C6" t="n">
-        <v>1012.78424</v>
+        <v>1015.8393</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -865,10 +865,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>84630000</v>
+        <v>53100000</v>
       </c>
       <c r="C7" t="n">
-        <v>1015.8393</v>
+        <v>1016.1278</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -876,10 +876,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>53100000</v>
+        <v>154600000</v>
       </c>
       <c r="C8" t="n">
-        <v>1016.1278</v>
+        <v>1016.7524</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -887,10 +887,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>154600000</v>
+        <v>166760000</v>
       </c>
       <c r="C9" t="n">
-        <v>1016.7524</v>
+        <v>1017.8712</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -898,10 +898,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>166760000</v>
+        <v>120700000</v>
       </c>
       <c r="C10" t="n">
-        <v>1017.8712</v>
+        <v>1017.9877</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -909,10 +909,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>120700000</v>
+        <v>136460000</v>
       </c>
       <c r="C11" t="n">
-        <v>1017.9877</v>
+        <v>1020.63074</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -920,10 +920,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>136460000</v>
+        <v>109500000</v>
       </c>
       <c r="C12" t="n">
-        <v>1020.63074</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -931,10 +931,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>109500000</v>
+        <v>103710000</v>
       </c>
       <c r="C13" t="n">
-        <v>1020.69635</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -942,10 +942,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>103710000</v>
+        <v>70020000</v>
       </c>
       <c r="C14" t="n">
-        <v>1021.90955</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -953,10 +953,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>70020000</v>
+        <v>105600000</v>
       </c>
       <c r="C15" t="n">
-        <v>1022.2438</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -964,10 +964,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>105600000</v>
+        <v>60970000</v>
       </c>
       <c r="C16" t="n">
-        <v>1022.24274</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -975,10 +975,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>60970000</v>
+        <v>135210000</v>
       </c>
       <c r="C17" t="n">
-        <v>1025.3103</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -986,10 +986,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>135210000</v>
+        <v>214050000</v>
       </c>
       <c r="C18" t="n">
-        <v>1028.5804</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -997,10 +997,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>214050000</v>
+        <v>170650000</v>
       </c>
       <c r="C19" t="n">
-        <v>1028.1958</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1008,10 +1008,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>170650000</v>
+        <v>129920000</v>
       </c>
       <c r="C20" t="n">
-        <v>1030.4104</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1019,10 +1019,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>129920000</v>
+        <v>90600000</v>
       </c>
       <c r="C21" t="n">
-        <v>1031.7577</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1030,10 +1030,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>90600000</v>
+        <v>94620000</v>
       </c>
       <c r="C22" t="n">
-        <v>1032.4374</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1041,10 +1041,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>94620000</v>
+        <v>76740000</v>
       </c>
       <c r="C23" t="n">
-        <v>1034.7297</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1052,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>76740000</v>
+        <v>60220000</v>
       </c>
       <c r="C24" t="n">
-        <v>1035.4338</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1063,10 +1063,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>60220000</v>
+        <v>80100000</v>
       </c>
       <c r="C25" t="n">
-        <v>1035.8505</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>80100000</v>
+        <v>144200000</v>
       </c>
       <c r="C26" t="n">
-        <v>1036.7753</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1085,10 +1085,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>144200000</v>
+        <v>66560000</v>
       </c>
       <c r="C27" t="n">
-        <v>1036.8966</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1096,10 +1096,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>66560000</v>
+        <v>69770000</v>
       </c>
       <c r="C28" t="n">
-        <v>1039.2858</v>
+        <v>1040.3352</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>69770000</v>
+        <v>59000000</v>
       </c>
       <c r="C29" t="n">
-        <v>1040.3352</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1118,10 +1118,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>59000000</v>
+        <v>97600000</v>
       </c>
       <c r="C30" t="n">
-        <v>1040.7654</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1129,10 +1129,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>97600000</v>
+        <v>139000000</v>
       </c>
       <c r="C31" t="n">
-        <v>1041.2943</v>
+        <v>1041.9935</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1140,10 +1140,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>139000000</v>
+        <v>215030000</v>
       </c>
       <c r="C32" t="n">
-        <v>1041.9935</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1151,10 +1151,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>215030000</v>
+        <v>117720000</v>
       </c>
       <c r="C33" t="n">
-        <v>1045.5352</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>117720000</v>
+        <v>55800000</v>
       </c>
       <c r="C34" t="n">
-        <v>1046.7697</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1173,10 +1173,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>55800000</v>
+        <v>135550000</v>
       </c>
       <c r="C35" t="n">
-        <v>1046.9908</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1184,10 +1184,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>135550000</v>
+        <v>89000000</v>
       </c>
       <c r="C36" t="n">
-        <v>1046.9497</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1195,10 +1195,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>89000000</v>
+        <v>58100000</v>
       </c>
       <c r="C37" t="n">
-        <v>1049.7869</v>
+        <v>1050.2393</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1206,10 +1206,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>58100000</v>
+        <v>86600000</v>
       </c>
       <c r="C38" t="n">
-        <v>1050.2393</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1217,10 +1217,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>86600000</v>
+        <v>95150000</v>
       </c>
       <c r="C39" t="n">
-        <v>1051.1277</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1228,10 +1228,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>95150000</v>
+        <v>147140000</v>
       </c>
       <c r="C40" t="n">
-        <v>1051.69</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1239,10 +1239,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>147140000</v>
+        <v>123760000</v>
       </c>
       <c r="C41" t="n">
-        <v>1051.1226</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1250,10 +1250,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>123760000</v>
+        <v>88880000</v>
       </c>
       <c r="C42" t="n">
-        <v>1053.3625</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1261,10 +1261,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>88880000</v>
+        <v>115600000</v>
       </c>
       <c r="C43" t="n">
-        <v>1053.5273</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1272,10 +1272,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>115600000</v>
+        <v>93120000</v>
       </c>
       <c r="C44" t="n">
-        <v>1053.941</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1283,10 +1283,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>93120000</v>
+        <v>162410000</v>
       </c>
       <c r="C45" t="n">
-        <v>1054.1022</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1294,10 +1294,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>162410000</v>
+        <v>191440000</v>
       </c>
       <c r="C46" t="n">
-        <v>1053.6134</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1305,10 +1305,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>191440000</v>
+        <v>98800000</v>
       </c>
       <c r="C47" t="n">
-        <v>1055.6161</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1316,10 +1316,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>98800000</v>
+        <v>151830000</v>
       </c>
       <c r="C48" t="n">
-        <v>1055.6309</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1327,10 +1327,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>151830000</v>
+        <v>63730000</v>
       </c>
       <c r="C49" t="n">
-        <v>1056.2124</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1338,10 +1338,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>63730000</v>
+        <v>154380000</v>
       </c>
       <c r="C50" t="n">
-        <v>1056.7262</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1349,10 +1349,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>154380000</v>
+        <v>127430000</v>
       </c>
       <c r="C51" t="n">
-        <v>1056.4021</v>
+        <v>1058.3726</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1360,10 +1360,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>127430000</v>
+        <v>90150000</v>
       </c>
       <c r="C52" t="n">
-        <v>1058.3726</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1371,10 +1371,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>90150000</v>
+        <v>78400000</v>
       </c>
       <c r="C53" t="n">
-        <v>1058.5518</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>78400000</v>
+        <v>102390000</v>
       </c>
       <c r="C54" t="n">
-        <v>1059.0238</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>102390000</v>
+        <v>106130000</v>
       </c>
       <c r="C55" t="n">
-        <v>1058.5037</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1404,10 +1404,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>106130000</v>
+        <v>81520000</v>
       </c>
       <c r="C56" t="n">
-        <v>1060.2593</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1415,10 +1415,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>81520000</v>
+        <v>107290000</v>
       </c>
       <c r="C57" t="n">
-        <v>1060.7654</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1426,10 +1426,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>107290000</v>
+        <v>78500000</v>
       </c>
       <c r="C58" t="n">
-        <v>1061.1646</v>
+        <v>1061.6616</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1437,10 +1437,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>78500000</v>
+        <v>115700000</v>
       </c>
       <c r="C59" t="n">
-        <v>1061.6616</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1448,10 +1448,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>115700000</v>
+        <v>135350000</v>
       </c>
       <c r="C60" t="n">
-        <v>1062.0686</v>
+        <v>1063.4131</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1459,10 +1459,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>135350000</v>
+        <v>156190000</v>
       </c>
       <c r="C61" t="n">
-        <v>1063.4131</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1470,10 +1470,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>156190000</v>
+        <v>203700000</v>
       </c>
       <c r="C62" t="n">
-        <v>1063.8278</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1481,10 +1481,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>203700000</v>
+        <v>153120000</v>
       </c>
       <c r="C63" t="n">
-        <v>1064.3394</v>
+        <v>1065.5394</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1492,10 +1492,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>153120000</v>
+        <v>154930000</v>
       </c>
       <c r="C64" t="n">
-        <v>1065.5394</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1503,10 +1503,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>154930000</v>
+        <v>101660000</v>
       </c>
       <c r="C65" t="n">
-        <v>1065.7025</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1514,10 +1514,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>101660000</v>
+        <v>90000000</v>
       </c>
       <c r="C66" t="n">
-        <v>1066.0099</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1525,10 +1525,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>90000000</v>
+        <v>266600000</v>
       </c>
       <c r="C67" t="n">
-        <v>1066.2288</v>
+        <v>1066.7456</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1536,10 +1536,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>266600000</v>
+        <v>146970000</v>
       </c>
       <c r="C68" t="n">
-        <v>1066.7456</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1547,10 +1547,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>146970000</v>
+        <v>61200000</v>
       </c>
       <c r="C69" t="n">
-        <v>1068.2128</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1558,10 +1558,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>61200000</v>
+        <v>69170000</v>
       </c>
       <c r="C70" t="n">
-        <v>1068.3644</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1569,10 +1569,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>69170000</v>
+        <v>41240000</v>
       </c>
       <c r="C71" t="n">
-        <v>1069.0115</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1580,10 +1580,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>41240000</v>
+        <v>145230000</v>
       </c>
       <c r="C72" t="n">
-        <v>1069.0428</v>
+        <v>1068.3027</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1591,10 +1591,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>145230000</v>
+        <v>120040000</v>
       </c>
       <c r="C73" t="n">
-        <v>1068.3027</v>
+        <v>1070.8257</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1602,10 +1602,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>120040000</v>
+        <v>105520000</v>
       </c>
       <c r="C74" t="n">
-        <v>1070.8257</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1613,10 +1613,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>105520000</v>
+        <v>180350000</v>
       </c>
       <c r="C75" t="n">
-        <v>1071.3093</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1624,10 +1624,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>180350000</v>
+        <v>157240000</v>
       </c>
       <c r="C76" t="n">
-        <v>1071.5227</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1635,10 +1635,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>157240000</v>
+        <v>204650000</v>
       </c>
       <c r="C77" t="n">
-        <v>1070.9691</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1646,10 +1646,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>204650000</v>
+        <v>127150000</v>
       </c>
       <c r="C78" t="n">
-        <v>1073.0979</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1657,10 +1657,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>127150000</v>
+        <v>54310000</v>
       </c>
       <c r="C79" t="n">
-        <v>1072.918</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1668,10 +1668,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>54310000</v>
+        <v>75470000</v>
       </c>
       <c r="C80" t="n">
-        <v>1074.1038</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1679,10 +1679,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>75470000</v>
+        <v>79680000</v>
       </c>
       <c r="C81" t="n">
-        <v>1073.4634</v>
+        <v>1075.5159</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1690,10 +1690,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>79680000</v>
+        <v>62750000</v>
       </c>
       <c r="C82" t="n">
-        <v>1075.5159</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1701,10 +1701,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>62750000</v>
+        <v>75600000</v>
       </c>
       <c r="C83" t="n">
-        <v>1075.8248</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1712,10 +1712,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>75600000</v>
+        <v>63990000</v>
       </c>
       <c r="C84" t="n">
-        <v>1076.5104</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1723,10 +1723,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>63990000</v>
+        <v>225590000</v>
       </c>
       <c r="C85" t="n">
-        <v>1076.5854</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1734,10 +1734,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>225590000</v>
+        <v>415320000</v>
       </c>
       <c r="C86" t="n">
-        <v>1075.3297</v>
+        <v>1189.2566</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1745,10 +1745,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>415320000</v>
+        <v>230200000</v>
       </c>
       <c r="C87" t="n">
-        <v>1189.2566</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1756,10 +1756,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>230200000</v>
+        <v>347690000</v>
       </c>
       <c r="C88" t="n">
-        <v>1199.1798</v>
+        <v>1162.0159</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1767,10 +1767,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>347690000</v>
+        <v>339050000</v>
       </c>
       <c r="C89" t="n">
-        <v>1162.0159</v>
+        <v>1082.272</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1778,10 +1778,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>339050000</v>
+        <v>335470000</v>
       </c>
       <c r="C90" t="n">
-        <v>1082.272</v>
+        <v>1092.0538</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1789,10 +1789,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>335470000</v>
+        <v>410800000</v>
       </c>
       <c r="C91" t="n">
-        <v>1092.0538</v>
+        <v>1135.2747</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1800,10 +1800,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>410800000</v>
+        <v>530219970</v>
       </c>
       <c r="C92" t="n">
-        <v>1135.2747</v>
+        <v>1176.6918</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1811,10 +1811,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>530219970</v>
+        <v>368410020</v>
       </c>
       <c r="C93" t="n">
-        <v>1176.6918</v>
+        <v>1173.9497</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1822,10 +1822,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>368410020</v>
+        <v>359710000</v>
       </c>
       <c r="C94" t="n">
-        <v>1173.9497</v>
+        <v>1164.8855</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1833,10 +1833,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>359710000</v>
+        <v>327350000</v>
       </c>
       <c r="C95" t="n">
-        <v>1164.8855</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1844,10 +1844,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>327350000</v>
+        <v>451770000</v>
       </c>
       <c r="C96" t="n">
-        <v>1171.4315</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1855,10 +1855,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>451770000</v>
+        <v>373390000</v>
       </c>
       <c r="C97" t="n">
-        <v>1169.5444</v>
+        <v>1182.7354</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1866,10 +1866,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>373390000</v>
+        <v>267550000</v>
       </c>
       <c r="C98" t="n">
-        <v>1182.7354</v>
+        <v>1201.8551</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1877,10 +1877,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>267550000</v>
+        <v>298740000</v>
       </c>
       <c r="C99" t="n">
-        <v>1201.8551</v>
+        <v>1150.9364</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1888,10 +1888,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>298740000</v>
+        <v>263150000</v>
       </c>
       <c r="C100" t="n">
-        <v>1150.9364</v>
+        <v>1115.3589</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1899,10 +1899,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>263150000</v>
+        <v>200590000</v>
       </c>
       <c r="C101" t="n">
-        <v>1115.3589</v>
+        <v>1114.4547</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1910,10 +1910,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>200590000</v>
+        <v>279730000</v>
       </c>
       <c r="C102" t="n">
-        <v>1114.4547</v>
+        <v>1128.0269</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1921,10 +1921,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>279730000</v>
+        <v>395650020</v>
       </c>
       <c r="C103" t="n">
-        <v>1128.0269</v>
+        <v>1124.8623</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>395650020</v>
+        <v>331410020</v>
       </c>
       <c r="C104" t="n">
-        <v>1124.8623</v>
+        <v>1130.4915</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1943,10 +1943,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>331410020</v>
+        <v>261090000</v>
       </c>
       <c r="C105" t="n">
-        <v>1130.4915</v>
+        <v>1135.9207</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1954,10 +1954,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>261090000</v>
+        <v>242790000</v>
       </c>
       <c r="C106" t="n">
-        <v>1135.9207</v>
+        <v>1144.8073</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1965,10 +1965,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>242790000</v>
+        <v>193430000</v>
       </c>
       <c r="C107" t="n">
-        <v>1144.8073</v>
+        <v>1134.3671</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1976,10 +1976,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>193430000</v>
+        <v>206570000</v>
       </c>
       <c r="C108" t="n">
-        <v>1134.3671</v>
+        <v>1143.0444</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1987,10 +1987,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>206570000</v>
+        <v>295490020</v>
       </c>
       <c r="C109" t="n">
-        <v>1143.0444</v>
+        <v>1144.6138</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1998,10 +1998,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>295490020</v>
+        <v>241590000</v>
       </c>
       <c r="C110" t="n">
-        <v>1144.6138</v>
+        <v>1142.3444</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2009,10 +2009,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>241590000</v>
+        <v>315600000</v>
       </c>
       <c r="C111" t="n">
-        <v>1142.3444</v>
+        <v>1136.4617</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2020,10 +2020,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>315600000</v>
+        <v>322010000</v>
       </c>
       <c r="C112" t="n">
-        <v>1136.4617</v>
+        <v>1148.4205</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2031,10 +2031,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>322010000</v>
+        <v>274060000</v>
       </c>
       <c r="C113" t="n">
-        <v>1148.4205</v>
+        <v>1162.3146</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>274060000</v>
+        <v>201240000</v>
       </c>
       <c r="C114" t="n">
-        <v>1162.3146</v>
+        <v>1175.8934</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2053,10 +2053,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>201240000</v>
+        <v>200400000</v>
       </c>
       <c r="C115" t="n">
-        <v>1175.8934</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2064,10 +2064,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>200400000</v>
+        <v>219350000</v>
       </c>
       <c r="C116" t="n">
-        <v>1196.2443</v>
+        <v>1182.2738</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2075,10 +2075,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>219350000</v>
+        <v>191080000</v>
       </c>
       <c r="C117" t="n">
-        <v>1182.2738</v>
+        <v>1185.7009</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2086,10 +2086,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>191080000</v>
+        <v>279980000</v>
       </c>
       <c r="C118" t="n">
-        <v>1185.7009</v>
+        <v>1184.3539</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2097,10 +2097,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>279980000</v>
+        <v>210400000</v>
       </c>
       <c r="C119" t="n">
-        <v>1184.3539</v>
+        <v>1190.1604</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2108,10 +2108,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>210400000</v>
+        <v>149050000</v>
       </c>
       <c r="C120" t="n">
-        <v>1190.1604</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2119,10 +2119,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>149050000</v>
+        <v>206060000</v>
       </c>
       <c r="C121" t="n">
-        <v>1189.0756</v>
+        <v>1187.3215</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2130,10 +2130,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>206060000</v>
+        <v>327800000</v>
       </c>
       <c r="C122" t="n">
-        <v>1187.3215</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2141,10 +2141,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>327800000</v>
+        <v>194900000</v>
       </c>
       <c r="C123" t="n">
-        <v>1187.3528</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2152,10 +2152,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>194900000</v>
+        <v>150070000</v>
       </c>
       <c r="C124" t="n">
-        <v>1183.6859</v>
+        <v>1186.3999</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2163,10 +2163,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>150070000</v>
+        <v>249730000</v>
       </c>
       <c r="C125" t="n">
-        <v>1186.3999</v>
+        <v>1184.7565</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2174,10 +2174,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>249730000</v>
+        <v>328930000</v>
       </c>
       <c r="C126" t="n">
-        <v>1184.7565</v>
+        <v>1177.4198</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2185,10 +2185,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>328930000</v>
+        <v>319130000</v>
       </c>
       <c r="C127" t="n">
-        <v>1177.4198</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>319130000</v>
+        <v>290900000</v>
       </c>
       <c r="C128" t="n">
-        <v>1146.302</v>
+        <v>1168.4825</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2207,10 +2207,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>290900000</v>
+        <v>272000000</v>
       </c>
       <c r="C129" t="n">
-        <v>1168.4825</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2218,10 +2218,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>272000000</v>
+        <v>459869980</v>
       </c>
       <c r="C130" t="n">
-        <v>1178.1132</v>
+        <v>1176.724</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2229,10 +2229,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>459869980</v>
+        <v>250980000</v>
       </c>
       <c r="C131" t="n">
-        <v>1176.724</v>
+        <v>1192.3014</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2240,10 +2240,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>250980000</v>
+        <v>317930020</v>
       </c>
       <c r="C132" t="n">
-        <v>1192.3014</v>
+        <v>1187.0327</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2251,10 +2251,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>317930020</v>
+        <v>359550000</v>
       </c>
       <c r="C133" t="n">
-        <v>1187.0327</v>
+        <v>1193.3121</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2262,10 +2262,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>359550000</v>
+        <v>279650000</v>
       </c>
       <c r="C134" t="n">
-        <v>1193.3121</v>
+        <v>1207.8153</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2273,10 +2273,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>279650000</v>
+        <v>286200000</v>
       </c>
       <c r="C135" t="n">
-        <v>1207.8153</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2284,10 +2284,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>286200000</v>
+        <v>343900000</v>
       </c>
       <c r="C136" t="n">
-        <v>1232.3434</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2295,10 +2295,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>343900000</v>
+        <v>310469980</v>
       </c>
       <c r="C137" t="n">
-        <v>1225.9089</v>
+        <v>1263.1807</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2306,10 +2306,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>310469980</v>
+        <v>324740000</v>
       </c>
       <c r="C138" t="n">
-        <v>1263.1807</v>
+        <v>1257.3591</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2317,10 +2317,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>324740000</v>
+        <v>301200000</v>
       </c>
       <c r="C139" t="n">
-        <v>1257.3591</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2328,10 +2328,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>301200000</v>
+        <v>298320000</v>
       </c>
       <c r="C140" t="n">
-        <v>1261.2496</v>
+        <v>1261.3674</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2339,10 +2339,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>298320000</v>
+        <v>393980000</v>
       </c>
       <c r="C141" t="n">
-        <v>1261.3674</v>
+        <v>1268.4539</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2350,10 +2350,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>393980000</v>
+        <v>398920000</v>
       </c>
       <c r="C142" t="n">
-        <v>1268.4539</v>
+        <v>1277.0442</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2361,10 +2361,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>398920000</v>
+        <v>323589980</v>
       </c>
       <c r="C143" t="n">
-        <v>1277.0442</v>
+        <v>1257.8407</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2372,10 +2372,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>323589980</v>
+        <v>307460000</v>
       </c>
       <c r="C144" t="n">
-        <v>1257.8407</v>
+        <v>1266.7705</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2383,10 +2383,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>307460000</v>
+        <v>297000000</v>
       </c>
       <c r="C145" t="n">
-        <v>1266.7705</v>
+        <v>1282.9014</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2394,10 +2394,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>297000000</v>
+        <v>291500000</v>
       </c>
       <c r="C146" t="n">
-        <v>1282.9014</v>
+        <v>1287.3074</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2405,10 +2405,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>291500000</v>
+        <v>242700000</v>
       </c>
       <c r="C147" t="n">
-        <v>1287.3074</v>
+        <v>1261.0431</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2416,10 +2416,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>242700000</v>
+        <v>183370000</v>
       </c>
       <c r="C148" t="n">
-        <v>1261.0431</v>
+        <v>1259.6431</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2427,10 +2427,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>183370000</v>
+        <v>241900000</v>
       </c>
       <c r="C149" t="n">
-        <v>1259.6431</v>
+        <v>1261.7827</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2438,10 +2438,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>241900000</v>
+        <v>273740000</v>
       </c>
       <c r="C150" t="n">
-        <v>1261.7827</v>
+        <v>1278.3439</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2449,10 +2449,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>273740000</v>
+        <v>212100000</v>
       </c>
       <c r="C151" t="n">
-        <v>1278.3439</v>
+        <v>1290.4368</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2460,10 +2460,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>212100000</v>
+        <v>308300000</v>
       </c>
       <c r="C152" t="n">
-        <v>1290.4368</v>
+        <v>1295.2062</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2471,10 +2471,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>308300000</v>
+        <v>165990000</v>
       </c>
       <c r="C153" t="n">
-        <v>1295.2062</v>
+        <v>1297.3245</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2482,10 +2482,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>165990000</v>
+        <v>328600000</v>
       </c>
       <c r="C154" t="n">
-        <v>1297.3245</v>
+        <v>1356.9905</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2493,10 +2493,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>328600000</v>
+        <v>213740000</v>
       </c>
       <c r="C155" t="n">
-        <v>1356.9905</v>
+        <v>1364.9016</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2504,10 +2504,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>213740000</v>
+        <v>220980000</v>
       </c>
       <c r="C156" t="n">
-        <v>1364.9016</v>
+        <v>1362.0563</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2515,10 +2515,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>220980000</v>
+        <v>311760000</v>
       </c>
       <c r="C157" t="n">
-        <v>1362.0563</v>
+        <v>1348.5603</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2526,10 +2526,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>311760000</v>
+        <v>324880000</v>
       </c>
       <c r="C158" t="n">
-        <v>1348.5603</v>
+        <v>1333.3021</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2537,10 +2537,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>324880000</v>
+        <v>194200000</v>
       </c>
       <c r="C159" t="n">
-        <v>1333.3021</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2548,10 +2548,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>194200000</v>
+        <v>219200000</v>
       </c>
       <c r="C160" t="n">
-        <v>1329.5576</v>
+        <v>1324.7318</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2559,10 +2559,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>219200000</v>
+        <v>265100000</v>
       </c>
       <c r="C161" t="n">
-        <v>1324.7318</v>
+        <v>1327.6051</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2570,10 +2570,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>265100000</v>
+        <v>318140000</v>
       </c>
       <c r="C162" t="n">
-        <v>1327.6051</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2581,10 +2581,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>318140000</v>
+        <v>323640000</v>
       </c>
       <c r="C163" t="n">
-        <v>1317.6909</v>
+        <v>1317.7236</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2592,10 +2592,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>323640000</v>
+        <v>258100000</v>
       </c>
       <c r="C164" t="n">
-        <v>1317.7236</v>
+        <v>1298.1354</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2603,10 +2603,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>258100000</v>
+        <v>245450000</v>
       </c>
       <c r="C165" t="n">
-        <v>1298.1354</v>
+        <v>1296.6604</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2614,10 +2614,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>245450000</v>
+        <v>388200000</v>
       </c>
       <c r="C166" t="n">
-        <v>1296.6604</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2625,10 +2625,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>388200000</v>
+        <v>218250000</v>
       </c>
       <c r="C167" t="n">
-        <v>1293.891</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2636,10 +2636,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>218250000</v>
+        <v>135000000</v>
       </c>
       <c r="C168" t="n">
-        <v>1299.0688</v>
+        <v>1311.6772</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2647,10 +2647,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>135000000</v>
+        <v>230420000</v>
       </c>
       <c r="C169" t="n">
-        <v>1311.6772</v>
+        <v>1322.6124</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2658,10 +2658,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>230420000</v>
+        <v>186010000</v>
       </c>
       <c r="C170" t="n">
-        <v>1322.6124</v>
+        <v>1349.7784</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2669,10 +2669,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>186010000</v>
+        <v>324380030</v>
       </c>
       <c r="C171" t="n">
-        <v>1349.7784</v>
+        <v>1353.8983</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2680,10 +2680,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>324380030</v>
+        <v>188250000</v>
       </c>
       <c r="C172" t="n">
-        <v>1353.8983</v>
+        <v>1360.0109</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2691,10 +2691,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>188250000</v>
+        <v>262170000</v>
       </c>
       <c r="C173" t="n">
-        <v>1360.0109</v>
+        <v>1338.8644</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2702,10 +2702,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>262170000</v>
+        <v>250290000</v>
       </c>
       <c r="C174" t="n">
-        <v>1338.8644</v>
+        <v>1330.1</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2713,10 +2713,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>250290000</v>
+        <v>396959970</v>
       </c>
       <c r="C175" t="n">
-        <v>1330.1</v>
+        <v>1365.2227</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2724,10 +2724,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>396959970</v>
+        <v>181300000</v>
       </c>
       <c r="C176" t="n">
-        <v>1365.2227</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2735,10 +2735,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>181300000</v>
+        <v>349490020</v>
       </c>
       <c r="C177" t="n">
-        <v>1361.4104</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2746,10 +2746,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>349490020</v>
+        <v>354610000</v>
       </c>
       <c r="C178" t="n">
-        <v>1362.602</v>
+        <v>1366.1195</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2757,10 +2757,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>354610000</v>
+        <v>268370000</v>
       </c>
       <c r="C179" t="n">
-        <v>1366.1195</v>
+        <v>1424.0857</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2768,10 +2768,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>268370000</v>
+        <v>217230000</v>
       </c>
       <c r="C180" t="n">
-        <v>1424.0857</v>
+        <v>1419.2256</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2779,10 +2779,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>217230000</v>
+        <v>202800000</v>
       </c>
       <c r="C181" t="n">
-        <v>1419.2256</v>
+        <v>1418.7972</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2790,10 +2790,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>202800000</v>
+        <v>182600000</v>
       </c>
       <c r="C182" t="n">
-        <v>1418.7972</v>
+        <v>1428.8694</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2801,10 +2801,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>182600000</v>
+        <v>186830000</v>
       </c>
       <c r="C183" t="n">
-        <v>1428.8694</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2812,10 +2812,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>186830000</v>
+        <v>256060000</v>
       </c>
       <c r="C184" t="n">
-        <v>1450.185</v>
+        <v>1463.7825</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2823,10 +2823,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>256060000</v>
+        <v>181350000</v>
       </c>
       <c r="C185" t="n">
-        <v>1463.7825</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2834,10 +2834,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>181350000</v>
+        <v>175400000</v>
       </c>
       <c r="C186" t="n">
-        <v>1464.3728</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2845,10 +2845,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>175400000</v>
+        <v>231000000</v>
       </c>
       <c r="C187" t="n">
-        <v>1473.9847</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2856,10 +2856,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>231000000</v>
+        <v>286250020</v>
       </c>
       <c r="C188" t="n">
-        <v>1474.4945</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2867,10 +2867,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>286250020</v>
+        <v>202930000</v>
       </c>
       <c r="C189" t="n">
-        <v>1475.4567</v>
+        <v>1432.339</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2878,10 +2878,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>202930000</v>
+        <v>275320000</v>
       </c>
       <c r="C190" t="n">
-        <v>1432.339</v>
+        <v>1355.8496</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2889,10 +2889,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>275320000</v>
+        <v>480600000</v>
       </c>
       <c r="C191" t="n">
-        <v>1355.8496</v>
+        <v>1349.3229</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2900,10 +2900,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>480600000</v>
+        <v>589150000</v>
       </c>
       <c r="C192" t="n">
-        <v>1349.3229</v>
+        <v>1328.0879</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2911,10 +2911,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>589150000</v>
+        <v>392600000</v>
       </c>
       <c r="C193" t="n">
-        <v>1328.0879</v>
+        <v>1331.5211</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2922,10 +2922,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>392600000</v>
+        <v>478160000</v>
       </c>
       <c r="C194" t="n">
-        <v>1331.5211</v>
+        <v>1341.6642</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2933,10 +2933,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>478160000</v>
+        <v>496829980</v>
       </c>
       <c r="C195" t="n">
-        <v>1341.6642</v>
+        <v>1374.023</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2944,10 +2944,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>496829980</v>
+        <v>295170020</v>
       </c>
       <c r="C196" t="n">
-        <v>1374.023</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2955,10 +2955,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>295170020</v>
+        <v>169440000</v>
       </c>
       <c r="C197" t="n">
-        <v>1424.7794</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2966,10 +2966,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>169440000</v>
+        <v>215520000</v>
       </c>
       <c r="C198" t="n">
-        <v>1424.6221</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2977,10 +2977,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>215520000</v>
+        <v>262840000</v>
       </c>
       <c r="C199" t="n">
-        <v>1424.9015</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2988,10 +2988,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>262840000</v>
+        <v>315000000</v>
       </c>
       <c r="C200" t="n">
-        <v>1429.9982</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2999,10 +2999,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>315000000</v>
+        <v>338970020</v>
       </c>
       <c r="C201" t="n">
-        <v>1430.0143</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3010,10 +3010,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>338970020</v>
+        <v>260880000</v>
       </c>
       <c r="C202" t="n">
-        <v>1430.0298</v>
+        <v>1445.8335</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3021,10 +3021,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>260880000</v>
+        <v>346149980</v>
       </c>
       <c r="C203" t="n">
-        <v>1445.8335</v>
+        <v>1360.4852</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>346149980</v>
+        <v>431149980</v>
       </c>
       <c r="C204" t="n">
-        <v>1360.4852</v>
+        <v>1374.5894</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3043,10 +3043,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>431149980</v>
+        <v>279500000</v>
       </c>
       <c r="C205" t="n">
-        <v>1374.5894</v>
+        <v>1391.1584</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3054,10 +3054,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>279500000</v>
+        <v>357400000</v>
       </c>
       <c r="C206" t="n">
-        <v>1391.1584</v>
+        <v>1450.9777</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3065,10 +3065,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>357400000</v>
+        <v>254070000</v>
       </c>
       <c r="C207" t="n">
-        <v>1450.9777</v>
+        <v>1468.5831</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3076,10 +3076,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>254070000</v>
+        <v>405740000</v>
       </c>
       <c r="C208" t="n">
-        <v>1468.5831</v>
+        <v>1487.8324</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3087,10 +3087,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>405740000</v>
+        <v>521350000</v>
       </c>
       <c r="C209" t="n">
-        <v>1487.8324</v>
+        <v>1487.4933</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3098,10 +3098,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>521350000</v>
+        <v>393340030</v>
       </c>
       <c r="C210" t="n">
-        <v>1487.4933</v>
+        <v>1484.1245</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3109,10 +3109,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>393340030</v>
+        <v>423890020</v>
       </c>
       <c r="C211" t="n">
-        <v>1484.1245</v>
+        <v>1487.8551</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3120,10 +3120,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>423890020</v>
+        <v>176000000</v>
       </c>
       <c r="C212" t="n">
-        <v>1487.8551</v>
+        <v>1399.3765</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3131,10 +3131,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>176000000</v>
+        <v>334980000</v>
       </c>
       <c r="C213" t="n">
-        <v>1399.3765</v>
+        <v>1470.861</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3142,10 +3142,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>334980000</v>
+        <v>139200000</v>
       </c>
       <c r="C214" t="n">
-        <v>1470.861</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3153,10 +3153,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>139200000</v>
+        <v>127040000</v>
       </c>
       <c r="C215" t="n">
-        <v>1451.923</v>
+        <v>1434.8278</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3164,10 +3164,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>127040000</v>
+        <v>189260000</v>
       </c>
       <c r="C216" t="n">
-        <v>1434.8278</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3175,10 +3175,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>189260000</v>
+        <v>275010000</v>
       </c>
       <c r="C217" t="n">
-        <v>1445.9563</v>
+        <v>1464.5471</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3186,10 +3186,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>275010000</v>
+        <v>194450000</v>
       </c>
       <c r="C218" t="n">
-        <v>1464.5471</v>
+        <v>1471.4448</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3197,10 +3197,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>194450000</v>
+        <v>196250000</v>
       </c>
       <c r="C219" t="n">
-        <v>1471.4448</v>
+        <v>1447.554</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3208,10 +3208,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>196250000</v>
+        <v>208000000</v>
       </c>
       <c r="C220" t="n">
-        <v>1447.554</v>
+        <v>1434.8108</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3219,10 +3219,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>208000000</v>
+        <v>209360000</v>
       </c>
       <c r="C221" t="n">
-        <v>1434.8108</v>
+        <v>1420.3701</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3230,10 +3230,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>209360000</v>
+        <v>212720000</v>
       </c>
       <c r="C222" t="n">
-        <v>1420.3701</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3241,10 +3241,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>212720000</v>
+        <v>241830000</v>
       </c>
       <c r="C223" t="n">
-        <v>1403.0524</v>
+        <v>1407.7981</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3252,10 +3252,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>241830000</v>
+        <v>312580000</v>
       </c>
       <c r="C224" t="n">
-        <v>1407.7981</v>
+        <v>1404.9167</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3263,10 +3263,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>312580000</v>
+        <v>179500000</v>
       </c>
       <c r="C225" t="n">
-        <v>1404.9167</v>
+        <v>1401.7583</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3274,10 +3274,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>179500000</v>
+        <v>107500000</v>
       </c>
       <c r="C226" t="n">
-        <v>1401.7583</v>
+        <v>1392.0065</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3285,10 +3285,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>107500000</v>
+        <v>242990000</v>
       </c>
       <c r="C227" t="n">
-        <v>1392.0065</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3296,10 +3296,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>242990000</v>
+        <v>254470000</v>
       </c>
       <c r="C228" t="n">
-        <v>1402.779</v>
+        <v>1418.5961</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3307,10 +3307,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>254470000</v>
+        <v>331130000</v>
       </c>
       <c r="C229" t="n">
-        <v>1418.5961</v>
+        <v>1446.057</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3318,10 +3318,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>331130000</v>
+        <v>237200000</v>
       </c>
       <c r="C230" t="n">
-        <v>1446.057</v>
+        <v>1450.5864</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3329,10 +3329,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>237200000</v>
+        <v>268310000</v>
       </c>
       <c r="C231" t="n">
-        <v>1450.5864</v>
+        <v>1450.6014</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3340,10 +3340,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>268310000</v>
+        <v>293410020</v>
       </c>
       <c r="C232" t="n">
-        <v>1450.6014</v>
+        <v>1449.8969</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3351,10 +3351,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>293410020</v>
+        <v>190400000</v>
       </c>
       <c r="C233" t="n">
-        <v>1449.8969</v>
+        <v>1454.6573</v>
       </c>
     </row>
     <row r="234" x14ac:dyDescent="0.25">
@@ -3362,10 +3362,10 @@
         <v>235</v>
       </c>
       <c r="B234" t="n">
-        <v>133300000</v>
+        <v>52500000</v>
       </c>
       <c r="C234" t="n">
-        <v>1454.259</v>
+        <v>1453.9807</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -25,9 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">3/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">4/12/2024 12:00:00</t>
   </si>
   <si>
@@ -722,6 +719,9 @@
   </si>
   <si>
     <t xml:space="preserve">3/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -810,10 +810,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>76610000</v>
+        <v>85800000</v>
       </c>
       <c r="C2" t="n">
-        <v>1012.0545</v>
+        <v>1012.7305</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>85800000</v>
+        <v>125840000</v>
       </c>
       <c r="C3" t="n">
-        <v>1012.7305</v>
+        <v>1013.0277</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -832,10 +832,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>125840000</v>
+        <v>136540000</v>
       </c>
       <c r="C4" t="n">
-        <v>1013.0277</v>
+        <v>1012.78424</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -843,10 +843,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>136540000</v>
+        <v>84630000</v>
       </c>
       <c r="C5" t="n">
-        <v>1012.78424</v>
+        <v>1015.8393</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -854,10 +854,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>84630000</v>
+        <v>53100000</v>
       </c>
       <c r="C6" t="n">
-        <v>1015.8393</v>
+        <v>1016.1278</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -865,10 +865,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>53100000</v>
+        <v>154600000</v>
       </c>
       <c r="C7" t="n">
-        <v>1016.1278</v>
+        <v>1016.7524</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -876,10 +876,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>154600000</v>
+        <v>166760000</v>
       </c>
       <c r="C8" t="n">
-        <v>1016.7524</v>
+        <v>1017.8712</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -887,10 +887,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>166760000</v>
+        <v>120700000</v>
       </c>
       <c r="C9" t="n">
-        <v>1017.8712</v>
+        <v>1017.9877</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -898,10 +898,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>120700000</v>
+        <v>136460000</v>
       </c>
       <c r="C10" t="n">
-        <v>1017.9877</v>
+        <v>1020.63074</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -909,10 +909,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>136460000</v>
+        <v>109500000</v>
       </c>
       <c r="C11" t="n">
-        <v>1020.63074</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -920,10 +920,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>109500000</v>
+        <v>103710000</v>
       </c>
       <c r="C12" t="n">
-        <v>1020.69635</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -931,10 +931,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>103710000</v>
+        <v>70020000</v>
       </c>
       <c r="C13" t="n">
-        <v>1021.90955</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -942,10 +942,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>70020000</v>
+        <v>105600000</v>
       </c>
       <c r="C14" t="n">
-        <v>1022.2438</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -953,10 +953,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>105600000</v>
+        <v>60970000</v>
       </c>
       <c r="C15" t="n">
-        <v>1022.24274</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -964,10 +964,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>60970000</v>
+        <v>135210000</v>
       </c>
       <c r="C16" t="n">
-        <v>1025.3103</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -975,10 +975,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>135210000</v>
+        <v>214050000</v>
       </c>
       <c r="C17" t="n">
-        <v>1028.5804</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -986,10 +986,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>214050000</v>
+        <v>170650000</v>
       </c>
       <c r="C18" t="n">
-        <v>1028.1958</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -997,10 +997,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>170650000</v>
+        <v>129920000</v>
       </c>
       <c r="C19" t="n">
-        <v>1030.4104</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1008,10 +1008,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>129920000</v>
+        <v>90600000</v>
       </c>
       <c r="C20" t="n">
-        <v>1031.7577</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1019,10 +1019,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>90600000</v>
+        <v>94620000</v>
       </c>
       <c r="C21" t="n">
-        <v>1032.4374</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1030,10 +1030,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>94620000</v>
+        <v>76740000</v>
       </c>
       <c r="C22" t="n">
-        <v>1034.7297</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1041,10 +1041,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>76740000</v>
+        <v>60220000</v>
       </c>
       <c r="C23" t="n">
-        <v>1035.4338</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1052,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>60220000</v>
+        <v>80100000</v>
       </c>
       <c r="C24" t="n">
-        <v>1035.8505</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1063,10 +1063,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>80100000</v>
+        <v>144200000</v>
       </c>
       <c r="C25" t="n">
-        <v>1036.7753</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>144200000</v>
+        <v>66560000</v>
       </c>
       <c r="C26" t="n">
-        <v>1036.8966</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1085,10 +1085,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>66560000</v>
+        <v>69770000</v>
       </c>
       <c r="C27" t="n">
-        <v>1039.2858</v>
+        <v>1040.3352</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1096,10 +1096,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>69770000</v>
+        <v>59000000</v>
       </c>
       <c r="C28" t="n">
-        <v>1040.3352</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>59000000</v>
+        <v>97600000</v>
       </c>
       <c r="C29" t="n">
-        <v>1040.7654</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1118,10 +1118,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>97600000</v>
+        <v>139000000</v>
       </c>
       <c r="C30" t="n">
-        <v>1041.2943</v>
+        <v>1041.9935</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1129,10 +1129,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>139000000</v>
+        <v>215030000</v>
       </c>
       <c r="C31" t="n">
-        <v>1041.9935</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1140,10 +1140,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>215030000</v>
+        <v>117720000</v>
       </c>
       <c r="C32" t="n">
-        <v>1045.5352</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1151,10 +1151,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>117720000</v>
+        <v>55800000</v>
       </c>
       <c r="C33" t="n">
-        <v>1046.7697</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>55800000</v>
+        <v>135550000</v>
       </c>
       <c r="C34" t="n">
-        <v>1046.9908</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1173,10 +1173,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>135550000</v>
+        <v>89000000</v>
       </c>
       <c r="C35" t="n">
-        <v>1046.9497</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1184,10 +1184,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>89000000</v>
+        <v>58100000</v>
       </c>
       <c r="C36" t="n">
-        <v>1049.7869</v>
+        <v>1050.2393</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1195,10 +1195,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>58100000</v>
+        <v>86600000</v>
       </c>
       <c r="C37" t="n">
-        <v>1050.2393</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1206,10 +1206,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>86600000</v>
+        <v>95150000</v>
       </c>
       <c r="C38" t="n">
-        <v>1051.1277</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1217,10 +1217,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>95150000</v>
+        <v>147140000</v>
       </c>
       <c r="C39" t="n">
-        <v>1051.69</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1228,10 +1228,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>147140000</v>
+        <v>123760000</v>
       </c>
       <c r="C40" t="n">
-        <v>1051.1226</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1239,10 +1239,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>123760000</v>
+        <v>88880000</v>
       </c>
       <c r="C41" t="n">
-        <v>1053.3625</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1250,10 +1250,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>88880000</v>
+        <v>115600000</v>
       </c>
       <c r="C42" t="n">
-        <v>1053.5273</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1261,10 +1261,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>115600000</v>
+        <v>93120000</v>
       </c>
       <c r="C43" t="n">
-        <v>1053.941</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1272,10 +1272,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>93120000</v>
+        <v>162410000</v>
       </c>
       <c r="C44" t="n">
-        <v>1054.1022</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1283,10 +1283,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>162410000</v>
+        <v>191440000</v>
       </c>
       <c r="C45" t="n">
-        <v>1053.6134</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1294,10 +1294,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>191440000</v>
+        <v>98800000</v>
       </c>
       <c r="C46" t="n">
-        <v>1055.6161</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1305,10 +1305,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>98800000</v>
+        <v>151830000</v>
       </c>
       <c r="C47" t="n">
-        <v>1055.6309</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1316,10 +1316,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>151830000</v>
+        <v>63730000</v>
       </c>
       <c r="C48" t="n">
-        <v>1056.2124</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1327,10 +1327,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>63730000</v>
+        <v>154380000</v>
       </c>
       <c r="C49" t="n">
-        <v>1056.7262</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1338,10 +1338,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>154380000</v>
+        <v>127430000</v>
       </c>
       <c r="C50" t="n">
-        <v>1056.4021</v>
+        <v>1058.3726</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1349,10 +1349,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>127430000</v>
+        <v>90150000</v>
       </c>
       <c r="C51" t="n">
-        <v>1058.3726</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1360,10 +1360,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>90150000</v>
+        <v>78400000</v>
       </c>
       <c r="C52" t="n">
-        <v>1058.5518</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1371,10 +1371,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>78400000</v>
+        <v>102390000</v>
       </c>
       <c r="C53" t="n">
-        <v>1059.0238</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>102390000</v>
+        <v>106130000</v>
       </c>
       <c r="C54" t="n">
-        <v>1058.5037</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>106130000</v>
+        <v>81520000</v>
       </c>
       <c r="C55" t="n">
-        <v>1060.2593</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1404,10 +1404,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>81520000</v>
+        <v>107290000</v>
       </c>
       <c r="C56" t="n">
-        <v>1060.7654</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1415,10 +1415,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>107290000</v>
+        <v>78500000</v>
       </c>
       <c r="C57" t="n">
-        <v>1061.1646</v>
+        <v>1061.6616</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1426,10 +1426,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>78500000</v>
+        <v>115700000</v>
       </c>
       <c r="C58" t="n">
-        <v>1061.6616</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1437,10 +1437,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>115700000</v>
+        <v>135350000</v>
       </c>
       <c r="C59" t="n">
-        <v>1062.0686</v>
+        <v>1063.4131</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1448,10 +1448,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>135350000</v>
+        <v>156190000</v>
       </c>
       <c r="C60" t="n">
-        <v>1063.4131</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1459,10 +1459,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>156190000</v>
+        <v>203700000</v>
       </c>
       <c r="C61" t="n">
-        <v>1063.8278</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1470,10 +1470,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>203700000</v>
+        <v>153120000</v>
       </c>
       <c r="C62" t="n">
-        <v>1064.3394</v>
+        <v>1065.5394</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1481,10 +1481,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>153120000</v>
+        <v>154930000</v>
       </c>
       <c r="C63" t="n">
-        <v>1065.5394</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1492,10 +1492,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>154930000</v>
+        <v>101660000</v>
       </c>
       <c r="C64" t="n">
-        <v>1065.7025</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1503,10 +1503,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>101660000</v>
+        <v>90000000</v>
       </c>
       <c r="C65" t="n">
-        <v>1066.0099</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1514,10 +1514,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>90000000</v>
+        <v>266600000</v>
       </c>
       <c r="C66" t="n">
-        <v>1066.2288</v>
+        <v>1066.7456</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1525,10 +1525,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>266600000</v>
+        <v>146970000</v>
       </c>
       <c r="C67" t="n">
-        <v>1066.7456</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1536,10 +1536,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>146970000</v>
+        <v>61200000</v>
       </c>
       <c r="C68" t="n">
-        <v>1068.2128</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1547,10 +1547,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>61200000</v>
+        <v>69170000</v>
       </c>
       <c r="C69" t="n">
-        <v>1068.3644</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1558,10 +1558,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>69170000</v>
+        <v>41240000</v>
       </c>
       <c r="C70" t="n">
-        <v>1069.0115</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1569,10 +1569,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>41240000</v>
+        <v>145230000</v>
       </c>
       <c r="C71" t="n">
-        <v>1069.0428</v>
+        <v>1068.3027</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1580,10 +1580,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>145230000</v>
+        <v>120040000</v>
       </c>
       <c r="C72" t="n">
-        <v>1068.3027</v>
+        <v>1070.8257</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1591,10 +1591,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>120040000</v>
+        <v>105520000</v>
       </c>
       <c r="C73" t="n">
-        <v>1070.8257</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1602,10 +1602,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>105520000</v>
+        <v>180350000</v>
       </c>
       <c r="C74" t="n">
-        <v>1071.3093</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1613,10 +1613,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>180350000</v>
+        <v>157240000</v>
       </c>
       <c r="C75" t="n">
-        <v>1071.5227</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1624,10 +1624,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>157240000</v>
+        <v>204650000</v>
       </c>
       <c r="C76" t="n">
-        <v>1070.9691</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1635,10 +1635,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>204650000</v>
+        <v>127150000</v>
       </c>
       <c r="C77" t="n">
-        <v>1073.0979</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1646,10 +1646,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>127150000</v>
+        <v>54310000</v>
       </c>
       <c r="C78" t="n">
-        <v>1072.918</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1657,10 +1657,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>54310000</v>
+        <v>75470000</v>
       </c>
       <c r="C79" t="n">
-        <v>1074.1038</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1668,10 +1668,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>75470000</v>
+        <v>79680000</v>
       </c>
       <c r="C80" t="n">
-        <v>1073.4634</v>
+        <v>1075.5159</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1679,10 +1679,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>79680000</v>
+        <v>62750000</v>
       </c>
       <c r="C81" t="n">
-        <v>1075.5159</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1690,10 +1690,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>62750000</v>
+        <v>75600000</v>
       </c>
       <c r="C82" t="n">
-        <v>1075.8248</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1701,10 +1701,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>75600000</v>
+        <v>63990000</v>
       </c>
       <c r="C83" t="n">
-        <v>1076.5104</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1712,10 +1712,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>63990000</v>
+        <v>225590000</v>
       </c>
       <c r="C84" t="n">
-        <v>1076.5854</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1723,10 +1723,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>225590000</v>
+        <v>415320000</v>
       </c>
       <c r="C85" t="n">
-        <v>1075.3297</v>
+        <v>1189.2566</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1734,10 +1734,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>415320000</v>
+        <v>230200000</v>
       </c>
       <c r="C86" t="n">
-        <v>1189.2566</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1745,10 +1745,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>230200000</v>
+        <v>347690000</v>
       </c>
       <c r="C87" t="n">
-        <v>1199.1798</v>
+        <v>1162.0159</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1756,10 +1756,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>347690000</v>
+        <v>339050000</v>
       </c>
       <c r="C88" t="n">
-        <v>1162.0159</v>
+        <v>1082.272</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1767,10 +1767,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>339050000</v>
+        <v>335470000</v>
       </c>
       <c r="C89" t="n">
-        <v>1082.272</v>
+        <v>1092.0538</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1778,10 +1778,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>335470000</v>
+        <v>410800000</v>
       </c>
       <c r="C90" t="n">
-        <v>1092.0538</v>
+        <v>1135.2747</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1789,10 +1789,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>410800000</v>
+        <v>530219970</v>
       </c>
       <c r="C91" t="n">
-        <v>1135.2747</v>
+        <v>1176.6918</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1800,10 +1800,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>530219970</v>
+        <v>368410020</v>
       </c>
       <c r="C92" t="n">
-        <v>1176.6918</v>
+        <v>1173.9497</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1811,10 +1811,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>368410020</v>
+        <v>359710000</v>
       </c>
       <c r="C93" t="n">
-        <v>1173.9497</v>
+        <v>1164.8855</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1822,10 +1822,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>359710000</v>
+        <v>327350000</v>
       </c>
       <c r="C94" t="n">
-        <v>1164.8855</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1833,10 +1833,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>327350000</v>
+        <v>451770000</v>
       </c>
       <c r="C95" t="n">
-        <v>1171.4315</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1844,10 +1844,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>451770000</v>
+        <v>373390000</v>
       </c>
       <c r="C96" t="n">
-        <v>1169.5444</v>
+        <v>1182.7354</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1855,10 +1855,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>373390000</v>
+        <v>267550000</v>
       </c>
       <c r="C97" t="n">
-        <v>1182.7354</v>
+        <v>1201.8551</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1866,10 +1866,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>267550000</v>
+        <v>298740000</v>
       </c>
       <c r="C98" t="n">
-        <v>1201.8551</v>
+        <v>1150.9364</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1877,10 +1877,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>298740000</v>
+        <v>263150000</v>
       </c>
       <c r="C99" t="n">
-        <v>1150.9364</v>
+        <v>1115.3589</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1888,10 +1888,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>263150000</v>
+        <v>200590000</v>
       </c>
       <c r="C100" t="n">
-        <v>1115.3589</v>
+        <v>1114.4547</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1899,10 +1899,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>200590000</v>
+        <v>279730000</v>
       </c>
       <c r="C101" t="n">
-        <v>1114.4547</v>
+        <v>1128.0269</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1910,10 +1910,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>279730000</v>
+        <v>395650020</v>
       </c>
       <c r="C102" t="n">
-        <v>1128.0269</v>
+        <v>1124.8623</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1921,10 +1921,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>395650020</v>
+        <v>331410020</v>
       </c>
       <c r="C103" t="n">
-        <v>1124.8623</v>
+        <v>1130.4915</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>331410020</v>
+        <v>261090000</v>
       </c>
       <c r="C104" t="n">
-        <v>1130.4915</v>
+        <v>1135.9207</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1943,10 +1943,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>261090000</v>
+        <v>242790000</v>
       </c>
       <c r="C105" t="n">
-        <v>1135.9207</v>
+        <v>1144.8073</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1954,10 +1954,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>242790000</v>
+        <v>193430000</v>
       </c>
       <c r="C106" t="n">
-        <v>1144.8073</v>
+        <v>1134.3671</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1965,10 +1965,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>193430000</v>
+        <v>206570000</v>
       </c>
       <c r="C107" t="n">
-        <v>1134.3671</v>
+        <v>1143.0444</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1976,10 +1976,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>206570000</v>
+        <v>295490020</v>
       </c>
       <c r="C108" t="n">
-        <v>1143.0444</v>
+        <v>1144.6138</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1987,10 +1987,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>295490020</v>
+        <v>241590000</v>
       </c>
       <c r="C109" t="n">
-        <v>1144.6138</v>
+        <v>1142.3444</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1998,10 +1998,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>241590000</v>
+        <v>315600000</v>
       </c>
       <c r="C110" t="n">
-        <v>1142.3444</v>
+        <v>1136.4617</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2009,10 +2009,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>315600000</v>
+        <v>322010000</v>
       </c>
       <c r="C111" t="n">
-        <v>1136.4617</v>
+        <v>1148.4205</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2020,10 +2020,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>322010000</v>
+        <v>274060000</v>
       </c>
       <c r="C112" t="n">
-        <v>1148.4205</v>
+        <v>1162.3146</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2031,10 +2031,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>274060000</v>
+        <v>201240000</v>
       </c>
       <c r="C113" t="n">
-        <v>1162.3146</v>
+        <v>1175.8934</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>201240000</v>
+        <v>200400000</v>
       </c>
       <c r="C114" t="n">
-        <v>1175.8934</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2053,10 +2053,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>200400000</v>
+        <v>219350000</v>
       </c>
       <c r="C115" t="n">
-        <v>1196.2443</v>
+        <v>1182.2738</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2064,10 +2064,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>219350000</v>
+        <v>191080000</v>
       </c>
       <c r="C116" t="n">
-        <v>1182.2738</v>
+        <v>1185.7009</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2075,10 +2075,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>191080000</v>
+        <v>279980000</v>
       </c>
       <c r="C117" t="n">
-        <v>1185.7009</v>
+        <v>1184.3539</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2086,10 +2086,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>279980000</v>
+        <v>210400000</v>
       </c>
       <c r="C118" t="n">
-        <v>1184.3539</v>
+        <v>1190.1604</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2097,10 +2097,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>210400000</v>
+        <v>149050000</v>
       </c>
       <c r="C119" t="n">
-        <v>1190.1604</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2108,10 +2108,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>149050000</v>
+        <v>206060000</v>
       </c>
       <c r="C120" t="n">
-        <v>1189.0756</v>
+        <v>1187.3215</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2119,10 +2119,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>206060000</v>
+        <v>327800000</v>
       </c>
       <c r="C121" t="n">
-        <v>1187.3215</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2130,10 +2130,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>327800000</v>
+        <v>194900000</v>
       </c>
       <c r="C122" t="n">
-        <v>1187.3528</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2141,10 +2141,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>194900000</v>
+        <v>150070000</v>
       </c>
       <c r="C123" t="n">
-        <v>1183.6859</v>
+        <v>1186.3999</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2152,10 +2152,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>150070000</v>
+        <v>249730000</v>
       </c>
       <c r="C124" t="n">
-        <v>1186.3999</v>
+        <v>1184.7565</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2163,10 +2163,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>249730000</v>
+        <v>328930000</v>
       </c>
       <c r="C125" t="n">
-        <v>1184.7565</v>
+        <v>1177.4198</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2174,10 +2174,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>328930000</v>
+        <v>319130000</v>
       </c>
       <c r="C126" t="n">
-        <v>1177.4198</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2185,10 +2185,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>319130000</v>
+        <v>290900000</v>
       </c>
       <c r="C127" t="n">
-        <v>1146.302</v>
+        <v>1168.4825</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>290900000</v>
+        <v>272000000</v>
       </c>
       <c r="C128" t="n">
-        <v>1168.4825</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2207,10 +2207,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>272000000</v>
+        <v>459869980</v>
       </c>
       <c r="C129" t="n">
-        <v>1178.1132</v>
+        <v>1176.724</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2218,10 +2218,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>459869980</v>
+        <v>250980000</v>
       </c>
       <c r="C130" t="n">
-        <v>1176.724</v>
+        <v>1192.3014</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2229,10 +2229,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>250980000</v>
+        <v>317930020</v>
       </c>
       <c r="C131" t="n">
-        <v>1192.3014</v>
+        <v>1187.0327</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2240,10 +2240,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>317930020</v>
+        <v>359550000</v>
       </c>
       <c r="C132" t="n">
-        <v>1187.0327</v>
+        <v>1193.3121</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2251,10 +2251,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>359550000</v>
+        <v>279650000</v>
       </c>
       <c r="C133" t="n">
-        <v>1193.3121</v>
+        <v>1207.8153</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2262,10 +2262,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>279650000</v>
+        <v>286200000</v>
       </c>
       <c r="C134" t="n">
-        <v>1207.8153</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2273,10 +2273,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>286200000</v>
+        <v>343900000</v>
       </c>
       <c r="C135" t="n">
-        <v>1232.3434</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2284,10 +2284,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>343900000</v>
+        <v>310469980</v>
       </c>
       <c r="C136" t="n">
-        <v>1225.9089</v>
+        <v>1263.1807</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2295,10 +2295,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>310469980</v>
+        <v>324740000</v>
       </c>
       <c r="C137" t="n">
-        <v>1263.1807</v>
+        <v>1257.3591</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2306,10 +2306,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>324740000</v>
+        <v>301200000</v>
       </c>
       <c r="C138" t="n">
-        <v>1257.3591</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2317,10 +2317,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>301200000</v>
+        <v>298320000</v>
       </c>
       <c r="C139" t="n">
-        <v>1261.2496</v>
+        <v>1261.3674</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2328,10 +2328,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>298320000</v>
+        <v>393980000</v>
       </c>
       <c r="C140" t="n">
-        <v>1261.3674</v>
+        <v>1268.4539</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2339,10 +2339,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>393980000</v>
+        <v>398920000</v>
       </c>
       <c r="C141" t="n">
-        <v>1268.4539</v>
+        <v>1277.0442</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2350,10 +2350,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>398920000</v>
+        <v>323589980</v>
       </c>
       <c r="C142" t="n">
-        <v>1277.0442</v>
+        <v>1257.8407</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2361,10 +2361,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>323589980</v>
+        <v>307460000</v>
       </c>
       <c r="C143" t="n">
-        <v>1257.8407</v>
+        <v>1266.7705</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2372,10 +2372,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>307460000</v>
+        <v>297000000</v>
       </c>
       <c r="C144" t="n">
-        <v>1266.7705</v>
+        <v>1282.9014</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2383,10 +2383,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>297000000</v>
+        <v>291500000</v>
       </c>
       <c r="C145" t="n">
-        <v>1282.9014</v>
+        <v>1287.3074</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2394,10 +2394,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>291500000</v>
+        <v>242700000</v>
       </c>
       <c r="C146" t="n">
-        <v>1287.3074</v>
+        <v>1261.0431</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2405,10 +2405,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>242700000</v>
+        <v>183370000</v>
       </c>
       <c r="C147" t="n">
-        <v>1261.0431</v>
+        <v>1259.6431</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2416,10 +2416,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>183370000</v>
+        <v>241900000</v>
       </c>
       <c r="C148" t="n">
-        <v>1259.6431</v>
+        <v>1261.7827</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2427,10 +2427,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>241900000</v>
+        <v>273740000</v>
       </c>
       <c r="C149" t="n">
-        <v>1261.7827</v>
+        <v>1278.3439</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2438,10 +2438,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>273740000</v>
+        <v>212100000</v>
       </c>
       <c r="C150" t="n">
-        <v>1278.3439</v>
+        <v>1290.4368</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2449,10 +2449,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>212100000</v>
+        <v>308300000</v>
       </c>
       <c r="C151" t="n">
-        <v>1290.4368</v>
+        <v>1295.2062</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2460,10 +2460,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>308300000</v>
+        <v>165990000</v>
       </c>
       <c r="C152" t="n">
-        <v>1295.2062</v>
+        <v>1297.3245</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2471,10 +2471,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>165990000</v>
+        <v>328600000</v>
       </c>
       <c r="C153" t="n">
-        <v>1297.3245</v>
+        <v>1356.9905</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2482,10 +2482,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>328600000</v>
+        <v>213740000</v>
       </c>
       <c r="C154" t="n">
-        <v>1356.9905</v>
+        <v>1364.9016</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2493,10 +2493,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>213740000</v>
+        <v>220980000</v>
       </c>
       <c r="C155" t="n">
-        <v>1364.9016</v>
+        <v>1362.0563</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2504,10 +2504,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>220980000</v>
+        <v>311760000</v>
       </c>
       <c r="C156" t="n">
-        <v>1362.0563</v>
+        <v>1348.5603</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2515,10 +2515,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>311760000</v>
+        <v>324880000</v>
       </c>
       <c r="C157" t="n">
-        <v>1348.5603</v>
+        <v>1333.3021</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2526,10 +2526,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>324880000</v>
+        <v>194200000</v>
       </c>
       <c r="C158" t="n">
-        <v>1333.3021</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2537,10 +2537,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>194200000</v>
+        <v>219200000</v>
       </c>
       <c r="C159" t="n">
-        <v>1329.5576</v>
+        <v>1324.7318</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2548,10 +2548,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>219200000</v>
+        <v>265100000</v>
       </c>
       <c r="C160" t="n">
-        <v>1324.7318</v>
+        <v>1327.6051</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2559,10 +2559,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>265100000</v>
+        <v>318140000</v>
       </c>
       <c r="C161" t="n">
-        <v>1327.6051</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2570,10 +2570,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>318140000</v>
+        <v>323640000</v>
       </c>
       <c r="C162" t="n">
-        <v>1317.6909</v>
+        <v>1317.7236</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2581,10 +2581,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>323640000</v>
+        <v>258100000</v>
       </c>
       <c r="C163" t="n">
-        <v>1317.7236</v>
+        <v>1298.1354</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2592,10 +2592,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>258100000</v>
+        <v>245450000</v>
       </c>
       <c r="C164" t="n">
-        <v>1298.1354</v>
+        <v>1296.6604</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2603,10 +2603,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>245450000</v>
+        <v>388200000</v>
       </c>
       <c r="C165" t="n">
-        <v>1296.6604</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2614,10 +2614,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>388200000</v>
+        <v>218250000</v>
       </c>
       <c r="C166" t="n">
-        <v>1293.891</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2625,10 +2625,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>218250000</v>
+        <v>135000000</v>
       </c>
       <c r="C167" t="n">
-        <v>1299.0688</v>
+        <v>1311.6772</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2636,10 +2636,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>135000000</v>
+        <v>230420000</v>
       </c>
       <c r="C168" t="n">
-        <v>1311.6772</v>
+        <v>1322.6124</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2647,10 +2647,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>230420000</v>
+        <v>186010000</v>
       </c>
       <c r="C169" t="n">
-        <v>1322.6124</v>
+        <v>1349.7784</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2658,10 +2658,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>186010000</v>
+        <v>324380030</v>
       </c>
       <c r="C170" t="n">
-        <v>1349.7784</v>
+        <v>1353.8983</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2669,10 +2669,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>324380030</v>
+        <v>188250000</v>
       </c>
       <c r="C171" t="n">
-        <v>1353.8983</v>
+        <v>1360.0109</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2680,10 +2680,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>188250000</v>
+        <v>262170000</v>
       </c>
       <c r="C172" t="n">
-        <v>1360.0109</v>
+        <v>1338.8644</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2691,10 +2691,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>262170000</v>
+        <v>250290000</v>
       </c>
       <c r="C173" t="n">
-        <v>1338.8644</v>
+        <v>1330.1</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2702,10 +2702,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>250290000</v>
+        <v>396959970</v>
       </c>
       <c r="C174" t="n">
-        <v>1330.1</v>
+        <v>1365.2227</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2713,10 +2713,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>396959970</v>
+        <v>181300000</v>
       </c>
       <c r="C175" t="n">
-        <v>1365.2227</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2724,10 +2724,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>181300000</v>
+        <v>349490020</v>
       </c>
       <c r="C176" t="n">
-        <v>1361.4104</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2735,10 +2735,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>349490020</v>
+        <v>354610000</v>
       </c>
       <c r="C177" t="n">
-        <v>1362.602</v>
+        <v>1366.1195</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2746,10 +2746,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>354610000</v>
+        <v>268370000</v>
       </c>
       <c r="C178" t="n">
-        <v>1366.1195</v>
+        <v>1424.0857</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2757,10 +2757,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>268370000</v>
+        <v>217230000</v>
       </c>
       <c r="C179" t="n">
-        <v>1424.0857</v>
+        <v>1419.2256</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2768,10 +2768,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>217230000</v>
+        <v>202800000</v>
       </c>
       <c r="C180" t="n">
-        <v>1419.2256</v>
+        <v>1418.7972</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2779,10 +2779,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>202800000</v>
+        <v>182600000</v>
       </c>
       <c r="C181" t="n">
-        <v>1418.7972</v>
+        <v>1428.8694</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2790,10 +2790,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>182600000</v>
+        <v>186830000</v>
       </c>
       <c r="C182" t="n">
-        <v>1428.8694</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2801,10 +2801,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>186830000</v>
+        <v>256060000</v>
       </c>
       <c r="C183" t="n">
-        <v>1450.185</v>
+        <v>1463.7825</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2812,10 +2812,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>256060000</v>
+        <v>181350000</v>
       </c>
       <c r="C184" t="n">
-        <v>1463.7825</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2823,10 +2823,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>181350000</v>
+        <v>175400000</v>
       </c>
       <c r="C185" t="n">
-        <v>1464.3728</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2834,10 +2834,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>175400000</v>
+        <v>231000000</v>
       </c>
       <c r="C186" t="n">
-        <v>1473.9847</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2845,10 +2845,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>231000000</v>
+        <v>286250020</v>
       </c>
       <c r="C187" t="n">
-        <v>1474.4945</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2856,10 +2856,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>286250020</v>
+        <v>202930000</v>
       </c>
       <c r="C188" t="n">
-        <v>1475.4567</v>
+        <v>1432.339</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2867,10 +2867,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>202930000</v>
+        <v>275320000</v>
       </c>
       <c r="C189" t="n">
-        <v>1432.339</v>
+        <v>1355.8496</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2878,10 +2878,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>275320000</v>
+        <v>480600000</v>
       </c>
       <c r="C190" t="n">
-        <v>1355.8496</v>
+        <v>1349.3229</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2889,10 +2889,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>480600000</v>
+        <v>589150000</v>
       </c>
       <c r="C191" t="n">
-        <v>1349.3229</v>
+        <v>1328.0879</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2900,10 +2900,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>589150000</v>
+        <v>392600000</v>
       </c>
       <c r="C192" t="n">
-        <v>1328.0879</v>
+        <v>1331.5211</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2911,10 +2911,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>392600000</v>
+        <v>478160000</v>
       </c>
       <c r="C193" t="n">
-        <v>1331.5211</v>
+        <v>1341.6642</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2922,10 +2922,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>478160000</v>
+        <v>496829980</v>
       </c>
       <c r="C194" t="n">
-        <v>1341.6642</v>
+        <v>1374.023</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2933,10 +2933,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>496829980</v>
+        <v>295170020</v>
       </c>
       <c r="C195" t="n">
-        <v>1374.023</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2944,10 +2944,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>295170020</v>
+        <v>169440000</v>
       </c>
       <c r="C196" t="n">
-        <v>1424.7794</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2955,10 +2955,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>169440000</v>
+        <v>215520000</v>
       </c>
       <c r="C197" t="n">
-        <v>1424.6221</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2966,10 +2966,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>215520000</v>
+        <v>262840000</v>
       </c>
       <c r="C198" t="n">
-        <v>1424.9015</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2977,10 +2977,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>262840000</v>
+        <v>315000000</v>
       </c>
       <c r="C199" t="n">
-        <v>1429.9982</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2988,10 +2988,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>315000000</v>
+        <v>338970020</v>
       </c>
       <c r="C200" t="n">
-        <v>1430.0143</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2999,10 +2999,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>338970020</v>
+        <v>260880000</v>
       </c>
       <c r="C201" t="n">
-        <v>1430.0298</v>
+        <v>1445.8335</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3010,10 +3010,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>260880000</v>
+        <v>346149980</v>
       </c>
       <c r="C202" t="n">
-        <v>1445.8335</v>
+        <v>1360.4852</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3021,10 +3021,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>346149980</v>
+        <v>431149980</v>
       </c>
       <c r="C203" t="n">
-        <v>1360.4852</v>
+        <v>1374.5894</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>431149980</v>
+        <v>279500000</v>
       </c>
       <c r="C204" t="n">
-        <v>1374.5894</v>
+        <v>1391.1584</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3043,10 +3043,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>279500000</v>
+        <v>357400000</v>
       </c>
       <c r="C205" t="n">
-        <v>1391.1584</v>
+        <v>1450.9777</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3054,10 +3054,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>357400000</v>
+        <v>254070000</v>
       </c>
       <c r="C206" t="n">
-        <v>1450.9777</v>
+        <v>1468.5831</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3065,10 +3065,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>254070000</v>
+        <v>405740000</v>
       </c>
       <c r="C207" t="n">
-        <v>1468.5831</v>
+        <v>1487.8324</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3076,10 +3076,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>405740000</v>
+        <v>521350000</v>
       </c>
       <c r="C208" t="n">
-        <v>1487.8324</v>
+        <v>1487.4933</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3087,10 +3087,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>521350000</v>
+        <v>393340030</v>
       </c>
       <c r="C209" t="n">
-        <v>1487.4933</v>
+        <v>1484.1245</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3098,10 +3098,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>393340030</v>
+        <v>423890020</v>
       </c>
       <c r="C210" t="n">
-        <v>1484.1245</v>
+        <v>1487.8551</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3109,10 +3109,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>423890020</v>
+        <v>176000000</v>
       </c>
       <c r="C211" t="n">
-        <v>1487.8551</v>
+        <v>1399.3765</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3120,10 +3120,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>176000000</v>
+        <v>334980000</v>
       </c>
       <c r="C212" t="n">
-        <v>1399.3765</v>
+        <v>1470.861</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3131,10 +3131,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>334980000</v>
+        <v>139200000</v>
       </c>
       <c r="C213" t="n">
-        <v>1470.861</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3142,10 +3142,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>139200000</v>
+        <v>127040000</v>
       </c>
       <c r="C214" t="n">
-        <v>1451.923</v>
+        <v>1434.8278</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3153,10 +3153,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>127040000</v>
+        <v>189260000</v>
       </c>
       <c r="C215" t="n">
-        <v>1434.8278</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3164,10 +3164,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>189260000</v>
+        <v>275010000</v>
       </c>
       <c r="C216" t="n">
-        <v>1445.9563</v>
+        <v>1464.5471</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3175,10 +3175,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>275010000</v>
+        <v>194450000</v>
       </c>
       <c r="C217" t="n">
-        <v>1464.5471</v>
+        <v>1471.4448</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3186,10 +3186,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>194450000</v>
+        <v>196250000</v>
       </c>
       <c r="C218" t="n">
-        <v>1471.4448</v>
+        <v>1447.554</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3197,10 +3197,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>196250000</v>
+        <v>208000000</v>
       </c>
       <c r="C219" t="n">
-        <v>1447.554</v>
+        <v>1434.8108</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3208,10 +3208,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>208000000</v>
+        <v>209360000</v>
       </c>
       <c r="C220" t="n">
-        <v>1434.8108</v>
+        <v>1420.3701</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3219,10 +3219,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>209360000</v>
+        <v>212720000</v>
       </c>
       <c r="C221" t="n">
-        <v>1420.3701</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3230,10 +3230,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>212720000</v>
+        <v>241830000</v>
       </c>
       <c r="C222" t="n">
-        <v>1403.0524</v>
+        <v>1407.7981</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3241,10 +3241,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>241830000</v>
+        <v>312580000</v>
       </c>
       <c r="C223" t="n">
-        <v>1407.7981</v>
+        <v>1404.9167</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3252,10 +3252,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>312580000</v>
+        <v>179500000</v>
       </c>
       <c r="C224" t="n">
-        <v>1404.9167</v>
+        <v>1401.7583</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3263,10 +3263,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>179500000</v>
+        <v>107500000</v>
       </c>
       <c r="C225" t="n">
-        <v>1401.7583</v>
+        <v>1392.0065</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3274,10 +3274,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>107500000</v>
+        <v>242990000</v>
       </c>
       <c r="C226" t="n">
-        <v>1392.0065</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3285,10 +3285,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>242990000</v>
+        <v>254470000</v>
       </c>
       <c r="C227" t="n">
-        <v>1402.779</v>
+        <v>1418.5961</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3296,10 +3296,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>254470000</v>
+        <v>331130000</v>
       </c>
       <c r="C228" t="n">
-        <v>1418.5961</v>
+        <v>1446.057</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3307,10 +3307,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>331130000</v>
+        <v>237200000</v>
       </c>
       <c r="C229" t="n">
-        <v>1446.057</v>
+        <v>1450.5864</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3318,10 +3318,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>237200000</v>
+        <v>268310000</v>
       </c>
       <c r="C230" t="n">
-        <v>1450.5864</v>
+        <v>1450.6014</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3329,10 +3329,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>268310000</v>
+        <v>293410020</v>
       </c>
       <c r="C231" t="n">
-        <v>1450.6014</v>
+        <v>1449.8969</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3340,10 +3340,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>293410020</v>
+        <v>190400000</v>
       </c>
       <c r="C232" t="n">
-        <v>1449.8969</v>
+        <v>1454.6573</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3351,10 +3351,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>190400000</v>
+        <v>147700000</v>
       </c>
       <c r="C233" t="n">
-        <v>1454.6573</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="234" x14ac:dyDescent="0.25">
@@ -3362,10 +3362,10 @@
         <v>235</v>
       </c>
       <c r="B234" t="n">
-        <v>52500000</v>
+        <v>67000000</v>
       </c>
       <c r="C234" t="n">
-        <v>1453.9807</v>
+        <v>1450.2876</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -25,15 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">4/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">9/12/2024 12:00:00</t>
   </si>
   <si>
@@ -722,6 +713,12 @@
   </si>
   <si>
     <t xml:space="preserve">4/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -786,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C234"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
@@ -810,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>85800000</v>
+        <v>84630000</v>
       </c>
       <c r="C2" t="n">
-        <v>1012.7305</v>
+        <v>1015.8393</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -821,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>125840000</v>
+        <v>53100000</v>
       </c>
       <c r="C3" t="n">
-        <v>1013.0277</v>
+        <v>1016.1278</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -832,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>136540000</v>
+        <v>154600000</v>
       </c>
       <c r="C4" t="n">
-        <v>1012.78424</v>
+        <v>1016.7524</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -843,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>84630000</v>
+        <v>166760000</v>
       </c>
       <c r="C5" t="n">
-        <v>1015.8393</v>
+        <v>1017.8712</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -854,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>53100000</v>
+        <v>120700000</v>
       </c>
       <c r="C6" t="n">
-        <v>1016.1278</v>
+        <v>1017.9877</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -865,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>154600000</v>
+        <v>136460000</v>
       </c>
       <c r="C7" t="n">
-        <v>1016.7524</v>
+        <v>1020.63074</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -876,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>166760000</v>
+        <v>109500000</v>
       </c>
       <c r="C8" t="n">
-        <v>1017.8712</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -887,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>120700000</v>
+        <v>103710000</v>
       </c>
       <c r="C9" t="n">
-        <v>1017.9877</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -898,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>136460000</v>
+        <v>70020000</v>
       </c>
       <c r="C10" t="n">
-        <v>1020.63074</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -909,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>109500000</v>
+        <v>105600000</v>
       </c>
       <c r="C11" t="n">
-        <v>1020.69635</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -920,10 +917,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>103710000</v>
+        <v>60970000</v>
       </c>
       <c r="C12" t="n">
-        <v>1021.90955</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -931,10 +928,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>70020000</v>
+        <v>135210000</v>
       </c>
       <c r="C13" t="n">
-        <v>1022.2438</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -942,10 +939,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>105600000</v>
+        <v>214050000</v>
       </c>
       <c r="C14" t="n">
-        <v>1022.24274</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -953,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>60970000</v>
+        <v>170650000</v>
       </c>
       <c r="C15" t="n">
-        <v>1025.3103</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -964,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>135210000</v>
+        <v>129920000</v>
       </c>
       <c r="C16" t="n">
-        <v>1028.5804</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -975,10 +972,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>214050000</v>
+        <v>90600000</v>
       </c>
       <c r="C17" t="n">
-        <v>1028.1958</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -986,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>170650000</v>
+        <v>94620000</v>
       </c>
       <c r="C18" t="n">
-        <v>1030.4104</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -997,10 +994,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>129920000</v>
+        <v>76740000</v>
       </c>
       <c r="C19" t="n">
-        <v>1031.7577</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1008,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>90600000</v>
+        <v>60220000</v>
       </c>
       <c r="C20" t="n">
-        <v>1032.4374</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1019,10 +1016,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>94620000</v>
+        <v>80100000</v>
       </c>
       <c r="C21" t="n">
-        <v>1034.7297</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1030,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>76740000</v>
+        <v>144200000</v>
       </c>
       <c r="C22" t="n">
-        <v>1035.4338</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1041,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>60220000</v>
+        <v>66560000</v>
       </c>
       <c r="C23" t="n">
-        <v>1035.8505</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1052,10 +1049,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>80100000</v>
+        <v>69770000</v>
       </c>
       <c r="C24" t="n">
-        <v>1036.7753</v>
+        <v>1040.3352</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1063,10 +1060,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>144200000</v>
+        <v>59000000</v>
       </c>
       <c r="C25" t="n">
-        <v>1036.8966</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1074,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>66560000</v>
+        <v>97600000</v>
       </c>
       <c r="C26" t="n">
-        <v>1039.2858</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1085,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>69770000</v>
+        <v>139000000</v>
       </c>
       <c r="C27" t="n">
-        <v>1040.3352</v>
+        <v>1041.9935</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1096,10 +1093,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>59000000</v>
+        <v>215030000</v>
       </c>
       <c r="C28" t="n">
-        <v>1040.7654</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1107,10 +1104,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>97600000</v>
+        <v>117720000</v>
       </c>
       <c r="C29" t="n">
-        <v>1041.2943</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1118,10 +1115,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>139000000</v>
+        <v>55800000</v>
       </c>
       <c r="C30" t="n">
-        <v>1041.9935</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1129,10 +1126,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>215030000</v>
+        <v>135550000</v>
       </c>
       <c r="C31" t="n">
-        <v>1045.5352</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1140,10 +1137,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>117720000</v>
+        <v>89000000</v>
       </c>
       <c r="C32" t="n">
-        <v>1046.7697</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1151,10 +1148,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>55800000</v>
+        <v>58100000</v>
       </c>
       <c r="C33" t="n">
-        <v>1046.9908</v>
+        <v>1050.2393</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1162,10 +1159,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>135550000</v>
+        <v>86600000</v>
       </c>
       <c r="C34" t="n">
-        <v>1046.9497</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1173,10 +1170,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>89000000</v>
+        <v>95150000</v>
       </c>
       <c r="C35" t="n">
-        <v>1049.7869</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1184,10 +1181,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>58100000</v>
+        <v>147140000</v>
       </c>
       <c r="C36" t="n">
-        <v>1050.2393</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1195,10 +1192,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>86600000</v>
+        <v>123760000</v>
       </c>
       <c r="C37" t="n">
-        <v>1051.1277</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1206,10 +1203,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>95150000</v>
+        <v>88880000</v>
       </c>
       <c r="C38" t="n">
-        <v>1051.69</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1217,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>147140000</v>
+        <v>115600000</v>
       </c>
       <c r="C39" t="n">
-        <v>1051.1226</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1228,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>123760000</v>
+        <v>93120000</v>
       </c>
       <c r="C40" t="n">
-        <v>1053.3625</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1239,10 +1236,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>88880000</v>
+        <v>162410000</v>
       </c>
       <c r="C41" t="n">
-        <v>1053.5273</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1250,10 +1247,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>115600000</v>
+        <v>191440000</v>
       </c>
       <c r="C42" t="n">
-        <v>1053.941</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1261,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>93120000</v>
+        <v>98800000</v>
       </c>
       <c r="C43" t="n">
-        <v>1054.1022</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1272,10 +1269,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>162410000</v>
+        <v>151830000</v>
       </c>
       <c r="C44" t="n">
-        <v>1053.6134</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1283,10 +1280,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>191440000</v>
+        <v>63730000</v>
       </c>
       <c r="C45" t="n">
-        <v>1055.6161</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1294,10 +1291,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>98800000</v>
+        <v>154380000</v>
       </c>
       <c r="C46" t="n">
-        <v>1055.6309</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1305,10 +1302,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>151830000</v>
+        <v>127430000</v>
       </c>
       <c r="C47" t="n">
-        <v>1056.2124</v>
+        <v>1058.3726</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1316,10 +1313,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>63730000</v>
+        <v>90150000</v>
       </c>
       <c r="C48" t="n">
-        <v>1056.7262</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1327,10 +1324,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>154380000</v>
+        <v>78400000</v>
       </c>
       <c r="C49" t="n">
-        <v>1056.4021</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1338,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>127430000</v>
+        <v>102390000</v>
       </c>
       <c r="C50" t="n">
-        <v>1058.3726</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1349,10 +1346,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>90150000</v>
+        <v>106130000</v>
       </c>
       <c r="C51" t="n">
-        <v>1058.5518</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1360,10 +1357,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>78400000</v>
+        <v>81520000</v>
       </c>
       <c r="C52" t="n">
-        <v>1059.0238</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1371,10 +1368,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>102390000</v>
+        <v>107290000</v>
       </c>
       <c r="C53" t="n">
-        <v>1058.5037</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1382,10 +1379,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>106130000</v>
+        <v>78500000</v>
       </c>
       <c r="C54" t="n">
-        <v>1060.2593</v>
+        <v>1061.6616</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1393,10 +1390,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>81520000</v>
+        <v>115700000</v>
       </c>
       <c r="C55" t="n">
-        <v>1060.7654</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1404,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>107290000</v>
+        <v>135350000</v>
       </c>
       <c r="C56" t="n">
-        <v>1061.1646</v>
+        <v>1063.4131</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1415,10 +1412,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>78500000</v>
+        <v>156190000</v>
       </c>
       <c r="C57" t="n">
-        <v>1061.6616</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1426,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>115700000</v>
+        <v>203700000</v>
       </c>
       <c r="C58" t="n">
-        <v>1062.0686</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1437,10 +1434,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>135350000</v>
+        <v>153120000</v>
       </c>
       <c r="C59" t="n">
-        <v>1063.4131</v>
+        <v>1065.5394</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1448,10 +1445,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>156190000</v>
+        <v>154930000</v>
       </c>
       <c r="C60" t="n">
-        <v>1063.8278</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1459,10 +1456,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>203700000</v>
+        <v>101660000</v>
       </c>
       <c r="C61" t="n">
-        <v>1064.3394</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1470,10 +1467,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>153120000</v>
+        <v>90000000</v>
       </c>
       <c r="C62" t="n">
-        <v>1065.5394</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1481,10 +1478,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>154930000</v>
+        <v>266600000</v>
       </c>
       <c r="C63" t="n">
-        <v>1065.7025</v>
+        <v>1066.7456</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1492,10 +1489,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>101660000</v>
+        <v>146970000</v>
       </c>
       <c r="C64" t="n">
-        <v>1066.0099</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1503,10 +1500,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>90000000</v>
+        <v>61200000</v>
       </c>
       <c r="C65" t="n">
-        <v>1066.2288</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1514,10 +1511,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>266600000</v>
+        <v>69170000</v>
       </c>
       <c r="C66" t="n">
-        <v>1066.7456</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1525,10 +1522,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>146970000</v>
+        <v>41240000</v>
       </c>
       <c r="C67" t="n">
-        <v>1068.2128</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1536,10 +1533,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>61200000</v>
+        <v>145230000</v>
       </c>
       <c r="C68" t="n">
-        <v>1068.3644</v>
+        <v>1068.3027</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1547,10 +1544,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>69170000</v>
+        <v>120040000</v>
       </c>
       <c r="C69" t="n">
-        <v>1069.0115</v>
+        <v>1070.8257</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1558,10 +1555,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>41240000</v>
+        <v>105520000</v>
       </c>
       <c r="C70" t="n">
-        <v>1069.0428</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1569,10 +1566,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>145230000</v>
+        <v>180350000</v>
       </c>
       <c r="C71" t="n">
-        <v>1068.3027</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1580,10 +1577,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>120040000</v>
+        <v>157240000</v>
       </c>
       <c r="C72" t="n">
-        <v>1070.8257</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1591,10 +1588,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>105520000</v>
+        <v>204650000</v>
       </c>
       <c r="C73" t="n">
-        <v>1071.3093</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1602,10 +1599,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>180350000</v>
+        <v>127150000</v>
       </c>
       <c r="C74" t="n">
-        <v>1071.5227</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1613,10 +1610,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>157240000</v>
+        <v>54310000</v>
       </c>
       <c r="C75" t="n">
-        <v>1070.9691</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1624,10 +1621,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>204650000</v>
+        <v>75470000</v>
       </c>
       <c r="C76" t="n">
-        <v>1073.0979</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1635,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>127150000</v>
+        <v>79680000</v>
       </c>
       <c r="C77" t="n">
-        <v>1072.918</v>
+        <v>1075.5159</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1646,10 +1643,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>54310000</v>
+        <v>62750000</v>
       </c>
       <c r="C78" t="n">
-        <v>1074.1038</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1657,10 +1654,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>75470000</v>
+        <v>75600000</v>
       </c>
       <c r="C79" t="n">
-        <v>1073.4634</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1668,10 +1665,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>79680000</v>
+        <v>63990000</v>
       </c>
       <c r="C80" t="n">
-        <v>1075.5159</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1679,10 +1676,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>62750000</v>
+        <v>225590000</v>
       </c>
       <c r="C81" t="n">
-        <v>1075.8248</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1690,10 +1687,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>75600000</v>
+        <v>415320000</v>
       </c>
       <c r="C82" t="n">
-        <v>1076.5104</v>
+        <v>1189.2566</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1701,10 +1698,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>63990000</v>
+        <v>230200000</v>
       </c>
       <c r="C83" t="n">
-        <v>1076.5854</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1712,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>225590000</v>
+        <v>347690000</v>
       </c>
       <c r="C84" t="n">
-        <v>1075.3297</v>
+        <v>1162.0159</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1723,10 +1720,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>415320000</v>
+        <v>339050000</v>
       </c>
       <c r="C85" t="n">
-        <v>1189.2566</v>
+        <v>1082.272</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1734,10 +1731,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>230200000</v>
+        <v>335470000</v>
       </c>
       <c r="C86" t="n">
-        <v>1199.1798</v>
+        <v>1092.0538</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1745,10 +1742,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>347690000</v>
+        <v>410800000</v>
       </c>
       <c r="C87" t="n">
-        <v>1162.0159</v>
+        <v>1135.2747</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1756,10 +1753,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>339050000</v>
+        <v>530219970</v>
       </c>
       <c r="C88" t="n">
-        <v>1082.272</v>
+        <v>1176.6918</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1767,10 +1764,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>335470000</v>
+        <v>368410020</v>
       </c>
       <c r="C89" t="n">
-        <v>1092.0538</v>
+        <v>1173.9497</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1778,10 +1775,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>410800000</v>
+        <v>359710000</v>
       </c>
       <c r="C90" t="n">
-        <v>1135.2747</v>
+        <v>1164.8855</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1789,10 +1786,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>530219970</v>
+        <v>327350000</v>
       </c>
       <c r="C91" t="n">
-        <v>1176.6918</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1800,10 +1797,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>368410020</v>
+        <v>451770000</v>
       </c>
       <c r="C92" t="n">
-        <v>1173.9497</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1811,10 +1808,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>359710000</v>
+        <v>373390000</v>
       </c>
       <c r="C93" t="n">
-        <v>1164.8855</v>
+        <v>1182.7354</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1822,10 +1819,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>327350000</v>
+        <v>267550000</v>
       </c>
       <c r="C94" t="n">
-        <v>1171.4315</v>
+        <v>1201.8551</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1833,10 +1830,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>451770000</v>
+        <v>298740000</v>
       </c>
       <c r="C95" t="n">
-        <v>1169.5444</v>
+        <v>1150.9364</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1844,10 +1841,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>373390000</v>
+        <v>263150000</v>
       </c>
       <c r="C96" t="n">
-        <v>1182.7354</v>
+        <v>1115.3589</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1855,10 +1852,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>267550000</v>
+        <v>200590000</v>
       </c>
       <c r="C97" t="n">
-        <v>1201.8551</v>
+        <v>1114.4547</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1866,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>298740000</v>
+        <v>279730000</v>
       </c>
       <c r="C98" t="n">
-        <v>1150.9364</v>
+        <v>1128.0269</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1877,10 +1874,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>263150000</v>
+        <v>395650020</v>
       </c>
       <c r="C99" t="n">
-        <v>1115.3589</v>
+        <v>1124.8623</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1888,10 +1885,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>200590000</v>
+        <v>331410020</v>
       </c>
       <c r="C100" t="n">
-        <v>1114.4547</v>
+        <v>1130.4915</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1899,10 +1896,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>279730000</v>
+        <v>261090000</v>
       </c>
       <c r="C101" t="n">
-        <v>1128.0269</v>
+        <v>1135.9207</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1910,10 +1907,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>395650020</v>
+        <v>242790000</v>
       </c>
       <c r="C102" t="n">
-        <v>1124.8623</v>
+        <v>1144.8073</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1921,10 +1918,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>331410020</v>
+        <v>193430000</v>
       </c>
       <c r="C103" t="n">
-        <v>1130.4915</v>
+        <v>1134.3671</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1932,10 +1929,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>261090000</v>
+        <v>206570000</v>
       </c>
       <c r="C104" t="n">
-        <v>1135.9207</v>
+        <v>1143.0444</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1943,10 +1940,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>242790000</v>
+        <v>295490020</v>
       </c>
       <c r="C105" t="n">
-        <v>1144.8073</v>
+        <v>1144.6138</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1954,10 +1951,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>193430000</v>
+        <v>241590000</v>
       </c>
       <c r="C106" t="n">
-        <v>1134.3671</v>
+        <v>1142.3444</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1965,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>206570000</v>
+        <v>315600000</v>
       </c>
       <c r="C107" t="n">
-        <v>1143.0444</v>
+        <v>1136.4617</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1976,10 +1973,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>295490020</v>
+        <v>322010000</v>
       </c>
       <c r="C108" t="n">
-        <v>1144.6138</v>
+        <v>1148.4205</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1987,10 +1984,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>241590000</v>
+        <v>274060000</v>
       </c>
       <c r="C109" t="n">
-        <v>1142.3444</v>
+        <v>1162.3146</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1998,10 +1995,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>315600000</v>
+        <v>201240000</v>
       </c>
       <c r="C110" t="n">
-        <v>1136.4617</v>
+        <v>1175.8934</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2009,10 +2006,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>322010000</v>
+        <v>200400000</v>
       </c>
       <c r="C111" t="n">
-        <v>1148.4205</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2020,10 +2017,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>274060000</v>
+        <v>219350000</v>
       </c>
       <c r="C112" t="n">
-        <v>1162.3146</v>
+        <v>1182.2738</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2031,10 +2028,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>201240000</v>
+        <v>191080000</v>
       </c>
       <c r="C113" t="n">
-        <v>1175.8934</v>
+        <v>1185.7009</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2042,10 +2039,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>200400000</v>
+        <v>279980000</v>
       </c>
       <c r="C114" t="n">
-        <v>1196.2443</v>
+        <v>1184.3539</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2053,10 +2050,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>219350000</v>
+        <v>210400000</v>
       </c>
       <c r="C115" t="n">
-        <v>1182.2738</v>
+        <v>1190.1604</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2064,10 +2061,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>191080000</v>
+        <v>149050000</v>
       </c>
       <c r="C116" t="n">
-        <v>1185.7009</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2075,10 +2072,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>279980000</v>
+        <v>206060000</v>
       </c>
       <c r="C117" t="n">
-        <v>1184.3539</v>
+        <v>1187.3215</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2086,10 +2083,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>210400000</v>
+        <v>327800000</v>
       </c>
       <c r="C118" t="n">
-        <v>1190.1604</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2097,10 +2094,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>149050000</v>
+        <v>194900000</v>
       </c>
       <c r="C119" t="n">
-        <v>1189.0756</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2108,10 +2105,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>206060000</v>
+        <v>150070000</v>
       </c>
       <c r="C120" t="n">
-        <v>1187.3215</v>
+        <v>1186.3999</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2119,10 +2116,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>327800000</v>
+        <v>249730000</v>
       </c>
       <c r="C121" t="n">
-        <v>1187.3528</v>
+        <v>1184.7565</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2130,10 +2127,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>194900000</v>
+        <v>328930000</v>
       </c>
       <c r="C122" t="n">
-        <v>1183.6859</v>
+        <v>1177.4198</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2141,10 +2138,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>150070000</v>
+        <v>319130000</v>
       </c>
       <c r="C123" t="n">
-        <v>1186.3999</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2152,10 +2149,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>249730000</v>
+        <v>290900000</v>
       </c>
       <c r="C124" t="n">
-        <v>1184.7565</v>
+        <v>1168.4825</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2163,10 +2160,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>328930000</v>
+        <v>272000000</v>
       </c>
       <c r="C125" t="n">
-        <v>1177.4198</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2174,10 +2171,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>319130000</v>
+        <v>459869980</v>
       </c>
       <c r="C126" t="n">
-        <v>1146.302</v>
+        <v>1176.724</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2185,10 +2182,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>290900000</v>
+        <v>250980000</v>
       </c>
       <c r="C127" t="n">
-        <v>1168.4825</v>
+        <v>1192.3014</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2196,10 +2193,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>272000000</v>
+        <v>317930020</v>
       </c>
       <c r="C128" t="n">
-        <v>1178.1132</v>
+        <v>1187.0327</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2207,10 +2204,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>459869980</v>
+        <v>359550000</v>
       </c>
       <c r="C129" t="n">
-        <v>1176.724</v>
+        <v>1193.3121</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2218,10 +2215,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>250980000</v>
+        <v>279650000</v>
       </c>
       <c r="C130" t="n">
-        <v>1192.3014</v>
+        <v>1207.8153</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2229,10 +2226,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>317930020</v>
+        <v>286200000</v>
       </c>
       <c r="C131" t="n">
-        <v>1187.0327</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2240,10 +2237,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>359550000</v>
+        <v>343900000</v>
       </c>
       <c r="C132" t="n">
-        <v>1193.3121</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2251,10 +2248,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>279650000</v>
+        <v>310469980</v>
       </c>
       <c r="C133" t="n">
-        <v>1207.8153</v>
+        <v>1263.1807</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2262,10 +2259,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>286200000</v>
+        <v>324740000</v>
       </c>
       <c r="C134" t="n">
-        <v>1232.3434</v>
+        <v>1257.3591</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2273,10 +2270,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>343900000</v>
+        <v>301200000</v>
       </c>
       <c r="C135" t="n">
-        <v>1225.9089</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2284,10 +2281,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>310469980</v>
+        <v>298320000</v>
       </c>
       <c r="C136" t="n">
-        <v>1263.1807</v>
+        <v>1261.3674</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2295,10 +2292,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>324740000</v>
+        <v>393980000</v>
       </c>
       <c r="C137" t="n">
-        <v>1257.3591</v>
+        <v>1268.4539</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2306,10 +2303,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>301200000</v>
+        <v>398920000</v>
       </c>
       <c r="C138" t="n">
-        <v>1261.2496</v>
+        <v>1277.0442</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2317,10 +2314,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>298320000</v>
+        <v>323589980</v>
       </c>
       <c r="C139" t="n">
-        <v>1261.3674</v>
+        <v>1257.8407</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2328,10 +2325,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>393980000</v>
+        <v>307460000</v>
       </c>
       <c r="C140" t="n">
-        <v>1268.4539</v>
+        <v>1266.7705</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2339,10 +2336,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>398920000</v>
+        <v>297000000</v>
       </c>
       <c r="C141" t="n">
-        <v>1277.0442</v>
+        <v>1282.9014</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2350,10 +2347,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>323589980</v>
+        <v>291500000</v>
       </c>
       <c r="C142" t="n">
-        <v>1257.8407</v>
+        <v>1287.3074</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2361,10 +2358,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>307460000</v>
+        <v>242700000</v>
       </c>
       <c r="C143" t="n">
-        <v>1266.7705</v>
+        <v>1261.0431</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2372,10 +2369,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>297000000</v>
+        <v>183370000</v>
       </c>
       <c r="C144" t="n">
-        <v>1282.9014</v>
+        <v>1259.6431</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2383,10 +2380,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>291500000</v>
+        <v>241900000</v>
       </c>
       <c r="C145" t="n">
-        <v>1287.3074</v>
+        <v>1261.7827</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2394,10 +2391,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>242700000</v>
+        <v>273740000</v>
       </c>
       <c r="C146" t="n">
-        <v>1261.0431</v>
+        <v>1278.3439</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2405,10 +2402,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>183370000</v>
+        <v>212100000</v>
       </c>
       <c r="C147" t="n">
-        <v>1259.6431</v>
+        <v>1290.4368</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2416,10 +2413,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>241900000</v>
+        <v>308300000</v>
       </c>
       <c r="C148" t="n">
-        <v>1261.7827</v>
+        <v>1295.2062</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2427,10 +2424,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>273740000</v>
+        <v>165990000</v>
       </c>
       <c r="C149" t="n">
-        <v>1278.3439</v>
+        <v>1297.3245</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2438,10 +2435,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>212100000</v>
+        <v>328600000</v>
       </c>
       <c r="C150" t="n">
-        <v>1290.4368</v>
+        <v>1356.9905</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2449,10 +2446,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>308300000</v>
+        <v>213740000</v>
       </c>
       <c r="C151" t="n">
-        <v>1295.2062</v>
+        <v>1364.9016</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2460,10 +2457,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>165990000</v>
+        <v>220980000</v>
       </c>
       <c r="C152" t="n">
-        <v>1297.3245</v>
+        <v>1362.0563</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2471,10 +2468,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>328600000</v>
+        <v>311760000</v>
       </c>
       <c r="C153" t="n">
-        <v>1356.9905</v>
+        <v>1348.5603</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2482,10 +2479,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>213740000</v>
+        <v>324880000</v>
       </c>
       <c r="C154" t="n">
-        <v>1364.9016</v>
+        <v>1333.3021</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2493,10 +2490,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>220980000</v>
+        <v>194200000</v>
       </c>
       <c r="C155" t="n">
-        <v>1362.0563</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2504,10 +2501,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>311760000</v>
+        <v>219200000</v>
       </c>
       <c r="C156" t="n">
-        <v>1348.5603</v>
+        <v>1324.7318</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2515,10 +2512,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>324880000</v>
+        <v>265100000</v>
       </c>
       <c r="C157" t="n">
-        <v>1333.3021</v>
+        <v>1327.6051</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2526,10 +2523,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>194200000</v>
+        <v>318140000</v>
       </c>
       <c r="C158" t="n">
-        <v>1329.5576</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2537,10 +2534,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>219200000</v>
+        <v>323640000</v>
       </c>
       <c r="C159" t="n">
-        <v>1324.7318</v>
+        <v>1317.7236</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2548,10 +2545,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>265100000</v>
+        <v>258100000</v>
       </c>
       <c r="C160" t="n">
-        <v>1327.6051</v>
+        <v>1298.1354</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2559,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>318140000</v>
+        <v>245450000</v>
       </c>
       <c r="C161" t="n">
-        <v>1317.6909</v>
+        <v>1296.6604</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2570,10 +2567,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>323640000</v>
+        <v>388200000</v>
       </c>
       <c r="C162" t="n">
-        <v>1317.7236</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2581,10 +2578,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>258100000</v>
+        <v>218250000</v>
       </c>
       <c r="C163" t="n">
-        <v>1298.1354</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2592,10 +2589,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>245450000</v>
+        <v>135000000</v>
       </c>
       <c r="C164" t="n">
-        <v>1296.6604</v>
+        <v>1311.6772</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2603,10 +2600,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>388200000</v>
+        <v>230420000</v>
       </c>
       <c r="C165" t="n">
-        <v>1293.891</v>
+        <v>1322.6124</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2614,10 +2611,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>218250000</v>
+        <v>186010000</v>
       </c>
       <c r="C166" t="n">
-        <v>1299.0688</v>
+        <v>1349.7784</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2625,10 +2622,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>135000000</v>
+        <v>324380030</v>
       </c>
       <c r="C167" t="n">
-        <v>1311.6772</v>
+        <v>1353.8983</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2636,10 +2633,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>230420000</v>
+        <v>188250000</v>
       </c>
       <c r="C168" t="n">
-        <v>1322.6124</v>
+        <v>1360.0109</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2647,10 +2644,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>186010000</v>
+        <v>262170000</v>
       </c>
       <c r="C169" t="n">
-        <v>1349.7784</v>
+        <v>1338.8644</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2658,10 +2655,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>324380030</v>
+        <v>250290000</v>
       </c>
       <c r="C170" t="n">
-        <v>1353.8983</v>
+        <v>1330.1</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2669,10 +2666,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>188250000</v>
+        <v>396959970</v>
       </c>
       <c r="C171" t="n">
-        <v>1360.0109</v>
+        <v>1365.2227</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2680,10 +2677,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>262170000</v>
+        <v>181300000</v>
       </c>
       <c r="C172" t="n">
-        <v>1338.8644</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2691,10 +2688,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>250290000</v>
+        <v>349490020</v>
       </c>
       <c r="C173" t="n">
-        <v>1330.1</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2702,10 +2699,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>396959970</v>
+        <v>354610000</v>
       </c>
       <c r="C174" t="n">
-        <v>1365.2227</v>
+        <v>1366.1195</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2713,10 +2710,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>181300000</v>
+        <v>268370000</v>
       </c>
       <c r="C175" t="n">
-        <v>1361.4104</v>
+        <v>1424.0857</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2724,10 +2721,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>349490020</v>
+        <v>217230000</v>
       </c>
       <c r="C176" t="n">
-        <v>1362.602</v>
+        <v>1419.2256</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2735,10 +2732,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>354610000</v>
+        <v>202800000</v>
       </c>
       <c r="C177" t="n">
-        <v>1366.1195</v>
+        <v>1418.7972</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2746,10 +2743,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>268370000</v>
+        <v>182600000</v>
       </c>
       <c r="C178" t="n">
-        <v>1424.0857</v>
+        <v>1428.8694</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2757,10 +2754,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>217230000</v>
+        <v>186830000</v>
       </c>
       <c r="C179" t="n">
-        <v>1419.2256</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2768,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>202800000</v>
+        <v>256060000</v>
       </c>
       <c r="C180" t="n">
-        <v>1418.7972</v>
+        <v>1463.7825</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2779,10 +2776,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>182600000</v>
+        <v>181350000</v>
       </c>
       <c r="C181" t="n">
-        <v>1428.8694</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2790,10 +2787,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>186830000</v>
+        <v>175400000</v>
       </c>
       <c r="C182" t="n">
-        <v>1450.185</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2801,10 +2798,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>256060000</v>
+        <v>231000000</v>
       </c>
       <c r="C183" t="n">
-        <v>1463.7825</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2812,10 +2809,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>181350000</v>
+        <v>286250020</v>
       </c>
       <c r="C184" t="n">
-        <v>1464.3728</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2823,10 +2820,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>175400000</v>
+        <v>202930000</v>
       </c>
       <c r="C185" t="n">
-        <v>1473.9847</v>
+        <v>1432.339</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2834,10 +2831,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>231000000</v>
+        <v>275320000</v>
       </c>
       <c r="C186" t="n">
-        <v>1474.4945</v>
+        <v>1355.8496</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2845,10 +2842,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>286250020</v>
+        <v>480600000</v>
       </c>
       <c r="C187" t="n">
-        <v>1475.4567</v>
+        <v>1349.3229</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2856,10 +2853,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>202930000</v>
+        <v>589150000</v>
       </c>
       <c r="C188" t="n">
-        <v>1432.339</v>
+        <v>1328.0879</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2867,10 +2864,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>275320000</v>
+        <v>392600000</v>
       </c>
       <c r="C189" t="n">
-        <v>1355.8496</v>
+        <v>1331.5211</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2878,10 +2875,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>480600000</v>
+        <v>478160000</v>
       </c>
       <c r="C190" t="n">
-        <v>1349.3229</v>
+        <v>1341.6642</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2889,10 +2886,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>589150000</v>
+        <v>496829980</v>
       </c>
       <c r="C191" t="n">
-        <v>1328.0879</v>
+        <v>1374.023</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2900,10 +2897,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>392600000</v>
+        <v>295170020</v>
       </c>
       <c r="C192" t="n">
-        <v>1331.5211</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2911,10 +2908,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>478160000</v>
+        <v>169440000</v>
       </c>
       <c r="C193" t="n">
-        <v>1341.6642</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2922,10 +2919,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>496829980</v>
+        <v>215520000</v>
       </c>
       <c r="C194" t="n">
-        <v>1374.023</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2933,10 +2930,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>295170020</v>
+        <v>262840000</v>
       </c>
       <c r="C195" t="n">
-        <v>1424.7794</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2944,10 +2941,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>169440000</v>
+        <v>315000000</v>
       </c>
       <c r="C196" t="n">
-        <v>1424.6221</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2955,10 +2952,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>215520000</v>
+        <v>338970020</v>
       </c>
       <c r="C197" t="n">
-        <v>1424.9015</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2966,10 +2963,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>262840000</v>
+        <v>260880000</v>
       </c>
       <c r="C198" t="n">
-        <v>1429.9982</v>
+        <v>1445.8335</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2977,10 +2974,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>315000000</v>
+        <v>346149980</v>
       </c>
       <c r="C199" t="n">
-        <v>1430.0143</v>
+        <v>1360.4852</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2988,10 +2985,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>338970020</v>
+        <v>431149980</v>
       </c>
       <c r="C200" t="n">
-        <v>1430.0298</v>
+        <v>1374.5894</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2999,10 +2996,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>260880000</v>
+        <v>279500000</v>
       </c>
       <c r="C201" t="n">
-        <v>1445.8335</v>
+        <v>1391.1584</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3010,10 +3007,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>346149980</v>
+        <v>357400000</v>
       </c>
       <c r="C202" t="n">
-        <v>1360.4852</v>
+        <v>1450.9777</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3021,10 +3018,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>431149980</v>
+        <v>254070000</v>
       </c>
       <c r="C203" t="n">
-        <v>1374.5894</v>
+        <v>1468.5831</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3032,10 +3029,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>279500000</v>
+        <v>405740000</v>
       </c>
       <c r="C204" t="n">
-        <v>1391.1584</v>
+        <v>1487.8324</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3043,10 +3040,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>357400000</v>
+        <v>521350000</v>
       </c>
       <c r="C205" t="n">
-        <v>1450.9777</v>
+        <v>1487.4933</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3054,10 +3051,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>254070000</v>
+        <v>393340030</v>
       </c>
       <c r="C206" t="n">
-        <v>1468.5831</v>
+        <v>1484.1245</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3065,10 +3062,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>405740000</v>
+        <v>423890020</v>
       </c>
       <c r="C207" t="n">
-        <v>1487.8324</v>
+        <v>1487.8551</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3076,10 +3073,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>521350000</v>
+        <v>176000000</v>
       </c>
       <c r="C208" t="n">
-        <v>1487.4933</v>
+        <v>1399.3765</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3087,10 +3084,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>393340030</v>
+        <v>334980000</v>
       </c>
       <c r="C209" t="n">
-        <v>1484.1245</v>
+        <v>1470.861</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3098,10 +3095,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>423890020</v>
+        <v>139200000</v>
       </c>
       <c r="C210" t="n">
-        <v>1487.8551</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3109,10 +3106,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>176000000</v>
+        <v>127040000</v>
       </c>
       <c r="C211" t="n">
-        <v>1399.3765</v>
+        <v>1434.8278</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3120,10 +3117,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>334980000</v>
+        <v>189260000</v>
       </c>
       <c r="C212" t="n">
-        <v>1470.861</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3131,10 +3128,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>139200000</v>
+        <v>275010000</v>
       </c>
       <c r="C213" t="n">
-        <v>1451.923</v>
+        <v>1464.5471</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3142,10 +3139,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>127040000</v>
+        <v>194450000</v>
       </c>
       <c r="C214" t="n">
-        <v>1434.8278</v>
+        <v>1471.4448</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3153,10 +3150,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>189260000</v>
+        <v>196250000</v>
       </c>
       <c r="C215" t="n">
-        <v>1445.9563</v>
+        <v>1447.554</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3164,10 +3161,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>275010000</v>
+        <v>208000000</v>
       </c>
       <c r="C216" t="n">
-        <v>1464.5471</v>
+        <v>1434.8108</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3175,10 +3172,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>194450000</v>
+        <v>209360000</v>
       </c>
       <c r="C217" t="n">
-        <v>1471.4448</v>
+        <v>1420.3701</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3186,10 +3183,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>196250000</v>
+        <v>212720000</v>
       </c>
       <c r="C218" t="n">
-        <v>1447.554</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3197,10 +3194,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>208000000</v>
+        <v>241830000</v>
       </c>
       <c r="C219" t="n">
-        <v>1434.8108</v>
+        <v>1407.7981</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3208,10 +3205,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>209360000</v>
+        <v>312580000</v>
       </c>
       <c r="C220" t="n">
-        <v>1420.3701</v>
+        <v>1404.9167</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3219,10 +3216,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>212720000</v>
+        <v>179500000</v>
       </c>
       <c r="C221" t="n">
-        <v>1403.0524</v>
+        <v>1401.7583</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3230,10 +3227,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>241830000</v>
+        <v>107500000</v>
       </c>
       <c r="C222" t="n">
-        <v>1407.7981</v>
+        <v>1392.0065</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3241,10 +3238,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>312580000</v>
+        <v>242990000</v>
       </c>
       <c r="C223" t="n">
-        <v>1404.9167</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3252,10 +3249,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>179500000</v>
+        <v>254470000</v>
       </c>
       <c r="C224" t="n">
-        <v>1401.7583</v>
+        <v>1418.5961</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3263,10 +3260,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>107500000</v>
+        <v>331130000</v>
       </c>
       <c r="C225" t="n">
-        <v>1392.0065</v>
+        <v>1446.057</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3274,10 +3271,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>242990000</v>
+        <v>237200000</v>
       </c>
       <c r="C226" t="n">
-        <v>1402.779</v>
+        <v>1450.5864</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3285,10 +3282,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>254470000</v>
+        <v>268310000</v>
       </c>
       <c r="C227" t="n">
-        <v>1418.5961</v>
+        <v>1450.6014</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3296,10 +3293,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>331130000</v>
+        <v>293410020</v>
       </c>
       <c r="C228" t="n">
-        <v>1446.057</v>
+        <v>1449.8969</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3307,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>237200000</v>
+        <v>190400000</v>
       </c>
       <c r="C229" t="n">
-        <v>1450.5864</v>
+        <v>1454.6573</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3318,10 +3315,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>268310000</v>
+        <v>147700000</v>
       </c>
       <c r="C230" t="n">
-        <v>1450.6014</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3329,10 +3326,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>293410020</v>
+        <v>152560000</v>
       </c>
       <c r="C231" t="n">
-        <v>1449.8969</v>
+        <v>1447.5764</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3340,10 +3337,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>190400000</v>
+        <v>195400000</v>
       </c>
       <c r="C232" t="n">
-        <v>1454.6573</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3351,21 +3348,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>147700000</v>
+        <v>10580000</v>
       </c>
       <c r="C233" t="n">
-        <v>1453.8477</v>
-      </c>
-    </row>
-    <row r="234" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>235</v>
-      </c>
-      <c r="B234" t="n">
-        <v>67000000</v>
-      </c>
-      <c r="C234" t="n">
-        <v>1450.2876</v>
+        <v>1438.0549</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -25,12 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">9/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">11/12/2024 12:00:00</t>
   </si>
   <si>
@@ -719,6 +713,12 @@
   </si>
   <si>
     <t xml:space="preserve">9/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -807,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>84630000</v>
+        <v>154600000</v>
       </c>
       <c r="C2" t="n">
-        <v>1015.8393</v>
+        <v>1016.7524</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -818,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>53100000</v>
+        <v>166760000</v>
       </c>
       <c r="C3" t="n">
-        <v>1016.1278</v>
+        <v>1017.8712</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -829,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>154600000</v>
+        <v>120700000</v>
       </c>
       <c r="C4" t="n">
-        <v>1016.7524</v>
+        <v>1017.9877</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -840,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>166760000</v>
+        <v>136460000</v>
       </c>
       <c r="C5" t="n">
-        <v>1017.8712</v>
+        <v>1020.63074</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>120700000</v>
+        <v>109500000</v>
       </c>
       <c r="C6" t="n">
-        <v>1017.9877</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -862,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>136460000</v>
+        <v>103710000</v>
       </c>
       <c r="C7" t="n">
-        <v>1020.63074</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>109500000</v>
+        <v>70020000</v>
       </c>
       <c r="C8" t="n">
-        <v>1020.69635</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -884,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>103710000</v>
+        <v>105600000</v>
       </c>
       <c r="C9" t="n">
-        <v>1021.90955</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -895,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>70020000</v>
+        <v>60970000</v>
       </c>
       <c r="C10" t="n">
-        <v>1022.2438</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -906,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>105600000</v>
+        <v>135210000</v>
       </c>
       <c r="C11" t="n">
-        <v>1022.24274</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -917,10 +917,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>60970000</v>
+        <v>214050000</v>
       </c>
       <c r="C12" t="n">
-        <v>1025.3103</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -928,10 +928,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>135210000</v>
+        <v>170650000</v>
       </c>
       <c r="C13" t="n">
-        <v>1028.5804</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -939,10 +939,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>214050000</v>
+        <v>129920000</v>
       </c>
       <c r="C14" t="n">
-        <v>1028.1958</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -950,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>170650000</v>
+        <v>90600000</v>
       </c>
       <c r="C15" t="n">
-        <v>1030.4104</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -961,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>129920000</v>
+        <v>94620000</v>
       </c>
       <c r="C16" t="n">
-        <v>1031.7577</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -972,10 +972,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>90600000</v>
+        <v>76740000</v>
       </c>
       <c r="C17" t="n">
-        <v>1032.4374</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -983,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>94620000</v>
+        <v>60220000</v>
       </c>
       <c r="C18" t="n">
-        <v>1034.7297</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -994,10 +994,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>76740000</v>
+        <v>80100000</v>
       </c>
       <c r="C19" t="n">
-        <v>1035.4338</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1005,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>60220000</v>
+        <v>144200000</v>
       </c>
       <c r="C20" t="n">
-        <v>1035.8505</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1016,10 +1016,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>80100000</v>
+        <v>66560000</v>
       </c>
       <c r="C21" t="n">
-        <v>1036.7753</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1027,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>144200000</v>
+        <v>69770000</v>
       </c>
       <c r="C22" t="n">
-        <v>1036.8966</v>
+        <v>1040.3352</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1038,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>66560000</v>
+        <v>59000000</v>
       </c>
       <c r="C23" t="n">
-        <v>1039.2858</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1049,10 +1049,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>69770000</v>
+        <v>97600000</v>
       </c>
       <c r="C24" t="n">
-        <v>1040.3352</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1060,10 +1060,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>59000000</v>
+        <v>139000000</v>
       </c>
       <c r="C25" t="n">
-        <v>1040.7654</v>
+        <v>1041.9935</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1071,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>97600000</v>
+        <v>215030000</v>
       </c>
       <c r="C26" t="n">
-        <v>1041.2943</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1082,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>139000000</v>
+        <v>117720000</v>
       </c>
       <c r="C27" t="n">
-        <v>1041.9935</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1093,10 +1093,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>215030000</v>
+        <v>55800000</v>
       </c>
       <c r="C28" t="n">
-        <v>1045.5352</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1104,10 +1104,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>117720000</v>
+        <v>135550000</v>
       </c>
       <c r="C29" t="n">
-        <v>1046.7697</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1115,10 +1115,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>55800000</v>
+        <v>89000000</v>
       </c>
       <c r="C30" t="n">
-        <v>1046.9908</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1126,10 +1126,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>135550000</v>
+        <v>58100000</v>
       </c>
       <c r="C31" t="n">
-        <v>1046.9497</v>
+        <v>1050.2393</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>89000000</v>
+        <v>86600000</v>
       </c>
       <c r="C32" t="n">
-        <v>1049.7869</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1148,10 +1148,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>58100000</v>
+        <v>95150000</v>
       </c>
       <c r="C33" t="n">
-        <v>1050.2393</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>86600000</v>
+        <v>147140000</v>
       </c>
       <c r="C34" t="n">
-        <v>1051.1277</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1170,10 +1170,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>95150000</v>
+        <v>123760000</v>
       </c>
       <c r="C35" t="n">
-        <v>1051.69</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1181,10 +1181,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>147140000</v>
+        <v>88880000</v>
       </c>
       <c r="C36" t="n">
-        <v>1051.1226</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1192,10 +1192,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>123760000</v>
+        <v>115600000</v>
       </c>
       <c r="C37" t="n">
-        <v>1053.3625</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1203,10 +1203,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>88880000</v>
+        <v>93120000</v>
       </c>
       <c r="C38" t="n">
-        <v>1053.5273</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1214,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>115600000</v>
+        <v>162410000</v>
       </c>
       <c r="C39" t="n">
-        <v>1053.941</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1225,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>93120000</v>
+        <v>191440000</v>
       </c>
       <c r="C40" t="n">
-        <v>1054.1022</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1236,10 +1236,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>162410000</v>
+        <v>98800000</v>
       </c>
       <c r="C41" t="n">
-        <v>1053.6134</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1247,10 +1247,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>191440000</v>
+        <v>151830000</v>
       </c>
       <c r="C42" t="n">
-        <v>1055.6161</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1258,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>98800000</v>
+        <v>63730000</v>
       </c>
       <c r="C43" t="n">
-        <v>1055.6309</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1269,10 +1269,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>151830000</v>
+        <v>154380000</v>
       </c>
       <c r="C44" t="n">
-        <v>1056.2124</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1280,10 +1280,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>63730000</v>
+        <v>127430000</v>
       </c>
       <c r="C45" t="n">
-        <v>1056.7262</v>
+        <v>1058.3726</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1291,10 +1291,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>154380000</v>
+        <v>90150000</v>
       </c>
       <c r="C46" t="n">
-        <v>1056.4021</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1302,10 +1302,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>127430000</v>
+        <v>78400000</v>
       </c>
       <c r="C47" t="n">
-        <v>1058.3726</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1313,10 +1313,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>90150000</v>
+        <v>102390000</v>
       </c>
       <c r="C48" t="n">
-        <v>1058.5518</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1324,10 +1324,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>78400000</v>
+        <v>106130000</v>
       </c>
       <c r="C49" t="n">
-        <v>1059.0238</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1335,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>102390000</v>
+        <v>81520000</v>
       </c>
       <c r="C50" t="n">
-        <v>1058.5037</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1346,10 +1346,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>106130000</v>
+        <v>107290000</v>
       </c>
       <c r="C51" t="n">
-        <v>1060.2593</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1357,10 +1357,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>81520000</v>
+        <v>78500000</v>
       </c>
       <c r="C52" t="n">
-        <v>1060.7654</v>
+        <v>1061.6616</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>107290000</v>
+        <v>115700000</v>
       </c>
       <c r="C53" t="n">
-        <v>1061.1646</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1379,10 +1379,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>78500000</v>
+        <v>135350000</v>
       </c>
       <c r="C54" t="n">
-        <v>1061.6616</v>
+        <v>1063.4131</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1390,10 +1390,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>115700000</v>
+        <v>156190000</v>
       </c>
       <c r="C55" t="n">
-        <v>1062.0686</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1401,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>135350000</v>
+        <v>203700000</v>
       </c>
       <c r="C56" t="n">
-        <v>1063.4131</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1412,10 +1412,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>156190000</v>
+        <v>153120000</v>
       </c>
       <c r="C57" t="n">
-        <v>1063.8278</v>
+        <v>1065.5394</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>203700000</v>
+        <v>154930000</v>
       </c>
       <c r="C58" t="n">
-        <v>1064.3394</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1434,10 +1434,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>153120000</v>
+        <v>101660000</v>
       </c>
       <c r="C59" t="n">
-        <v>1065.5394</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>154930000</v>
+        <v>90000000</v>
       </c>
       <c r="C60" t="n">
-        <v>1065.7025</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1456,10 +1456,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>101660000</v>
+        <v>266600000</v>
       </c>
       <c r="C61" t="n">
-        <v>1066.0099</v>
+        <v>1066.7456</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1467,10 +1467,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>90000000</v>
+        <v>146970000</v>
       </c>
       <c r="C62" t="n">
-        <v>1066.2288</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1478,10 +1478,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>266600000</v>
+        <v>61200000</v>
       </c>
       <c r="C63" t="n">
-        <v>1066.7456</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1489,10 +1489,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>146970000</v>
+        <v>69170000</v>
       </c>
       <c r="C64" t="n">
-        <v>1068.2128</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1500,10 +1500,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>61200000</v>
+        <v>41240000</v>
       </c>
       <c r="C65" t="n">
-        <v>1068.3644</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1511,10 +1511,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>69170000</v>
+        <v>145230000</v>
       </c>
       <c r="C66" t="n">
-        <v>1069.0115</v>
+        <v>1068.3027</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1522,10 +1522,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>41240000</v>
+        <v>120040000</v>
       </c>
       <c r="C67" t="n">
-        <v>1069.0428</v>
+        <v>1070.8257</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1533,10 +1533,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>145230000</v>
+        <v>105520000</v>
       </c>
       <c r="C68" t="n">
-        <v>1068.3027</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1544,10 +1544,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>120040000</v>
+        <v>180350000</v>
       </c>
       <c r="C69" t="n">
-        <v>1070.8257</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1555,10 +1555,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>105520000</v>
+        <v>157240000</v>
       </c>
       <c r="C70" t="n">
-        <v>1071.3093</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1566,10 +1566,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>180350000</v>
+        <v>204650000</v>
       </c>
       <c r="C71" t="n">
-        <v>1071.5227</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1577,10 +1577,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>157240000</v>
+        <v>127150000</v>
       </c>
       <c r="C72" t="n">
-        <v>1070.9691</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1588,10 +1588,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>204650000</v>
+        <v>54310000</v>
       </c>
       <c r="C73" t="n">
-        <v>1073.0979</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1599,10 +1599,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>127150000</v>
+        <v>75470000</v>
       </c>
       <c r="C74" t="n">
-        <v>1072.918</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1610,10 +1610,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>54310000</v>
+        <v>79680000</v>
       </c>
       <c r="C75" t="n">
-        <v>1074.1038</v>
+        <v>1075.5159</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1621,10 +1621,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>75470000</v>
+        <v>62750000</v>
       </c>
       <c r="C76" t="n">
-        <v>1073.4634</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1632,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>79680000</v>
+        <v>75600000</v>
       </c>
       <c r="C77" t="n">
-        <v>1075.5159</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1643,10 +1643,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>62750000</v>
+        <v>63990000</v>
       </c>
       <c r="C78" t="n">
-        <v>1075.8248</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1654,10 +1654,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>75600000</v>
+        <v>225590000</v>
       </c>
       <c r="C79" t="n">
-        <v>1076.5104</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1665,10 +1665,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>63990000</v>
+        <v>415320000</v>
       </c>
       <c r="C80" t="n">
-        <v>1076.5854</v>
+        <v>1189.2566</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1676,10 +1676,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>225590000</v>
+        <v>230200000</v>
       </c>
       <c r="C81" t="n">
-        <v>1075.3297</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1687,10 +1687,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>415320000</v>
+        <v>347690000</v>
       </c>
       <c r="C82" t="n">
-        <v>1189.2566</v>
+        <v>1162.0159</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1698,10 +1698,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>230200000</v>
+        <v>339050000</v>
       </c>
       <c r="C83" t="n">
-        <v>1199.1798</v>
+        <v>1082.272</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1709,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>347690000</v>
+        <v>335470000</v>
       </c>
       <c r="C84" t="n">
-        <v>1162.0159</v>
+        <v>1092.0538</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1720,10 +1720,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>339050000</v>
+        <v>410800000</v>
       </c>
       <c r="C85" t="n">
-        <v>1082.272</v>
+        <v>1135.2747</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1731,10 +1731,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>335470000</v>
+        <v>530219970</v>
       </c>
       <c r="C86" t="n">
-        <v>1092.0538</v>
+        <v>1176.6918</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1742,10 +1742,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>410800000</v>
+        <v>368410020</v>
       </c>
       <c r="C87" t="n">
-        <v>1135.2747</v>
+        <v>1173.9497</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1753,10 +1753,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>530219970</v>
+        <v>359710000</v>
       </c>
       <c r="C88" t="n">
-        <v>1176.6918</v>
+        <v>1164.8855</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1764,10 +1764,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>368410020</v>
+        <v>327350000</v>
       </c>
       <c r="C89" t="n">
-        <v>1173.9497</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1775,10 +1775,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>359710000</v>
+        <v>451770000</v>
       </c>
       <c r="C90" t="n">
-        <v>1164.8855</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1786,10 +1786,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>327350000</v>
+        <v>373390000</v>
       </c>
       <c r="C91" t="n">
-        <v>1171.4315</v>
+        <v>1182.7354</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1797,10 +1797,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>451770000</v>
+        <v>267550000</v>
       </c>
       <c r="C92" t="n">
-        <v>1169.5444</v>
+        <v>1201.8551</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1808,10 +1808,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>373390000</v>
+        <v>298740000</v>
       </c>
       <c r="C93" t="n">
-        <v>1182.7354</v>
+        <v>1150.9364</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1819,10 +1819,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>267550000</v>
+        <v>263150000</v>
       </c>
       <c r="C94" t="n">
-        <v>1201.8551</v>
+        <v>1115.3589</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1830,10 +1830,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>298740000</v>
+        <v>200590000</v>
       </c>
       <c r="C95" t="n">
-        <v>1150.9364</v>
+        <v>1114.4547</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1841,10 +1841,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>263150000</v>
+        <v>279730000</v>
       </c>
       <c r="C96" t="n">
-        <v>1115.3589</v>
+        <v>1128.0269</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1852,10 +1852,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>200590000</v>
+        <v>395650020</v>
       </c>
       <c r="C97" t="n">
-        <v>1114.4547</v>
+        <v>1124.8623</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1863,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>279730000</v>
+        <v>331410020</v>
       </c>
       <c r="C98" t="n">
-        <v>1128.0269</v>
+        <v>1130.4915</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1874,10 +1874,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>395650020</v>
+        <v>261090000</v>
       </c>
       <c r="C99" t="n">
-        <v>1124.8623</v>
+        <v>1135.9207</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1885,10 +1885,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>331410020</v>
+        <v>242790000</v>
       </c>
       <c r="C100" t="n">
-        <v>1130.4915</v>
+        <v>1144.8073</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1896,10 +1896,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>261090000</v>
+        <v>193430000</v>
       </c>
       <c r="C101" t="n">
-        <v>1135.9207</v>
+        <v>1134.3671</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1907,10 +1907,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>242790000</v>
+        <v>206570000</v>
       </c>
       <c r="C102" t="n">
-        <v>1144.8073</v>
+        <v>1143.0444</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>193430000</v>
+        <v>295490020</v>
       </c>
       <c r="C103" t="n">
-        <v>1134.3671</v>
+        <v>1144.6138</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1929,10 +1929,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>206570000</v>
+        <v>241590000</v>
       </c>
       <c r="C104" t="n">
-        <v>1143.0444</v>
+        <v>1142.3444</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1940,10 +1940,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>295490020</v>
+        <v>315600000</v>
       </c>
       <c r="C105" t="n">
-        <v>1144.6138</v>
+        <v>1136.4617</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1951,10 +1951,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>241590000</v>
+        <v>322010000</v>
       </c>
       <c r="C106" t="n">
-        <v>1142.3444</v>
+        <v>1148.4205</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1962,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>315600000</v>
+        <v>274060000</v>
       </c>
       <c r="C107" t="n">
-        <v>1136.4617</v>
+        <v>1162.3146</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1973,10 +1973,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>322010000</v>
+        <v>201240000</v>
       </c>
       <c r="C108" t="n">
-        <v>1148.4205</v>
+        <v>1175.8934</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1984,10 +1984,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>274060000</v>
+        <v>200400000</v>
       </c>
       <c r="C109" t="n">
-        <v>1162.3146</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1995,10 +1995,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>201240000</v>
+        <v>219350000</v>
       </c>
       <c r="C110" t="n">
-        <v>1175.8934</v>
+        <v>1182.2738</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2006,10 +2006,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>200400000</v>
+        <v>191080000</v>
       </c>
       <c r="C111" t="n">
-        <v>1196.2443</v>
+        <v>1185.7009</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2017,10 +2017,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>219350000</v>
+        <v>279980000</v>
       </c>
       <c r="C112" t="n">
-        <v>1182.2738</v>
+        <v>1184.3539</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2028,10 +2028,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>191080000</v>
+        <v>210400000</v>
       </c>
       <c r="C113" t="n">
-        <v>1185.7009</v>
+        <v>1190.1604</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2039,10 +2039,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>279980000</v>
+        <v>149050000</v>
       </c>
       <c r="C114" t="n">
-        <v>1184.3539</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2050,10 +2050,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>210400000</v>
+        <v>206060000</v>
       </c>
       <c r="C115" t="n">
-        <v>1190.1604</v>
+        <v>1187.3215</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2061,10 +2061,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>149050000</v>
+        <v>327800000</v>
       </c>
       <c r="C116" t="n">
-        <v>1189.0756</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2072,10 +2072,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>206060000</v>
+        <v>194900000</v>
       </c>
       <c r="C117" t="n">
-        <v>1187.3215</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2083,10 +2083,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>327800000</v>
+        <v>150070000</v>
       </c>
       <c r="C118" t="n">
-        <v>1187.3528</v>
+        <v>1186.3999</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2094,10 +2094,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>194900000</v>
+        <v>249730000</v>
       </c>
       <c r="C119" t="n">
-        <v>1183.6859</v>
+        <v>1184.7565</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2105,10 +2105,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>150070000</v>
+        <v>328930000</v>
       </c>
       <c r="C120" t="n">
-        <v>1186.3999</v>
+        <v>1177.4198</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2116,10 +2116,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>249730000</v>
+        <v>319130000</v>
       </c>
       <c r="C121" t="n">
-        <v>1184.7565</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2127,10 +2127,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>328930000</v>
+        <v>290900000</v>
       </c>
       <c r="C122" t="n">
-        <v>1177.4198</v>
+        <v>1168.4825</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2138,10 +2138,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>319130000</v>
+        <v>272000000</v>
       </c>
       <c r="C123" t="n">
-        <v>1146.302</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2149,10 +2149,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>290900000</v>
+        <v>459869980</v>
       </c>
       <c r="C124" t="n">
-        <v>1168.4825</v>
+        <v>1176.724</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2160,10 +2160,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>272000000</v>
+        <v>250980000</v>
       </c>
       <c r="C125" t="n">
-        <v>1178.1132</v>
+        <v>1192.3014</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2171,10 +2171,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>459869980</v>
+        <v>317930020</v>
       </c>
       <c r="C126" t="n">
-        <v>1176.724</v>
+        <v>1187.0327</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>250980000</v>
+        <v>359550000</v>
       </c>
       <c r="C127" t="n">
-        <v>1192.3014</v>
+        <v>1193.3121</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2193,10 +2193,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>317930020</v>
+        <v>279650000</v>
       </c>
       <c r="C128" t="n">
-        <v>1187.0327</v>
+        <v>1207.8153</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2204,10 +2204,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>359550000</v>
+        <v>286200000</v>
       </c>
       <c r="C129" t="n">
-        <v>1193.3121</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>279650000</v>
+        <v>343900000</v>
       </c>
       <c r="C130" t="n">
-        <v>1207.8153</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2226,10 +2226,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>286200000</v>
+        <v>310469980</v>
       </c>
       <c r="C131" t="n">
-        <v>1232.3434</v>
+        <v>1263.1807</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2237,10 +2237,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>343900000</v>
+        <v>324740000</v>
       </c>
       <c r="C132" t="n">
-        <v>1225.9089</v>
+        <v>1257.3591</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2248,10 +2248,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>310469980</v>
+        <v>301200000</v>
       </c>
       <c r="C133" t="n">
-        <v>1263.1807</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2259,10 +2259,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>324740000</v>
+        <v>298320000</v>
       </c>
       <c r="C134" t="n">
-        <v>1257.3591</v>
+        <v>1261.3674</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2270,10 +2270,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>301200000</v>
+        <v>393980000</v>
       </c>
       <c r="C135" t="n">
-        <v>1261.2496</v>
+        <v>1268.4539</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2281,10 +2281,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>298320000</v>
+        <v>398920000</v>
       </c>
       <c r="C136" t="n">
-        <v>1261.3674</v>
+        <v>1277.0442</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2292,10 +2292,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>393980000</v>
+        <v>323589980</v>
       </c>
       <c r="C137" t="n">
-        <v>1268.4539</v>
+        <v>1257.8407</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2303,10 +2303,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>398920000</v>
+        <v>307460000</v>
       </c>
       <c r="C138" t="n">
-        <v>1277.0442</v>
+        <v>1266.7705</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2314,10 +2314,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>323589980</v>
+        <v>297000000</v>
       </c>
       <c r="C139" t="n">
-        <v>1257.8407</v>
+        <v>1282.9014</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2325,10 +2325,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>307460000</v>
+        <v>291500000</v>
       </c>
       <c r="C140" t="n">
-        <v>1266.7705</v>
+        <v>1287.3074</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2336,10 +2336,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>297000000</v>
+        <v>242700000</v>
       </c>
       <c r="C141" t="n">
-        <v>1282.9014</v>
+        <v>1261.0431</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2347,10 +2347,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>291500000</v>
+        <v>183370000</v>
       </c>
       <c r="C142" t="n">
-        <v>1287.3074</v>
+        <v>1259.6431</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2358,10 +2358,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>242700000</v>
+        <v>241900000</v>
       </c>
       <c r="C143" t="n">
-        <v>1261.0431</v>
+        <v>1261.7827</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2369,10 +2369,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>183370000</v>
+        <v>273740000</v>
       </c>
       <c r="C144" t="n">
-        <v>1259.6431</v>
+        <v>1278.3439</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2380,10 +2380,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>241900000</v>
+        <v>212100000</v>
       </c>
       <c r="C145" t="n">
-        <v>1261.7827</v>
+        <v>1290.4368</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2391,10 +2391,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>273740000</v>
+        <v>308300000</v>
       </c>
       <c r="C146" t="n">
-        <v>1278.3439</v>
+        <v>1295.2062</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2402,10 +2402,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>212100000</v>
+        <v>165990000</v>
       </c>
       <c r="C147" t="n">
-        <v>1290.4368</v>
+        <v>1297.3245</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2413,10 +2413,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>308300000</v>
+        <v>328600000</v>
       </c>
       <c r="C148" t="n">
-        <v>1295.2062</v>
+        <v>1356.9905</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2424,10 +2424,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>165990000</v>
+        <v>213740000</v>
       </c>
       <c r="C149" t="n">
-        <v>1297.3245</v>
+        <v>1364.9016</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2435,10 +2435,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>328600000</v>
+        <v>220980000</v>
       </c>
       <c r="C150" t="n">
-        <v>1356.9905</v>
+        <v>1362.0563</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2446,10 +2446,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>213740000</v>
+        <v>311760000</v>
       </c>
       <c r="C151" t="n">
-        <v>1364.9016</v>
+        <v>1348.5603</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2457,10 +2457,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>220980000</v>
+        <v>324880000</v>
       </c>
       <c r="C152" t="n">
-        <v>1362.0563</v>
+        <v>1333.3021</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2468,10 +2468,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>311760000</v>
+        <v>194200000</v>
       </c>
       <c r="C153" t="n">
-        <v>1348.5603</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2479,10 +2479,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>324880000</v>
+        <v>219200000</v>
       </c>
       <c r="C154" t="n">
-        <v>1333.3021</v>
+        <v>1324.7318</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2490,10 +2490,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>194200000</v>
+        <v>265100000</v>
       </c>
       <c r="C155" t="n">
-        <v>1329.5576</v>
+        <v>1327.6051</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2501,10 +2501,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>219200000</v>
+        <v>318140000</v>
       </c>
       <c r="C156" t="n">
-        <v>1324.7318</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2512,10 +2512,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>265100000</v>
+        <v>323640000</v>
       </c>
       <c r="C157" t="n">
-        <v>1327.6051</v>
+        <v>1317.7236</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2523,10 +2523,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>318140000</v>
+        <v>258100000</v>
       </c>
       <c r="C158" t="n">
-        <v>1317.6909</v>
+        <v>1298.1354</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2534,10 +2534,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>323640000</v>
+        <v>245450000</v>
       </c>
       <c r="C159" t="n">
-        <v>1317.7236</v>
+        <v>1296.6604</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2545,10 +2545,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>258100000</v>
+        <v>388200000</v>
       </c>
       <c r="C160" t="n">
-        <v>1298.1354</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2556,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>245450000</v>
+        <v>218250000</v>
       </c>
       <c r="C161" t="n">
-        <v>1296.6604</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2567,10 +2567,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>388200000</v>
+        <v>135000000</v>
       </c>
       <c r="C162" t="n">
-        <v>1293.891</v>
+        <v>1311.6772</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2578,10 +2578,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>218250000</v>
+        <v>230420000</v>
       </c>
       <c r="C163" t="n">
-        <v>1299.0688</v>
+        <v>1322.6124</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2589,10 +2589,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>135000000</v>
+        <v>186010000</v>
       </c>
       <c r="C164" t="n">
-        <v>1311.6772</v>
+        <v>1349.7784</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2600,10 +2600,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>230420000</v>
+        <v>324380030</v>
       </c>
       <c r="C165" t="n">
-        <v>1322.6124</v>
+        <v>1353.8983</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2611,10 +2611,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>186010000</v>
+        <v>188250000</v>
       </c>
       <c r="C166" t="n">
-        <v>1349.7784</v>
+        <v>1360.0109</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2622,10 +2622,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>324380030</v>
+        <v>262170000</v>
       </c>
       <c r="C167" t="n">
-        <v>1353.8983</v>
+        <v>1338.8644</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2633,10 +2633,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>188250000</v>
+        <v>250290000</v>
       </c>
       <c r="C168" t="n">
-        <v>1360.0109</v>
+        <v>1330.1</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2644,10 +2644,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>262170000</v>
+        <v>396959970</v>
       </c>
       <c r="C169" t="n">
-        <v>1338.8644</v>
+        <v>1365.2227</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2655,10 +2655,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>250290000</v>
+        <v>181300000</v>
       </c>
       <c r="C170" t="n">
-        <v>1330.1</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2666,10 +2666,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>396959970</v>
+        <v>349490020</v>
       </c>
       <c r="C171" t="n">
-        <v>1365.2227</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2677,10 +2677,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>181300000</v>
+        <v>354610000</v>
       </c>
       <c r="C172" t="n">
-        <v>1361.4104</v>
+        <v>1366.1195</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2688,10 +2688,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>349490020</v>
+        <v>268370000</v>
       </c>
       <c r="C173" t="n">
-        <v>1362.602</v>
+        <v>1424.0857</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2699,10 +2699,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>354610000</v>
+        <v>217230000</v>
       </c>
       <c r="C174" t="n">
-        <v>1366.1195</v>
+        <v>1419.2256</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2710,10 +2710,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>268370000</v>
+        <v>202800000</v>
       </c>
       <c r="C175" t="n">
-        <v>1424.0857</v>
+        <v>1418.7972</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2721,10 +2721,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>217230000</v>
+        <v>182600000</v>
       </c>
       <c r="C176" t="n">
-        <v>1419.2256</v>
+        <v>1428.8694</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2732,10 +2732,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>202800000</v>
+        <v>186830000</v>
       </c>
       <c r="C177" t="n">
-        <v>1418.7972</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2743,10 +2743,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>182600000</v>
+        <v>256060000</v>
       </c>
       <c r="C178" t="n">
-        <v>1428.8694</v>
+        <v>1463.7825</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2754,10 +2754,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>186830000</v>
+        <v>181350000</v>
       </c>
       <c r="C179" t="n">
-        <v>1450.185</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2765,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>256060000</v>
+        <v>175400000</v>
       </c>
       <c r="C180" t="n">
-        <v>1463.7825</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2776,10 +2776,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>181350000</v>
+        <v>231000000</v>
       </c>
       <c r="C181" t="n">
-        <v>1464.3728</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2787,10 +2787,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>175400000</v>
+        <v>286250020</v>
       </c>
       <c r="C182" t="n">
-        <v>1473.9847</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2798,10 +2798,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>231000000</v>
+        <v>202930000</v>
       </c>
       <c r="C183" t="n">
-        <v>1474.4945</v>
+        <v>1432.339</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2809,10 +2809,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>286250020</v>
+        <v>275320000</v>
       </c>
       <c r="C184" t="n">
-        <v>1475.4567</v>
+        <v>1355.8496</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2820,10 +2820,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>202930000</v>
+        <v>480600000</v>
       </c>
       <c r="C185" t="n">
-        <v>1432.339</v>
+        <v>1349.3229</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2831,10 +2831,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>275320000</v>
+        <v>589150000</v>
       </c>
       <c r="C186" t="n">
-        <v>1355.8496</v>
+        <v>1328.0879</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2842,10 +2842,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>480600000</v>
+        <v>392600000</v>
       </c>
       <c r="C187" t="n">
-        <v>1349.3229</v>
+        <v>1331.5211</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2853,10 +2853,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>589150000</v>
+        <v>478160000</v>
       </c>
       <c r="C188" t="n">
-        <v>1328.0879</v>
+        <v>1341.6642</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2864,10 +2864,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>392600000</v>
+        <v>496829980</v>
       </c>
       <c r="C189" t="n">
-        <v>1331.5211</v>
+        <v>1374.023</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2875,10 +2875,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>478160000</v>
+        <v>295170020</v>
       </c>
       <c r="C190" t="n">
-        <v>1341.6642</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2886,10 +2886,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>496829980</v>
+        <v>169440000</v>
       </c>
       <c r="C191" t="n">
-        <v>1374.023</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2897,10 +2897,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>295170020</v>
+        <v>215520000</v>
       </c>
       <c r="C192" t="n">
-        <v>1424.7794</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2908,10 +2908,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>169440000</v>
+        <v>262840000</v>
       </c>
       <c r="C193" t="n">
-        <v>1424.6221</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2919,10 +2919,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>215520000</v>
+        <v>315000000</v>
       </c>
       <c r="C194" t="n">
-        <v>1424.9015</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2930,10 +2930,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>262840000</v>
+        <v>338970020</v>
       </c>
       <c r="C195" t="n">
-        <v>1429.9982</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2941,10 +2941,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>315000000</v>
+        <v>260880000</v>
       </c>
       <c r="C196" t="n">
-        <v>1430.0143</v>
+        <v>1445.8335</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2952,10 +2952,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>338970020</v>
+        <v>346149980</v>
       </c>
       <c r="C197" t="n">
-        <v>1430.0298</v>
+        <v>1360.4852</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2963,10 +2963,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>260880000</v>
+        <v>431149980</v>
       </c>
       <c r="C198" t="n">
-        <v>1445.8335</v>
+        <v>1374.5894</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2974,10 +2974,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>346149980</v>
+        <v>279500000</v>
       </c>
       <c r="C199" t="n">
-        <v>1360.4852</v>
+        <v>1391.1584</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2985,10 +2985,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>431149980</v>
+        <v>357400000</v>
       </c>
       <c r="C200" t="n">
-        <v>1374.5894</v>
+        <v>1450.9777</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2996,10 +2996,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>279500000</v>
+        <v>254070000</v>
       </c>
       <c r="C201" t="n">
-        <v>1391.1584</v>
+        <v>1468.5831</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3007,10 +3007,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>357400000</v>
+        <v>405740000</v>
       </c>
       <c r="C202" t="n">
-        <v>1450.9777</v>
+        <v>1487.8324</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3018,10 +3018,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>254070000</v>
+        <v>521350000</v>
       </c>
       <c r="C203" t="n">
-        <v>1468.5831</v>
+        <v>1487.4933</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3029,10 +3029,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>405740000</v>
+        <v>393340030</v>
       </c>
       <c r="C204" t="n">
-        <v>1487.8324</v>
+        <v>1484.1245</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3040,10 +3040,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>521350000</v>
+        <v>423890020</v>
       </c>
       <c r="C205" t="n">
-        <v>1487.4933</v>
+        <v>1487.8551</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3051,10 +3051,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>393340030</v>
+        <v>176000000</v>
       </c>
       <c r="C206" t="n">
-        <v>1484.1245</v>
+        <v>1399.3765</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3062,10 +3062,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>423890020</v>
+        <v>334980000</v>
       </c>
       <c r="C207" t="n">
-        <v>1487.8551</v>
+        <v>1470.861</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3073,10 +3073,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>176000000</v>
+        <v>139200000</v>
       </c>
       <c r="C208" t="n">
-        <v>1399.3765</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3084,10 +3084,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>334980000</v>
+        <v>127040000</v>
       </c>
       <c r="C209" t="n">
-        <v>1470.861</v>
+        <v>1434.8278</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3095,10 +3095,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>139200000</v>
+        <v>189260000</v>
       </c>
       <c r="C210" t="n">
-        <v>1451.923</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3106,10 +3106,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>127040000</v>
+        <v>275010000</v>
       </c>
       <c r="C211" t="n">
-        <v>1434.8278</v>
+        <v>1464.5471</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3117,10 +3117,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>189260000</v>
+        <v>194450000</v>
       </c>
       <c r="C212" t="n">
-        <v>1445.9563</v>
+        <v>1471.4448</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>275010000</v>
+        <v>196250000</v>
       </c>
       <c r="C213" t="n">
-        <v>1464.5471</v>
+        <v>1447.554</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3139,10 +3139,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>194450000</v>
+        <v>208000000</v>
       </c>
       <c r="C214" t="n">
-        <v>1471.4448</v>
+        <v>1434.8108</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3150,10 +3150,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>196250000</v>
+        <v>209360000</v>
       </c>
       <c r="C215" t="n">
-        <v>1447.554</v>
+        <v>1420.3701</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3161,10 +3161,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>208000000</v>
+        <v>212720000</v>
       </c>
       <c r="C216" t="n">
-        <v>1434.8108</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3172,10 +3172,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>209360000</v>
+        <v>241830000</v>
       </c>
       <c r="C217" t="n">
-        <v>1420.3701</v>
+        <v>1407.7981</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3183,10 +3183,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>212720000</v>
+        <v>312580000</v>
       </c>
       <c r="C218" t="n">
-        <v>1403.0524</v>
+        <v>1404.9167</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3194,10 +3194,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>241830000</v>
+        <v>179500000</v>
       </c>
       <c r="C219" t="n">
-        <v>1407.7981</v>
+        <v>1401.7583</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3205,10 +3205,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>312580000</v>
+        <v>107500000</v>
       </c>
       <c r="C220" t="n">
-        <v>1404.9167</v>
+        <v>1392.0065</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>179500000</v>
+        <v>242990000</v>
       </c>
       <c r="C221" t="n">
-        <v>1401.7583</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3227,10 +3227,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>107500000</v>
+        <v>254470000</v>
       </c>
       <c r="C222" t="n">
-        <v>1392.0065</v>
+        <v>1418.5961</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3238,10 +3238,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>242990000</v>
+        <v>331130000</v>
       </c>
       <c r="C223" t="n">
-        <v>1402.779</v>
+        <v>1446.057</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3249,10 +3249,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>254470000</v>
+        <v>237200000</v>
       </c>
       <c r="C224" t="n">
-        <v>1418.5961</v>
+        <v>1450.5864</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3260,10 +3260,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>331130000</v>
+        <v>268310000</v>
       </c>
       <c r="C225" t="n">
-        <v>1446.057</v>
+        <v>1450.6014</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3271,10 +3271,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>237200000</v>
+        <v>293410020</v>
       </c>
       <c r="C226" t="n">
-        <v>1450.5864</v>
+        <v>1449.8969</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3282,10 +3282,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>268310000</v>
+        <v>190400000</v>
       </c>
       <c r="C227" t="n">
-        <v>1450.6014</v>
+        <v>1454.6573</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3293,10 +3293,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>293410020</v>
+        <v>147700000</v>
       </c>
       <c r="C228" t="n">
-        <v>1449.8969</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3304,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>190400000</v>
+        <v>152560000</v>
       </c>
       <c r="C229" t="n">
-        <v>1454.6573</v>
+        <v>1447.5764</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3315,10 +3315,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>147700000</v>
+        <v>195400000</v>
       </c>
       <c r="C230" t="n">
-        <v>1453.8477</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3326,10 +3326,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>152560000</v>
+        <v>185680000</v>
       </c>
       <c r="C231" t="n">
-        <v>1447.5764</v>
+        <v>1439.3232</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3337,10 +3337,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>195400000</v>
+        <v>158700000</v>
       </c>
       <c r="C232" t="n">
-        <v>1440.0085</v>
+        <v>1438.0428</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3348,10 +3348,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>10580000</v>
+        <v>6000000</v>
       </c>
       <c r="C233" t="n">
-        <v>1438.0549</v>
+        <v>1436.5833</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -25,15 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">11/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">16/12/2024 12:00:00</t>
   </si>
   <si>
@@ -719,6 +710,12 @@
   </si>
   <si>
     <t xml:space="preserve">11/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -783,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C233"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
@@ -807,10 +804,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>154600000</v>
+        <v>136460000</v>
       </c>
       <c r="C2" t="n">
-        <v>1016.7524</v>
+        <v>1020.63074</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -818,10 +815,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>166760000</v>
+        <v>109500000</v>
       </c>
       <c r="C3" t="n">
-        <v>1017.8712</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -829,10 +826,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>120700000</v>
+        <v>103710000</v>
       </c>
       <c r="C4" t="n">
-        <v>1017.9877</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -840,10 +837,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>136460000</v>
+        <v>70020000</v>
       </c>
       <c r="C5" t="n">
-        <v>1020.63074</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -851,10 +848,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>109500000</v>
+        <v>105600000</v>
       </c>
       <c r="C6" t="n">
-        <v>1020.69635</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -862,10 +859,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>103710000</v>
+        <v>60970000</v>
       </c>
       <c r="C7" t="n">
-        <v>1021.90955</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -873,10 +870,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>70020000</v>
+        <v>135210000</v>
       </c>
       <c r="C8" t="n">
-        <v>1022.2438</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -884,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>105600000</v>
+        <v>214050000</v>
       </c>
       <c r="C9" t="n">
-        <v>1022.24274</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -895,10 +892,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>60970000</v>
+        <v>170650000</v>
       </c>
       <c r="C10" t="n">
-        <v>1025.3103</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -906,10 +903,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>135210000</v>
+        <v>129920000</v>
       </c>
       <c r="C11" t="n">
-        <v>1028.5804</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -917,10 +914,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>214050000</v>
+        <v>90600000</v>
       </c>
       <c r="C12" t="n">
-        <v>1028.1958</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -928,10 +925,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>170650000</v>
+        <v>94620000</v>
       </c>
       <c r="C13" t="n">
-        <v>1030.4104</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -939,10 +936,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>129920000</v>
+        <v>76740000</v>
       </c>
       <c r="C14" t="n">
-        <v>1031.7577</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -950,10 +947,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>90600000</v>
+        <v>60220000</v>
       </c>
       <c r="C15" t="n">
-        <v>1032.4374</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -961,10 +958,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>94620000</v>
+        <v>80100000</v>
       </c>
       <c r="C16" t="n">
-        <v>1034.7297</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -972,10 +969,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>76740000</v>
+        <v>144200000</v>
       </c>
       <c r="C17" t="n">
-        <v>1035.4338</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -983,10 +980,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>60220000</v>
+        <v>66560000</v>
       </c>
       <c r="C18" t="n">
-        <v>1035.8505</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -994,10 +991,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>80100000</v>
+        <v>69770000</v>
       </c>
       <c r="C19" t="n">
-        <v>1036.7753</v>
+        <v>1040.3352</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1005,10 +1002,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>144200000</v>
+        <v>59000000</v>
       </c>
       <c r="C20" t="n">
-        <v>1036.8966</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1016,10 +1013,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>66560000</v>
+        <v>97600000</v>
       </c>
       <c r="C21" t="n">
-        <v>1039.2858</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1027,10 +1024,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>69770000</v>
+        <v>139000000</v>
       </c>
       <c r="C22" t="n">
-        <v>1040.3352</v>
+        <v>1041.9935</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1038,10 +1035,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>59000000</v>
+        <v>215030000</v>
       </c>
       <c r="C23" t="n">
-        <v>1040.7654</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1049,10 +1046,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>97600000</v>
+        <v>117720000</v>
       </c>
       <c r="C24" t="n">
-        <v>1041.2943</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1060,10 +1057,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>139000000</v>
+        <v>55800000</v>
       </c>
       <c r="C25" t="n">
-        <v>1041.9935</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1071,10 +1068,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>215030000</v>
+        <v>135550000</v>
       </c>
       <c r="C26" t="n">
-        <v>1045.5352</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1082,10 +1079,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>117720000</v>
+        <v>89000000</v>
       </c>
       <c r="C27" t="n">
-        <v>1046.7697</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1093,10 +1090,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>55800000</v>
+        <v>58100000</v>
       </c>
       <c r="C28" t="n">
-        <v>1046.9908</v>
+        <v>1050.2393</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1104,10 +1101,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>135550000</v>
+        <v>86600000</v>
       </c>
       <c r="C29" t="n">
-        <v>1046.9497</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1115,10 +1112,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>89000000</v>
+        <v>95150000</v>
       </c>
       <c r="C30" t="n">
-        <v>1049.7869</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1126,10 +1123,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>58100000</v>
+        <v>147140000</v>
       </c>
       <c r="C31" t="n">
-        <v>1050.2393</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1137,10 +1134,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>86600000</v>
+        <v>123760000</v>
       </c>
       <c r="C32" t="n">
-        <v>1051.1277</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1148,10 +1145,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>95150000</v>
+        <v>88880000</v>
       </c>
       <c r="C33" t="n">
-        <v>1051.69</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1159,10 +1156,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>147140000</v>
+        <v>115600000</v>
       </c>
       <c r="C34" t="n">
-        <v>1051.1226</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1170,10 +1167,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>123760000</v>
+        <v>93120000</v>
       </c>
       <c r="C35" t="n">
-        <v>1053.3625</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1181,10 +1178,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>88880000</v>
+        <v>162410000</v>
       </c>
       <c r="C36" t="n">
-        <v>1053.5273</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1192,10 +1189,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>115600000</v>
+        <v>191440000</v>
       </c>
       <c r="C37" t="n">
-        <v>1053.941</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1203,10 +1200,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>93120000</v>
+        <v>98800000</v>
       </c>
       <c r="C38" t="n">
-        <v>1054.1022</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1214,10 +1211,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>162410000</v>
+        <v>151830000</v>
       </c>
       <c r="C39" t="n">
-        <v>1053.6134</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1225,10 +1222,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>191440000</v>
+        <v>63730000</v>
       </c>
       <c r="C40" t="n">
-        <v>1055.6161</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1236,10 +1233,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>98800000</v>
+        <v>154380000</v>
       </c>
       <c r="C41" t="n">
-        <v>1055.6309</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1247,10 +1244,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>151830000</v>
+        <v>127430000</v>
       </c>
       <c r="C42" t="n">
-        <v>1056.2124</v>
+        <v>1058.3726</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1258,10 +1255,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>63730000</v>
+        <v>90150000</v>
       </c>
       <c r="C43" t="n">
-        <v>1056.7262</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1269,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>154380000</v>
+        <v>78400000</v>
       </c>
       <c r="C44" t="n">
-        <v>1056.4021</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1280,10 +1277,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>127430000</v>
+        <v>102390000</v>
       </c>
       <c r="C45" t="n">
-        <v>1058.3726</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1291,10 +1288,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>90150000</v>
+        <v>106130000</v>
       </c>
       <c r="C46" t="n">
-        <v>1058.5518</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1302,10 +1299,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>78400000</v>
+        <v>81520000</v>
       </c>
       <c r="C47" t="n">
-        <v>1059.0238</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1313,10 +1310,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>102390000</v>
+        <v>107290000</v>
       </c>
       <c r="C48" t="n">
-        <v>1058.5037</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1324,10 +1321,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>106130000</v>
+        <v>78500000</v>
       </c>
       <c r="C49" t="n">
-        <v>1060.2593</v>
+        <v>1061.6616</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1335,10 +1332,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>81520000</v>
+        <v>115700000</v>
       </c>
       <c r="C50" t="n">
-        <v>1060.7654</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1346,10 +1343,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>107290000</v>
+        <v>135350000</v>
       </c>
       <c r="C51" t="n">
-        <v>1061.1646</v>
+        <v>1063.4131</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1357,10 +1354,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>78500000</v>
+        <v>156190000</v>
       </c>
       <c r="C52" t="n">
-        <v>1061.6616</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1368,10 +1365,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>115700000</v>
+        <v>203700000</v>
       </c>
       <c r="C53" t="n">
-        <v>1062.0686</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1379,10 +1376,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>135350000</v>
+        <v>153120000</v>
       </c>
       <c r="C54" t="n">
-        <v>1063.4131</v>
+        <v>1065.5394</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1390,10 +1387,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>156190000</v>
+        <v>154930000</v>
       </c>
       <c r="C55" t="n">
-        <v>1063.8278</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1401,10 +1398,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>203700000</v>
+        <v>101660000</v>
       </c>
       <c r="C56" t="n">
-        <v>1064.3394</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1412,10 +1409,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>153120000</v>
+        <v>90000000</v>
       </c>
       <c r="C57" t="n">
-        <v>1065.5394</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1423,10 +1420,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>154930000</v>
+        <v>266600000</v>
       </c>
       <c r="C58" t="n">
-        <v>1065.7025</v>
+        <v>1066.7456</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1434,10 +1431,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>101660000</v>
+        <v>146970000</v>
       </c>
       <c r="C59" t="n">
-        <v>1066.0099</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1445,10 +1442,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>90000000</v>
+        <v>61200000</v>
       </c>
       <c r="C60" t="n">
-        <v>1066.2288</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1456,10 +1453,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>266600000</v>
+        <v>69170000</v>
       </c>
       <c r="C61" t="n">
-        <v>1066.7456</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1467,10 +1464,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>146970000</v>
+        <v>41240000</v>
       </c>
       <c r="C62" t="n">
-        <v>1068.2128</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1478,10 +1475,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>61200000</v>
+        <v>145230000</v>
       </c>
       <c r="C63" t="n">
-        <v>1068.3644</v>
+        <v>1068.3027</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1489,10 +1486,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>69170000</v>
+        <v>120040000</v>
       </c>
       <c r="C64" t="n">
-        <v>1069.0115</v>
+        <v>1070.8257</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1500,10 +1497,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>41240000</v>
+        <v>105520000</v>
       </c>
       <c r="C65" t="n">
-        <v>1069.0428</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1511,10 +1508,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>145230000</v>
+        <v>180350000</v>
       </c>
       <c r="C66" t="n">
-        <v>1068.3027</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1522,10 +1519,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>120040000</v>
+        <v>157240000</v>
       </c>
       <c r="C67" t="n">
-        <v>1070.8257</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1533,10 +1530,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>105520000</v>
+        <v>204650000</v>
       </c>
       <c r="C68" t="n">
-        <v>1071.3093</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1544,10 +1541,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>180350000</v>
+        <v>127150000</v>
       </c>
       <c r="C69" t="n">
-        <v>1071.5227</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1555,10 +1552,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>157240000</v>
+        <v>54310000</v>
       </c>
       <c r="C70" t="n">
-        <v>1070.9691</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1566,10 +1563,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>204650000</v>
+        <v>75470000</v>
       </c>
       <c r="C71" t="n">
-        <v>1073.0979</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1577,10 +1574,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>127150000</v>
+        <v>79680000</v>
       </c>
       <c r="C72" t="n">
-        <v>1072.918</v>
+        <v>1075.5159</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1588,10 +1585,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>54310000</v>
+        <v>62750000</v>
       </c>
       <c r="C73" t="n">
-        <v>1074.1038</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1599,10 +1596,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>75470000</v>
+        <v>75600000</v>
       </c>
       <c r="C74" t="n">
-        <v>1073.4634</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1610,10 +1607,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>79680000</v>
+        <v>63990000</v>
       </c>
       <c r="C75" t="n">
-        <v>1075.5159</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1621,10 +1618,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>62750000</v>
+        <v>225590000</v>
       </c>
       <c r="C76" t="n">
-        <v>1075.8248</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1632,10 +1629,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>75600000</v>
+        <v>415320000</v>
       </c>
       <c r="C77" t="n">
-        <v>1076.5104</v>
+        <v>1189.2566</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1643,10 +1640,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>63990000</v>
+        <v>230200000</v>
       </c>
       <c r="C78" t="n">
-        <v>1076.5854</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1654,10 +1651,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>225590000</v>
+        <v>347690000</v>
       </c>
       <c r="C79" t="n">
-        <v>1075.3297</v>
+        <v>1162.0159</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1665,10 +1662,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>415320000</v>
+        <v>339050000</v>
       </c>
       <c r="C80" t="n">
-        <v>1189.2566</v>
+        <v>1082.272</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1676,10 +1673,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>230200000</v>
+        <v>335470000</v>
       </c>
       <c r="C81" t="n">
-        <v>1199.1798</v>
+        <v>1092.0538</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1687,10 +1684,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>347690000</v>
+        <v>410800000</v>
       </c>
       <c r="C82" t="n">
-        <v>1162.0159</v>
+        <v>1135.2747</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1698,10 +1695,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>339050000</v>
+        <v>530219970</v>
       </c>
       <c r="C83" t="n">
-        <v>1082.272</v>
+        <v>1176.6918</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1709,10 +1706,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>335470000</v>
+        <v>368410020</v>
       </c>
       <c r="C84" t="n">
-        <v>1092.0538</v>
+        <v>1173.9497</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1720,10 +1717,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>410800000</v>
+        <v>359710000</v>
       </c>
       <c r="C85" t="n">
-        <v>1135.2747</v>
+        <v>1164.8855</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1731,10 +1728,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>530219970</v>
+        <v>327350000</v>
       </c>
       <c r="C86" t="n">
-        <v>1176.6918</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1742,10 +1739,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>368410020</v>
+        <v>451770000</v>
       </c>
       <c r="C87" t="n">
-        <v>1173.9497</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1753,10 +1750,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>359710000</v>
+        <v>373390000</v>
       </c>
       <c r="C88" t="n">
-        <v>1164.8855</v>
+        <v>1182.7354</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1764,10 +1761,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>327350000</v>
+        <v>267550000</v>
       </c>
       <c r="C89" t="n">
-        <v>1171.4315</v>
+        <v>1201.8551</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1775,10 +1772,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>451770000</v>
+        <v>298740000</v>
       </c>
       <c r="C90" t="n">
-        <v>1169.5444</v>
+        <v>1150.9364</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1786,10 +1783,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>373390000</v>
+        <v>263150000</v>
       </c>
       <c r="C91" t="n">
-        <v>1182.7354</v>
+        <v>1115.3589</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1797,10 +1794,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>267550000</v>
+        <v>200590000</v>
       </c>
       <c r="C92" t="n">
-        <v>1201.8551</v>
+        <v>1114.4547</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1808,10 +1805,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>298740000</v>
+        <v>279730000</v>
       </c>
       <c r="C93" t="n">
-        <v>1150.9364</v>
+        <v>1128.0269</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1819,10 +1816,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>263150000</v>
+        <v>395650020</v>
       </c>
       <c r="C94" t="n">
-        <v>1115.3589</v>
+        <v>1124.8623</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1830,10 +1827,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>200590000</v>
+        <v>331410020</v>
       </c>
       <c r="C95" t="n">
-        <v>1114.4547</v>
+        <v>1130.4915</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1841,10 +1838,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>279730000</v>
+        <v>261090000</v>
       </c>
       <c r="C96" t="n">
-        <v>1128.0269</v>
+        <v>1135.9207</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1852,10 +1849,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>395650020</v>
+        <v>242790000</v>
       </c>
       <c r="C97" t="n">
-        <v>1124.8623</v>
+        <v>1144.8073</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1863,10 +1860,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>331410020</v>
+        <v>193430000</v>
       </c>
       <c r="C98" t="n">
-        <v>1130.4915</v>
+        <v>1134.3671</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1874,10 +1871,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>261090000</v>
+        <v>206570000</v>
       </c>
       <c r="C99" t="n">
-        <v>1135.9207</v>
+        <v>1143.0444</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1885,10 +1882,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>242790000</v>
+        <v>295490020</v>
       </c>
       <c r="C100" t="n">
-        <v>1144.8073</v>
+        <v>1144.6138</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1896,10 +1893,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>193430000</v>
+        <v>241590000</v>
       </c>
       <c r="C101" t="n">
-        <v>1134.3671</v>
+        <v>1142.3444</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1907,10 +1904,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>206570000</v>
+        <v>315600000</v>
       </c>
       <c r="C102" t="n">
-        <v>1143.0444</v>
+        <v>1136.4617</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1918,10 +1915,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>295490020</v>
+        <v>322010000</v>
       </c>
       <c r="C103" t="n">
-        <v>1144.6138</v>
+        <v>1148.4205</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1929,10 +1926,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>241590000</v>
+        <v>274060000</v>
       </c>
       <c r="C104" t="n">
-        <v>1142.3444</v>
+        <v>1162.3146</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1940,10 +1937,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>315600000</v>
+        <v>201240000</v>
       </c>
       <c r="C105" t="n">
-        <v>1136.4617</v>
+        <v>1175.8934</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1951,10 +1948,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>322010000</v>
+        <v>200400000</v>
       </c>
       <c r="C106" t="n">
-        <v>1148.4205</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1962,10 +1959,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>274060000</v>
+        <v>219350000</v>
       </c>
       <c r="C107" t="n">
-        <v>1162.3146</v>
+        <v>1182.2738</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1973,10 +1970,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>201240000</v>
+        <v>191080000</v>
       </c>
       <c r="C108" t="n">
-        <v>1175.8934</v>
+        <v>1185.7009</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1984,10 +1981,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>200400000</v>
+        <v>279980000</v>
       </c>
       <c r="C109" t="n">
-        <v>1196.2443</v>
+        <v>1184.3539</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1995,10 +1992,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>219350000</v>
+        <v>210400000</v>
       </c>
       <c r="C110" t="n">
-        <v>1182.2738</v>
+        <v>1190.1604</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2006,10 +2003,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>191080000</v>
+        <v>149050000</v>
       </c>
       <c r="C111" t="n">
-        <v>1185.7009</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2017,10 +2014,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>279980000</v>
+        <v>206060000</v>
       </c>
       <c r="C112" t="n">
-        <v>1184.3539</v>
+        <v>1187.3215</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2028,10 +2025,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>210400000</v>
+        <v>327800000</v>
       </c>
       <c r="C113" t="n">
-        <v>1190.1604</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2039,10 +2036,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>149050000</v>
+        <v>194900000</v>
       </c>
       <c r="C114" t="n">
-        <v>1189.0756</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2050,10 +2047,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>206060000</v>
+        <v>150070000</v>
       </c>
       <c r="C115" t="n">
-        <v>1187.3215</v>
+        <v>1186.3999</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2061,10 +2058,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>327800000</v>
+        <v>249730000</v>
       </c>
       <c r="C116" t="n">
-        <v>1187.3528</v>
+        <v>1184.7565</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2072,10 +2069,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>194900000</v>
+        <v>328930000</v>
       </c>
       <c r="C117" t="n">
-        <v>1183.6859</v>
+        <v>1177.4198</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2083,10 +2080,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>150070000</v>
+        <v>319130000</v>
       </c>
       <c r="C118" t="n">
-        <v>1186.3999</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2094,10 +2091,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>249730000</v>
+        <v>290900000</v>
       </c>
       <c r="C119" t="n">
-        <v>1184.7565</v>
+        <v>1168.4825</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2105,10 +2102,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>328930000</v>
+        <v>272000000</v>
       </c>
       <c r="C120" t="n">
-        <v>1177.4198</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2116,10 +2113,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>319130000</v>
+        <v>459869980</v>
       </c>
       <c r="C121" t="n">
-        <v>1146.302</v>
+        <v>1176.724</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2127,10 +2124,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>290900000</v>
+        <v>250980000</v>
       </c>
       <c r="C122" t="n">
-        <v>1168.4825</v>
+        <v>1192.3014</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2138,10 +2135,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>272000000</v>
+        <v>317930020</v>
       </c>
       <c r="C123" t="n">
-        <v>1178.1132</v>
+        <v>1187.0327</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2149,10 +2146,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>459869980</v>
+        <v>359550000</v>
       </c>
       <c r="C124" t="n">
-        <v>1176.724</v>
+        <v>1193.3121</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2160,10 +2157,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>250980000</v>
+        <v>279650000</v>
       </c>
       <c r="C125" t="n">
-        <v>1192.3014</v>
+        <v>1207.8153</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2171,10 +2168,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>317930020</v>
+        <v>286200000</v>
       </c>
       <c r="C126" t="n">
-        <v>1187.0327</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2182,10 +2179,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>359550000</v>
+        <v>343900000</v>
       </c>
       <c r="C127" t="n">
-        <v>1193.3121</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2193,10 +2190,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>279650000</v>
+        <v>310469980</v>
       </c>
       <c r="C128" t="n">
-        <v>1207.8153</v>
+        <v>1263.1807</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2204,10 +2201,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>286200000</v>
+        <v>324740000</v>
       </c>
       <c r="C129" t="n">
-        <v>1232.3434</v>
+        <v>1257.3591</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2215,10 +2212,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>343900000</v>
+        <v>301200000</v>
       </c>
       <c r="C130" t="n">
-        <v>1225.9089</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2226,10 +2223,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>310469980</v>
+        <v>298320000</v>
       </c>
       <c r="C131" t="n">
-        <v>1263.1807</v>
+        <v>1261.3674</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2237,10 +2234,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>324740000</v>
+        <v>393980000</v>
       </c>
       <c r="C132" t="n">
-        <v>1257.3591</v>
+        <v>1268.4539</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2248,10 +2245,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>301200000</v>
+        <v>398920000</v>
       </c>
       <c r="C133" t="n">
-        <v>1261.2496</v>
+        <v>1277.0442</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2259,10 +2256,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>298320000</v>
+        <v>323589980</v>
       </c>
       <c r="C134" t="n">
-        <v>1261.3674</v>
+        <v>1257.8407</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2270,10 +2267,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>393980000</v>
+        <v>307460000</v>
       </c>
       <c r="C135" t="n">
-        <v>1268.4539</v>
+        <v>1266.7705</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2281,10 +2278,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>398920000</v>
+        <v>297000000</v>
       </c>
       <c r="C136" t="n">
-        <v>1277.0442</v>
+        <v>1282.9014</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2292,10 +2289,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>323589980</v>
+        <v>291500000</v>
       </c>
       <c r="C137" t="n">
-        <v>1257.8407</v>
+        <v>1287.3074</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2303,10 +2300,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>307460000</v>
+        <v>242700000</v>
       </c>
       <c r="C138" t="n">
-        <v>1266.7705</v>
+        <v>1261.0431</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2314,10 +2311,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>297000000</v>
+        <v>183370000</v>
       </c>
       <c r="C139" t="n">
-        <v>1282.9014</v>
+        <v>1259.6431</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2325,10 +2322,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>291500000</v>
+        <v>241900000</v>
       </c>
       <c r="C140" t="n">
-        <v>1287.3074</v>
+        <v>1261.7827</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2336,10 +2333,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>242700000</v>
+        <v>273740000</v>
       </c>
       <c r="C141" t="n">
-        <v>1261.0431</v>
+        <v>1278.3439</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2347,10 +2344,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>183370000</v>
+        <v>212100000</v>
       </c>
       <c r="C142" t="n">
-        <v>1259.6431</v>
+        <v>1290.4368</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2358,10 +2355,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>241900000</v>
+        <v>308300000</v>
       </c>
       <c r="C143" t="n">
-        <v>1261.7827</v>
+        <v>1295.2062</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2369,10 +2366,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>273740000</v>
+        <v>165990000</v>
       </c>
       <c r="C144" t="n">
-        <v>1278.3439</v>
+        <v>1297.3245</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2380,10 +2377,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>212100000</v>
+        <v>328600000</v>
       </c>
       <c r="C145" t="n">
-        <v>1290.4368</v>
+        <v>1356.9905</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2391,10 +2388,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>308300000</v>
+        <v>213740000</v>
       </c>
       <c r="C146" t="n">
-        <v>1295.2062</v>
+        <v>1364.9016</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2402,10 +2399,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>165990000</v>
+        <v>220980000</v>
       </c>
       <c r="C147" t="n">
-        <v>1297.3245</v>
+        <v>1362.0563</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2413,10 +2410,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>328600000</v>
+        <v>311760000</v>
       </c>
       <c r="C148" t="n">
-        <v>1356.9905</v>
+        <v>1348.5603</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2424,10 +2421,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>213740000</v>
+        <v>324880000</v>
       </c>
       <c r="C149" t="n">
-        <v>1364.9016</v>
+        <v>1333.3021</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2435,10 +2432,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>220980000</v>
+        <v>194200000</v>
       </c>
       <c r="C150" t="n">
-        <v>1362.0563</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2446,10 +2443,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>311760000</v>
+        <v>219200000</v>
       </c>
       <c r="C151" t="n">
-        <v>1348.5603</v>
+        <v>1324.7318</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2457,10 +2454,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>324880000</v>
+        <v>265100000</v>
       </c>
       <c r="C152" t="n">
-        <v>1333.3021</v>
+        <v>1327.6051</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2468,10 +2465,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>194200000</v>
+        <v>318140000</v>
       </c>
       <c r="C153" t="n">
-        <v>1329.5576</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2479,10 +2476,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>219200000</v>
+        <v>323640000</v>
       </c>
       <c r="C154" t="n">
-        <v>1324.7318</v>
+        <v>1317.7236</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2490,10 +2487,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>265100000</v>
+        <v>258100000</v>
       </c>
       <c r="C155" t="n">
-        <v>1327.6051</v>
+        <v>1298.1354</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2501,10 +2498,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>318140000</v>
+        <v>245450000</v>
       </c>
       <c r="C156" t="n">
-        <v>1317.6909</v>
+        <v>1296.6604</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2512,10 +2509,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>323640000</v>
+        <v>388200000</v>
       </c>
       <c r="C157" t="n">
-        <v>1317.7236</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2523,10 +2520,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>258100000</v>
+        <v>218250000</v>
       </c>
       <c r="C158" t="n">
-        <v>1298.1354</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2534,10 +2531,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>245450000</v>
+        <v>135000000</v>
       </c>
       <c r="C159" t="n">
-        <v>1296.6604</v>
+        <v>1311.6772</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2545,10 +2542,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>388200000</v>
+        <v>230420000</v>
       </c>
       <c r="C160" t="n">
-        <v>1293.891</v>
+        <v>1322.6124</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2556,10 +2553,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>218250000</v>
+        <v>186010000</v>
       </c>
       <c r="C161" t="n">
-        <v>1299.0688</v>
+        <v>1349.7784</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2567,10 +2564,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>135000000</v>
+        <v>324380030</v>
       </c>
       <c r="C162" t="n">
-        <v>1311.6772</v>
+        <v>1353.8983</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2578,10 +2575,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>230420000</v>
+        <v>188250000</v>
       </c>
       <c r="C163" t="n">
-        <v>1322.6124</v>
+        <v>1360.0109</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2589,10 +2586,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>186010000</v>
+        <v>262170000</v>
       </c>
       <c r="C164" t="n">
-        <v>1349.7784</v>
+        <v>1338.8644</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2600,10 +2597,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>324380030</v>
+        <v>250290000</v>
       </c>
       <c r="C165" t="n">
-        <v>1353.8983</v>
+        <v>1330.1</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2611,10 +2608,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>188250000</v>
+        <v>396959970</v>
       </c>
       <c r="C166" t="n">
-        <v>1360.0109</v>
+        <v>1365.2227</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2622,10 +2619,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>262170000</v>
+        <v>181300000</v>
       </c>
       <c r="C167" t="n">
-        <v>1338.8644</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2633,10 +2630,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>250290000</v>
+        <v>349490020</v>
       </c>
       <c r="C168" t="n">
-        <v>1330.1</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2644,10 +2641,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>396959970</v>
+        <v>354610000</v>
       </c>
       <c r="C169" t="n">
-        <v>1365.2227</v>
+        <v>1366.1195</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2655,10 +2652,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>181300000</v>
+        <v>268370000</v>
       </c>
       <c r="C170" t="n">
-        <v>1361.4104</v>
+        <v>1424.0857</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2666,10 +2663,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>349490020</v>
+        <v>217230000</v>
       </c>
       <c r="C171" t="n">
-        <v>1362.602</v>
+        <v>1419.2256</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2677,10 +2674,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>354610000</v>
+        <v>202800000</v>
       </c>
       <c r="C172" t="n">
-        <v>1366.1195</v>
+        <v>1418.7972</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2688,10 +2685,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>268370000</v>
+        <v>182600000</v>
       </c>
       <c r="C173" t="n">
-        <v>1424.0857</v>
+        <v>1428.8694</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2699,10 +2696,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>217230000</v>
+        <v>186830000</v>
       </c>
       <c r="C174" t="n">
-        <v>1419.2256</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2710,10 +2707,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>202800000</v>
+        <v>256060000</v>
       </c>
       <c r="C175" t="n">
-        <v>1418.7972</v>
+        <v>1463.7825</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2721,10 +2718,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>182600000</v>
+        <v>181350000</v>
       </c>
       <c r="C176" t="n">
-        <v>1428.8694</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2732,10 +2729,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>186830000</v>
+        <v>175400000</v>
       </c>
       <c r="C177" t="n">
-        <v>1450.185</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2743,10 +2740,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>256060000</v>
+        <v>231000000</v>
       </c>
       <c r="C178" t="n">
-        <v>1463.7825</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2754,10 +2751,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>181350000</v>
+        <v>286250020</v>
       </c>
       <c r="C179" t="n">
-        <v>1464.3728</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2765,10 +2762,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>175400000</v>
+        <v>202930000</v>
       </c>
       <c r="C180" t="n">
-        <v>1473.9847</v>
+        <v>1432.339</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2776,10 +2773,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>231000000</v>
+        <v>275320000</v>
       </c>
       <c r="C181" t="n">
-        <v>1474.4945</v>
+        <v>1355.8496</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2787,10 +2784,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>286250020</v>
+        <v>480600000</v>
       </c>
       <c r="C182" t="n">
-        <v>1475.4567</v>
+        <v>1349.3229</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2798,10 +2795,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>202930000</v>
+        <v>589150000</v>
       </c>
       <c r="C183" t="n">
-        <v>1432.339</v>
+        <v>1328.0879</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2809,10 +2806,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>275320000</v>
+        <v>392600000</v>
       </c>
       <c r="C184" t="n">
-        <v>1355.8496</v>
+        <v>1331.5211</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2820,10 +2817,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>480600000</v>
+        <v>478160000</v>
       </c>
       <c r="C185" t="n">
-        <v>1349.3229</v>
+        <v>1341.6642</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2831,10 +2828,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>589150000</v>
+        <v>496829980</v>
       </c>
       <c r="C186" t="n">
-        <v>1328.0879</v>
+        <v>1374.023</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2842,10 +2839,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>392600000</v>
+        <v>295170020</v>
       </c>
       <c r="C187" t="n">
-        <v>1331.5211</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2853,10 +2850,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>478160000</v>
+        <v>169440000</v>
       </c>
       <c r="C188" t="n">
-        <v>1341.6642</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2864,10 +2861,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>496829980</v>
+        <v>215520000</v>
       </c>
       <c r="C189" t="n">
-        <v>1374.023</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2875,10 +2872,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>295170020</v>
+        <v>262840000</v>
       </c>
       <c r="C190" t="n">
-        <v>1424.7794</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2886,10 +2883,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>169440000</v>
+        <v>315000000</v>
       </c>
       <c r="C191" t="n">
-        <v>1424.6221</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2897,10 +2894,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>215520000</v>
+        <v>338970020</v>
       </c>
       <c r="C192" t="n">
-        <v>1424.9015</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2908,10 +2905,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>262840000</v>
+        <v>260880000</v>
       </c>
       <c r="C193" t="n">
-        <v>1429.9982</v>
+        <v>1445.8335</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2919,10 +2916,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>315000000</v>
+        <v>346149980</v>
       </c>
       <c r="C194" t="n">
-        <v>1430.0143</v>
+        <v>1360.4852</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2930,10 +2927,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>338970020</v>
+        <v>431149980</v>
       </c>
       <c r="C195" t="n">
-        <v>1430.0298</v>
+        <v>1374.5894</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2941,10 +2938,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>260880000</v>
+        <v>279500000</v>
       </c>
       <c r="C196" t="n">
-        <v>1445.8335</v>
+        <v>1391.1584</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2952,10 +2949,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>346149980</v>
+        <v>357400000</v>
       </c>
       <c r="C197" t="n">
-        <v>1360.4852</v>
+        <v>1450.9777</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2963,10 +2960,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>431149980</v>
+        <v>254070000</v>
       </c>
       <c r="C198" t="n">
-        <v>1374.5894</v>
+        <v>1468.5831</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2974,10 +2971,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>279500000</v>
+        <v>405740000</v>
       </c>
       <c r="C199" t="n">
-        <v>1391.1584</v>
+        <v>1487.8324</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2985,10 +2982,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>357400000</v>
+        <v>521350000</v>
       </c>
       <c r="C200" t="n">
-        <v>1450.9777</v>
+        <v>1487.4933</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2996,10 +2993,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>254070000</v>
+        <v>393340030</v>
       </c>
       <c r="C201" t="n">
-        <v>1468.5831</v>
+        <v>1484.1245</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3007,10 +3004,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>405740000</v>
+        <v>423890020</v>
       </c>
       <c r="C202" t="n">
-        <v>1487.8324</v>
+        <v>1487.8551</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3018,10 +3015,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>521350000</v>
+        <v>176000000</v>
       </c>
       <c r="C203" t="n">
-        <v>1487.4933</v>
+        <v>1399.3765</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3029,10 +3026,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>393340030</v>
+        <v>334980000</v>
       </c>
       <c r="C204" t="n">
-        <v>1484.1245</v>
+        <v>1470.861</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3040,10 +3037,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>423890020</v>
+        <v>139200000</v>
       </c>
       <c r="C205" t="n">
-        <v>1487.8551</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3051,10 +3048,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>176000000</v>
+        <v>127040000</v>
       </c>
       <c r="C206" t="n">
-        <v>1399.3765</v>
+        <v>1434.8278</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3062,10 +3059,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>334980000</v>
+        <v>189260000</v>
       </c>
       <c r="C207" t="n">
-        <v>1470.861</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3073,10 +3070,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>139200000</v>
+        <v>275010000</v>
       </c>
       <c r="C208" t="n">
-        <v>1451.923</v>
+        <v>1464.5471</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3084,10 +3081,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>127040000</v>
+        <v>194450000</v>
       </c>
       <c r="C209" t="n">
-        <v>1434.8278</v>
+        <v>1471.4448</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3095,10 +3092,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>189260000</v>
+        <v>196250000</v>
       </c>
       <c r="C210" t="n">
-        <v>1445.9563</v>
+        <v>1447.554</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3106,10 +3103,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>275010000</v>
+        <v>208000000</v>
       </c>
       <c r="C211" t="n">
-        <v>1464.5471</v>
+        <v>1434.8108</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3117,10 +3114,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>194450000</v>
+        <v>209360000</v>
       </c>
       <c r="C212" t="n">
-        <v>1471.4448</v>
+        <v>1420.3701</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3128,10 +3125,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>196250000</v>
+        <v>212720000</v>
       </c>
       <c r="C213" t="n">
-        <v>1447.554</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3139,10 +3136,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>208000000</v>
+        <v>241830000</v>
       </c>
       <c r="C214" t="n">
-        <v>1434.8108</v>
+        <v>1407.7981</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3150,10 +3147,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>209360000</v>
+        <v>312580000</v>
       </c>
       <c r="C215" t="n">
-        <v>1420.3701</v>
+        <v>1404.9167</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3161,10 +3158,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>212720000</v>
+        <v>179500000</v>
       </c>
       <c r="C216" t="n">
-        <v>1403.0524</v>
+        <v>1401.7583</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3172,10 +3169,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>241830000</v>
+        <v>107500000</v>
       </c>
       <c r="C217" t="n">
-        <v>1407.7981</v>
+        <v>1392.0065</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3183,10 +3180,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>312580000</v>
+        <v>242990000</v>
       </c>
       <c r="C218" t="n">
-        <v>1404.9167</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3194,10 +3191,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>179500000</v>
+        <v>254470000</v>
       </c>
       <c r="C219" t="n">
-        <v>1401.7583</v>
+        <v>1418.5961</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3205,10 +3202,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>107500000</v>
+        <v>331130000</v>
       </c>
       <c r="C220" t="n">
-        <v>1392.0065</v>
+        <v>1446.057</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3216,10 +3213,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>242990000</v>
+        <v>237200000</v>
       </c>
       <c r="C221" t="n">
-        <v>1402.779</v>
+        <v>1450.5864</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3227,10 +3224,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>254470000</v>
+        <v>268310000</v>
       </c>
       <c r="C222" t="n">
-        <v>1418.5961</v>
+        <v>1450.6014</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3238,10 +3235,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>331130000</v>
+        <v>293410020</v>
       </c>
       <c r="C223" t="n">
-        <v>1446.057</v>
+        <v>1449.8969</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3249,10 +3246,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>237200000</v>
+        <v>190400000</v>
       </c>
       <c r="C224" t="n">
-        <v>1450.5864</v>
+        <v>1454.6573</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3260,10 +3257,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>268310000</v>
+        <v>147700000</v>
       </c>
       <c r="C225" t="n">
-        <v>1450.6014</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3271,10 +3268,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>293410020</v>
+        <v>152560000</v>
       </c>
       <c r="C226" t="n">
-        <v>1449.8969</v>
+        <v>1447.5764</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3282,10 +3279,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>190400000</v>
+        <v>195400000</v>
       </c>
       <c r="C227" t="n">
-        <v>1454.6573</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3293,10 +3290,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>147700000</v>
+        <v>185680000</v>
       </c>
       <c r="C228" t="n">
-        <v>1453.8477</v>
+        <v>1439.3232</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3304,10 +3301,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>152560000</v>
+        <v>158700000</v>
       </c>
       <c r="C229" t="n">
-        <v>1447.5764</v>
+        <v>1438.0428</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3315,10 +3312,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>195400000</v>
+        <v>250300000</v>
       </c>
       <c r="C230" t="n">
-        <v>1440.0085</v>
+        <v>1437.9939</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3326,10 +3323,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>185680000</v>
+        <v>192580000</v>
       </c>
       <c r="C231" t="n">
-        <v>1439.3232</v>
+        <v>1439.1218</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3337,21 +3334,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>158700000</v>
+        <v>140220000</v>
       </c>
       <c r="C232" t="n">
-        <v>1438.0428</v>
-      </c>
-    </row>
-    <row r="233" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>234</v>
-      </c>
-      <c r="B233" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="C233" t="n">
-        <v>1436.5833</v>
+        <v>1441.0989</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -716,6 +716,9 @@
   </si>
   <si>
     <t xml:space="preserve">15/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C232"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
@@ -3334,10 +3337,21 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>140220000</v>
+        <v>244040000</v>
       </c>
       <c r="C232" t="n">
-        <v>1441.0989</v>
+        <v>1440.4755</v>
+      </c>
+    </row>
+    <row r="233" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>234</v>
+      </c>
+      <c r="B233" t="n">
+        <v>81500000</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1450.1505</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -25,9 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">16/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">17/12/2024 12:00:00</t>
   </si>
   <si>
@@ -719,6 +716,9 @@
   </si>
   <si>
     <t xml:space="preserve">16/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -807,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>136460000</v>
+        <v>109500000</v>
       </c>
       <c r="C2" t="n">
-        <v>1020.63074</v>
+        <v>1020.69635</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -818,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>109500000</v>
+        <v>103710000</v>
       </c>
       <c r="C3" t="n">
-        <v>1020.69635</v>
+        <v>1021.90955</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -829,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>103710000</v>
+        <v>70020000</v>
       </c>
       <c r="C4" t="n">
-        <v>1021.90955</v>
+        <v>1022.2438</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -840,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>70020000</v>
+        <v>105600000</v>
       </c>
       <c r="C5" t="n">
-        <v>1022.2438</v>
+        <v>1022.24274</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>105600000</v>
+        <v>60970000</v>
       </c>
       <c r="C6" t="n">
-        <v>1022.24274</v>
+        <v>1025.3103</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -862,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>60970000</v>
+        <v>135210000</v>
       </c>
       <c r="C7" t="n">
-        <v>1025.3103</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>135210000</v>
+        <v>214050000</v>
       </c>
       <c r="C8" t="n">
-        <v>1028.5804</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -884,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>214050000</v>
+        <v>170650000</v>
       </c>
       <c r="C9" t="n">
-        <v>1028.1958</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -895,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>170650000</v>
+        <v>129920000</v>
       </c>
       <c r="C10" t="n">
-        <v>1030.4104</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -906,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>129920000</v>
+        <v>90600000</v>
       </c>
       <c r="C11" t="n">
-        <v>1031.7577</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -917,10 +917,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>90600000</v>
+        <v>94620000</v>
       </c>
       <c r="C12" t="n">
-        <v>1032.4374</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -928,10 +928,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>94620000</v>
+        <v>76740000</v>
       </c>
       <c r="C13" t="n">
-        <v>1034.7297</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -939,10 +939,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>76740000</v>
+        <v>60220000</v>
       </c>
       <c r="C14" t="n">
-        <v>1035.4338</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -950,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>60220000</v>
+        <v>80100000</v>
       </c>
       <c r="C15" t="n">
-        <v>1035.8505</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -961,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>80100000</v>
+        <v>144200000</v>
       </c>
       <c r="C16" t="n">
-        <v>1036.7753</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -972,10 +972,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>144200000</v>
+        <v>66560000</v>
       </c>
       <c r="C17" t="n">
-        <v>1036.8966</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -983,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>66560000</v>
+        <v>69770000</v>
       </c>
       <c r="C18" t="n">
-        <v>1039.2858</v>
+        <v>1040.3387</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -994,10 +994,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>69770000</v>
+        <v>59000000</v>
       </c>
       <c r="C19" t="n">
-        <v>1040.3352</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1005,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>59000000</v>
+        <v>97600000</v>
       </c>
       <c r="C20" t="n">
-        <v>1040.7654</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1016,10 +1016,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>97600000</v>
+        <v>139000000</v>
       </c>
       <c r="C21" t="n">
-        <v>1041.2943</v>
+        <v>1041.9989</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1027,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>139000000</v>
+        <v>215030000</v>
       </c>
       <c r="C22" t="n">
-        <v>1041.9935</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1038,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>215030000</v>
+        <v>117720000</v>
       </c>
       <c r="C23" t="n">
-        <v>1045.5352</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1049,10 +1049,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>117720000</v>
+        <v>55800000</v>
       </c>
       <c r="C24" t="n">
-        <v>1046.7697</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1060,10 +1060,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>55800000</v>
+        <v>135550000</v>
       </c>
       <c r="C25" t="n">
-        <v>1046.9908</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1071,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>135550000</v>
+        <v>89000000</v>
       </c>
       <c r="C26" t="n">
-        <v>1046.9497</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1082,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>89000000</v>
+        <v>58100000</v>
       </c>
       <c r="C27" t="n">
-        <v>1049.7869</v>
+        <v>1050.2952</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1093,10 +1093,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>58100000</v>
+        <v>86600000</v>
       </c>
       <c r="C28" t="n">
-        <v>1050.2393</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1104,10 +1104,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>86600000</v>
+        <v>95150000</v>
       </c>
       <c r="C29" t="n">
-        <v>1051.1277</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1115,10 +1115,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>95150000</v>
+        <v>147140000</v>
       </c>
       <c r="C30" t="n">
-        <v>1051.69</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1126,10 +1126,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>147140000</v>
+        <v>123760000</v>
       </c>
       <c r="C31" t="n">
-        <v>1051.1226</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>123760000</v>
+        <v>88880000</v>
       </c>
       <c r="C32" t="n">
-        <v>1053.3625</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1148,10 +1148,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>88880000</v>
+        <v>115600000</v>
       </c>
       <c r="C33" t="n">
-        <v>1053.5273</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>115600000</v>
+        <v>93120000</v>
       </c>
       <c r="C34" t="n">
-        <v>1053.941</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1170,10 +1170,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>93120000</v>
+        <v>162410000</v>
       </c>
       <c r="C35" t="n">
-        <v>1054.1022</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1181,10 +1181,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>162410000</v>
+        <v>191440000</v>
       </c>
       <c r="C36" t="n">
-        <v>1053.6134</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1192,10 +1192,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>191440000</v>
+        <v>98800000</v>
       </c>
       <c r="C37" t="n">
-        <v>1055.6161</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1203,10 +1203,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>98800000</v>
+        <v>151830000</v>
       </c>
       <c r="C38" t="n">
-        <v>1055.6309</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1214,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>151830000</v>
+        <v>63730000</v>
       </c>
       <c r="C39" t="n">
-        <v>1056.2124</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1225,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>63730000</v>
+        <v>154380000</v>
       </c>
       <c r="C40" t="n">
-        <v>1056.7262</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1236,10 +1236,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>154380000</v>
+        <v>127430000</v>
       </c>
       <c r="C41" t="n">
-        <v>1056.4021</v>
+        <v>1058.3744</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1247,10 +1247,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>127430000</v>
+        <v>90150000</v>
       </c>
       <c r="C42" t="n">
-        <v>1058.3726</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1258,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>90150000</v>
+        <v>78400000</v>
       </c>
       <c r="C43" t="n">
-        <v>1058.5518</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1269,10 +1269,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>78400000</v>
+        <v>102390000</v>
       </c>
       <c r="C44" t="n">
-        <v>1059.0238</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1280,10 +1280,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>102390000</v>
+        <v>106130000</v>
       </c>
       <c r="C45" t="n">
-        <v>1058.5037</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1291,10 +1291,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>106130000</v>
+        <v>81520000</v>
       </c>
       <c r="C46" t="n">
-        <v>1060.2593</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1302,10 +1302,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>81520000</v>
+        <v>107290000</v>
       </c>
       <c r="C47" t="n">
-        <v>1060.7654</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1313,10 +1313,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>107290000</v>
+        <v>78500000</v>
       </c>
       <c r="C48" t="n">
-        <v>1061.1646</v>
+        <v>1061.6664</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1324,10 +1324,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>78500000</v>
+        <v>115700000</v>
       </c>
       <c r="C49" t="n">
-        <v>1061.6616</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1335,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>115700000</v>
+        <v>135350000</v>
       </c>
       <c r="C50" t="n">
-        <v>1062.0686</v>
+        <v>1063.415</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1346,10 +1346,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>135350000</v>
+        <v>156190000</v>
       </c>
       <c r="C51" t="n">
-        <v>1063.4131</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1357,10 +1357,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>156190000</v>
+        <v>203700000</v>
       </c>
       <c r="C52" t="n">
-        <v>1063.8278</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>203700000</v>
+        <v>153120000</v>
       </c>
       <c r="C53" t="n">
-        <v>1064.3394</v>
+        <v>1065.541</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1379,10 +1379,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>153120000</v>
+        <v>154930000</v>
       </c>
       <c r="C54" t="n">
-        <v>1065.5394</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1390,10 +1390,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>154930000</v>
+        <v>101660000</v>
       </c>
       <c r="C55" t="n">
-        <v>1065.7025</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1401,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>101660000</v>
+        <v>90000000</v>
       </c>
       <c r="C56" t="n">
-        <v>1066.0099</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1412,10 +1412,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>90000000</v>
+        <v>266600000</v>
       </c>
       <c r="C57" t="n">
-        <v>1066.2288</v>
+        <v>1066.7559</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>266600000</v>
+        <v>146970000</v>
       </c>
       <c r="C58" t="n">
-        <v>1066.7456</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1434,10 +1434,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>146970000</v>
+        <v>61200000</v>
       </c>
       <c r="C59" t="n">
-        <v>1068.2128</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>61200000</v>
+        <v>69170000</v>
       </c>
       <c r="C60" t="n">
-        <v>1068.3644</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1456,10 +1456,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>69170000</v>
+        <v>41240000</v>
       </c>
       <c r="C61" t="n">
-        <v>1069.0115</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1467,10 +1467,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>41240000</v>
+        <v>145230000</v>
       </c>
       <c r="C62" t="n">
-        <v>1069.0428</v>
+        <v>1068.306</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1478,10 +1478,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>145230000</v>
+        <v>120040000</v>
       </c>
       <c r="C63" t="n">
-        <v>1068.3027</v>
+        <v>1070.8301</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1489,10 +1489,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>120040000</v>
+        <v>105520000</v>
       </c>
       <c r="C64" t="n">
-        <v>1070.8257</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1500,10 +1500,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>105520000</v>
+        <v>180350000</v>
       </c>
       <c r="C65" t="n">
-        <v>1071.3093</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1511,10 +1511,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>180350000</v>
+        <v>157240000</v>
       </c>
       <c r="C66" t="n">
-        <v>1071.5227</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1522,10 +1522,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>157240000</v>
+        <v>204650000</v>
       </c>
       <c r="C67" t="n">
-        <v>1070.9691</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1533,10 +1533,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>204650000</v>
+        <v>127150000</v>
       </c>
       <c r="C68" t="n">
-        <v>1073.0979</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1544,10 +1544,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>127150000</v>
+        <v>54310000</v>
       </c>
       <c r="C69" t="n">
-        <v>1072.918</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1555,10 +1555,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>54310000</v>
+        <v>75470000</v>
       </c>
       <c r="C70" t="n">
-        <v>1074.1038</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1566,10 +1566,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>75470000</v>
+        <v>79680000</v>
       </c>
       <c r="C71" t="n">
-        <v>1073.4634</v>
+        <v>1075.5189</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1577,10 +1577,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>79680000</v>
+        <v>62750000</v>
       </c>
       <c r="C72" t="n">
-        <v>1075.5159</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1588,10 +1588,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>62750000</v>
+        <v>75600000</v>
       </c>
       <c r="C73" t="n">
-        <v>1075.8248</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1599,10 +1599,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>75600000</v>
+        <v>63990000</v>
       </c>
       <c r="C74" t="n">
-        <v>1076.5104</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1610,10 +1610,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>63990000</v>
+        <v>225590000</v>
       </c>
       <c r="C75" t="n">
-        <v>1076.5854</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1621,10 +1621,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>225590000</v>
+        <v>415320000</v>
       </c>
       <c r="C76" t="n">
-        <v>1075.3297</v>
+        <v>1189.3408</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1632,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>415320000</v>
+        <v>230200000</v>
       </c>
       <c r="C77" t="n">
-        <v>1189.2566</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1643,10 +1643,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>230200000</v>
+        <v>347690000</v>
       </c>
       <c r="C78" t="n">
-        <v>1199.1798</v>
+        <v>1162.0289</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1654,10 +1654,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>347690000</v>
+        <v>339050000</v>
       </c>
       <c r="C79" t="n">
-        <v>1162.0159</v>
+        <v>1082.2896</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1665,10 +1665,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>339050000</v>
+        <v>335470000</v>
       </c>
       <c r="C80" t="n">
-        <v>1082.272</v>
+        <v>1092.0658</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1676,10 +1676,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>335470000</v>
+        <v>410800000</v>
       </c>
       <c r="C81" t="n">
-        <v>1092.0538</v>
+        <v>1135.2954</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1687,10 +1687,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>410800000</v>
+        <v>530219970</v>
       </c>
       <c r="C82" t="n">
-        <v>1135.2747</v>
+        <v>1176.7036</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1698,10 +1698,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>530219970</v>
+        <v>368410020</v>
       </c>
       <c r="C83" t="n">
-        <v>1176.6918</v>
+        <v>1173.9578</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1709,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>368410020</v>
+        <v>359710000</v>
       </c>
       <c r="C84" t="n">
-        <v>1173.9497</v>
+        <v>1164.9523</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1720,10 +1720,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>359710000</v>
+        <v>327350000</v>
       </c>
       <c r="C85" t="n">
-        <v>1164.8855</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1731,10 +1731,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>327350000</v>
+        <v>451770000</v>
       </c>
       <c r="C86" t="n">
-        <v>1171.4315</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1742,10 +1742,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>451770000</v>
+        <v>373390000</v>
       </c>
       <c r="C87" t="n">
-        <v>1169.5444</v>
+        <v>1182.737</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1753,10 +1753,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>373390000</v>
+        <v>267550000</v>
       </c>
       <c r="C88" t="n">
-        <v>1182.7354</v>
+        <v>1201.8673</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1764,10 +1764,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>267550000</v>
+        <v>298740000</v>
       </c>
       <c r="C89" t="n">
-        <v>1201.8551</v>
+        <v>1150.9767</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1775,10 +1775,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>298740000</v>
+        <v>263150000</v>
       </c>
       <c r="C90" t="n">
-        <v>1150.9364</v>
+        <v>1115.3778</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1786,10 +1786,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>263150000</v>
+        <v>200590000</v>
       </c>
       <c r="C91" t="n">
-        <v>1115.3589</v>
+        <v>1114.4697</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1797,10 +1797,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>200590000</v>
+        <v>279730000</v>
       </c>
       <c r="C92" t="n">
-        <v>1114.4547</v>
+        <v>1128.0413</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1808,10 +1808,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>279730000</v>
+        <v>395650020</v>
       </c>
       <c r="C93" t="n">
-        <v>1128.0269</v>
+        <v>1124.8636</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1819,10 +1819,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>395650020</v>
+        <v>331410020</v>
       </c>
       <c r="C94" t="n">
-        <v>1124.8623</v>
+        <v>1130.4976</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1830,10 +1830,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>331410020</v>
+        <v>261090000</v>
       </c>
       <c r="C95" t="n">
-        <v>1130.4915</v>
+        <v>1135.9226</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1841,10 +1841,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>261090000</v>
+        <v>242790000</v>
       </c>
       <c r="C96" t="n">
-        <v>1135.9207</v>
+        <v>1144.8372</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1852,10 +1852,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>242790000</v>
+        <v>193430000</v>
       </c>
       <c r="C97" t="n">
-        <v>1144.8073</v>
+        <v>1134.38</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1863,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>193430000</v>
+        <v>206570000</v>
       </c>
       <c r="C98" t="n">
-        <v>1134.3671</v>
+        <v>1143.0493</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1874,10 +1874,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>206570000</v>
+        <v>295490020</v>
       </c>
       <c r="C99" t="n">
-        <v>1143.0444</v>
+        <v>1144.6212</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1885,10 +1885,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>295490020</v>
+        <v>241590000</v>
       </c>
       <c r="C100" t="n">
-        <v>1144.6138</v>
+        <v>1142.3527</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1896,10 +1896,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>241590000</v>
+        <v>315600000</v>
       </c>
       <c r="C101" t="n">
-        <v>1142.3444</v>
+        <v>1136.4631</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1907,10 +1907,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>315600000</v>
+        <v>322010000</v>
       </c>
       <c r="C102" t="n">
-        <v>1136.4617</v>
+        <v>1148.4313</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>322010000</v>
+        <v>274060000</v>
       </c>
       <c r="C103" t="n">
-        <v>1148.4205</v>
+        <v>1162.3182</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1929,10 +1929,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>274060000</v>
+        <v>201240000</v>
       </c>
       <c r="C104" t="n">
-        <v>1162.3146</v>
+        <v>1175.9083</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1940,10 +1940,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>201240000</v>
+        <v>200400000</v>
       </c>
       <c r="C105" t="n">
-        <v>1175.8934</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1951,10 +1951,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>200400000</v>
+        <v>219350000</v>
       </c>
       <c r="C106" t="n">
-        <v>1196.2443</v>
+        <v>1182.2898</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1962,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>219350000</v>
+        <v>191080000</v>
       </c>
       <c r="C107" t="n">
-        <v>1182.2738</v>
+        <v>1185.7532</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1973,10 +1973,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>191080000</v>
+        <v>279980000</v>
       </c>
       <c r="C108" t="n">
-        <v>1185.7009</v>
+        <v>1184.3556</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1984,10 +1984,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>279980000</v>
+        <v>210400000</v>
       </c>
       <c r="C109" t="n">
-        <v>1184.3539</v>
+        <v>1190.1663</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1995,10 +1995,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>210400000</v>
+        <v>149050000</v>
       </c>
       <c r="C110" t="n">
-        <v>1190.1604</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2006,10 +2006,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>149050000</v>
+        <v>206060000</v>
       </c>
       <c r="C111" t="n">
-        <v>1189.0756</v>
+        <v>1187.324</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2017,10 +2017,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>206060000</v>
+        <v>327800000</v>
       </c>
       <c r="C112" t="n">
-        <v>1187.3215</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2028,10 +2028,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>327800000</v>
+        <v>194900000</v>
       </c>
       <c r="C113" t="n">
-        <v>1187.3528</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2039,10 +2039,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>194900000</v>
+        <v>150070000</v>
       </c>
       <c r="C114" t="n">
-        <v>1183.6859</v>
+        <v>1186.4066</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2050,10 +2050,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>150070000</v>
+        <v>249730000</v>
       </c>
       <c r="C115" t="n">
-        <v>1186.3999</v>
+        <v>1184.7783</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2061,10 +2061,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>249730000</v>
+        <v>328930000</v>
       </c>
       <c r="C116" t="n">
-        <v>1184.7565</v>
+        <v>1177.422</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2072,10 +2072,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>328930000</v>
+        <v>319130000</v>
       </c>
       <c r="C117" t="n">
-        <v>1177.4198</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2083,10 +2083,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>319130000</v>
+        <v>290900000</v>
       </c>
       <c r="C118" t="n">
-        <v>1146.302</v>
+        <v>1168.4946</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2094,10 +2094,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>290900000</v>
+        <v>272000000</v>
       </c>
       <c r="C119" t="n">
-        <v>1168.4825</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2105,10 +2105,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>272000000</v>
+        <v>459869980</v>
       </c>
       <c r="C120" t="n">
-        <v>1178.1132</v>
+        <v>1176.7383</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2116,10 +2116,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>459869980</v>
+        <v>250980000</v>
       </c>
       <c r="C121" t="n">
-        <v>1176.724</v>
+        <v>1192.3033</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2127,10 +2127,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>250980000</v>
+        <v>317930020</v>
       </c>
       <c r="C122" t="n">
-        <v>1192.3014</v>
+        <v>1187.0343</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2138,10 +2138,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>317930020</v>
+        <v>359550000</v>
       </c>
       <c r="C123" t="n">
-        <v>1187.0327</v>
+        <v>1193.3302</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2149,10 +2149,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>359550000</v>
+        <v>279650000</v>
       </c>
       <c r="C124" t="n">
-        <v>1193.3121</v>
+        <v>1207.8232</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2160,10 +2160,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>279650000</v>
+        <v>286200000</v>
       </c>
       <c r="C125" t="n">
-        <v>1207.8153</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2171,10 +2171,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>286200000</v>
+        <v>343900000</v>
       </c>
       <c r="C126" t="n">
-        <v>1232.3434</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>343900000</v>
+        <v>310469980</v>
       </c>
       <c r="C127" t="n">
-        <v>1225.9089</v>
+        <v>1263.1934</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2193,10 +2193,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>310469980</v>
+        <v>324740000</v>
       </c>
       <c r="C128" t="n">
-        <v>1263.1807</v>
+        <v>1257.3682</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2204,10 +2204,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>324740000</v>
+        <v>301200000</v>
       </c>
       <c r="C129" t="n">
-        <v>1257.3591</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>301200000</v>
+        <v>298320000</v>
       </c>
       <c r="C130" t="n">
-        <v>1261.2496</v>
+        <v>1261.3844</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2226,10 +2226,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>298320000</v>
+        <v>393980000</v>
       </c>
       <c r="C131" t="n">
-        <v>1261.3674</v>
+        <v>1268.4626</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2237,10 +2237,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>393980000</v>
+        <v>398920000</v>
       </c>
       <c r="C132" t="n">
-        <v>1268.4539</v>
+        <v>1277.0555</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2248,10 +2248,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>398920000</v>
+        <v>323589980</v>
       </c>
       <c r="C133" t="n">
-        <v>1277.0442</v>
+        <v>1257.8584</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2259,10 +2259,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>323589980</v>
+        <v>307460000</v>
       </c>
       <c r="C134" t="n">
-        <v>1257.8407</v>
+        <v>1266.7869</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2270,10 +2270,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>307460000</v>
+        <v>297000000</v>
       </c>
       <c r="C135" t="n">
-        <v>1266.7705</v>
+        <v>1282.9048</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2281,10 +2281,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>297000000</v>
+        <v>291500000</v>
       </c>
       <c r="C136" t="n">
-        <v>1282.9014</v>
+        <v>1287.3202</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2292,10 +2292,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>291500000</v>
+        <v>242700000</v>
       </c>
       <c r="C137" t="n">
-        <v>1287.3074</v>
+        <v>1261.1036</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2303,10 +2303,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>242700000</v>
+        <v>183370000</v>
       </c>
       <c r="C138" t="n">
-        <v>1261.0431</v>
+        <v>1259.6484</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2314,10 +2314,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>183370000</v>
+        <v>241900000</v>
       </c>
       <c r="C139" t="n">
-        <v>1259.6431</v>
+        <v>1261.8157</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2325,10 +2325,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>241900000</v>
+        <v>273740000</v>
       </c>
       <c r="C140" t="n">
-        <v>1261.7827</v>
+        <v>1278.3525</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2336,10 +2336,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>273740000</v>
+        <v>212100000</v>
       </c>
       <c r="C141" t="n">
-        <v>1278.3439</v>
+        <v>1290.4521</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2347,10 +2347,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>212100000</v>
+        <v>308300000</v>
       </c>
       <c r="C142" t="n">
-        <v>1290.4368</v>
+        <v>1295.2175</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2358,10 +2358,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>308300000</v>
+        <v>165990000</v>
       </c>
       <c r="C143" t="n">
-        <v>1295.2062</v>
+        <v>1297.3605</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2369,10 +2369,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>165990000</v>
+        <v>328600000</v>
       </c>
       <c r="C144" t="n">
-        <v>1297.3245</v>
+        <v>1357.0087</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2380,10 +2380,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>328600000</v>
+        <v>213740000</v>
       </c>
       <c r="C145" t="n">
-        <v>1356.9905</v>
+        <v>1364.9274</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2391,10 +2391,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>213740000</v>
+        <v>220980000</v>
       </c>
       <c r="C146" t="n">
-        <v>1364.9016</v>
+        <v>1362.0619</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2402,10 +2402,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>220980000</v>
+        <v>311760000</v>
       </c>
       <c r="C147" t="n">
-        <v>1362.0563</v>
+        <v>1348.57</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2413,10 +2413,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>311760000</v>
+        <v>324880000</v>
       </c>
       <c r="C148" t="n">
-        <v>1348.5603</v>
+        <v>1333.3085</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2424,10 +2424,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>324880000</v>
+        <v>194200000</v>
       </c>
       <c r="C149" t="n">
-        <v>1333.3021</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2435,10 +2435,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>194200000</v>
+        <v>219200000</v>
       </c>
       <c r="C150" t="n">
-        <v>1329.5576</v>
+        <v>1324.7351</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2446,10 +2446,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>219200000</v>
+        <v>265100000</v>
       </c>
       <c r="C151" t="n">
-        <v>1324.7318</v>
+        <v>1327.6069</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2457,10 +2457,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>265100000</v>
+        <v>318140000</v>
       </c>
       <c r="C152" t="n">
-        <v>1327.6051</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2468,10 +2468,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>318140000</v>
+        <v>323640000</v>
       </c>
       <c r="C153" t="n">
-        <v>1317.6909</v>
+        <v>1317.75</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2479,10 +2479,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>323640000</v>
+        <v>258100000</v>
       </c>
       <c r="C154" t="n">
-        <v>1317.7236</v>
+        <v>1298.143</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2490,10 +2490,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>258100000</v>
+        <v>245450000</v>
       </c>
       <c r="C155" t="n">
-        <v>1298.1354</v>
+        <v>1296.6727</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2501,10 +2501,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>245450000</v>
+        <v>388200000</v>
       </c>
       <c r="C156" t="n">
-        <v>1296.6604</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2512,10 +2512,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>388200000</v>
+        <v>218250000</v>
       </c>
       <c r="C157" t="n">
-        <v>1293.891</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2523,10 +2523,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>218250000</v>
+        <v>135000000</v>
       </c>
       <c r="C158" t="n">
-        <v>1299.0688</v>
+        <v>1311.6884</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2534,10 +2534,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>135000000</v>
+        <v>230420000</v>
       </c>
       <c r="C159" t="n">
-        <v>1311.6772</v>
+        <v>1322.621</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2545,10 +2545,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>230420000</v>
+        <v>186010000</v>
       </c>
       <c r="C160" t="n">
-        <v>1322.6124</v>
+        <v>1349.7838</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2556,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>186010000</v>
+        <v>324380030</v>
       </c>
       <c r="C161" t="n">
-        <v>1349.7784</v>
+        <v>1353.8998</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2567,10 +2567,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>324380030</v>
+        <v>188250000</v>
       </c>
       <c r="C162" t="n">
-        <v>1353.8983</v>
+        <v>1360.0135</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2578,10 +2578,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>188250000</v>
+        <v>262170000</v>
       </c>
       <c r="C163" t="n">
-        <v>1360.0109</v>
+        <v>1338.8757</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2589,10 +2589,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>262170000</v>
+        <v>250290000</v>
       </c>
       <c r="C164" t="n">
-        <v>1338.8644</v>
+        <v>1330.1678</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2600,10 +2600,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>250290000</v>
+        <v>396959970</v>
       </c>
       <c r="C165" t="n">
-        <v>1330.1</v>
+        <v>1365.224</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2611,10 +2611,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>396959970</v>
+        <v>181300000</v>
       </c>
       <c r="C166" t="n">
-        <v>1365.2227</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2622,10 +2622,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>181300000</v>
+        <v>349490020</v>
       </c>
       <c r="C167" t="n">
-        <v>1361.4104</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2633,10 +2633,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>349490020</v>
+        <v>354610000</v>
       </c>
       <c r="C168" t="n">
-        <v>1362.602</v>
+        <v>1366.1288</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2644,10 +2644,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>354610000</v>
+        <v>268370000</v>
       </c>
       <c r="C169" t="n">
-        <v>1366.1195</v>
+        <v>1424.0941</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2655,10 +2655,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>268370000</v>
+        <v>217230000</v>
       </c>
       <c r="C170" t="n">
-        <v>1424.0857</v>
+        <v>1419.2301</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2666,10 +2666,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>217230000</v>
+        <v>202800000</v>
       </c>
       <c r="C171" t="n">
-        <v>1419.2256</v>
+        <v>1418.7997</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2677,10 +2677,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>202800000</v>
+        <v>182600000</v>
       </c>
       <c r="C172" t="n">
-        <v>1418.7972</v>
+        <v>1428.8804</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2688,10 +2688,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>182600000</v>
+        <v>186830000</v>
       </c>
       <c r="C173" t="n">
-        <v>1428.8694</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2699,10 +2699,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>186830000</v>
+        <v>256060000</v>
       </c>
       <c r="C174" t="n">
-        <v>1450.185</v>
+        <v>1463.845</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2710,10 +2710,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>256060000</v>
+        <v>181350000</v>
       </c>
       <c r="C175" t="n">
-        <v>1463.7825</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2721,10 +2721,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>181350000</v>
+        <v>175400000</v>
       </c>
       <c r="C176" t="n">
-        <v>1464.3728</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2732,10 +2732,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>175400000</v>
+        <v>231000000</v>
       </c>
       <c r="C177" t="n">
-        <v>1473.9847</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2743,10 +2743,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>231000000</v>
+        <v>286250020</v>
       </c>
       <c r="C178" t="n">
-        <v>1474.4945</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2754,10 +2754,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>286250020</v>
+        <v>202930000</v>
       </c>
       <c r="C179" t="n">
-        <v>1475.4567</v>
+        <v>1432.3635</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2765,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>202930000</v>
+        <v>275320000</v>
       </c>
       <c r="C180" t="n">
-        <v>1432.339</v>
+        <v>1355.8541</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2776,10 +2776,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>275320000</v>
+        <v>480600000</v>
       </c>
       <c r="C181" t="n">
-        <v>1355.8496</v>
+        <v>1349.3301</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2787,10 +2787,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>480600000</v>
+        <v>589150000</v>
       </c>
       <c r="C182" t="n">
-        <v>1349.3229</v>
+        <v>1328.1084</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2798,10 +2798,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>589150000</v>
+        <v>392600000</v>
       </c>
       <c r="C183" t="n">
-        <v>1328.0879</v>
+        <v>1331.5554</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2809,10 +2809,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>392600000</v>
+        <v>478160000</v>
       </c>
       <c r="C184" t="n">
-        <v>1331.5211</v>
+        <v>1341.6771</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2820,10 +2820,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>478160000</v>
+        <v>496829980</v>
       </c>
       <c r="C185" t="n">
-        <v>1341.6642</v>
+        <v>1374.025</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2831,10 +2831,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>496829980</v>
+        <v>295170020</v>
       </c>
       <c r="C186" t="n">
-        <v>1374.023</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2842,10 +2842,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>295170020</v>
+        <v>169440000</v>
       </c>
       <c r="C187" t="n">
-        <v>1424.7794</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2853,10 +2853,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>169440000</v>
+        <v>215520000</v>
       </c>
       <c r="C188" t="n">
-        <v>1424.6221</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2864,10 +2864,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>215520000</v>
+        <v>262840000</v>
       </c>
       <c r="C189" t="n">
-        <v>1424.9015</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2875,10 +2875,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>262840000</v>
+        <v>315000000</v>
       </c>
       <c r="C190" t="n">
-        <v>1429.9982</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2886,10 +2886,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>315000000</v>
+        <v>338970020</v>
       </c>
       <c r="C191" t="n">
-        <v>1430.0143</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2897,10 +2897,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>338970020</v>
+        <v>260880000</v>
       </c>
       <c r="C192" t="n">
-        <v>1430.0298</v>
+        <v>1445.8451</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2908,10 +2908,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>260880000</v>
+        <v>346149980</v>
       </c>
       <c r="C193" t="n">
-        <v>1445.8335</v>
+        <v>1360.5026</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2919,10 +2919,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>346149980</v>
+        <v>431149980</v>
       </c>
       <c r="C194" t="n">
-        <v>1360.4852</v>
+        <v>1374.594</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2930,10 +2930,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>431149980</v>
+        <v>279500000</v>
       </c>
       <c r="C195" t="n">
-        <v>1374.5894</v>
+        <v>1391.4231</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2941,10 +2941,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>279500000</v>
+        <v>357400000</v>
       </c>
       <c r="C196" t="n">
-        <v>1391.1584</v>
+        <v>1451.0302</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2952,10 +2952,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>357400000</v>
+        <v>254070000</v>
       </c>
       <c r="C197" t="n">
-        <v>1450.9777</v>
+        <v>1468.6167</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2963,10 +2963,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>254070000</v>
+        <v>405740000</v>
       </c>
       <c r="C198" t="n">
-        <v>1468.5831</v>
+        <v>1487.8336</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2974,10 +2974,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>405740000</v>
+        <v>521350000</v>
       </c>
       <c r="C199" t="n">
-        <v>1487.8324</v>
+        <v>1487.5168</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2985,10 +2985,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>521350000</v>
+        <v>393340030</v>
       </c>
       <c r="C200" t="n">
-        <v>1487.4933</v>
+        <v>1484.1284</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2996,10 +2996,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>393340030</v>
+        <v>423890020</v>
       </c>
       <c r="C201" t="n">
-        <v>1484.1245</v>
+        <v>1487.86</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3007,10 +3007,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>423890020</v>
+        <v>176000000</v>
       </c>
       <c r="C202" t="n">
-        <v>1487.8551</v>
+        <v>1399.3921</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3018,10 +3018,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>176000000</v>
+        <v>334980000</v>
       </c>
       <c r="C203" t="n">
-        <v>1399.3765</v>
+        <v>1470.8683</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3029,10 +3029,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>334980000</v>
+        <v>139200000</v>
       </c>
       <c r="C204" t="n">
-        <v>1470.861</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3040,10 +3040,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>139200000</v>
+        <v>127040000</v>
       </c>
       <c r="C205" t="n">
-        <v>1451.923</v>
+        <v>1434.8594</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3051,10 +3051,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>127040000</v>
+        <v>189260000</v>
       </c>
       <c r="C206" t="n">
-        <v>1434.8278</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3062,10 +3062,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>189260000</v>
+        <v>275010000</v>
       </c>
       <c r="C207" t="n">
-        <v>1445.9563</v>
+        <v>1464.5646</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3073,10 +3073,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>275010000</v>
+        <v>194450000</v>
       </c>
       <c r="C208" t="n">
-        <v>1464.5471</v>
+        <v>1471.4487</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3084,10 +3084,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>194450000</v>
+        <v>196250000</v>
       </c>
       <c r="C209" t="n">
-        <v>1471.4448</v>
+        <v>1447.6355</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3095,10 +3095,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>196250000</v>
+        <v>208000000</v>
       </c>
       <c r="C210" t="n">
-        <v>1447.554</v>
+        <v>1434.8132</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3106,10 +3106,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>208000000</v>
+        <v>209360000</v>
       </c>
       <c r="C211" t="n">
-        <v>1434.8108</v>
+        <v>1420.3748</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3117,10 +3117,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>209360000</v>
+        <v>212720000</v>
       </c>
       <c r="C212" t="n">
-        <v>1420.3701</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>212720000</v>
+        <v>241830000</v>
       </c>
       <c r="C213" t="n">
-        <v>1403.0524</v>
+        <v>1407.8024</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3139,10 +3139,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>241830000</v>
+        <v>312580000</v>
       </c>
       <c r="C214" t="n">
-        <v>1407.7981</v>
+        <v>1404.9287</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3150,10 +3150,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>312580000</v>
+        <v>179500000</v>
       </c>
       <c r="C215" t="n">
-        <v>1404.9167</v>
+        <v>1401.7639</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3161,10 +3161,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>179500000</v>
+        <v>107500000</v>
       </c>
       <c r="C216" t="n">
-        <v>1401.7583</v>
+        <v>1392.025</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3172,10 +3172,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>107500000</v>
+        <v>242990000</v>
       </c>
       <c r="C217" t="n">
-        <v>1392.0065</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3183,10 +3183,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>242990000</v>
+        <v>254470000</v>
       </c>
       <c r="C218" t="n">
-        <v>1402.779</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3194,10 +3194,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>254470000</v>
+        <v>331130000</v>
       </c>
       <c r="C219" t="n">
-        <v>1418.5961</v>
+        <v>1446.06</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3205,10 +3205,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>331130000</v>
+        <v>237200000</v>
       </c>
       <c r="C220" t="n">
-        <v>1446.057</v>
+        <v>1450.5885</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>237200000</v>
+        <v>268310000</v>
       </c>
       <c r="C221" t="n">
-        <v>1450.5864</v>
+        <v>1450.6201</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3227,10 +3227,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>268310000</v>
+        <v>293410020</v>
       </c>
       <c r="C222" t="n">
-        <v>1450.6014</v>
+        <v>1449.9003</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3238,10 +3238,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>293410020</v>
+        <v>190400000</v>
       </c>
       <c r="C223" t="n">
-        <v>1449.8969</v>
+        <v>1454.6627</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3249,10 +3249,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>190400000</v>
+        <v>147700000</v>
       </c>
       <c r="C224" t="n">
-        <v>1454.6573</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3260,10 +3260,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>147700000</v>
+        <v>152560000</v>
       </c>
       <c r="C225" t="n">
-        <v>1453.8477</v>
+        <v>1447.5896</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3271,10 +3271,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>152560000</v>
+        <v>195400000</v>
       </c>
       <c r="C226" t="n">
-        <v>1447.5764</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3282,10 +3282,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>195400000</v>
+        <v>185680000</v>
       </c>
       <c r="C227" t="n">
-        <v>1440.0085</v>
+        <v>1439.3232</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3293,10 +3293,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>185680000</v>
+        <v>158700000</v>
       </c>
       <c r="C228" t="n">
-        <v>1439.3232</v>
+        <v>1438.0428</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3304,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>158700000</v>
+        <v>250300000</v>
       </c>
       <c r="C229" t="n">
-        <v>1438.0428</v>
+        <v>1437.9939</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3315,10 +3315,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>250300000</v>
+        <v>192580000</v>
       </c>
       <c r="C230" t="n">
-        <v>1437.9939</v>
+        <v>1439.1218</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3326,10 +3326,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>192580000</v>
+        <v>244040000</v>
       </c>
       <c r="C231" t="n">
-        <v>1439.1218</v>
+        <v>1440.4795</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3337,10 +3337,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>244040000</v>
+        <v>298200000</v>
       </c>
       <c r="C232" t="n">
-        <v>1440.4755</v>
+        <v>1452.0646</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3348,10 +3348,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>81500000</v>
+        <v>253000000</v>
       </c>
       <c r="C233" t="n">
-        <v>1450.1505</v>
+        <v>1448.7827</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -25,21 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">17/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">26/12/2024 12:00:00</t>
   </si>
   <si>
@@ -719,6 +704,21 @@
   </si>
   <si>
     <t xml:space="preserve">17/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -788,7 +788,7 @@
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
     <col min="2" max="2" customWidth="1" width="9.714285714285714" bestFit="1"/>
-    <col min="3" max="3" customWidth="1" width="10.714285714285714" bestFit="1"/>
+    <col min="3" max="3" customWidth="1" width="9.714285714285714" bestFit="1"/>
   </cols>
   <sheetData>
     <row r="1" x14ac:dyDescent="0.25">
@@ -807,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>109500000</v>
+        <v>135210000</v>
       </c>
       <c r="C2" t="n">
-        <v>1020.69635</v>
+        <v>1028.5804</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -818,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>103710000</v>
+        <v>214050000</v>
       </c>
       <c r="C3" t="n">
-        <v>1021.90955</v>
+        <v>1028.1958</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -829,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>70020000</v>
+        <v>170650000</v>
       </c>
       <c r="C4" t="n">
-        <v>1022.2438</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -840,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>105600000</v>
+        <v>129920000</v>
       </c>
       <c r="C5" t="n">
-        <v>1022.24274</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>60970000</v>
+        <v>90600000</v>
       </c>
       <c r="C6" t="n">
-        <v>1025.3103</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -862,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>135210000</v>
+        <v>94620000</v>
       </c>
       <c r="C7" t="n">
-        <v>1028.5804</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>214050000</v>
+        <v>76740000</v>
       </c>
       <c r="C8" t="n">
-        <v>1028.1958</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -884,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>170650000</v>
+        <v>60220000</v>
       </c>
       <c r="C9" t="n">
-        <v>1030.4104</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -895,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>129920000</v>
+        <v>80100000</v>
       </c>
       <c r="C10" t="n">
-        <v>1031.7577</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -906,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>90600000</v>
+        <v>144200000</v>
       </c>
       <c r="C11" t="n">
-        <v>1032.4374</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -917,10 +917,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>94620000</v>
+        <v>66560000</v>
       </c>
       <c r="C12" t="n">
-        <v>1034.7297</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -928,10 +928,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>76740000</v>
+        <v>69770000</v>
       </c>
       <c r="C13" t="n">
-        <v>1035.4338</v>
+        <v>1040.3387</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -939,10 +939,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>60220000</v>
+        <v>59000000</v>
       </c>
       <c r="C14" t="n">
-        <v>1035.8505</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -950,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>80100000</v>
+        <v>97600000</v>
       </c>
       <c r="C15" t="n">
-        <v>1036.7753</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -961,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>144200000</v>
+        <v>139000000</v>
       </c>
       <c r="C16" t="n">
-        <v>1036.8966</v>
+        <v>1041.9989</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -972,10 +972,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>66560000</v>
+        <v>215030000</v>
       </c>
       <c r="C17" t="n">
-        <v>1039.2858</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -983,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>69770000</v>
+        <v>117720000</v>
       </c>
       <c r="C18" t="n">
-        <v>1040.3387</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -994,10 +994,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>59000000</v>
+        <v>55800000</v>
       </c>
       <c r="C19" t="n">
-        <v>1040.7654</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1005,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>97600000</v>
+        <v>135550000</v>
       </c>
       <c r="C20" t="n">
-        <v>1041.2943</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1016,10 +1016,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>139000000</v>
+        <v>89000000</v>
       </c>
       <c r="C21" t="n">
-        <v>1041.9989</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1027,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>215030000</v>
+        <v>58100000</v>
       </c>
       <c r="C22" t="n">
-        <v>1045.5352</v>
+        <v>1050.2952</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1038,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>117720000</v>
+        <v>86600000</v>
       </c>
       <c r="C23" t="n">
-        <v>1046.7697</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1049,10 +1049,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>55800000</v>
+        <v>95150000</v>
       </c>
       <c r="C24" t="n">
-        <v>1046.9908</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1060,10 +1060,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>135550000</v>
+        <v>147140000</v>
       </c>
       <c r="C25" t="n">
-        <v>1046.9497</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1071,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>89000000</v>
+        <v>123760000</v>
       </c>
       <c r="C26" t="n">
-        <v>1049.7869</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1082,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>58100000</v>
+        <v>88880000</v>
       </c>
       <c r="C27" t="n">
-        <v>1050.2952</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1093,10 +1093,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>86600000</v>
+        <v>115600000</v>
       </c>
       <c r="C28" t="n">
-        <v>1051.1277</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1104,10 +1104,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>95150000</v>
+        <v>93120000</v>
       </c>
       <c r="C29" t="n">
-        <v>1051.69</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1115,10 +1115,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>147140000</v>
+        <v>162410000</v>
       </c>
       <c r="C30" t="n">
-        <v>1051.1226</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1126,10 +1126,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>123760000</v>
+        <v>191440000</v>
       </c>
       <c r="C31" t="n">
-        <v>1053.3625</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>88880000</v>
+        <v>98800000</v>
       </c>
       <c r="C32" t="n">
-        <v>1053.5273</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1148,10 +1148,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>115600000</v>
+        <v>151830000</v>
       </c>
       <c r="C33" t="n">
-        <v>1053.941</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>93120000</v>
+        <v>63730000</v>
       </c>
       <c r="C34" t="n">
-        <v>1054.1022</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1170,10 +1170,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>162410000</v>
+        <v>154380000</v>
       </c>
       <c r="C35" t="n">
-        <v>1053.6134</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1181,10 +1181,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>191440000</v>
+        <v>127430000</v>
       </c>
       <c r="C36" t="n">
-        <v>1055.6161</v>
+        <v>1058.3744</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1192,10 +1192,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>98800000</v>
+        <v>90150000</v>
       </c>
       <c r="C37" t="n">
-        <v>1055.6309</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1203,10 +1203,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>151830000</v>
+        <v>78400000</v>
       </c>
       <c r="C38" t="n">
-        <v>1056.2124</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1214,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>63730000</v>
+        <v>102390000</v>
       </c>
       <c r="C39" t="n">
-        <v>1056.7262</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1225,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>154380000</v>
+        <v>106130000</v>
       </c>
       <c r="C40" t="n">
-        <v>1056.4021</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1236,10 +1236,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>127430000</v>
+        <v>81520000</v>
       </c>
       <c r="C41" t="n">
-        <v>1058.3744</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1247,10 +1247,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>90150000</v>
+        <v>107290000</v>
       </c>
       <c r="C42" t="n">
-        <v>1058.5518</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1258,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>78400000</v>
+        <v>78500000</v>
       </c>
       <c r="C43" t="n">
-        <v>1059.0238</v>
+        <v>1061.6664</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1269,10 +1269,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>102390000</v>
+        <v>115700000</v>
       </c>
       <c r="C44" t="n">
-        <v>1058.5037</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1280,10 +1280,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>106130000</v>
+        <v>135350000</v>
       </c>
       <c r="C45" t="n">
-        <v>1060.2593</v>
+        <v>1063.415</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1291,10 +1291,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>81520000</v>
+        <v>156190000</v>
       </c>
       <c r="C46" t="n">
-        <v>1060.7654</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1302,10 +1302,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>107290000</v>
+        <v>203700000</v>
       </c>
       <c r="C47" t="n">
-        <v>1061.1646</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1313,10 +1313,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>78500000</v>
+        <v>153120000</v>
       </c>
       <c r="C48" t="n">
-        <v>1061.6664</v>
+        <v>1065.541</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1324,10 +1324,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>115700000</v>
+        <v>154930000</v>
       </c>
       <c r="C49" t="n">
-        <v>1062.0686</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1335,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>135350000</v>
+        <v>101660000</v>
       </c>
       <c r="C50" t="n">
-        <v>1063.415</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1346,10 +1346,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>156190000</v>
+        <v>90000000</v>
       </c>
       <c r="C51" t="n">
-        <v>1063.8278</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1357,10 +1357,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>203700000</v>
+        <v>266600000</v>
       </c>
       <c r="C52" t="n">
-        <v>1064.3394</v>
+        <v>1066.7559</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>153120000</v>
+        <v>146970000</v>
       </c>
       <c r="C53" t="n">
-        <v>1065.541</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1379,10 +1379,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>154930000</v>
+        <v>61200000</v>
       </c>
       <c r="C54" t="n">
-        <v>1065.7025</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1390,10 +1390,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>101660000</v>
+        <v>69170000</v>
       </c>
       <c r="C55" t="n">
-        <v>1066.0099</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1401,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>90000000</v>
+        <v>41240000</v>
       </c>
       <c r="C56" t="n">
-        <v>1066.2288</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1412,10 +1412,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>266600000</v>
+        <v>145230000</v>
       </c>
       <c r="C57" t="n">
-        <v>1066.7559</v>
+        <v>1068.306</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>146970000</v>
+        <v>120040000</v>
       </c>
       <c r="C58" t="n">
-        <v>1068.2128</v>
+        <v>1070.8301</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1434,10 +1434,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>61200000</v>
+        <v>105520000</v>
       </c>
       <c r="C59" t="n">
-        <v>1068.3644</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>69170000</v>
+        <v>180350000</v>
       </c>
       <c r="C60" t="n">
-        <v>1069.0115</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1456,10 +1456,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>41240000</v>
+        <v>157240000</v>
       </c>
       <c r="C61" t="n">
-        <v>1069.0428</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1467,10 +1467,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>145230000</v>
+        <v>204650000</v>
       </c>
       <c r="C62" t="n">
-        <v>1068.306</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1478,10 +1478,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>120040000</v>
+        <v>127150000</v>
       </c>
       <c r="C63" t="n">
-        <v>1070.8301</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1489,10 +1489,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>105520000</v>
+        <v>54310000</v>
       </c>
       <c r="C64" t="n">
-        <v>1071.3093</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1500,10 +1500,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>180350000</v>
+        <v>75470000</v>
       </c>
       <c r="C65" t="n">
-        <v>1071.5227</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1511,10 +1511,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>157240000</v>
+        <v>79680000</v>
       </c>
       <c r="C66" t="n">
-        <v>1070.9691</v>
+        <v>1075.5189</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1522,10 +1522,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>204650000</v>
+        <v>62750000</v>
       </c>
       <c r="C67" t="n">
-        <v>1073.0979</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1533,10 +1533,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>127150000</v>
+        <v>75600000</v>
       </c>
       <c r="C68" t="n">
-        <v>1072.918</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1544,10 +1544,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>54310000</v>
+        <v>63990000</v>
       </c>
       <c r="C69" t="n">
-        <v>1074.1038</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1555,10 +1555,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>75470000</v>
+        <v>225590000</v>
       </c>
       <c r="C70" t="n">
-        <v>1073.4634</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1566,10 +1566,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>79680000</v>
+        <v>415320000</v>
       </c>
       <c r="C71" t="n">
-        <v>1075.5189</v>
+        <v>1189.3408</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1577,10 +1577,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>62750000</v>
+        <v>230200000</v>
       </c>
       <c r="C72" t="n">
-        <v>1075.8248</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1588,10 +1588,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>75600000</v>
+        <v>347690000</v>
       </c>
       <c r="C73" t="n">
-        <v>1076.5104</v>
+        <v>1162.0289</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1599,10 +1599,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>63990000</v>
+        <v>339050000</v>
       </c>
       <c r="C74" t="n">
-        <v>1076.5854</v>
+        <v>1082.2896</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1610,10 +1610,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>225590000</v>
+        <v>335470000</v>
       </c>
       <c r="C75" t="n">
-        <v>1075.3297</v>
+        <v>1092.0658</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1621,10 +1621,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>415320000</v>
+        <v>410800000</v>
       </c>
       <c r="C76" t="n">
-        <v>1189.3408</v>
+        <v>1135.2954</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1632,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>230200000</v>
+        <v>530219970</v>
       </c>
       <c r="C77" t="n">
-        <v>1199.1798</v>
+        <v>1176.7036</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1643,10 +1643,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>347690000</v>
+        <v>368410020</v>
       </c>
       <c r="C78" t="n">
-        <v>1162.0289</v>
+        <v>1173.9578</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1654,10 +1654,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>339050000</v>
+        <v>359710000</v>
       </c>
       <c r="C79" t="n">
-        <v>1082.2896</v>
+        <v>1164.9523</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1665,10 +1665,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>335470000</v>
+        <v>327350000</v>
       </c>
       <c r="C80" t="n">
-        <v>1092.0658</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1676,10 +1676,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>410800000</v>
+        <v>451770000</v>
       </c>
       <c r="C81" t="n">
-        <v>1135.2954</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1687,10 +1687,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>530219970</v>
+        <v>373390000</v>
       </c>
       <c r="C82" t="n">
-        <v>1176.7036</v>
+        <v>1182.737</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1698,10 +1698,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>368410020</v>
+        <v>267550000</v>
       </c>
       <c r="C83" t="n">
-        <v>1173.9578</v>
+        <v>1201.8673</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1709,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>359710000</v>
+        <v>298740000</v>
       </c>
       <c r="C84" t="n">
-        <v>1164.9523</v>
+        <v>1150.9767</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1720,10 +1720,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>327350000</v>
+        <v>263150000</v>
       </c>
       <c r="C85" t="n">
-        <v>1171.4315</v>
+        <v>1115.3778</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1731,10 +1731,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>451770000</v>
+        <v>200590000</v>
       </c>
       <c r="C86" t="n">
-        <v>1169.5444</v>
+        <v>1114.4697</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1742,10 +1742,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>373390000</v>
+        <v>279730000</v>
       </c>
       <c r="C87" t="n">
-        <v>1182.737</v>
+        <v>1128.0413</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1753,10 +1753,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>267550000</v>
+        <v>395650020</v>
       </c>
       <c r="C88" t="n">
-        <v>1201.8673</v>
+        <v>1124.8636</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1764,10 +1764,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>298740000</v>
+        <v>331410020</v>
       </c>
       <c r="C89" t="n">
-        <v>1150.9767</v>
+        <v>1130.4976</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1775,10 +1775,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>263150000</v>
+        <v>261090000</v>
       </c>
       <c r="C90" t="n">
-        <v>1115.3778</v>
+        <v>1135.9226</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1786,10 +1786,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>200590000</v>
+        <v>242790000</v>
       </c>
       <c r="C91" t="n">
-        <v>1114.4697</v>
+        <v>1144.8372</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1797,10 +1797,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>279730000</v>
+        <v>193430000</v>
       </c>
       <c r="C92" t="n">
-        <v>1128.0413</v>
+        <v>1134.38</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1808,10 +1808,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>395650020</v>
+        <v>206570000</v>
       </c>
       <c r="C93" t="n">
-        <v>1124.8636</v>
+        <v>1143.0493</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1819,10 +1819,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>331410020</v>
+        <v>295490020</v>
       </c>
       <c r="C94" t="n">
-        <v>1130.4976</v>
+        <v>1144.6212</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1830,10 +1830,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>261090000</v>
+        <v>241590000</v>
       </c>
       <c r="C95" t="n">
-        <v>1135.9226</v>
+        <v>1142.3527</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1841,10 +1841,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>242790000</v>
+        <v>315600000</v>
       </c>
       <c r="C96" t="n">
-        <v>1144.8372</v>
+        <v>1136.4631</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1852,10 +1852,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>193430000</v>
+        <v>322010000</v>
       </c>
       <c r="C97" t="n">
-        <v>1134.38</v>
+        <v>1148.4313</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1863,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>206570000</v>
+        <v>274060000</v>
       </c>
       <c r="C98" t="n">
-        <v>1143.0493</v>
+        <v>1162.3182</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1874,10 +1874,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>295490020</v>
+        <v>201240000</v>
       </c>
       <c r="C99" t="n">
-        <v>1144.6212</v>
+        <v>1175.9083</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1885,10 +1885,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>241590000</v>
+        <v>200400000</v>
       </c>
       <c r="C100" t="n">
-        <v>1142.3527</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1896,10 +1896,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>315600000</v>
+        <v>219350000</v>
       </c>
       <c r="C101" t="n">
-        <v>1136.4631</v>
+        <v>1182.2898</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1907,10 +1907,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>322010000</v>
+        <v>191080000</v>
       </c>
       <c r="C102" t="n">
-        <v>1148.4313</v>
+        <v>1185.7532</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>274060000</v>
+        <v>279980000</v>
       </c>
       <c r="C103" t="n">
-        <v>1162.3182</v>
+        <v>1184.3556</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1929,10 +1929,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>201240000</v>
+        <v>210400000</v>
       </c>
       <c r="C104" t="n">
-        <v>1175.9083</v>
+        <v>1190.1663</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1940,10 +1940,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>200400000</v>
+        <v>149050000</v>
       </c>
       <c r="C105" t="n">
-        <v>1196.2443</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1951,10 +1951,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>219350000</v>
+        <v>206060000</v>
       </c>
       <c r="C106" t="n">
-        <v>1182.2898</v>
+        <v>1187.324</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1962,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>191080000</v>
+        <v>327800000</v>
       </c>
       <c r="C107" t="n">
-        <v>1185.7532</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1973,10 +1973,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>279980000</v>
+        <v>194900000</v>
       </c>
       <c r="C108" t="n">
-        <v>1184.3556</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1984,10 +1984,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>210400000</v>
+        <v>150070000</v>
       </c>
       <c r="C109" t="n">
-        <v>1190.1663</v>
+        <v>1186.4066</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1995,10 +1995,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>149050000</v>
+        <v>249730000</v>
       </c>
       <c r="C110" t="n">
-        <v>1189.0756</v>
+        <v>1184.7783</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2006,10 +2006,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>206060000</v>
+        <v>328930000</v>
       </c>
       <c r="C111" t="n">
-        <v>1187.324</v>
+        <v>1177.422</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2017,10 +2017,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>327800000</v>
+        <v>319130000</v>
       </c>
       <c r="C112" t="n">
-        <v>1187.3528</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2028,10 +2028,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>194900000</v>
+        <v>290900000</v>
       </c>
       <c r="C113" t="n">
-        <v>1183.6859</v>
+        <v>1168.4946</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2039,10 +2039,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>150070000</v>
+        <v>272000000</v>
       </c>
       <c r="C114" t="n">
-        <v>1186.4066</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2050,10 +2050,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>249730000</v>
+        <v>459869980</v>
       </c>
       <c r="C115" t="n">
-        <v>1184.7783</v>
+        <v>1176.7383</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2061,10 +2061,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>328930000</v>
+        <v>250980000</v>
       </c>
       <c r="C116" t="n">
-        <v>1177.422</v>
+        <v>1192.3033</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2072,10 +2072,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>319130000</v>
+        <v>317930020</v>
       </c>
       <c r="C117" t="n">
-        <v>1146.302</v>
+        <v>1187.0343</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2083,10 +2083,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>290900000</v>
+        <v>359550000</v>
       </c>
       <c r="C118" t="n">
-        <v>1168.4946</v>
+        <v>1193.3302</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2094,10 +2094,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>272000000</v>
+        <v>279650000</v>
       </c>
       <c r="C119" t="n">
-        <v>1178.1132</v>
+        <v>1207.8232</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2105,10 +2105,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>459869980</v>
+        <v>286200000</v>
       </c>
       <c r="C120" t="n">
-        <v>1176.7383</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2116,10 +2116,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>250980000</v>
+        <v>343900000</v>
       </c>
       <c r="C121" t="n">
-        <v>1192.3033</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2127,10 +2127,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>317930020</v>
+        <v>310469980</v>
       </c>
       <c r="C122" t="n">
-        <v>1187.0343</v>
+        <v>1263.1934</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2138,10 +2138,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>359550000</v>
+        <v>324740000</v>
       </c>
       <c r="C123" t="n">
-        <v>1193.3302</v>
+        <v>1257.3682</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2149,10 +2149,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>279650000</v>
+        <v>301200000</v>
       </c>
       <c r="C124" t="n">
-        <v>1207.8232</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2160,10 +2160,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>286200000</v>
+        <v>298320000</v>
       </c>
       <c r="C125" t="n">
-        <v>1232.3434</v>
+        <v>1261.3844</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2171,10 +2171,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>343900000</v>
+        <v>393980000</v>
       </c>
       <c r="C126" t="n">
-        <v>1225.9089</v>
+        <v>1268.4626</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>310469980</v>
+        <v>398920000</v>
       </c>
       <c r="C127" t="n">
-        <v>1263.1934</v>
+        <v>1277.0555</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2193,10 +2193,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>324740000</v>
+        <v>323589980</v>
       </c>
       <c r="C128" t="n">
-        <v>1257.3682</v>
+        <v>1257.8584</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2204,10 +2204,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>301200000</v>
+        <v>307460000</v>
       </c>
       <c r="C129" t="n">
-        <v>1261.2496</v>
+        <v>1266.7869</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>298320000</v>
+        <v>297000000</v>
       </c>
       <c r="C130" t="n">
-        <v>1261.3844</v>
+        <v>1282.9048</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2226,10 +2226,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>393980000</v>
+        <v>291500000</v>
       </c>
       <c r="C131" t="n">
-        <v>1268.4626</v>
+        <v>1287.3202</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2237,10 +2237,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>398920000</v>
+        <v>242700000</v>
       </c>
       <c r="C132" t="n">
-        <v>1277.0555</v>
+        <v>1261.1036</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2248,10 +2248,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>323589980</v>
+        <v>183370000</v>
       </c>
       <c r="C133" t="n">
-        <v>1257.8584</v>
+        <v>1259.6484</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2259,10 +2259,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>307460000</v>
+        <v>241900000</v>
       </c>
       <c r="C134" t="n">
-        <v>1266.7869</v>
+        <v>1261.8157</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2270,10 +2270,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>297000000</v>
+        <v>273740000</v>
       </c>
       <c r="C135" t="n">
-        <v>1282.9048</v>
+        <v>1278.3525</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2281,10 +2281,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>291500000</v>
+        <v>212100000</v>
       </c>
       <c r="C136" t="n">
-        <v>1287.3202</v>
+        <v>1290.4521</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2292,10 +2292,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>242700000</v>
+        <v>308300000</v>
       </c>
       <c r="C137" t="n">
-        <v>1261.1036</v>
+        <v>1295.2175</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2303,10 +2303,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>183370000</v>
+        <v>165990000</v>
       </c>
       <c r="C138" t="n">
-        <v>1259.6484</v>
+        <v>1297.3605</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2314,10 +2314,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>241900000</v>
+        <v>328600000</v>
       </c>
       <c r="C139" t="n">
-        <v>1261.8157</v>
+        <v>1357.0087</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2325,10 +2325,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>273740000</v>
+        <v>213740000</v>
       </c>
       <c r="C140" t="n">
-        <v>1278.3525</v>
+        <v>1364.9274</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2336,10 +2336,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>212100000</v>
+        <v>220980000</v>
       </c>
       <c r="C141" t="n">
-        <v>1290.4521</v>
+        <v>1362.0619</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2347,10 +2347,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>308300000</v>
+        <v>311760000</v>
       </c>
       <c r="C142" t="n">
-        <v>1295.2175</v>
+        <v>1348.57</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2358,10 +2358,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>165990000</v>
+        <v>324880000</v>
       </c>
       <c r="C143" t="n">
-        <v>1297.3605</v>
+        <v>1333.3085</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2369,10 +2369,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>328600000</v>
+        <v>194200000</v>
       </c>
       <c r="C144" t="n">
-        <v>1357.0087</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2380,10 +2380,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>213740000</v>
+        <v>219200000</v>
       </c>
       <c r="C145" t="n">
-        <v>1364.9274</v>
+        <v>1324.7351</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2391,10 +2391,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>220980000</v>
+        <v>265100000</v>
       </c>
       <c r="C146" t="n">
-        <v>1362.0619</v>
+        <v>1327.6069</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2402,10 +2402,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>311760000</v>
+        <v>318140000</v>
       </c>
       <c r="C147" t="n">
-        <v>1348.57</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2413,10 +2413,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>324880000</v>
+        <v>323640000</v>
       </c>
       <c r="C148" t="n">
-        <v>1333.3085</v>
+        <v>1317.75</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2424,10 +2424,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>194200000</v>
+        <v>258100000</v>
       </c>
       <c r="C149" t="n">
-        <v>1329.5576</v>
+        <v>1298.143</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2435,10 +2435,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>219200000</v>
+        <v>245450000</v>
       </c>
       <c r="C150" t="n">
-        <v>1324.7351</v>
+        <v>1296.6727</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2446,10 +2446,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>265100000</v>
+        <v>388200000</v>
       </c>
       <c r="C151" t="n">
-        <v>1327.6069</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2457,10 +2457,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>318140000</v>
+        <v>218250000</v>
       </c>
       <c r="C152" t="n">
-        <v>1317.6909</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2468,10 +2468,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>323640000</v>
+        <v>135000000</v>
       </c>
       <c r="C153" t="n">
-        <v>1317.75</v>
+        <v>1311.6884</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2479,10 +2479,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>258100000</v>
+        <v>230420000</v>
       </c>
       <c r="C154" t="n">
-        <v>1298.143</v>
+        <v>1322.621</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2490,10 +2490,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>245450000</v>
+        <v>186010000</v>
       </c>
       <c r="C155" t="n">
-        <v>1296.6727</v>
+        <v>1349.7838</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2501,10 +2501,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>388200000</v>
+        <v>324380030</v>
       </c>
       <c r="C156" t="n">
-        <v>1293.891</v>
+        <v>1353.8998</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2512,10 +2512,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>218250000</v>
+        <v>188250000</v>
       </c>
       <c r="C157" t="n">
-        <v>1299.0688</v>
+        <v>1360.0135</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2523,10 +2523,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>135000000</v>
+        <v>262170000</v>
       </c>
       <c r="C158" t="n">
-        <v>1311.6884</v>
+        <v>1338.8757</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2534,10 +2534,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>230420000</v>
+        <v>250290000</v>
       </c>
       <c r="C159" t="n">
-        <v>1322.621</v>
+        <v>1330.1678</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2545,10 +2545,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>186010000</v>
+        <v>396959970</v>
       </c>
       <c r="C160" t="n">
-        <v>1349.7838</v>
+        <v>1365.224</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2556,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>324380030</v>
+        <v>181300000</v>
       </c>
       <c r="C161" t="n">
-        <v>1353.8998</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2567,10 +2567,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>188250000</v>
+        <v>349490020</v>
       </c>
       <c r="C162" t="n">
-        <v>1360.0135</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2578,10 +2578,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>262170000</v>
+        <v>354610000</v>
       </c>
       <c r="C163" t="n">
-        <v>1338.8757</v>
+        <v>1366.1288</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2589,10 +2589,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>250290000</v>
+        <v>268370000</v>
       </c>
       <c r="C164" t="n">
-        <v>1330.1678</v>
+        <v>1424.0941</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2600,10 +2600,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>396959970</v>
+        <v>217230000</v>
       </c>
       <c r="C165" t="n">
-        <v>1365.224</v>
+        <v>1419.2301</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2611,10 +2611,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>181300000</v>
+        <v>202800000</v>
       </c>
       <c r="C166" t="n">
-        <v>1361.4104</v>
+        <v>1418.7997</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2622,10 +2622,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>349490020</v>
+        <v>182600000</v>
       </c>
       <c r="C167" t="n">
-        <v>1362.602</v>
+        <v>1428.8804</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2633,10 +2633,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>354610000</v>
+        <v>186830000</v>
       </c>
       <c r="C168" t="n">
-        <v>1366.1288</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2644,10 +2644,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>268370000</v>
+        <v>256060000</v>
       </c>
       <c r="C169" t="n">
-        <v>1424.0941</v>
+        <v>1463.845</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2655,10 +2655,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>217230000</v>
+        <v>181350000</v>
       </c>
       <c r="C170" t="n">
-        <v>1419.2301</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2666,10 +2666,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>202800000</v>
+        <v>175400000</v>
       </c>
       <c r="C171" t="n">
-        <v>1418.7997</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2677,10 +2677,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>182600000</v>
+        <v>231000000</v>
       </c>
       <c r="C172" t="n">
-        <v>1428.8804</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2688,10 +2688,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>186830000</v>
+        <v>286250020</v>
       </c>
       <c r="C173" t="n">
-        <v>1450.185</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2699,10 +2699,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>256060000</v>
+        <v>202930000</v>
       </c>
       <c r="C174" t="n">
-        <v>1463.845</v>
+        <v>1432.3635</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2710,10 +2710,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>181350000</v>
+        <v>275320000</v>
       </c>
       <c r="C175" t="n">
-        <v>1464.3728</v>
+        <v>1355.8541</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2721,10 +2721,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>175400000</v>
+        <v>480600000</v>
       </c>
       <c r="C176" t="n">
-        <v>1473.9847</v>
+        <v>1349.3301</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2732,10 +2732,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>231000000</v>
+        <v>589150000</v>
       </c>
       <c r="C177" t="n">
-        <v>1474.4945</v>
+        <v>1328.1084</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2743,10 +2743,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>286250020</v>
+        <v>392600000</v>
       </c>
       <c r="C178" t="n">
-        <v>1475.4567</v>
+        <v>1331.5554</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2754,10 +2754,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>202930000</v>
+        <v>478160000</v>
       </c>
       <c r="C179" t="n">
-        <v>1432.3635</v>
+        <v>1341.6771</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2765,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>275320000</v>
+        <v>496829980</v>
       </c>
       <c r="C180" t="n">
-        <v>1355.8541</v>
+        <v>1374.025</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2776,10 +2776,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>480600000</v>
+        <v>295170020</v>
       </c>
       <c r="C181" t="n">
-        <v>1349.3301</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2787,10 +2787,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>589150000</v>
+        <v>169440000</v>
       </c>
       <c r="C182" t="n">
-        <v>1328.1084</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2798,10 +2798,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>392600000</v>
+        <v>215520000</v>
       </c>
       <c r="C183" t="n">
-        <v>1331.5554</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2809,10 +2809,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>478160000</v>
+        <v>262840000</v>
       </c>
       <c r="C184" t="n">
-        <v>1341.6771</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2820,10 +2820,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>496829980</v>
+        <v>315000000</v>
       </c>
       <c r="C185" t="n">
-        <v>1374.025</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2831,10 +2831,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>295170020</v>
+        <v>338970020</v>
       </c>
       <c r="C186" t="n">
-        <v>1424.7794</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2842,10 +2842,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>169440000</v>
+        <v>260880000</v>
       </c>
       <c r="C187" t="n">
-        <v>1424.6221</v>
+        <v>1445.8451</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2853,10 +2853,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>215520000</v>
+        <v>346149980</v>
       </c>
       <c r="C188" t="n">
-        <v>1424.9015</v>
+        <v>1360.5026</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2864,10 +2864,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>262840000</v>
+        <v>431149980</v>
       </c>
       <c r="C189" t="n">
-        <v>1429.9982</v>
+        <v>1374.594</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2875,10 +2875,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>315000000</v>
+        <v>279500000</v>
       </c>
       <c r="C190" t="n">
-        <v>1430.0143</v>
+        <v>1391.4231</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2886,10 +2886,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>338970020</v>
+        <v>357400000</v>
       </c>
       <c r="C191" t="n">
-        <v>1430.0298</v>
+        <v>1451.0302</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2897,10 +2897,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>260880000</v>
+        <v>254070000</v>
       </c>
       <c r="C192" t="n">
-        <v>1445.8451</v>
+        <v>1468.6167</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2908,10 +2908,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>346149980</v>
+        <v>405740000</v>
       </c>
       <c r="C193" t="n">
-        <v>1360.5026</v>
+        <v>1487.8336</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2919,10 +2919,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>431149980</v>
+        <v>521350000</v>
       </c>
       <c r="C194" t="n">
-        <v>1374.594</v>
+        <v>1487.5168</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2930,10 +2930,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>279500000</v>
+        <v>393340030</v>
       </c>
       <c r="C195" t="n">
-        <v>1391.4231</v>
+        <v>1484.1284</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2941,10 +2941,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>357400000</v>
+        <v>423890020</v>
       </c>
       <c r="C196" t="n">
-        <v>1451.0302</v>
+        <v>1487.86</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2952,10 +2952,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>254070000</v>
+        <v>176000000</v>
       </c>
       <c r="C197" t="n">
-        <v>1468.6167</v>
+        <v>1399.3921</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2963,10 +2963,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>405740000</v>
+        <v>334980000</v>
       </c>
       <c r="C198" t="n">
-        <v>1487.8336</v>
+        <v>1470.8683</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2974,10 +2974,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>521350000</v>
+        <v>139200000</v>
       </c>
       <c r="C199" t="n">
-        <v>1487.5168</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2985,10 +2985,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>393340030</v>
+        <v>127040000</v>
       </c>
       <c r="C200" t="n">
-        <v>1484.1284</v>
+        <v>1434.8594</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2996,10 +2996,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>423890020</v>
+        <v>189260000</v>
       </c>
       <c r="C201" t="n">
-        <v>1487.86</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3007,10 +3007,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>176000000</v>
+        <v>275010000</v>
       </c>
       <c r="C202" t="n">
-        <v>1399.3921</v>
+        <v>1464.5646</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3018,10 +3018,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>334980000</v>
+        <v>194450000</v>
       </c>
       <c r="C203" t="n">
-        <v>1470.8683</v>
+        <v>1471.4487</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3029,10 +3029,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>139200000</v>
+        <v>196250000</v>
       </c>
       <c r="C204" t="n">
-        <v>1451.923</v>
+        <v>1447.6355</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3040,10 +3040,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>127040000</v>
+        <v>208000000</v>
       </c>
       <c r="C205" t="n">
-        <v>1434.8594</v>
+        <v>1434.8132</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3051,10 +3051,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>189260000</v>
+        <v>209360000</v>
       </c>
       <c r="C206" t="n">
-        <v>1445.9563</v>
+        <v>1420.3748</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3062,10 +3062,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>275010000</v>
+        <v>212720000</v>
       </c>
       <c r="C207" t="n">
-        <v>1464.5646</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3073,10 +3073,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>194450000</v>
+        <v>241830000</v>
       </c>
       <c r="C208" t="n">
-        <v>1471.4487</v>
+        <v>1407.8024</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3084,10 +3084,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>196250000</v>
+        <v>312580000</v>
       </c>
       <c r="C209" t="n">
-        <v>1447.6355</v>
+        <v>1404.9287</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3095,10 +3095,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>208000000</v>
+        <v>179500000</v>
       </c>
       <c r="C210" t="n">
-        <v>1434.8132</v>
+        <v>1401.7639</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3106,10 +3106,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>209360000</v>
+        <v>107500000</v>
       </c>
       <c r="C211" t="n">
-        <v>1420.3748</v>
+        <v>1392.025</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3117,10 +3117,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>212720000</v>
+        <v>242990000</v>
       </c>
       <c r="C212" t="n">
-        <v>1403.0524</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>241830000</v>
+        <v>254470000</v>
       </c>
       <c r="C213" t="n">
-        <v>1407.8024</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3139,10 +3139,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>312580000</v>
+        <v>331130000</v>
       </c>
       <c r="C214" t="n">
-        <v>1404.9287</v>
+        <v>1446.06</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3150,10 +3150,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>179500000</v>
+        <v>237200000</v>
       </c>
       <c r="C215" t="n">
-        <v>1401.7639</v>
+        <v>1450.5885</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3161,10 +3161,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>107500000</v>
+        <v>268310000</v>
       </c>
       <c r="C216" t="n">
-        <v>1392.025</v>
+        <v>1450.6201</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3172,10 +3172,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>242990000</v>
+        <v>293410020</v>
       </c>
       <c r="C217" t="n">
-        <v>1402.779</v>
+        <v>1449.9003</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3183,10 +3183,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>254470000</v>
+        <v>190400000</v>
       </c>
       <c r="C218" t="n">
-        <v>1418.6</v>
+        <v>1454.6627</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3194,10 +3194,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>331130000</v>
+        <v>147700000</v>
       </c>
       <c r="C219" t="n">
-        <v>1446.06</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3205,10 +3205,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>237200000</v>
+        <v>152560000</v>
       </c>
       <c r="C220" t="n">
-        <v>1450.5885</v>
+        <v>1447.5896</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>268310000</v>
+        <v>195400000</v>
       </c>
       <c r="C221" t="n">
-        <v>1450.6201</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3227,10 +3227,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>293410020</v>
+        <v>185680000</v>
       </c>
       <c r="C222" t="n">
-        <v>1449.9003</v>
+        <v>1439.3232</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3238,10 +3238,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>190400000</v>
+        <v>158700000</v>
       </c>
       <c r="C223" t="n">
-        <v>1454.6627</v>
+        <v>1438.0428</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3249,10 +3249,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>147700000</v>
+        <v>250300000</v>
       </c>
       <c r="C224" t="n">
-        <v>1453.8477</v>
+        <v>1437.9939</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3260,10 +3260,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>152560000</v>
+        <v>192580000</v>
       </c>
       <c r="C225" t="n">
-        <v>1447.5896</v>
+        <v>1439.1218</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3271,10 +3271,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>195400000</v>
+        <v>244040000</v>
       </c>
       <c r="C226" t="n">
-        <v>1440.0085</v>
+        <v>1440.4795</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3282,10 +3282,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>185680000</v>
+        <v>298200000</v>
       </c>
       <c r="C227" t="n">
-        <v>1439.3232</v>
+        <v>1452.0646</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3293,10 +3293,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>158700000</v>
+        <v>182310000</v>
       </c>
       <c r="C228" t="n">
-        <v>1438.0428</v>
+        <v>1449.3583</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3304,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>250300000</v>
+        <v>349300000</v>
       </c>
       <c r="C229" t="n">
-        <v>1437.9939</v>
+        <v>1453.4788</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3315,10 +3315,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>192580000</v>
+        <v>247100000</v>
       </c>
       <c r="C230" t="n">
-        <v>1439.1218</v>
+        <v>1452.151</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3326,10 +3326,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>244040000</v>
+        <v>245750000</v>
       </c>
       <c r="C231" t="n">
-        <v>1440.4795</v>
+        <v>1451.3027</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3337,10 +3337,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>298200000</v>
+        <v>335240030</v>
       </c>
       <c r="C232" t="n">
-        <v>1452.0646</v>
+        <v>1450.3435</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3348,10 +3348,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>253000000</v>
+        <v>100000000</v>
       </c>
       <c r="C233" t="n">
-        <v>1448.7827</v>
+        <v>1452.3898</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -25,12 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">26/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/12/2024 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">30/12/2024 12:00:00</t>
   </si>
   <si>
@@ -719,6 +713,9 @@
   </si>
   <si>
     <t xml:space="preserve">26/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/12/2025 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -783,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C233"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
@@ -807,10 +804,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>135210000</v>
+        <v>170650000</v>
       </c>
       <c r="C2" t="n">
-        <v>1028.5804</v>
+        <v>1030.4104</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -818,10 +815,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>214050000</v>
+        <v>129920000</v>
       </c>
       <c r="C3" t="n">
-        <v>1028.1958</v>
+        <v>1031.7577</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -829,10 +826,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>170650000</v>
+        <v>90600000</v>
       </c>
       <c r="C4" t="n">
-        <v>1030.4104</v>
+        <v>1032.4374</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -840,10 +837,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>129920000</v>
+        <v>94620000</v>
       </c>
       <c r="C5" t="n">
-        <v>1031.7577</v>
+        <v>1034.7297</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -851,10 +848,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>90600000</v>
+        <v>76740000</v>
       </c>
       <c r="C6" t="n">
-        <v>1032.4374</v>
+        <v>1035.4338</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -862,10 +859,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>94620000</v>
+        <v>60220000</v>
       </c>
       <c r="C7" t="n">
-        <v>1034.7297</v>
+        <v>1035.8505</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -873,10 +870,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>76740000</v>
+        <v>80100000</v>
       </c>
       <c r="C8" t="n">
-        <v>1035.4338</v>
+        <v>1036.7753</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -884,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>60220000</v>
+        <v>144200000</v>
       </c>
       <c r="C9" t="n">
-        <v>1035.8505</v>
+        <v>1036.8966</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -895,10 +892,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>80100000</v>
+        <v>66560000</v>
       </c>
       <c r="C10" t="n">
-        <v>1036.7753</v>
+        <v>1039.2858</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -906,10 +903,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>144200000</v>
+        <v>69770000</v>
       </c>
       <c r="C11" t="n">
-        <v>1036.8966</v>
+        <v>1040.3387</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -917,10 +914,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>66560000</v>
+        <v>59000000</v>
       </c>
       <c r="C12" t="n">
-        <v>1039.2858</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -928,10 +925,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>69770000</v>
+        <v>97600000</v>
       </c>
       <c r="C13" t="n">
-        <v>1040.3387</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -939,10 +936,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>59000000</v>
+        <v>139000000</v>
       </c>
       <c r="C14" t="n">
-        <v>1040.7654</v>
+        <v>1041.9989</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -950,10 +947,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>97600000</v>
+        <v>215030000</v>
       </c>
       <c r="C15" t="n">
-        <v>1041.2943</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -961,10 +958,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>139000000</v>
+        <v>117720000</v>
       </c>
       <c r="C16" t="n">
-        <v>1041.9989</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -972,10 +969,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>215030000</v>
+        <v>55800000</v>
       </c>
       <c r="C17" t="n">
-        <v>1045.5352</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -983,10 +980,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>117720000</v>
+        <v>135550000</v>
       </c>
       <c r="C18" t="n">
-        <v>1046.7697</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -994,10 +991,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>55800000</v>
+        <v>89000000</v>
       </c>
       <c r="C19" t="n">
-        <v>1046.9908</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1005,10 +1002,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>135550000</v>
+        <v>58100000</v>
       </c>
       <c r="C20" t="n">
-        <v>1046.9497</v>
+        <v>1050.2952</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1016,10 +1013,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>89000000</v>
+        <v>86600000</v>
       </c>
       <c r="C21" t="n">
-        <v>1049.7869</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1027,10 +1024,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>58100000</v>
+        <v>95150000</v>
       </c>
       <c r="C22" t="n">
-        <v>1050.2952</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1038,10 +1035,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>86600000</v>
+        <v>147140000</v>
       </c>
       <c r="C23" t="n">
-        <v>1051.1277</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1049,10 +1046,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>95150000</v>
+        <v>123760000</v>
       </c>
       <c r="C24" t="n">
-        <v>1051.69</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1060,10 +1057,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>147140000</v>
+        <v>88880000</v>
       </c>
       <c r="C25" t="n">
-        <v>1051.1226</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1071,10 +1068,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>123760000</v>
+        <v>115600000</v>
       </c>
       <c r="C26" t="n">
-        <v>1053.3625</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1082,10 +1079,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>88880000</v>
+        <v>93120000</v>
       </c>
       <c r="C27" t="n">
-        <v>1053.5273</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1093,10 +1090,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>115600000</v>
+        <v>162410000</v>
       </c>
       <c r="C28" t="n">
-        <v>1053.941</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1104,10 +1101,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>93120000</v>
+        <v>191440000</v>
       </c>
       <c r="C29" t="n">
-        <v>1054.1022</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1115,10 +1112,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>162410000</v>
+        <v>98800000</v>
       </c>
       <c r="C30" t="n">
-        <v>1053.6134</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1126,10 +1123,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>191440000</v>
+        <v>151830000</v>
       </c>
       <c r="C31" t="n">
-        <v>1055.6161</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1137,10 +1134,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>98800000</v>
+        <v>63730000</v>
       </c>
       <c r="C32" t="n">
-        <v>1055.6309</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1148,10 +1145,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>151830000</v>
+        <v>154380000</v>
       </c>
       <c r="C33" t="n">
-        <v>1056.2124</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1159,10 +1156,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>63730000</v>
+        <v>127430000</v>
       </c>
       <c r="C34" t="n">
-        <v>1056.7262</v>
+        <v>1058.3744</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1170,10 +1167,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>154380000</v>
+        <v>90150000</v>
       </c>
       <c r="C35" t="n">
-        <v>1056.4021</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1181,10 +1178,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>127430000</v>
+        <v>78400000</v>
       </c>
       <c r="C36" t="n">
-        <v>1058.3744</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1192,10 +1189,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>90150000</v>
+        <v>102390000</v>
       </c>
       <c r="C37" t="n">
-        <v>1058.5518</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1203,10 +1200,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>78400000</v>
+        <v>106130000</v>
       </c>
       <c r="C38" t="n">
-        <v>1059.0238</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1214,10 +1211,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>102390000</v>
+        <v>81520000</v>
       </c>
       <c r="C39" t="n">
-        <v>1058.5037</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1225,10 +1222,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>106130000</v>
+        <v>107290000</v>
       </c>
       <c r="C40" t="n">
-        <v>1060.2593</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1236,10 +1233,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>81520000</v>
+        <v>78500000</v>
       </c>
       <c r="C41" t="n">
-        <v>1060.7654</v>
+        <v>1061.6664</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1247,10 +1244,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>107290000</v>
+        <v>115700000</v>
       </c>
       <c r="C42" t="n">
-        <v>1061.1646</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1258,10 +1255,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>78500000</v>
+        <v>135350000</v>
       </c>
       <c r="C43" t="n">
-        <v>1061.6664</v>
+        <v>1063.415</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1269,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>115700000</v>
+        <v>156190000</v>
       </c>
       <c r="C44" t="n">
-        <v>1062.0686</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1280,10 +1277,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>135350000</v>
+        <v>203700000</v>
       </c>
       <c r="C45" t="n">
-        <v>1063.415</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1291,10 +1288,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>156190000</v>
+        <v>153120000</v>
       </c>
       <c r="C46" t="n">
-        <v>1063.8278</v>
+        <v>1065.541</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1302,10 +1299,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>203700000</v>
+        <v>154930000</v>
       </c>
       <c r="C47" t="n">
-        <v>1064.3394</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1313,10 +1310,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>153120000</v>
+        <v>101660000</v>
       </c>
       <c r="C48" t="n">
-        <v>1065.541</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1324,10 +1321,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>154930000</v>
+        <v>90000000</v>
       </c>
       <c r="C49" t="n">
-        <v>1065.7025</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1335,10 +1332,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>101660000</v>
+        <v>266600000</v>
       </c>
       <c r="C50" t="n">
-        <v>1066.0099</v>
+        <v>1066.7559</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1346,10 +1343,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>90000000</v>
+        <v>146970000</v>
       </c>
       <c r="C51" t="n">
-        <v>1066.2288</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1357,10 +1354,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>266600000</v>
+        <v>61200000</v>
       </c>
       <c r="C52" t="n">
-        <v>1066.7559</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1368,10 +1365,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>146970000</v>
+        <v>69170000</v>
       </c>
       <c r="C53" t="n">
-        <v>1068.2128</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1379,10 +1376,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>61200000</v>
+        <v>41240000</v>
       </c>
       <c r="C54" t="n">
-        <v>1068.3644</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1390,10 +1387,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>69170000</v>
+        <v>145230000</v>
       </c>
       <c r="C55" t="n">
-        <v>1069.0115</v>
+        <v>1068.306</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1401,10 +1398,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>41240000</v>
+        <v>120040000</v>
       </c>
       <c r="C56" t="n">
-        <v>1069.0428</v>
+        <v>1070.8301</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1412,10 +1409,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>145230000</v>
+        <v>105520000</v>
       </c>
       <c r="C57" t="n">
-        <v>1068.306</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1423,10 +1420,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>120040000</v>
+        <v>180350000</v>
       </c>
       <c r="C58" t="n">
-        <v>1070.8301</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1434,10 +1431,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>105520000</v>
+        <v>157240000</v>
       </c>
       <c r="C59" t="n">
-        <v>1071.3093</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1445,10 +1442,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>180350000</v>
+        <v>204650000</v>
       </c>
       <c r="C60" t="n">
-        <v>1071.5227</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1456,10 +1453,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>157240000</v>
+        <v>127150000</v>
       </c>
       <c r="C61" t="n">
-        <v>1070.9691</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1467,10 +1464,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>204650000</v>
+        <v>54310000</v>
       </c>
       <c r="C62" t="n">
-        <v>1073.0979</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1478,10 +1475,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>127150000</v>
+        <v>75470000</v>
       </c>
       <c r="C63" t="n">
-        <v>1072.918</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1489,10 +1486,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>54310000</v>
+        <v>79680000</v>
       </c>
       <c r="C64" t="n">
-        <v>1074.1038</v>
+        <v>1075.5189</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1500,10 +1497,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>75470000</v>
+        <v>62750000</v>
       </c>
       <c r="C65" t="n">
-        <v>1073.4634</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1511,10 +1508,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>79680000</v>
+        <v>75600000</v>
       </c>
       <c r="C66" t="n">
-        <v>1075.5189</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1522,10 +1519,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>62750000</v>
+        <v>63990000</v>
       </c>
       <c r="C67" t="n">
-        <v>1075.8248</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1533,10 +1530,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>75600000</v>
+        <v>225590000</v>
       </c>
       <c r="C68" t="n">
-        <v>1076.5104</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1544,10 +1541,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>63990000</v>
+        <v>415320000</v>
       </c>
       <c r="C69" t="n">
-        <v>1076.5854</v>
+        <v>1189.3408</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1555,10 +1552,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>225590000</v>
+        <v>230200000</v>
       </c>
       <c r="C70" t="n">
-        <v>1075.3297</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1566,10 +1563,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>415320000</v>
+        <v>347690000</v>
       </c>
       <c r="C71" t="n">
-        <v>1189.3408</v>
+        <v>1162.0289</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1577,10 +1574,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>230200000</v>
+        <v>339050000</v>
       </c>
       <c r="C72" t="n">
-        <v>1199.1798</v>
+        <v>1082.2896</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1588,10 +1585,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>347690000</v>
+        <v>335470000</v>
       </c>
       <c r="C73" t="n">
-        <v>1162.0289</v>
+        <v>1092.0658</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1599,10 +1596,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>339050000</v>
+        <v>410800000</v>
       </c>
       <c r="C74" t="n">
-        <v>1082.2896</v>
+        <v>1135.2954</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1610,10 +1607,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>335470000</v>
+        <v>530219970</v>
       </c>
       <c r="C75" t="n">
-        <v>1092.0658</v>
+        <v>1176.7036</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1621,10 +1618,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>410800000</v>
+        <v>368410020</v>
       </c>
       <c r="C76" t="n">
-        <v>1135.2954</v>
+        <v>1173.9578</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1632,10 +1629,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>530219970</v>
+        <v>359710000</v>
       </c>
       <c r="C77" t="n">
-        <v>1176.7036</v>
+        <v>1164.9523</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1643,10 +1640,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>368410020</v>
+        <v>327350000</v>
       </c>
       <c r="C78" t="n">
-        <v>1173.9578</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1654,10 +1651,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>359710000</v>
+        <v>451770000</v>
       </c>
       <c r="C79" t="n">
-        <v>1164.9523</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1665,10 +1662,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>327350000</v>
+        <v>373390000</v>
       </c>
       <c r="C80" t="n">
-        <v>1171.4315</v>
+        <v>1182.737</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1676,10 +1673,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>451770000</v>
+        <v>267550000</v>
       </c>
       <c r="C81" t="n">
-        <v>1169.5444</v>
+        <v>1201.8673</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1687,10 +1684,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>373390000</v>
+        <v>298740000</v>
       </c>
       <c r="C82" t="n">
-        <v>1182.737</v>
+        <v>1150.9767</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1698,10 +1695,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>267550000</v>
+        <v>263150000</v>
       </c>
       <c r="C83" t="n">
-        <v>1201.8673</v>
+        <v>1115.3778</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1709,10 +1706,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>298740000</v>
+        <v>200590000</v>
       </c>
       <c r="C84" t="n">
-        <v>1150.9767</v>
+        <v>1114.4697</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1720,10 +1717,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>263150000</v>
+        <v>279730000</v>
       </c>
       <c r="C85" t="n">
-        <v>1115.3778</v>
+        <v>1128.0413</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1731,10 +1728,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>200590000</v>
+        <v>395650020</v>
       </c>
       <c r="C86" t="n">
-        <v>1114.4697</v>
+        <v>1124.8636</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1742,10 +1739,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>279730000</v>
+        <v>331410020</v>
       </c>
       <c r="C87" t="n">
-        <v>1128.0413</v>
+        <v>1130.4976</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1753,10 +1750,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>395650020</v>
+        <v>261090000</v>
       </c>
       <c r="C88" t="n">
-        <v>1124.8636</v>
+        <v>1135.9226</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1764,10 +1761,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>331410020</v>
+        <v>242790000</v>
       </c>
       <c r="C89" t="n">
-        <v>1130.4976</v>
+        <v>1144.8372</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1775,10 +1772,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>261090000</v>
+        <v>193430000</v>
       </c>
       <c r="C90" t="n">
-        <v>1135.9226</v>
+        <v>1134.38</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1786,10 +1783,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>242790000</v>
+        <v>206570000</v>
       </c>
       <c r="C91" t="n">
-        <v>1144.8372</v>
+        <v>1143.0493</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1797,10 +1794,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>193430000</v>
+        <v>295490020</v>
       </c>
       <c r="C92" t="n">
-        <v>1134.38</v>
+        <v>1144.6212</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1808,10 +1805,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>206570000</v>
+        <v>241590000</v>
       </c>
       <c r="C93" t="n">
-        <v>1143.0493</v>
+        <v>1142.3527</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1819,10 +1816,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>295490020</v>
+        <v>315600000</v>
       </c>
       <c r="C94" t="n">
-        <v>1144.6212</v>
+        <v>1136.4631</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1830,10 +1827,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>241590000</v>
+        <v>322010000</v>
       </c>
       <c r="C95" t="n">
-        <v>1142.3527</v>
+        <v>1148.4313</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1841,10 +1838,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>315600000</v>
+        <v>274060000</v>
       </c>
       <c r="C96" t="n">
-        <v>1136.4631</v>
+        <v>1162.3182</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1852,10 +1849,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>322010000</v>
+        <v>201240000</v>
       </c>
       <c r="C97" t="n">
-        <v>1148.4313</v>
+        <v>1175.9083</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1863,10 +1860,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>274060000</v>
+        <v>200400000</v>
       </c>
       <c r="C98" t="n">
-        <v>1162.3182</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1874,10 +1871,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>201240000</v>
+        <v>219350000</v>
       </c>
       <c r="C99" t="n">
-        <v>1175.9083</v>
+        <v>1182.2898</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1885,10 +1882,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>200400000</v>
+        <v>191080000</v>
       </c>
       <c r="C100" t="n">
-        <v>1196.2443</v>
+        <v>1185.7532</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1896,10 +1893,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>219350000</v>
+        <v>279980000</v>
       </c>
       <c r="C101" t="n">
-        <v>1182.2898</v>
+        <v>1184.3556</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1907,10 +1904,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>191080000</v>
+        <v>210400000</v>
       </c>
       <c r="C102" t="n">
-        <v>1185.7532</v>
+        <v>1190.1663</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1918,10 +1915,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>279980000</v>
+        <v>149050000</v>
       </c>
       <c r="C103" t="n">
-        <v>1184.3556</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1929,10 +1926,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>210400000</v>
+        <v>206060000</v>
       </c>
       <c r="C104" t="n">
-        <v>1190.1663</v>
+        <v>1187.324</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1940,10 +1937,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>149050000</v>
+        <v>327800000</v>
       </c>
       <c r="C105" t="n">
-        <v>1189.0756</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1951,10 +1948,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>206060000</v>
+        <v>194900000</v>
       </c>
       <c r="C106" t="n">
-        <v>1187.324</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1962,10 +1959,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>327800000</v>
+        <v>150070000</v>
       </c>
       <c r="C107" t="n">
-        <v>1187.3528</v>
+        <v>1186.4066</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1973,10 +1970,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>194900000</v>
+        <v>249730000</v>
       </c>
       <c r="C108" t="n">
-        <v>1183.6859</v>
+        <v>1184.7783</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1984,10 +1981,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>150070000</v>
+        <v>328930000</v>
       </c>
       <c r="C109" t="n">
-        <v>1186.4066</v>
+        <v>1177.422</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1995,10 +1992,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>249730000</v>
+        <v>319130000</v>
       </c>
       <c r="C110" t="n">
-        <v>1184.7783</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2006,10 +2003,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>328930000</v>
+        <v>290900000</v>
       </c>
       <c r="C111" t="n">
-        <v>1177.422</v>
+        <v>1168.4946</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2017,10 +2014,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>319130000</v>
+        <v>272000000</v>
       </c>
       <c r="C112" t="n">
-        <v>1146.302</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2028,10 +2025,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>290900000</v>
+        <v>459869980</v>
       </c>
       <c r="C113" t="n">
-        <v>1168.4946</v>
+        <v>1176.7383</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2039,10 +2036,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>272000000</v>
+        <v>250980000</v>
       </c>
       <c r="C114" t="n">
-        <v>1178.1132</v>
+        <v>1192.3033</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2050,10 +2047,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>459869980</v>
+        <v>317930020</v>
       </c>
       <c r="C115" t="n">
-        <v>1176.7383</v>
+        <v>1187.0343</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2061,10 +2058,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>250980000</v>
+        <v>359550000</v>
       </c>
       <c r="C116" t="n">
-        <v>1192.3033</v>
+        <v>1193.3302</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2072,10 +2069,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>317930020</v>
+        <v>279650000</v>
       </c>
       <c r="C117" t="n">
-        <v>1187.0343</v>
+        <v>1207.8232</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2083,10 +2080,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>359550000</v>
+        <v>286200000</v>
       </c>
       <c r="C118" t="n">
-        <v>1193.3302</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2094,10 +2091,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>279650000</v>
+        <v>343900000</v>
       </c>
       <c r="C119" t="n">
-        <v>1207.8232</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2105,10 +2102,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>286200000</v>
+        <v>310469980</v>
       </c>
       <c r="C120" t="n">
-        <v>1232.3434</v>
+        <v>1263.1934</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2116,10 +2113,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>343900000</v>
+        <v>324740000</v>
       </c>
       <c r="C121" t="n">
-        <v>1225.9089</v>
+        <v>1257.3682</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2127,10 +2124,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>310469980</v>
+        <v>301200000</v>
       </c>
       <c r="C122" t="n">
-        <v>1263.1934</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2138,10 +2135,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>324740000</v>
+        <v>298320000</v>
       </c>
       <c r="C123" t="n">
-        <v>1257.3682</v>
+        <v>1261.3844</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2149,10 +2146,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>301200000</v>
+        <v>393980000</v>
       </c>
       <c r="C124" t="n">
-        <v>1261.2496</v>
+        <v>1268.4626</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2160,10 +2157,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>298320000</v>
+        <v>398920000</v>
       </c>
       <c r="C125" t="n">
-        <v>1261.3844</v>
+        <v>1277.0555</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2171,10 +2168,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>393980000</v>
+        <v>323589980</v>
       </c>
       <c r="C126" t="n">
-        <v>1268.4626</v>
+        <v>1257.8584</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2182,10 +2179,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>398920000</v>
+        <v>307460000</v>
       </c>
       <c r="C127" t="n">
-        <v>1277.0555</v>
+        <v>1266.7869</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2193,10 +2190,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>323589980</v>
+        <v>297000000</v>
       </c>
       <c r="C128" t="n">
-        <v>1257.8584</v>
+        <v>1282.9048</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2204,10 +2201,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>307460000</v>
+        <v>291500000</v>
       </c>
       <c r="C129" t="n">
-        <v>1266.7869</v>
+        <v>1287.3202</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2215,10 +2212,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>297000000</v>
+        <v>242700000</v>
       </c>
       <c r="C130" t="n">
-        <v>1282.9048</v>
+        <v>1261.1036</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2226,10 +2223,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>291500000</v>
+        <v>183370000</v>
       </c>
       <c r="C131" t="n">
-        <v>1287.3202</v>
+        <v>1259.6484</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2237,10 +2234,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>242700000</v>
+        <v>241900000</v>
       </c>
       <c r="C132" t="n">
-        <v>1261.1036</v>
+        <v>1261.8157</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2248,10 +2245,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>183370000</v>
+        <v>273740000</v>
       </c>
       <c r="C133" t="n">
-        <v>1259.6484</v>
+        <v>1278.3525</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2259,10 +2256,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>241900000</v>
+        <v>212100000</v>
       </c>
       <c r="C134" t="n">
-        <v>1261.8157</v>
+        <v>1290.4521</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2270,10 +2267,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>273740000</v>
+        <v>308300000</v>
       </c>
       <c r="C135" t="n">
-        <v>1278.3525</v>
+        <v>1295.2175</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2281,10 +2278,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>212100000</v>
+        <v>165990000</v>
       </c>
       <c r="C136" t="n">
-        <v>1290.4521</v>
+        <v>1297.3605</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2292,10 +2289,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>308300000</v>
+        <v>328600000</v>
       </c>
       <c r="C137" t="n">
-        <v>1295.2175</v>
+        <v>1357.0087</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2303,10 +2300,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>165990000</v>
+        <v>213740000</v>
       </c>
       <c r="C138" t="n">
-        <v>1297.3605</v>
+        <v>1364.9274</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2314,10 +2311,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>328600000</v>
+        <v>220980000</v>
       </c>
       <c r="C139" t="n">
-        <v>1357.0087</v>
+        <v>1362.0619</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2325,10 +2322,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>213740000</v>
+        <v>311760000</v>
       </c>
       <c r="C140" t="n">
-        <v>1364.9274</v>
+        <v>1348.57</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2336,10 +2333,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>220980000</v>
+        <v>324880000</v>
       </c>
       <c r="C141" t="n">
-        <v>1362.0619</v>
+        <v>1333.3085</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2347,10 +2344,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>311760000</v>
+        <v>194200000</v>
       </c>
       <c r="C142" t="n">
-        <v>1348.57</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2358,10 +2355,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>324880000</v>
+        <v>219200000</v>
       </c>
       <c r="C143" t="n">
-        <v>1333.3085</v>
+        <v>1324.7351</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2369,10 +2366,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>194200000</v>
+        <v>265100000</v>
       </c>
       <c r="C144" t="n">
-        <v>1329.5576</v>
+        <v>1327.6069</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2380,10 +2377,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>219200000</v>
+        <v>318140000</v>
       </c>
       <c r="C145" t="n">
-        <v>1324.7351</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2391,10 +2388,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>265100000</v>
+        <v>323640000</v>
       </c>
       <c r="C146" t="n">
-        <v>1327.6069</v>
+        <v>1317.75</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2402,10 +2399,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>318140000</v>
+        <v>258100000</v>
       </c>
       <c r="C147" t="n">
-        <v>1317.6909</v>
+        <v>1298.143</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2413,10 +2410,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>323640000</v>
+        <v>245450000</v>
       </c>
       <c r="C148" t="n">
-        <v>1317.75</v>
+        <v>1296.6727</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2424,10 +2421,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>258100000</v>
+        <v>388200000</v>
       </c>
       <c r="C149" t="n">
-        <v>1298.143</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2435,10 +2432,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>245450000</v>
+        <v>218250000</v>
       </c>
       <c r="C150" t="n">
-        <v>1296.6727</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2446,10 +2443,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>388200000</v>
+        <v>135000000</v>
       </c>
       <c r="C151" t="n">
-        <v>1293.891</v>
+        <v>1311.6884</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2457,10 +2454,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>218250000</v>
+        <v>230420000</v>
       </c>
       <c r="C152" t="n">
-        <v>1299.0688</v>
+        <v>1322.621</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2468,10 +2465,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>135000000</v>
+        <v>186010000</v>
       </c>
       <c r="C153" t="n">
-        <v>1311.6884</v>
+        <v>1349.7838</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2479,10 +2476,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>230420000</v>
+        <v>324380030</v>
       </c>
       <c r="C154" t="n">
-        <v>1322.621</v>
+        <v>1353.8998</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2490,10 +2487,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>186010000</v>
+        <v>188250000</v>
       </c>
       <c r="C155" t="n">
-        <v>1349.7838</v>
+        <v>1360.0135</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2501,10 +2498,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>324380030</v>
+        <v>262170000</v>
       </c>
       <c r="C156" t="n">
-        <v>1353.8998</v>
+        <v>1338.8757</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2512,10 +2509,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>188250000</v>
+        <v>250290000</v>
       </c>
       <c r="C157" t="n">
-        <v>1360.0135</v>
+        <v>1330.1678</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2523,10 +2520,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>262170000</v>
+        <v>396959970</v>
       </c>
       <c r="C158" t="n">
-        <v>1338.8757</v>
+        <v>1365.224</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2534,10 +2531,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>250290000</v>
+        <v>181300000</v>
       </c>
       <c r="C159" t="n">
-        <v>1330.1678</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2545,10 +2542,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>396959970</v>
+        <v>349490020</v>
       </c>
       <c r="C160" t="n">
-        <v>1365.224</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2556,10 +2553,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>181300000</v>
+        <v>354610000</v>
       </c>
       <c r="C161" t="n">
-        <v>1361.4104</v>
+        <v>1366.1288</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2567,10 +2564,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>349490020</v>
+        <v>268370000</v>
       </c>
       <c r="C162" t="n">
-        <v>1362.602</v>
+        <v>1424.0941</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2578,10 +2575,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>354610000</v>
+        <v>217230000</v>
       </c>
       <c r="C163" t="n">
-        <v>1366.1288</v>
+        <v>1419.2301</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2589,10 +2586,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>268370000</v>
+        <v>202800000</v>
       </c>
       <c r="C164" t="n">
-        <v>1424.0941</v>
+        <v>1418.7997</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2600,10 +2597,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>217230000</v>
+        <v>182600000</v>
       </c>
       <c r="C165" t="n">
-        <v>1419.2301</v>
+        <v>1428.8804</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2611,10 +2608,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>202800000</v>
+        <v>186830000</v>
       </c>
       <c r="C166" t="n">
-        <v>1418.7997</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2622,10 +2619,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>182600000</v>
+        <v>256060000</v>
       </c>
       <c r="C167" t="n">
-        <v>1428.8804</v>
+        <v>1463.845</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2633,10 +2630,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>186830000</v>
+        <v>181350000</v>
       </c>
       <c r="C168" t="n">
-        <v>1450.185</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2644,10 +2641,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>256060000</v>
+        <v>175400000</v>
       </c>
       <c r="C169" t="n">
-        <v>1463.845</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2655,10 +2652,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>181350000</v>
+        <v>231000000</v>
       </c>
       <c r="C170" t="n">
-        <v>1464.3728</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2666,10 +2663,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>175400000</v>
+        <v>286250020</v>
       </c>
       <c r="C171" t="n">
-        <v>1473.9847</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2677,10 +2674,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>231000000</v>
+        <v>202930000</v>
       </c>
       <c r="C172" t="n">
-        <v>1474.4945</v>
+        <v>1432.3635</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2688,10 +2685,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>286250020</v>
+        <v>275320000</v>
       </c>
       <c r="C173" t="n">
-        <v>1475.4567</v>
+        <v>1355.8541</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2699,10 +2696,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>202930000</v>
+        <v>480600000</v>
       </c>
       <c r="C174" t="n">
-        <v>1432.3635</v>
+        <v>1349.3301</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2710,10 +2707,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>275320000</v>
+        <v>589150000</v>
       </c>
       <c r="C175" t="n">
-        <v>1355.8541</v>
+        <v>1328.1084</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2721,10 +2718,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>480600000</v>
+        <v>392600000</v>
       </c>
       <c r="C176" t="n">
-        <v>1349.3301</v>
+        <v>1331.5554</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2732,10 +2729,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>589150000</v>
+        <v>478160000</v>
       </c>
       <c r="C177" t="n">
-        <v>1328.1084</v>
+        <v>1341.6771</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2743,10 +2740,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>392600000</v>
+        <v>496829980</v>
       </c>
       <c r="C178" t="n">
-        <v>1331.5554</v>
+        <v>1374.025</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2754,10 +2751,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>478160000</v>
+        <v>295170020</v>
       </c>
       <c r="C179" t="n">
-        <v>1341.6771</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2765,10 +2762,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>496829980</v>
+        <v>169440000</v>
       </c>
       <c r="C180" t="n">
-        <v>1374.025</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2776,10 +2773,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>295170020</v>
+        <v>215520000</v>
       </c>
       <c r="C181" t="n">
-        <v>1424.7794</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2787,10 +2784,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>169440000</v>
+        <v>262840000</v>
       </c>
       <c r="C182" t="n">
-        <v>1424.6221</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2798,10 +2795,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>215520000</v>
+        <v>315000000</v>
       </c>
       <c r="C183" t="n">
-        <v>1424.9015</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2809,10 +2806,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>262840000</v>
+        <v>338970020</v>
       </c>
       <c r="C184" t="n">
-        <v>1429.9982</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2820,10 +2817,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>315000000</v>
+        <v>260880000</v>
       </c>
       <c r="C185" t="n">
-        <v>1430.0143</v>
+        <v>1445.8451</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2831,10 +2828,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>338970020</v>
+        <v>346149980</v>
       </c>
       <c r="C186" t="n">
-        <v>1430.0298</v>
+        <v>1360.5026</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2842,10 +2839,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>260880000</v>
+        <v>431149980</v>
       </c>
       <c r="C187" t="n">
-        <v>1445.8451</v>
+        <v>1374.594</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2853,10 +2850,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>346149980</v>
+        <v>279500000</v>
       </c>
       <c r="C188" t="n">
-        <v>1360.5026</v>
+        <v>1391.4231</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2864,10 +2861,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>431149980</v>
+        <v>357400000</v>
       </c>
       <c r="C189" t="n">
-        <v>1374.594</v>
+        <v>1451.0302</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2875,10 +2872,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>279500000</v>
+        <v>254070000</v>
       </c>
       <c r="C190" t="n">
-        <v>1391.4231</v>
+        <v>1468.6167</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2886,10 +2883,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>357400000</v>
+        <v>405740000</v>
       </c>
       <c r="C191" t="n">
-        <v>1451.0302</v>
+        <v>1487.8336</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2897,10 +2894,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>254070000</v>
+        <v>521350000</v>
       </c>
       <c r="C192" t="n">
-        <v>1468.6167</v>
+        <v>1487.5168</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2908,10 +2905,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>405740000</v>
+        <v>393340030</v>
       </c>
       <c r="C193" t="n">
-        <v>1487.8336</v>
+        <v>1484.1284</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2919,10 +2916,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>521350000</v>
+        <v>423890020</v>
       </c>
       <c r="C194" t="n">
-        <v>1487.5168</v>
+        <v>1487.86</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2930,10 +2927,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>393340030</v>
+        <v>176000000</v>
       </c>
       <c r="C195" t="n">
-        <v>1484.1284</v>
+        <v>1399.3921</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2941,10 +2938,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>423890020</v>
+        <v>334980000</v>
       </c>
       <c r="C196" t="n">
-        <v>1487.86</v>
+        <v>1470.8683</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2952,10 +2949,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>176000000</v>
+        <v>139200000</v>
       </c>
       <c r="C197" t="n">
-        <v>1399.3921</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2963,10 +2960,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>334980000</v>
+        <v>127040000</v>
       </c>
       <c r="C198" t="n">
-        <v>1470.8683</v>
+        <v>1434.8594</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2974,10 +2971,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>139200000</v>
+        <v>189260000</v>
       </c>
       <c r="C199" t="n">
-        <v>1451.923</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2985,10 +2982,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>127040000</v>
+        <v>275010000</v>
       </c>
       <c r="C200" t="n">
-        <v>1434.8594</v>
+        <v>1464.5646</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2996,10 +2993,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>189260000</v>
+        <v>194450000</v>
       </c>
       <c r="C201" t="n">
-        <v>1445.9563</v>
+        <v>1471.4487</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3007,10 +3004,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>275010000</v>
+        <v>196250000</v>
       </c>
       <c r="C202" t="n">
-        <v>1464.5646</v>
+        <v>1447.6355</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3018,10 +3015,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>194450000</v>
+        <v>208000000</v>
       </c>
       <c r="C203" t="n">
-        <v>1471.4487</v>
+        <v>1434.8132</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3029,10 +3026,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>196250000</v>
+        <v>209360000</v>
       </c>
       <c r="C204" t="n">
-        <v>1447.6355</v>
+        <v>1420.3748</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3040,10 +3037,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>208000000</v>
+        <v>212720000</v>
       </c>
       <c r="C205" t="n">
-        <v>1434.8132</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3051,10 +3048,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>209360000</v>
+        <v>241830000</v>
       </c>
       <c r="C206" t="n">
-        <v>1420.3748</v>
+        <v>1407.8024</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3062,10 +3059,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>212720000</v>
+        <v>312580000</v>
       </c>
       <c r="C207" t="n">
-        <v>1403.0524</v>
+        <v>1404.9287</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3073,10 +3070,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>241830000</v>
+        <v>179500000</v>
       </c>
       <c r="C208" t="n">
-        <v>1407.8024</v>
+        <v>1401.7639</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3084,10 +3081,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>312580000</v>
+        <v>107500000</v>
       </c>
       <c r="C209" t="n">
-        <v>1404.9287</v>
+        <v>1392.025</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3095,10 +3092,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>179500000</v>
+        <v>242990000</v>
       </c>
       <c r="C210" t="n">
-        <v>1401.7639</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3106,10 +3103,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>107500000</v>
+        <v>254470000</v>
       </c>
       <c r="C211" t="n">
-        <v>1392.025</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3117,10 +3114,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>242990000</v>
+        <v>331130000</v>
       </c>
       <c r="C212" t="n">
-        <v>1402.779</v>
+        <v>1446.06</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3128,10 +3125,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>254470000</v>
+        <v>237200000</v>
       </c>
       <c r="C213" t="n">
-        <v>1418.6</v>
+        <v>1450.5885</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3139,10 +3136,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>331130000</v>
+        <v>268310000</v>
       </c>
       <c r="C214" t="n">
-        <v>1446.06</v>
+        <v>1450.6201</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3150,10 +3147,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>237200000</v>
+        <v>293410020</v>
       </c>
       <c r="C215" t="n">
-        <v>1450.5885</v>
+        <v>1449.9003</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3161,10 +3158,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>268310000</v>
+        <v>190400000</v>
       </c>
       <c r="C216" t="n">
-        <v>1450.6201</v>
+        <v>1454.6627</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3172,10 +3169,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>293410020</v>
+        <v>147700000</v>
       </c>
       <c r="C217" t="n">
-        <v>1449.9003</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3183,10 +3180,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>190400000</v>
+        <v>152560000</v>
       </c>
       <c r="C218" t="n">
-        <v>1454.6627</v>
+        <v>1447.5896</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3194,10 +3191,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>147700000</v>
+        <v>195400000</v>
       </c>
       <c r="C219" t="n">
-        <v>1453.8477</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3205,10 +3202,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>152560000</v>
+        <v>185680000</v>
       </c>
       <c r="C220" t="n">
-        <v>1447.5896</v>
+        <v>1439.3232</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3216,10 +3213,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>195400000</v>
+        <v>158700000</v>
       </c>
       <c r="C221" t="n">
-        <v>1440.0085</v>
+        <v>1438.0428</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3227,10 +3224,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>185680000</v>
+        <v>250300000</v>
       </c>
       <c r="C222" t="n">
-        <v>1439.3232</v>
+        <v>1437.9939</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3238,10 +3235,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>158700000</v>
+        <v>192580000</v>
       </c>
       <c r="C223" t="n">
-        <v>1438.0428</v>
+        <v>1439.1218</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3249,10 +3246,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>250300000</v>
+        <v>244040000</v>
       </c>
       <c r="C224" t="n">
-        <v>1437.9939</v>
+        <v>1440.4795</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3260,10 +3257,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>192580000</v>
+        <v>298200000</v>
       </c>
       <c r="C225" t="n">
-        <v>1439.1218</v>
+        <v>1452.0646</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3271,10 +3268,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>244040000</v>
+        <v>182310000</v>
       </c>
       <c r="C226" t="n">
-        <v>1440.4795</v>
+        <v>1449.3583</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3282,10 +3279,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>298200000</v>
+        <v>349300000</v>
       </c>
       <c r="C227" t="n">
-        <v>1452.0646</v>
+        <v>1453.4788</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3293,10 +3290,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>182310000</v>
+        <v>247100000</v>
       </c>
       <c r="C228" t="n">
-        <v>1449.3583</v>
+        <v>1452.151</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3304,10 +3301,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>349300000</v>
+        <v>245750000</v>
       </c>
       <c r="C229" t="n">
-        <v>1453.4788</v>
+        <v>1451.3027</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3315,10 +3312,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>247100000</v>
+        <v>335240030</v>
       </c>
       <c r="C230" t="n">
-        <v>1452.151</v>
+        <v>1450.3435</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3326,10 +3323,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>245750000</v>
+        <v>275000000</v>
       </c>
       <c r="C231" t="n">
-        <v>1451.3027</v>
+        <v>1451.9496</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3337,21 +3334,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>335240030</v>
+        <v>903739970</v>
       </c>
       <c r="C232" t="n">
-        <v>1450.3435</v>
-      </c>
-    </row>
-    <row r="233" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>234</v>
-      </c>
-      <c r="B233" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="C233" t="n">
-        <v>1452.3898</v>
+        <v>1455.7809</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -25,33 +25,6 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">30/12/2024 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/1/2025 12:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">14/1/2025 12:00:00</t>
   </si>
   <si>
@@ -716,6 +689,36 @@
   </si>
   <si>
     <t xml:space="preserve">29/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/12/2025 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/1/2026 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/1/2026 12:00:00</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C232"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
@@ -804,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>170650000</v>
+        <v>69770000</v>
       </c>
       <c r="C2" t="n">
-        <v>1030.4104</v>
+        <v>1040.3387</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -815,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>129920000</v>
+        <v>59000000</v>
       </c>
       <c r="C3" t="n">
-        <v>1031.7577</v>
+        <v>1040.7654</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -826,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>90600000</v>
+        <v>97600000</v>
       </c>
       <c r="C4" t="n">
-        <v>1032.4374</v>
+        <v>1041.2943</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -837,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>94620000</v>
+        <v>139000000</v>
       </c>
       <c r="C5" t="n">
-        <v>1034.7297</v>
+        <v>1041.9989</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -848,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>76740000</v>
+        <v>215030000</v>
       </c>
       <c r="C6" t="n">
-        <v>1035.4338</v>
+        <v>1045.5352</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -859,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>60220000</v>
+        <v>117720000</v>
       </c>
       <c r="C7" t="n">
-        <v>1035.8505</v>
+        <v>1046.7697</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -870,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>80100000</v>
+        <v>55800000</v>
       </c>
       <c r="C8" t="n">
-        <v>1036.7753</v>
+        <v>1046.9908</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -881,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>144200000</v>
+        <v>135550000</v>
       </c>
       <c r="C9" t="n">
-        <v>1036.8966</v>
+        <v>1046.9497</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -892,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>66560000</v>
+        <v>89000000</v>
       </c>
       <c r="C10" t="n">
-        <v>1039.2858</v>
+        <v>1049.7869</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -903,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>69770000</v>
+        <v>58100000</v>
       </c>
       <c r="C11" t="n">
-        <v>1040.3387</v>
+        <v>1050.2952</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -914,10 +917,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>59000000</v>
+        <v>86600000</v>
       </c>
       <c r="C12" t="n">
-        <v>1040.7654</v>
+        <v>1051.1277</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -925,10 +928,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>97600000</v>
+        <v>95150000</v>
       </c>
       <c r="C13" t="n">
-        <v>1041.2943</v>
+        <v>1051.69</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -936,10 +939,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>139000000</v>
+        <v>147140000</v>
       </c>
       <c r="C14" t="n">
-        <v>1041.9989</v>
+        <v>1051.1226</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -947,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>215030000</v>
+        <v>123760000</v>
       </c>
       <c r="C15" t="n">
-        <v>1045.5352</v>
+        <v>1053.3625</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -958,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>117720000</v>
+        <v>88880000</v>
       </c>
       <c r="C16" t="n">
-        <v>1046.7697</v>
+        <v>1053.5273</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -969,10 +972,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>55800000</v>
+        <v>115600000</v>
       </c>
       <c r="C17" t="n">
-        <v>1046.9908</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -980,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>135550000</v>
+        <v>93120000</v>
       </c>
       <c r="C18" t="n">
-        <v>1046.9497</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -991,10 +994,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>89000000</v>
+        <v>162410000</v>
       </c>
       <c r="C19" t="n">
-        <v>1049.7869</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1002,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>58100000</v>
+        <v>191440000</v>
       </c>
       <c r="C20" t="n">
-        <v>1050.2952</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1013,10 +1016,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>86600000</v>
+        <v>98800000</v>
       </c>
       <c r="C21" t="n">
-        <v>1051.1277</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1024,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>95150000</v>
+        <v>151830000</v>
       </c>
       <c r="C22" t="n">
-        <v>1051.69</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1035,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>147140000</v>
+        <v>63730000</v>
       </c>
       <c r="C23" t="n">
-        <v>1051.1226</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1046,10 +1049,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>123760000</v>
+        <v>154380000</v>
       </c>
       <c r="C24" t="n">
-        <v>1053.3625</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1057,10 +1060,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>88880000</v>
+        <v>127430000</v>
       </c>
       <c r="C25" t="n">
-        <v>1053.5273</v>
+        <v>1058.3744</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1068,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>115600000</v>
+        <v>90150000</v>
       </c>
       <c r="C26" t="n">
-        <v>1053.941</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1079,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>93120000</v>
+        <v>78400000</v>
       </c>
       <c r="C27" t="n">
-        <v>1054.1022</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1090,10 +1093,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>162410000</v>
+        <v>102390000</v>
       </c>
       <c r="C28" t="n">
-        <v>1053.6134</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1101,10 +1104,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>191440000</v>
+        <v>106130000</v>
       </c>
       <c r="C29" t="n">
-        <v>1055.6161</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1112,10 +1115,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>98800000</v>
+        <v>81520000</v>
       </c>
       <c r="C30" t="n">
-        <v>1055.6309</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1123,10 +1126,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>151830000</v>
+        <v>107290000</v>
       </c>
       <c r="C31" t="n">
-        <v>1056.2124</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1134,10 +1137,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>63730000</v>
+        <v>78500000</v>
       </c>
       <c r="C32" t="n">
-        <v>1056.7262</v>
+        <v>1061.6664</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1145,10 +1148,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>154380000</v>
+        <v>115700000</v>
       </c>
       <c r="C33" t="n">
-        <v>1056.4021</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1156,10 +1159,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>127430000</v>
+        <v>135350000</v>
       </c>
       <c r="C34" t="n">
-        <v>1058.3744</v>
+        <v>1063.415</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1167,10 +1170,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>90150000</v>
+        <v>156190000</v>
       </c>
       <c r="C35" t="n">
-        <v>1058.5518</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1178,10 +1181,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>78400000</v>
+        <v>203700000</v>
       </c>
       <c r="C36" t="n">
-        <v>1059.0238</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1189,10 +1192,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>102390000</v>
+        <v>153120000</v>
       </c>
       <c r="C37" t="n">
-        <v>1058.5037</v>
+        <v>1065.541</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1200,10 +1203,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>106130000</v>
+        <v>154930000</v>
       </c>
       <c r="C38" t="n">
-        <v>1060.2593</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1211,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>81520000</v>
+        <v>101660000</v>
       </c>
       <c r="C39" t="n">
-        <v>1060.7654</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1222,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>107290000</v>
+        <v>90000000</v>
       </c>
       <c r="C40" t="n">
-        <v>1061.1646</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1233,10 +1236,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>78500000</v>
+        <v>266600000</v>
       </c>
       <c r="C41" t="n">
-        <v>1061.6664</v>
+        <v>1066.7559</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1244,10 +1247,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>115700000</v>
+        <v>146970000</v>
       </c>
       <c r="C42" t="n">
-        <v>1062.0686</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1255,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>135350000</v>
+        <v>61200000</v>
       </c>
       <c r="C43" t="n">
-        <v>1063.415</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1266,10 +1269,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>156190000</v>
+        <v>69170000</v>
       </c>
       <c r="C44" t="n">
-        <v>1063.8278</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1277,10 +1280,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>203700000</v>
+        <v>41240000</v>
       </c>
       <c r="C45" t="n">
-        <v>1064.3394</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1288,10 +1291,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>153120000</v>
+        <v>145230000</v>
       </c>
       <c r="C46" t="n">
-        <v>1065.541</v>
+        <v>1068.306</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1299,10 +1302,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>154930000</v>
+        <v>120040000</v>
       </c>
       <c r="C47" t="n">
-        <v>1065.7025</v>
+        <v>1070.8301</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1310,10 +1313,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>101660000</v>
+        <v>105520000</v>
       </c>
       <c r="C48" t="n">
-        <v>1066.0099</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1321,10 +1324,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>90000000</v>
+        <v>180350000</v>
       </c>
       <c r="C49" t="n">
-        <v>1066.2288</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1332,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>266600000</v>
+        <v>157240000</v>
       </c>
       <c r="C50" t="n">
-        <v>1066.7559</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1343,10 +1346,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>146970000</v>
+        <v>204650000</v>
       </c>
       <c r="C51" t="n">
-        <v>1068.2128</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1354,10 +1357,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>61200000</v>
+        <v>127150000</v>
       </c>
       <c r="C52" t="n">
-        <v>1068.3644</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1365,10 +1368,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>69170000</v>
+        <v>54310000</v>
       </c>
       <c r="C53" t="n">
-        <v>1069.0115</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1376,10 +1379,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>41240000</v>
+        <v>75470000</v>
       </c>
       <c r="C54" t="n">
-        <v>1069.0428</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1387,10 +1390,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>145230000</v>
+        <v>79680000</v>
       </c>
       <c r="C55" t="n">
-        <v>1068.306</v>
+        <v>1075.5189</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1398,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>120040000</v>
+        <v>62750000</v>
       </c>
       <c r="C56" t="n">
-        <v>1070.8301</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1409,10 +1412,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>105520000</v>
+        <v>75600000</v>
       </c>
       <c r="C57" t="n">
-        <v>1071.3093</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1420,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>180350000</v>
+        <v>63990000</v>
       </c>
       <c r="C58" t="n">
-        <v>1071.5227</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1431,10 +1434,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>157240000</v>
+        <v>225590000</v>
       </c>
       <c r="C59" t="n">
-        <v>1070.9691</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1442,10 +1445,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>204650000</v>
+        <v>415320000</v>
       </c>
       <c r="C60" t="n">
-        <v>1073.0979</v>
+        <v>1189.3408</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1453,10 +1456,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>127150000</v>
+        <v>230200000</v>
       </c>
       <c r="C61" t="n">
-        <v>1072.918</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1464,10 +1467,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>54310000</v>
+        <v>347690000</v>
       </c>
       <c r="C62" t="n">
-        <v>1074.1038</v>
+        <v>1162.0289</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1475,10 +1478,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>75470000</v>
+        <v>339050000</v>
       </c>
       <c r="C63" t="n">
-        <v>1073.4634</v>
+        <v>1082.2896</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1486,10 +1489,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>79680000</v>
+        <v>335470000</v>
       </c>
       <c r="C64" t="n">
-        <v>1075.5189</v>
+        <v>1092.0658</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1497,10 +1500,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>62750000</v>
+        <v>410800000</v>
       </c>
       <c r="C65" t="n">
-        <v>1075.8248</v>
+        <v>1135.2954</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1508,10 +1511,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>75600000</v>
+        <v>530219970</v>
       </c>
       <c r="C66" t="n">
-        <v>1076.5104</v>
+        <v>1176.7036</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1519,10 +1522,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>63990000</v>
+        <v>368410020</v>
       </c>
       <c r="C67" t="n">
-        <v>1076.5854</v>
+        <v>1173.9578</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1530,10 +1533,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>225590000</v>
+        <v>359710000</v>
       </c>
       <c r="C68" t="n">
-        <v>1075.3297</v>
+        <v>1164.9523</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1541,10 +1544,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>415320000</v>
+        <v>327350000</v>
       </c>
       <c r="C69" t="n">
-        <v>1189.3408</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1552,10 +1555,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>230200000</v>
+        <v>451770000</v>
       </c>
       <c r="C70" t="n">
-        <v>1199.1798</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1563,10 +1566,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>347690000</v>
+        <v>373390000</v>
       </c>
       <c r="C71" t="n">
-        <v>1162.0289</v>
+        <v>1182.737</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1574,10 +1577,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>339050000</v>
+        <v>267550000</v>
       </c>
       <c r="C72" t="n">
-        <v>1082.2896</v>
+        <v>1201.8673</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1585,10 +1588,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>335470000</v>
+        <v>298740000</v>
       </c>
       <c r="C73" t="n">
-        <v>1092.0658</v>
+        <v>1150.9767</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1596,10 +1599,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>410800000</v>
+        <v>263150000</v>
       </c>
       <c r="C74" t="n">
-        <v>1135.2954</v>
+        <v>1115.3778</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1607,10 +1610,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>530219970</v>
+        <v>200590000</v>
       </c>
       <c r="C75" t="n">
-        <v>1176.7036</v>
+        <v>1114.4697</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1618,10 +1621,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>368410020</v>
+        <v>279730000</v>
       </c>
       <c r="C76" t="n">
-        <v>1173.9578</v>
+        <v>1128.0413</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1629,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>359710000</v>
+        <v>395650020</v>
       </c>
       <c r="C77" t="n">
-        <v>1164.9523</v>
+        <v>1124.8636</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1640,10 +1643,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>327350000</v>
+        <v>331410020</v>
       </c>
       <c r="C78" t="n">
-        <v>1171.4315</v>
+        <v>1130.4976</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1651,10 +1654,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>451770000</v>
+        <v>261090000</v>
       </c>
       <c r="C79" t="n">
-        <v>1169.5444</v>
+        <v>1135.9226</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1662,10 +1665,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>373390000</v>
+        <v>242790000</v>
       </c>
       <c r="C80" t="n">
-        <v>1182.737</v>
+        <v>1144.8372</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1673,10 +1676,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>267550000</v>
+        <v>193430000</v>
       </c>
       <c r="C81" t="n">
-        <v>1201.8673</v>
+        <v>1134.38</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1684,10 +1687,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>298740000</v>
+        <v>206570000</v>
       </c>
       <c r="C82" t="n">
-        <v>1150.9767</v>
+        <v>1143.0493</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1695,10 +1698,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>263150000</v>
+        <v>295490020</v>
       </c>
       <c r="C83" t="n">
-        <v>1115.3778</v>
+        <v>1144.6212</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1706,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>200590000</v>
+        <v>241590000</v>
       </c>
       <c r="C84" t="n">
-        <v>1114.4697</v>
+        <v>1142.3527</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1717,10 +1720,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>279730000</v>
+        <v>315600000</v>
       </c>
       <c r="C85" t="n">
-        <v>1128.0413</v>
+        <v>1136.4631</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1728,10 +1731,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>395650020</v>
+        <v>322010000</v>
       </c>
       <c r="C86" t="n">
-        <v>1124.8636</v>
+        <v>1148.4313</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1739,10 +1742,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>331410020</v>
+        <v>274060000</v>
       </c>
       <c r="C87" t="n">
-        <v>1130.4976</v>
+        <v>1162.3182</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1750,10 +1753,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>261090000</v>
+        <v>201240000</v>
       </c>
       <c r="C88" t="n">
-        <v>1135.9226</v>
+        <v>1175.9083</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1761,10 +1764,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>242790000</v>
+        <v>200400000</v>
       </c>
       <c r="C89" t="n">
-        <v>1144.8372</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1772,10 +1775,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>193430000</v>
+        <v>219350000</v>
       </c>
       <c r="C90" t="n">
-        <v>1134.38</v>
+        <v>1182.2898</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1783,10 +1786,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>206570000</v>
+        <v>191080000</v>
       </c>
       <c r="C91" t="n">
-        <v>1143.0493</v>
+        <v>1185.7532</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1794,10 +1797,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>295490020</v>
+        <v>279980000</v>
       </c>
       <c r="C92" t="n">
-        <v>1144.6212</v>
+        <v>1184.3556</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1805,10 +1808,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>241590000</v>
+        <v>210400000</v>
       </c>
       <c r="C93" t="n">
-        <v>1142.3527</v>
+        <v>1190.1663</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1816,10 +1819,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>315600000</v>
+        <v>149050000</v>
       </c>
       <c r="C94" t="n">
-        <v>1136.4631</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1827,10 +1830,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>322010000</v>
+        <v>206060000</v>
       </c>
       <c r="C95" t="n">
-        <v>1148.4313</v>
+        <v>1187.324</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1838,10 +1841,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>274060000</v>
+        <v>327800000</v>
       </c>
       <c r="C96" t="n">
-        <v>1162.3182</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1849,10 +1852,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>201240000</v>
+        <v>194900000</v>
       </c>
       <c r="C97" t="n">
-        <v>1175.9083</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1860,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>200400000</v>
+        <v>150070000</v>
       </c>
       <c r="C98" t="n">
-        <v>1196.2443</v>
+        <v>1186.4066</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1871,10 +1874,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>219350000</v>
+        <v>249730000</v>
       </c>
       <c r="C99" t="n">
-        <v>1182.2898</v>
+        <v>1184.7783</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1882,10 +1885,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>191080000</v>
+        <v>328930000</v>
       </c>
       <c r="C100" t="n">
-        <v>1185.7532</v>
+        <v>1177.422</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1893,10 +1896,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>279980000</v>
+        <v>319130000</v>
       </c>
       <c r="C101" t="n">
-        <v>1184.3556</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1904,10 +1907,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>210400000</v>
+        <v>290900000</v>
       </c>
       <c r="C102" t="n">
-        <v>1190.1663</v>
+        <v>1168.4946</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1915,10 +1918,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>149050000</v>
+        <v>272000000</v>
       </c>
       <c r="C103" t="n">
-        <v>1189.0756</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1926,10 +1929,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>206060000</v>
+        <v>459869980</v>
       </c>
       <c r="C104" t="n">
-        <v>1187.324</v>
+        <v>1176.7383</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1937,10 +1940,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>327800000</v>
+        <v>250980000</v>
       </c>
       <c r="C105" t="n">
-        <v>1187.3528</v>
+        <v>1192.3033</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1948,10 +1951,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>194900000</v>
+        <v>317930020</v>
       </c>
       <c r="C106" t="n">
-        <v>1183.6859</v>
+        <v>1187.0343</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1959,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>150070000</v>
+        <v>359550000</v>
       </c>
       <c r="C107" t="n">
-        <v>1186.4066</v>
+        <v>1193.3302</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1970,10 +1973,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>249730000</v>
+        <v>279650000</v>
       </c>
       <c r="C108" t="n">
-        <v>1184.7783</v>
+        <v>1207.8232</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1981,10 +1984,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>328930000</v>
+        <v>286200000</v>
       </c>
       <c r="C109" t="n">
-        <v>1177.422</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1992,10 +1995,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>319130000</v>
+        <v>343900000</v>
       </c>
       <c r="C110" t="n">
-        <v>1146.302</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2003,10 +2006,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>290900000</v>
+        <v>310469980</v>
       </c>
       <c r="C111" t="n">
-        <v>1168.4946</v>
+        <v>1263.1934</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2014,10 +2017,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>272000000</v>
+        <v>324740000</v>
       </c>
       <c r="C112" t="n">
-        <v>1178.1132</v>
+        <v>1257.3682</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2025,10 +2028,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>459869980</v>
+        <v>301200000</v>
       </c>
       <c r="C113" t="n">
-        <v>1176.7383</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2036,10 +2039,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>250980000</v>
+        <v>298320000</v>
       </c>
       <c r="C114" t="n">
-        <v>1192.3033</v>
+        <v>1261.3844</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2047,10 +2050,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>317930020</v>
+        <v>393980000</v>
       </c>
       <c r="C115" t="n">
-        <v>1187.0343</v>
+        <v>1268.4626</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2058,10 +2061,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>359550000</v>
+        <v>398920000</v>
       </c>
       <c r="C116" t="n">
-        <v>1193.3302</v>
+        <v>1277.0555</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2069,10 +2072,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>279650000</v>
+        <v>323589980</v>
       </c>
       <c r="C117" t="n">
-        <v>1207.8232</v>
+        <v>1257.8584</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2080,10 +2083,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>286200000</v>
+        <v>307460000</v>
       </c>
       <c r="C118" t="n">
-        <v>1232.3434</v>
+        <v>1266.7869</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2091,10 +2094,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>343900000</v>
+        <v>297000000</v>
       </c>
       <c r="C119" t="n">
-        <v>1225.9089</v>
+        <v>1282.9048</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2102,10 +2105,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>310469980</v>
+        <v>291500000</v>
       </c>
       <c r="C120" t="n">
-        <v>1263.1934</v>
+        <v>1287.3202</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2113,10 +2116,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>324740000</v>
+        <v>242700000</v>
       </c>
       <c r="C121" t="n">
-        <v>1257.3682</v>
+        <v>1261.1036</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2124,10 +2127,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>301200000</v>
+        <v>183370000</v>
       </c>
       <c r="C122" t="n">
-        <v>1261.2496</v>
+        <v>1259.6484</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2135,10 +2138,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>298320000</v>
+        <v>241900000</v>
       </c>
       <c r="C123" t="n">
-        <v>1261.3844</v>
+        <v>1261.8157</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2146,10 +2149,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>393980000</v>
+        <v>273740000</v>
       </c>
       <c r="C124" t="n">
-        <v>1268.4626</v>
+        <v>1278.3525</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2157,10 +2160,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>398920000</v>
+        <v>212100000</v>
       </c>
       <c r="C125" t="n">
-        <v>1277.0555</v>
+        <v>1290.4521</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2168,10 +2171,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>323589980</v>
+        <v>308300000</v>
       </c>
       <c r="C126" t="n">
-        <v>1257.8584</v>
+        <v>1295.2175</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2179,10 +2182,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>307460000</v>
+        <v>165990000</v>
       </c>
       <c r="C127" t="n">
-        <v>1266.7869</v>
+        <v>1297.3605</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2190,10 +2193,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>297000000</v>
+        <v>328600000</v>
       </c>
       <c r="C128" t="n">
-        <v>1282.9048</v>
+        <v>1357.0087</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2201,10 +2204,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>291500000</v>
+        <v>213740000</v>
       </c>
       <c r="C129" t="n">
-        <v>1287.3202</v>
+        <v>1364.9274</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2212,10 +2215,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>242700000</v>
+        <v>220980000</v>
       </c>
       <c r="C130" t="n">
-        <v>1261.1036</v>
+        <v>1362.0619</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2223,10 +2226,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>183370000</v>
+        <v>311760000</v>
       </c>
       <c r="C131" t="n">
-        <v>1259.6484</v>
+        <v>1348.57</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2234,10 +2237,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>241900000</v>
+        <v>324880000</v>
       </c>
       <c r="C132" t="n">
-        <v>1261.8157</v>
+        <v>1333.3085</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2245,10 +2248,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>273740000</v>
+        <v>194200000</v>
       </c>
       <c r="C133" t="n">
-        <v>1278.3525</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2256,10 +2259,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>212100000</v>
+        <v>219200000</v>
       </c>
       <c r="C134" t="n">
-        <v>1290.4521</v>
+        <v>1324.7351</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2267,10 +2270,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>308300000</v>
+        <v>265100000</v>
       </c>
       <c r="C135" t="n">
-        <v>1295.2175</v>
+        <v>1327.6069</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2278,10 +2281,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>165990000</v>
+        <v>318140000</v>
       </c>
       <c r="C136" t="n">
-        <v>1297.3605</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2289,10 +2292,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>328600000</v>
+        <v>323640000</v>
       </c>
       <c r="C137" t="n">
-        <v>1357.0087</v>
+        <v>1317.75</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2300,10 +2303,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>213740000</v>
+        <v>258100000</v>
       </c>
       <c r="C138" t="n">
-        <v>1364.9274</v>
+        <v>1298.143</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2311,10 +2314,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>220980000</v>
+        <v>245450000</v>
       </c>
       <c r="C139" t="n">
-        <v>1362.0619</v>
+        <v>1296.6727</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2322,10 +2325,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>311760000</v>
+        <v>388200000</v>
       </c>
       <c r="C140" t="n">
-        <v>1348.57</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2333,10 +2336,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>324880000</v>
+        <v>218250000</v>
       </c>
       <c r="C141" t="n">
-        <v>1333.3085</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2344,10 +2347,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>194200000</v>
+        <v>135000000</v>
       </c>
       <c r="C142" t="n">
-        <v>1329.5576</v>
+        <v>1311.6884</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2355,10 +2358,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>219200000</v>
+        <v>230420000</v>
       </c>
       <c r="C143" t="n">
-        <v>1324.7351</v>
+        <v>1322.621</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2366,10 +2369,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>265100000</v>
+        <v>186010000</v>
       </c>
       <c r="C144" t="n">
-        <v>1327.6069</v>
+        <v>1349.7838</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2377,10 +2380,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>318140000</v>
+        <v>324380030</v>
       </c>
       <c r="C145" t="n">
-        <v>1317.6909</v>
+        <v>1353.8998</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2388,10 +2391,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>323640000</v>
+        <v>188250000</v>
       </c>
       <c r="C146" t="n">
-        <v>1317.75</v>
+        <v>1360.0135</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2399,10 +2402,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>258100000</v>
+        <v>262170000</v>
       </c>
       <c r="C147" t="n">
-        <v>1298.143</v>
+        <v>1338.8757</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2410,10 +2413,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>245450000</v>
+        <v>250290000</v>
       </c>
       <c r="C148" t="n">
-        <v>1296.6727</v>
+        <v>1330.1678</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2421,10 +2424,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>388200000</v>
+        <v>396959970</v>
       </c>
       <c r="C149" t="n">
-        <v>1293.891</v>
+        <v>1365.224</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2432,10 +2435,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>218250000</v>
+        <v>181300000</v>
       </c>
       <c r="C150" t="n">
-        <v>1299.0688</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2443,10 +2446,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>135000000</v>
+        <v>349490020</v>
       </c>
       <c r="C151" t="n">
-        <v>1311.6884</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2454,10 +2457,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>230420000</v>
+        <v>354610000</v>
       </c>
       <c r="C152" t="n">
-        <v>1322.621</v>
+        <v>1366.1288</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2465,10 +2468,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>186010000</v>
+        <v>268370000</v>
       </c>
       <c r="C153" t="n">
-        <v>1349.7838</v>
+        <v>1424.0941</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2476,10 +2479,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>324380030</v>
+        <v>217230000</v>
       </c>
       <c r="C154" t="n">
-        <v>1353.8998</v>
+        <v>1419.2301</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2487,10 +2490,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>188250000</v>
+        <v>202800000</v>
       </c>
       <c r="C155" t="n">
-        <v>1360.0135</v>
+        <v>1418.7997</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2498,10 +2501,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>262170000</v>
+        <v>182600000</v>
       </c>
       <c r="C156" t="n">
-        <v>1338.8757</v>
+        <v>1428.8804</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2509,10 +2512,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>250290000</v>
+        <v>186830000</v>
       </c>
       <c r="C157" t="n">
-        <v>1330.1678</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2520,10 +2523,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>396959970</v>
+        <v>256060000</v>
       </c>
       <c r="C158" t="n">
-        <v>1365.224</v>
+        <v>1463.845</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2531,10 +2534,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>181300000</v>
+        <v>181350000</v>
       </c>
       <c r="C159" t="n">
-        <v>1361.4104</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2542,10 +2545,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>349490020</v>
+        <v>175400000</v>
       </c>
       <c r="C160" t="n">
-        <v>1362.602</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2553,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>354610000</v>
+        <v>231000000</v>
       </c>
       <c r="C161" t="n">
-        <v>1366.1288</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2564,10 +2567,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>268370000</v>
+        <v>286250020</v>
       </c>
       <c r="C162" t="n">
-        <v>1424.0941</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2575,10 +2578,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>217230000</v>
+        <v>202930000</v>
       </c>
       <c r="C163" t="n">
-        <v>1419.2301</v>
+        <v>1432.3635</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2586,10 +2589,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>202800000</v>
+        <v>275320000</v>
       </c>
       <c r="C164" t="n">
-        <v>1418.7997</v>
+        <v>1355.8541</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2597,10 +2600,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>182600000</v>
+        <v>480600000</v>
       </c>
       <c r="C165" t="n">
-        <v>1428.8804</v>
+        <v>1349.3301</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2608,10 +2611,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>186830000</v>
+        <v>589150000</v>
       </c>
       <c r="C166" t="n">
-        <v>1450.185</v>
+        <v>1328.1084</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2619,10 +2622,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>256060000</v>
+        <v>392600000</v>
       </c>
       <c r="C167" t="n">
-        <v>1463.845</v>
+        <v>1331.5554</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2630,10 +2633,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>181350000</v>
+        <v>478160000</v>
       </c>
       <c r="C168" t="n">
-        <v>1464.3728</v>
+        <v>1341.6771</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2641,10 +2644,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>175400000</v>
+        <v>496829980</v>
       </c>
       <c r="C169" t="n">
-        <v>1473.9847</v>
+        <v>1374.025</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2652,10 +2655,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>231000000</v>
+        <v>295170020</v>
       </c>
       <c r="C170" t="n">
-        <v>1474.4945</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2663,10 +2666,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>286250020</v>
+        <v>169440000</v>
       </c>
       <c r="C171" t="n">
-        <v>1475.4567</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2674,10 +2677,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>202930000</v>
+        <v>215520000</v>
       </c>
       <c r="C172" t="n">
-        <v>1432.3635</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2685,10 +2688,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>275320000</v>
+        <v>262840000</v>
       </c>
       <c r="C173" t="n">
-        <v>1355.8541</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2696,10 +2699,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>480600000</v>
+        <v>315000000</v>
       </c>
       <c r="C174" t="n">
-        <v>1349.3301</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2707,10 +2710,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>589150000</v>
+        <v>338970020</v>
       </c>
       <c r="C175" t="n">
-        <v>1328.1084</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2718,10 +2721,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>392600000</v>
+        <v>260880000</v>
       </c>
       <c r="C176" t="n">
-        <v>1331.5554</v>
+        <v>1445.8451</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2729,10 +2732,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>478160000</v>
+        <v>346149980</v>
       </c>
       <c r="C177" t="n">
-        <v>1341.6771</v>
+        <v>1360.5026</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2740,10 +2743,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>496829980</v>
+        <v>431149980</v>
       </c>
       <c r="C178" t="n">
-        <v>1374.025</v>
+        <v>1374.594</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2751,10 +2754,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>295170020</v>
+        <v>279500000</v>
       </c>
       <c r="C179" t="n">
-        <v>1424.7794</v>
+        <v>1391.4231</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2762,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>169440000</v>
+        <v>357400000</v>
       </c>
       <c r="C180" t="n">
-        <v>1424.6221</v>
+        <v>1451.0302</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2773,10 +2776,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>215520000</v>
+        <v>254070000</v>
       </c>
       <c r="C181" t="n">
-        <v>1424.9015</v>
+        <v>1468.6167</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2784,10 +2787,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>262840000</v>
+        <v>405740000</v>
       </c>
       <c r="C182" t="n">
-        <v>1429.9982</v>
+        <v>1487.8336</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2795,10 +2798,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>315000000</v>
+        <v>521350000</v>
       </c>
       <c r="C183" t="n">
-        <v>1430.0143</v>
+        <v>1487.5168</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2806,10 +2809,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>338970020</v>
+        <v>393340030</v>
       </c>
       <c r="C184" t="n">
-        <v>1430.0298</v>
+        <v>1484.1284</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2817,10 +2820,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>260880000</v>
+        <v>423890020</v>
       </c>
       <c r="C185" t="n">
-        <v>1445.8451</v>
+        <v>1487.86</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2828,10 +2831,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>346149980</v>
+        <v>176000000</v>
       </c>
       <c r="C186" t="n">
-        <v>1360.5026</v>
+        <v>1399.3921</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2839,10 +2842,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>431149980</v>
+        <v>334980000</v>
       </c>
       <c r="C187" t="n">
-        <v>1374.594</v>
+        <v>1470.8683</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2850,10 +2853,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>279500000</v>
+        <v>139200000</v>
       </c>
       <c r="C188" t="n">
-        <v>1391.4231</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2861,10 +2864,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>357400000</v>
+        <v>127040000</v>
       </c>
       <c r="C189" t="n">
-        <v>1451.0302</v>
+        <v>1434.8594</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2872,10 +2875,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>254070000</v>
+        <v>189260000</v>
       </c>
       <c r="C190" t="n">
-        <v>1468.6167</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2883,10 +2886,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>405740000</v>
+        <v>275010000</v>
       </c>
       <c r="C191" t="n">
-        <v>1487.8336</v>
+        <v>1464.5646</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2894,10 +2897,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>521350000</v>
+        <v>194450000</v>
       </c>
       <c r="C192" t="n">
-        <v>1487.5168</v>
+        <v>1471.4487</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2905,10 +2908,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>393340030</v>
+        <v>196250000</v>
       </c>
       <c r="C193" t="n">
-        <v>1484.1284</v>
+        <v>1447.6355</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2916,10 +2919,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>423890020</v>
+        <v>208000000</v>
       </c>
       <c r="C194" t="n">
-        <v>1487.86</v>
+        <v>1434.8132</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2927,10 +2930,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>176000000</v>
+        <v>209360000</v>
       </c>
       <c r="C195" t="n">
-        <v>1399.3921</v>
+        <v>1420.3748</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2938,10 +2941,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>334980000</v>
+        <v>212720000</v>
       </c>
       <c r="C196" t="n">
-        <v>1470.8683</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2949,10 +2952,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>139200000</v>
+        <v>241830000</v>
       </c>
       <c r="C197" t="n">
-        <v>1451.923</v>
+        <v>1407.8024</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2960,10 +2963,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>127040000</v>
+        <v>312580000</v>
       </c>
       <c r="C198" t="n">
-        <v>1434.8594</v>
+        <v>1404.9287</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2971,10 +2974,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>189260000</v>
+        <v>179500000</v>
       </c>
       <c r="C199" t="n">
-        <v>1445.9563</v>
+        <v>1401.7639</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2982,10 +2985,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>275010000</v>
+        <v>107500000</v>
       </c>
       <c r="C200" t="n">
-        <v>1464.5646</v>
+        <v>1392.025</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2993,10 +2996,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>194450000</v>
+        <v>242990000</v>
       </c>
       <c r="C201" t="n">
-        <v>1471.4487</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3004,10 +3007,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>196250000</v>
+        <v>254470000</v>
       </c>
       <c r="C202" t="n">
-        <v>1447.6355</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3015,10 +3018,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>208000000</v>
+        <v>331130000</v>
       </c>
       <c r="C203" t="n">
-        <v>1434.8132</v>
+        <v>1446.06</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3026,10 +3029,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>209360000</v>
+        <v>237200000</v>
       </c>
       <c r="C204" t="n">
-        <v>1420.3748</v>
+        <v>1450.5885</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3037,10 +3040,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>212720000</v>
+        <v>268310000</v>
       </c>
       <c r="C205" t="n">
-        <v>1403.0524</v>
+        <v>1450.6201</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3048,10 +3051,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>241830000</v>
+        <v>293410020</v>
       </c>
       <c r="C206" t="n">
-        <v>1407.8024</v>
+        <v>1449.9003</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3059,10 +3062,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>312580000</v>
+        <v>190400000</v>
       </c>
       <c r="C207" t="n">
-        <v>1404.9287</v>
+        <v>1454.6627</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3070,10 +3073,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>179500000</v>
+        <v>147700000</v>
       </c>
       <c r="C208" t="n">
-        <v>1401.7639</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3081,10 +3084,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>107500000</v>
+        <v>152560000</v>
       </c>
       <c r="C209" t="n">
-        <v>1392.025</v>
+        <v>1447.5896</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3092,10 +3095,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>242990000</v>
+        <v>195400000</v>
       </c>
       <c r="C210" t="n">
-        <v>1402.779</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3103,10 +3106,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>254470000</v>
+        <v>185680000</v>
       </c>
       <c r="C211" t="n">
-        <v>1418.6</v>
+        <v>1439.3232</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3114,10 +3117,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>331130000</v>
+        <v>158700000</v>
       </c>
       <c r="C212" t="n">
-        <v>1446.06</v>
+        <v>1438.0428</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3125,10 +3128,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>237200000</v>
+        <v>250300000</v>
       </c>
       <c r="C213" t="n">
-        <v>1450.5885</v>
+        <v>1437.9939</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3136,10 +3139,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>268310000</v>
+        <v>192580000</v>
       </c>
       <c r="C214" t="n">
-        <v>1450.6201</v>
+        <v>1439.1218</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3147,10 +3150,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>293410020</v>
+        <v>244040000</v>
       </c>
       <c r="C215" t="n">
-        <v>1449.9003</v>
+        <v>1440.4795</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3158,10 +3161,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>190400000</v>
+        <v>298200000</v>
       </c>
       <c r="C216" t="n">
-        <v>1454.6627</v>
+        <v>1452.0646</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3169,10 +3172,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>147700000</v>
+        <v>182310000</v>
       </c>
       <c r="C217" t="n">
-        <v>1453.8477</v>
+        <v>1449.3583</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3180,10 +3183,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>152560000</v>
+        <v>349300000</v>
       </c>
       <c r="C218" t="n">
-        <v>1447.5896</v>
+        <v>1453.4788</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3191,10 +3194,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>195400000</v>
+        <v>247100000</v>
       </c>
       <c r="C219" t="n">
-        <v>1440.0085</v>
+        <v>1452.151</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3202,10 +3205,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>185680000</v>
+        <v>245750000</v>
       </c>
       <c r="C220" t="n">
-        <v>1439.3232</v>
+        <v>1451.3027</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3213,10 +3216,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>158700000</v>
+        <v>335240030</v>
       </c>
       <c r="C221" t="n">
-        <v>1438.0428</v>
+        <v>1450.3435</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3224,10 +3227,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>250300000</v>
+        <v>275000000</v>
       </c>
       <c r="C222" t="n">
-        <v>1437.9939</v>
+        <v>1451.9496</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3235,10 +3238,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>192580000</v>
+        <v>451869980</v>
       </c>
       <c r="C223" t="n">
-        <v>1439.1218</v>
+        <v>1455.7809</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3246,10 +3249,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>244040000</v>
+        <v>216460000</v>
       </c>
       <c r="C224" t="n">
-        <v>1440.4795</v>
+        <v>1459.2133</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3257,10 +3260,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>298200000</v>
+        <v>257600000</v>
       </c>
       <c r="C225" t="n">
-        <v>1452.0646</v>
+        <v>1469.6405</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3268,10 +3271,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>182310000</v>
+        <v>188200000</v>
       </c>
       <c r="C226" t="n">
-        <v>1449.3583</v>
+        <v>1473.0568</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3279,10 +3282,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>349300000</v>
+        <v>130800000</v>
       </c>
       <c r="C227" t="n">
-        <v>1453.4788</v>
+        <v>1467.733</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3290,10 +3293,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>247100000</v>
+        <v>156300000</v>
       </c>
       <c r="C228" t="n">
-        <v>1452.151</v>
+        <v>1466.4419</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3301,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>245750000</v>
+        <v>222610000</v>
       </c>
       <c r="C229" t="n">
-        <v>1451.3027</v>
+        <v>1459.4448</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3312,10 +3315,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>335240030</v>
+        <v>225200000</v>
       </c>
       <c r="C230" t="n">
-        <v>1450.3435</v>
+        <v>1466.5925</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3323,10 +3326,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>275000000</v>
+        <v>120370000</v>
       </c>
       <c r="C231" t="n">
-        <v>1451.9496</v>
+        <v>1466.7234</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3334,10 +3337,21 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>903739970</v>
+        <v>280909980</v>
       </c>
       <c r="C232" t="n">
-        <v>1455.7809</v>
+        <v>1463.5974</v>
+      </c>
+    </row>
+    <row r="233" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>234</v>
+      </c>
+      <c r="B233" t="n">
+        <v>305240000</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1454.3422</v>
       </c>
     </row>
   </sheetData>

--- a/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
+++ b/UST$T  (USA TRANSF A PESOS TRANSF) (8).xlsx
@@ -25,700 +25,700 @@
     <t xml:space="preserve">Precio</t>
   </si>
   <si>
-    <t xml:space="preserve">14/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/1/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/2/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/3/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/4/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/5/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/6/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/7/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/8/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/9/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/10/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/11/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/12/2025 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/1/2026 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/1/2026 12:00:00</t>
+    <t xml:space="preserve">4/2/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/2/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/2/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/2/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/3/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/3/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/3/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/3/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/4/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/4/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/4/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/4/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/4/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/5/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/5/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/5/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/5/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/5/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/6/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/6/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/6/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/6/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/6/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/6/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/6/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/7/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/7/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/7/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/7/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/7/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/8/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/8/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/8/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/8/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/8/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/9/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/9/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/9/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/9/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/9/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/9/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/9/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/9/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/1/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/1/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/1/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/1/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/1/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/1/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/2/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/2/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/2/2026 </t>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
   <dimension ref="A1:C233"/>
   <sheetFormatPr x14ac:dyDescent="0.25" customHeight="1" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="19.714285714285715" bestFit="1"/>
+    <col min="1" max="1" customWidth="1" width="10.714285714285714" bestFit="1"/>
     <col min="2" max="2" customWidth="1" width="9.714285714285714" bestFit="1"/>
     <col min="3" max="3" customWidth="1" width="9.714285714285714" bestFit="1"/>
   </cols>
@@ -807,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>69770000</v>
+        <v>115600000</v>
       </c>
       <c r="C2" t="n">
-        <v>1040.3387</v>
+        <v>1053.941</v>
       </c>
     </row>
     <row r="3" x14ac:dyDescent="0.25">
@@ -818,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>59000000</v>
+        <v>93120000</v>
       </c>
       <c r="C3" t="n">
-        <v>1040.7654</v>
+        <v>1054.1022</v>
       </c>
     </row>
     <row r="4" x14ac:dyDescent="0.25">
@@ -829,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>97600000</v>
+        <v>162410000</v>
       </c>
       <c r="C4" t="n">
-        <v>1041.2943</v>
+        <v>1053.6134</v>
       </c>
     </row>
     <row r="5" x14ac:dyDescent="0.25">
@@ -840,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>139000000</v>
+        <v>191440000</v>
       </c>
       <c r="C5" t="n">
-        <v>1041.9989</v>
+        <v>1055.6161</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>215030000</v>
+        <v>98800000</v>
       </c>
       <c r="C6" t="n">
-        <v>1045.5352</v>
+        <v>1055.6309</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.25">
@@ -862,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>117720000</v>
+        <v>151830000</v>
       </c>
       <c r="C7" t="n">
-        <v>1046.7697</v>
+        <v>1056.2124</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>55800000</v>
+        <v>63730000</v>
       </c>
       <c r="C8" t="n">
-        <v>1046.9908</v>
+        <v>1056.7262</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.25">
@@ -884,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>135550000</v>
+        <v>154380000</v>
       </c>
       <c r="C9" t="n">
-        <v>1046.9497</v>
+        <v>1056.4021</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.25">
@@ -895,10 +895,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>89000000</v>
+        <v>127430000</v>
       </c>
       <c r="C10" t="n">
-        <v>1049.7869</v>
+        <v>1058.3744</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25">
@@ -906,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>58100000</v>
+        <v>90150000</v>
       </c>
       <c r="C11" t="n">
-        <v>1050.2952</v>
+        <v>1058.5518</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25">
@@ -917,10 +917,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>86600000</v>
+        <v>78400000</v>
       </c>
       <c r="C12" t="n">
-        <v>1051.1277</v>
+        <v>1059.0238</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25">
@@ -928,10 +928,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>95150000</v>
+        <v>102390000</v>
       </c>
       <c r="C13" t="n">
-        <v>1051.69</v>
+        <v>1058.5037</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25">
@@ -939,10 +939,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>147140000</v>
+        <v>106130000</v>
       </c>
       <c r="C14" t="n">
-        <v>1051.1226</v>
+        <v>1060.2593</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25">
@@ -950,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>123760000</v>
+        <v>81520000</v>
       </c>
       <c r="C15" t="n">
-        <v>1053.3625</v>
+        <v>1060.7654</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25">
@@ -961,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>88880000</v>
+        <v>107290000</v>
       </c>
       <c r="C16" t="n">
-        <v>1053.5273</v>
+        <v>1061.1646</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25">
@@ -972,10 +972,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>115600000</v>
+        <v>78500000</v>
       </c>
       <c r="C17" t="n">
-        <v>1053.941</v>
+        <v>1061.6664</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
@@ -983,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>93120000</v>
+        <v>115700000</v>
       </c>
       <c r="C18" t="n">
-        <v>1054.1022</v>
+        <v>1062.0686</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25">
@@ -994,10 +994,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>162410000</v>
+        <v>135350000</v>
       </c>
       <c r="C19" t="n">
-        <v>1053.6134</v>
+        <v>1063.415</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
@@ -1005,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>191440000</v>
+        <v>156190000</v>
       </c>
       <c r="C20" t="n">
-        <v>1055.6161</v>
+        <v>1063.8278</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25">
@@ -1016,10 +1016,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>98800000</v>
+        <v>203700000</v>
       </c>
       <c r="C21" t="n">
-        <v>1055.6309</v>
+        <v>1064.3394</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25">
@@ -1027,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>151830000</v>
+        <v>153120000</v>
       </c>
       <c r="C22" t="n">
-        <v>1056.2124</v>
+        <v>1065.541</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25">
@@ -1038,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>63730000</v>
+        <v>154930000</v>
       </c>
       <c r="C23" t="n">
-        <v>1056.7262</v>
+        <v>1065.7025</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25">
@@ -1049,10 +1049,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>154380000</v>
+        <v>101660000</v>
       </c>
       <c r="C24" t="n">
-        <v>1056.4021</v>
+        <v>1066.0099</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25">
@@ -1060,10 +1060,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>127430000</v>
+        <v>90000000</v>
       </c>
       <c r="C25" t="n">
-        <v>1058.3744</v>
+        <v>1066.2288</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25">
@@ -1071,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>90150000</v>
+        <v>266600000</v>
       </c>
       <c r="C26" t="n">
-        <v>1058.5518</v>
+        <v>1066.7559</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
@@ -1082,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>78400000</v>
+        <v>146970000</v>
       </c>
       <c r="C27" t="n">
-        <v>1059.0238</v>
+        <v>1068.2128</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25">
@@ -1093,10 +1093,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>102390000</v>
+        <v>61200000</v>
       </c>
       <c r="C28" t="n">
-        <v>1058.5037</v>
+        <v>1068.3644</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
@@ -1104,10 +1104,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>106130000</v>
+        <v>69170000</v>
       </c>
       <c r="C29" t="n">
-        <v>1060.2593</v>
+        <v>1069.0115</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25">
@@ -1115,10 +1115,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>81520000</v>
+        <v>41240000</v>
       </c>
       <c r="C30" t="n">
-        <v>1060.7654</v>
+        <v>1069.0428</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25">
@@ -1126,10 +1126,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>107290000</v>
+        <v>145230000</v>
       </c>
       <c r="C31" t="n">
-        <v>1061.1646</v>
+        <v>1068.306</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>78500000</v>
+        <v>120040000</v>
       </c>
       <c r="C32" t="n">
-        <v>1061.6664</v>
+        <v>1070.8301</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
@@ -1148,10 +1148,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>115700000</v>
+        <v>105520000</v>
       </c>
       <c r="C33" t="n">
-        <v>1062.0686</v>
+        <v>1071.3093</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>135350000</v>
+        <v>180350000</v>
       </c>
       <c r="C34" t="n">
-        <v>1063.415</v>
+        <v>1071.5227</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
@@ -1170,10 +1170,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>156190000</v>
+        <v>157240000</v>
       </c>
       <c r="C35" t="n">
-        <v>1063.8278</v>
+        <v>1070.9691</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
@@ -1181,10 +1181,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>203700000</v>
+        <v>204650000</v>
       </c>
       <c r="C36" t="n">
-        <v>1064.3394</v>
+        <v>1073.0979</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
@@ -1192,10 +1192,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>153120000</v>
+        <v>127150000</v>
       </c>
       <c r="C37" t="n">
-        <v>1065.541</v>
+        <v>1072.918</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25">
@@ -1203,10 +1203,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>154930000</v>
+        <v>54310000</v>
       </c>
       <c r="C38" t="n">
-        <v>1065.7025</v>
+        <v>1074.1038</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
@@ -1214,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>101660000</v>
+        <v>75470000</v>
       </c>
       <c r="C39" t="n">
-        <v>1066.0099</v>
+        <v>1073.4634</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25">
@@ -1225,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>90000000</v>
+        <v>79680000</v>
       </c>
       <c r="C40" t="n">
-        <v>1066.2288</v>
+        <v>1075.5189</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25">
@@ -1236,10 +1236,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>266600000</v>
+        <v>62750000</v>
       </c>
       <c r="C41" t="n">
-        <v>1066.7559</v>
+        <v>1075.8248</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25">
@@ -1247,10 +1247,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>146970000</v>
+        <v>75600000</v>
       </c>
       <c r="C42" t="n">
-        <v>1068.2128</v>
+        <v>1076.5104</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25">
@@ -1258,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>61200000</v>
+        <v>63990000</v>
       </c>
       <c r="C43" t="n">
-        <v>1068.3644</v>
+        <v>1076.5854</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25">
@@ -1269,10 +1269,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>69170000</v>
+        <v>225590000</v>
       </c>
       <c r="C44" t="n">
-        <v>1069.0115</v>
+        <v>1075.3297</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25">
@@ -1280,10 +1280,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>41240000</v>
+        <v>415320000</v>
       </c>
       <c r="C45" t="n">
-        <v>1069.0428</v>
+        <v>1189.3408</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25">
@@ -1291,10 +1291,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>145230000</v>
+        <v>230200000</v>
       </c>
       <c r="C46" t="n">
-        <v>1068.306</v>
+        <v>1199.1798</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25">
@@ -1302,10 +1302,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>120040000</v>
+        <v>347690000</v>
       </c>
       <c r="C47" t="n">
-        <v>1070.8301</v>
+        <v>1162.0289</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25">
@@ -1313,10 +1313,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>105520000</v>
+        <v>339050000</v>
       </c>
       <c r="C48" t="n">
-        <v>1071.3093</v>
+        <v>1082.2896</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25">
@@ -1324,10 +1324,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>180350000</v>
+        <v>335470000</v>
       </c>
       <c r="C49" t="n">
-        <v>1071.5227</v>
+        <v>1092.0658</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25">
@@ -1335,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>157240000</v>
+        <v>410800000</v>
       </c>
       <c r="C50" t="n">
-        <v>1070.9691</v>
+        <v>1135.2954</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25">
@@ -1346,10 +1346,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>204650000</v>
+        <v>530219970</v>
       </c>
       <c r="C51" t="n">
-        <v>1073.0979</v>
+        <v>1176.7036</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25">
@@ -1357,10 +1357,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>127150000</v>
+        <v>368410020</v>
       </c>
       <c r="C52" t="n">
-        <v>1072.918</v>
+        <v>1173.9578</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>54310000</v>
+        <v>359710000</v>
       </c>
       <c r="C53" t="n">
-        <v>1074.1038</v>
+        <v>1164.9523</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25">
@@ -1379,10 +1379,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>75470000</v>
+        <v>327350000</v>
       </c>
       <c r="C54" t="n">
-        <v>1073.4634</v>
+        <v>1171.4315</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25">
@@ -1390,10 +1390,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>79680000</v>
+        <v>451770000</v>
       </c>
       <c r="C55" t="n">
-        <v>1075.5189</v>
+        <v>1169.5444</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.25">
@@ -1401,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>62750000</v>
+        <v>373390000</v>
       </c>
       <c r="C56" t="n">
-        <v>1075.8248</v>
+        <v>1182.737</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.25">
@@ -1412,10 +1412,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>75600000</v>
+        <v>267550000</v>
       </c>
       <c r="C57" t="n">
-        <v>1076.5104</v>
+        <v>1201.8673</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.25">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>63990000</v>
+        <v>298740000</v>
       </c>
       <c r="C58" t="n">
-        <v>1076.5854</v>
+        <v>1150.9767</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.25">
@@ -1434,10 +1434,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>225590000</v>
+        <v>263150000</v>
       </c>
       <c r="C59" t="n">
-        <v>1075.3297</v>
+        <v>1115.3778</v>
       </c>
     </row>
     <row r="60" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>415320000</v>
+        <v>200590000</v>
       </c>
       <c r="C60" t="n">
-        <v>1189.3408</v>
+        <v>1114.4697</v>
       </c>
     </row>
     <row r="61" x14ac:dyDescent="0.25">
@@ -1456,10 +1456,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>230200000</v>
+        <v>279730000</v>
       </c>
       <c r="C61" t="n">
-        <v>1199.1798</v>
+        <v>1128.0413</v>
       </c>
     </row>
     <row r="62" x14ac:dyDescent="0.25">
@@ -1467,10 +1467,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>347690000</v>
+        <v>395650020</v>
       </c>
       <c r="C62" t="n">
-        <v>1162.0289</v>
+        <v>1124.8636</v>
       </c>
     </row>
     <row r="63" x14ac:dyDescent="0.25">
@@ -1478,10 +1478,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>339050000</v>
+        <v>331410020</v>
       </c>
       <c r="C63" t="n">
-        <v>1082.2896</v>
+        <v>1130.4976</v>
       </c>
     </row>
     <row r="64" x14ac:dyDescent="0.25">
@@ -1489,10 +1489,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>335470000</v>
+        <v>261090000</v>
       </c>
       <c r="C64" t="n">
-        <v>1092.0658</v>
+        <v>1135.9226</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25">
@@ -1500,10 +1500,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>410800000</v>
+        <v>242790000</v>
       </c>
       <c r="C65" t="n">
-        <v>1135.2954</v>
+        <v>1144.8372</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25">
@@ -1511,10 +1511,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>530219970</v>
+        <v>193430000</v>
       </c>
       <c r="C66" t="n">
-        <v>1176.7036</v>
+        <v>1134.38</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25">
@@ -1522,10 +1522,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>368410020</v>
+        <v>206570000</v>
       </c>
       <c r="C67" t="n">
-        <v>1173.9578</v>
+        <v>1143.0493</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25">
@@ -1533,10 +1533,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>359710000</v>
+        <v>295490020</v>
       </c>
       <c r="C68" t="n">
-        <v>1164.9523</v>
+        <v>1144.6212</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25">
@@ -1544,10 +1544,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>327350000</v>
+        <v>241590000</v>
       </c>
       <c r="C69" t="n">
-        <v>1171.4315</v>
+        <v>1142.3527</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25">
@@ -1555,10 +1555,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>451770000</v>
+        <v>315600000</v>
       </c>
       <c r="C70" t="n">
-        <v>1169.5444</v>
+        <v>1136.4631</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25">
@@ -1566,10 +1566,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>373390000</v>
+        <v>322010000</v>
       </c>
       <c r="C71" t="n">
-        <v>1182.737</v>
+        <v>1148.4313</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25">
@@ -1577,10 +1577,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>267550000</v>
+        <v>274060000</v>
       </c>
       <c r="C72" t="n">
-        <v>1201.8673</v>
+        <v>1162.3182</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25">
@@ -1588,10 +1588,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>298740000</v>
+        <v>201240000</v>
       </c>
       <c r="C73" t="n">
-        <v>1150.9767</v>
+        <v>1175.9083</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25">
@@ -1599,10 +1599,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>263150000</v>
+        <v>200400000</v>
       </c>
       <c r="C74" t="n">
-        <v>1115.3778</v>
+        <v>1196.2443</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25">
@@ -1610,10 +1610,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>200590000</v>
+        <v>219350000</v>
       </c>
       <c r="C75" t="n">
-        <v>1114.4697</v>
+        <v>1182.2898</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25">
@@ -1621,10 +1621,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>279730000</v>
+        <v>191080000</v>
       </c>
       <c r="C76" t="n">
-        <v>1128.0413</v>
+        <v>1185.7532</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25">
@@ -1632,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>395650020</v>
+        <v>279980000</v>
       </c>
       <c r="C77" t="n">
-        <v>1124.8636</v>
+        <v>1184.3556</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25">
@@ -1643,10 +1643,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>331410020</v>
+        <v>210400000</v>
       </c>
       <c r="C78" t="n">
-        <v>1130.4976</v>
+        <v>1190.1663</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25">
@@ -1654,10 +1654,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>261090000</v>
+        <v>149050000</v>
       </c>
       <c r="C79" t="n">
-        <v>1135.9226</v>
+        <v>1189.0756</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25">
@@ -1665,10 +1665,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>242790000</v>
+        <v>206060000</v>
       </c>
       <c r="C80" t="n">
-        <v>1144.8372</v>
+        <v>1187.324</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25">
@@ -1676,10 +1676,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>193430000</v>
+        <v>327800000</v>
       </c>
       <c r="C81" t="n">
-        <v>1134.38</v>
+        <v>1187.3528</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25">
@@ -1687,10 +1687,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>206570000</v>
+        <v>194900000</v>
       </c>
       <c r="C82" t="n">
-        <v>1143.0493</v>
+        <v>1183.6859</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25">
@@ -1698,10 +1698,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>295490020</v>
+        <v>150070000</v>
       </c>
       <c r="C83" t="n">
-        <v>1144.6212</v>
+        <v>1186.4066</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25">
@@ -1709,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>241590000</v>
+        <v>249730000</v>
       </c>
       <c r="C84" t="n">
-        <v>1142.3527</v>
+        <v>1184.7783</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25">
@@ -1720,10 +1720,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>315600000</v>
+        <v>328930000</v>
       </c>
       <c r="C85" t="n">
-        <v>1136.4631</v>
+        <v>1177.422</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25">
@@ -1731,10 +1731,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>322010000</v>
+        <v>319130000</v>
       </c>
       <c r="C86" t="n">
-        <v>1148.4313</v>
+        <v>1146.302</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25">
@@ -1742,10 +1742,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>274060000</v>
+        <v>290900000</v>
       </c>
       <c r="C87" t="n">
-        <v>1162.3182</v>
+        <v>1168.4946</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25">
@@ -1753,10 +1753,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>201240000</v>
+        <v>272000000</v>
       </c>
       <c r="C88" t="n">
-        <v>1175.9083</v>
+        <v>1178.1132</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25">
@@ -1764,10 +1764,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>200400000</v>
+        <v>459869980</v>
       </c>
       <c r="C89" t="n">
-        <v>1196.2443</v>
+        <v>1176.7383</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25">
@@ -1775,10 +1775,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>219350000</v>
+        <v>250980000</v>
       </c>
       <c r="C90" t="n">
-        <v>1182.2898</v>
+        <v>1192.3033</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25">
@@ -1786,10 +1786,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>191080000</v>
+        <v>317930020</v>
       </c>
       <c r="C91" t="n">
-        <v>1185.7532</v>
+        <v>1187.0343</v>
       </c>
     </row>
     <row r="92" x14ac:dyDescent="0.25">
@@ -1797,10 +1797,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>279980000</v>
+        <v>359550000</v>
       </c>
       <c r="C92" t="n">
-        <v>1184.3556</v>
+        <v>1193.3302</v>
       </c>
     </row>
     <row r="93" x14ac:dyDescent="0.25">
@@ -1808,10 +1808,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>210400000</v>
+        <v>279650000</v>
       </c>
       <c r="C93" t="n">
-        <v>1190.1663</v>
+        <v>1207.8232</v>
       </c>
     </row>
     <row r="94" x14ac:dyDescent="0.25">
@@ -1819,10 +1819,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>149050000</v>
+        <v>286200000</v>
       </c>
       <c r="C94" t="n">
-        <v>1189.0756</v>
+        <v>1232.3434</v>
       </c>
     </row>
     <row r="95" x14ac:dyDescent="0.25">
@@ -1830,10 +1830,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>206060000</v>
+        <v>343900000</v>
       </c>
       <c r="C95" t="n">
-        <v>1187.324</v>
+        <v>1225.9089</v>
       </c>
     </row>
     <row r="96" x14ac:dyDescent="0.25">
@@ -1841,10 +1841,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>327800000</v>
+        <v>310469980</v>
       </c>
       <c r="C96" t="n">
-        <v>1187.3528</v>
+        <v>1263.1934</v>
       </c>
     </row>
     <row r="97" x14ac:dyDescent="0.25">
@@ -1852,10 +1852,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>194900000</v>
+        <v>324740000</v>
       </c>
       <c r="C97" t="n">
-        <v>1183.6859</v>
+        <v>1257.3682</v>
       </c>
     </row>
     <row r="98" x14ac:dyDescent="0.25">
@@ -1863,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>150070000</v>
+        <v>301200000</v>
       </c>
       <c r="C98" t="n">
-        <v>1186.4066</v>
+        <v>1261.2496</v>
       </c>
     </row>
     <row r="99" x14ac:dyDescent="0.25">
@@ -1874,10 +1874,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>249730000</v>
+        <v>298320000</v>
       </c>
       <c r="C99" t="n">
-        <v>1184.7783</v>
+        <v>1261.3844</v>
       </c>
     </row>
     <row r="100" x14ac:dyDescent="0.25">
@@ -1885,10 +1885,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>328930000</v>
+        <v>393980000</v>
       </c>
       <c r="C100" t="n">
-        <v>1177.422</v>
+        <v>1268.4626</v>
       </c>
     </row>
     <row r="101" x14ac:dyDescent="0.25">
@@ -1896,10 +1896,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>319130000</v>
+        <v>398920000</v>
       </c>
       <c r="C101" t="n">
-        <v>1146.302</v>
+        <v>1277.0555</v>
       </c>
     </row>
     <row r="102" x14ac:dyDescent="0.25">
@@ -1907,10 +1907,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>290900000</v>
+        <v>323589980</v>
       </c>
       <c r="C102" t="n">
-        <v>1168.4946</v>
+        <v>1257.8584</v>
       </c>
     </row>
     <row r="103" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>272000000</v>
+        <v>307460000</v>
       </c>
       <c r="C103" t="n">
-        <v>1178.1132</v>
+        <v>1266.7869</v>
       </c>
     </row>
     <row r="104" x14ac:dyDescent="0.25">
@@ -1929,10 +1929,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>459869980</v>
+        <v>297000000</v>
       </c>
       <c r="C104" t="n">
-        <v>1176.7383</v>
+        <v>1282.9048</v>
       </c>
     </row>
     <row r="105" x14ac:dyDescent="0.25">
@@ -1940,10 +1940,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>250980000</v>
+        <v>291500000</v>
       </c>
       <c r="C105" t="n">
-        <v>1192.3033</v>
+        <v>1287.3202</v>
       </c>
     </row>
     <row r="106" x14ac:dyDescent="0.25">
@@ -1951,10 +1951,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>317930020</v>
+        <v>242700000</v>
       </c>
       <c r="C106" t="n">
-        <v>1187.0343</v>
+        <v>1261.1036</v>
       </c>
     </row>
     <row r="107" x14ac:dyDescent="0.25">
@@ -1962,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>359550000</v>
+        <v>183370000</v>
       </c>
       <c r="C107" t="n">
-        <v>1193.3302</v>
+        <v>1259.6484</v>
       </c>
     </row>
     <row r="108" x14ac:dyDescent="0.25">
@@ -1973,10 +1973,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>279650000</v>
+        <v>241900000</v>
       </c>
       <c r="C108" t="n">
-        <v>1207.8232</v>
+        <v>1261.8157</v>
       </c>
     </row>
     <row r="109" x14ac:dyDescent="0.25">
@@ -1984,10 +1984,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>286200000</v>
+        <v>273740000</v>
       </c>
       <c r="C109" t="n">
-        <v>1232.3434</v>
+        <v>1278.3525</v>
       </c>
     </row>
     <row r="110" x14ac:dyDescent="0.25">
@@ -1995,10 +1995,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>343900000</v>
+        <v>212100000</v>
       </c>
       <c r="C110" t="n">
-        <v>1225.9089</v>
+        <v>1290.4521</v>
       </c>
     </row>
     <row r="111" x14ac:dyDescent="0.25">
@@ -2006,10 +2006,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>310469980</v>
+        <v>308300000</v>
       </c>
       <c r="C111" t="n">
-        <v>1263.1934</v>
+        <v>1295.2175</v>
       </c>
     </row>
     <row r="112" x14ac:dyDescent="0.25">
@@ -2017,10 +2017,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>324740000</v>
+        <v>165990000</v>
       </c>
       <c r="C112" t="n">
-        <v>1257.3682</v>
+        <v>1297.3605</v>
       </c>
     </row>
     <row r="113" x14ac:dyDescent="0.25">
@@ -2028,10 +2028,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>301200000</v>
+        <v>328600000</v>
       </c>
       <c r="C113" t="n">
-        <v>1261.2496</v>
+        <v>1357.0087</v>
       </c>
     </row>
     <row r="114" x14ac:dyDescent="0.25">
@@ -2039,10 +2039,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>298320000</v>
+        <v>213740000</v>
       </c>
       <c r="C114" t="n">
-        <v>1261.3844</v>
+        <v>1364.9274</v>
       </c>
     </row>
     <row r="115" x14ac:dyDescent="0.25">
@@ -2050,10 +2050,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>393980000</v>
+        <v>220980000</v>
       </c>
       <c r="C115" t="n">
-        <v>1268.4626</v>
+        <v>1362.0619</v>
       </c>
     </row>
     <row r="116" x14ac:dyDescent="0.25">
@@ -2061,10 +2061,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>398920000</v>
+        <v>311760000</v>
       </c>
       <c r="C116" t="n">
-        <v>1277.0555</v>
+        <v>1348.57</v>
       </c>
     </row>
     <row r="117" x14ac:dyDescent="0.25">
@@ -2072,10 +2072,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>323589980</v>
+        <v>324880000</v>
       </c>
       <c r="C117" t="n">
-        <v>1257.8584</v>
+        <v>1333.3085</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.25">
@@ -2083,10 +2083,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>307460000</v>
+        <v>194200000</v>
       </c>
       <c r="C118" t="n">
-        <v>1266.7869</v>
+        <v>1329.5576</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.25">
@@ -2094,10 +2094,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>297000000</v>
+        <v>219200000</v>
       </c>
       <c r="C119" t="n">
-        <v>1282.9048</v>
+        <v>1324.7351</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.25">
@@ -2105,10 +2105,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>291500000</v>
+        <v>265100000</v>
       </c>
       <c r="C120" t="n">
-        <v>1287.3202</v>
+        <v>1327.6069</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.25">
@@ -2116,10 +2116,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>242700000</v>
+        <v>318140000</v>
       </c>
       <c r="C121" t="n">
-        <v>1261.1036</v>
+        <v>1317.6909</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.25">
@@ -2127,10 +2127,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>183370000</v>
+        <v>323640000</v>
       </c>
       <c r="C122" t="n">
-        <v>1259.6484</v>
+        <v>1317.75</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.25">
@@ -2138,10 +2138,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>241900000</v>
+        <v>258100000</v>
       </c>
       <c r="C123" t="n">
-        <v>1261.8157</v>
+        <v>1298.143</v>
       </c>
     </row>
     <row r="124" x14ac:dyDescent="0.25">
@@ -2149,10 +2149,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>273740000</v>
+        <v>245450000</v>
       </c>
       <c r="C124" t="n">
-        <v>1278.3525</v>
+        <v>1296.6727</v>
       </c>
     </row>
     <row r="125" x14ac:dyDescent="0.25">
@@ -2160,10 +2160,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>212100000</v>
+        <v>388200000</v>
       </c>
       <c r="C125" t="n">
-        <v>1290.4521</v>
+        <v>1293.891</v>
       </c>
     </row>
     <row r="126" x14ac:dyDescent="0.25">
@@ -2171,10 +2171,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>308300000</v>
+        <v>218250000</v>
       </c>
       <c r="C126" t="n">
-        <v>1295.2175</v>
+        <v>1299.0688</v>
       </c>
     </row>
     <row r="127" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>165990000</v>
+        <v>135000000</v>
       </c>
       <c r="C127" t="n">
-        <v>1297.3605</v>
+        <v>1311.6884</v>
       </c>
     </row>
     <row r="128" x14ac:dyDescent="0.25">
@@ -2193,10 +2193,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>328600000</v>
+        <v>230420000</v>
       </c>
       <c r="C128" t="n">
-        <v>1357.0087</v>
+        <v>1322.621</v>
       </c>
     </row>
     <row r="129" x14ac:dyDescent="0.25">
@@ -2204,10 +2204,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>213740000</v>
+        <v>186010000</v>
       </c>
       <c r="C129" t="n">
-        <v>1364.9274</v>
+        <v>1349.7838</v>
       </c>
     </row>
     <row r="130" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>220980000</v>
+        <v>324380030</v>
       </c>
       <c r="C130" t="n">
-        <v>1362.0619</v>
+        <v>1353.8998</v>
       </c>
     </row>
     <row r="131" x14ac:dyDescent="0.25">
@@ -2226,10 +2226,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>311760000</v>
+        <v>188250000</v>
       </c>
       <c r="C131" t="n">
-        <v>1348.57</v>
+        <v>1360.0135</v>
       </c>
     </row>
     <row r="132" x14ac:dyDescent="0.25">
@@ -2237,10 +2237,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>324880000</v>
+        <v>262170000</v>
       </c>
       <c r="C132" t="n">
-        <v>1333.3085</v>
+        <v>1338.8757</v>
       </c>
     </row>
     <row r="133" x14ac:dyDescent="0.25">
@@ -2248,10 +2248,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>194200000</v>
+        <v>250290000</v>
       </c>
       <c r="C133" t="n">
-        <v>1329.5576</v>
+        <v>1330.1678</v>
       </c>
     </row>
     <row r="134" x14ac:dyDescent="0.25">
@@ -2259,10 +2259,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>219200000</v>
+        <v>396959970</v>
       </c>
       <c r="C134" t="n">
-        <v>1324.7351</v>
+        <v>1365.224</v>
       </c>
     </row>
     <row r="135" x14ac:dyDescent="0.25">
@@ -2270,10 +2270,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>265100000</v>
+        <v>181300000</v>
       </c>
       <c r="C135" t="n">
-        <v>1327.6069</v>
+        <v>1361.4104</v>
       </c>
     </row>
     <row r="136" x14ac:dyDescent="0.25">
@@ -2281,10 +2281,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>318140000</v>
+        <v>349490020</v>
       </c>
       <c r="C136" t="n">
-        <v>1317.6909</v>
+        <v>1362.602</v>
       </c>
     </row>
     <row r="137" x14ac:dyDescent="0.25">
@@ -2292,10 +2292,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>323640000</v>
+        <v>354610000</v>
       </c>
       <c r="C137" t="n">
-        <v>1317.75</v>
+        <v>1366.1288</v>
       </c>
     </row>
     <row r="138" x14ac:dyDescent="0.25">
@@ -2303,10 +2303,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>258100000</v>
+        <v>268370000</v>
       </c>
       <c r="C138" t="n">
-        <v>1298.143</v>
+        <v>1424.0941</v>
       </c>
     </row>
     <row r="139" x14ac:dyDescent="0.25">
@@ -2314,10 +2314,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>245450000</v>
+        <v>217230000</v>
       </c>
       <c r="C139" t="n">
-        <v>1296.6727</v>
+        <v>1419.2301</v>
       </c>
     </row>
     <row r="140" x14ac:dyDescent="0.25">
@@ -2325,10 +2325,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>388200000</v>
+        <v>202800000</v>
       </c>
       <c r="C140" t="n">
-        <v>1293.891</v>
+        <v>1418.7997</v>
       </c>
     </row>
     <row r="141" x14ac:dyDescent="0.25">
@@ -2336,10 +2336,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>218250000</v>
+        <v>182600000</v>
       </c>
       <c r="C141" t="n">
-        <v>1299.0688</v>
+        <v>1428.8804</v>
       </c>
     </row>
     <row r="142" x14ac:dyDescent="0.25">
@@ -2347,10 +2347,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>135000000</v>
+        <v>186830000</v>
       </c>
       <c r="C142" t="n">
-        <v>1311.6884</v>
+        <v>1450.185</v>
       </c>
     </row>
     <row r="143" x14ac:dyDescent="0.25">
@@ -2358,10 +2358,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>230420000</v>
+        <v>256060000</v>
       </c>
       <c r="C143" t="n">
-        <v>1322.621</v>
+        <v>1463.845</v>
       </c>
     </row>
     <row r="144" x14ac:dyDescent="0.25">
@@ -2369,10 +2369,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>186010000</v>
+        <v>181350000</v>
       </c>
       <c r="C144" t="n">
-        <v>1349.7838</v>
+        <v>1464.3728</v>
       </c>
     </row>
     <row r="145" x14ac:dyDescent="0.25">
@@ -2380,10 +2380,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>324380030</v>
+        <v>175400000</v>
       </c>
       <c r="C145" t="n">
-        <v>1353.8998</v>
+        <v>1473.9847</v>
       </c>
     </row>
     <row r="146" x14ac:dyDescent="0.25">
@@ -2391,10 +2391,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>188250000</v>
+        <v>231000000</v>
       </c>
       <c r="C146" t="n">
-        <v>1360.0135</v>
+        <v>1474.4945</v>
       </c>
     </row>
     <row r="147" x14ac:dyDescent="0.25">
@@ -2402,10 +2402,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>262170000</v>
+        <v>286250020</v>
       </c>
       <c r="C147" t="n">
-        <v>1338.8757</v>
+        <v>1475.4567</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.25">
@@ -2413,10 +2413,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>250290000</v>
+        <v>202930000</v>
       </c>
       <c r="C148" t="n">
-        <v>1330.1678</v>
+        <v>1432.3635</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.25">
@@ -2424,10 +2424,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>396959970</v>
+        <v>275320000</v>
       </c>
       <c r="C149" t="n">
-        <v>1365.224</v>
+        <v>1355.8541</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.25">
@@ -2435,10 +2435,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>181300000</v>
+        <v>480600000</v>
       </c>
       <c r="C150" t="n">
-        <v>1361.4104</v>
+        <v>1349.3301</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.25">
@@ -2446,10 +2446,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>349490020</v>
+        <v>589150000</v>
       </c>
       <c r="C151" t="n">
-        <v>1362.602</v>
+        <v>1328.1084</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.25">
@@ -2457,10 +2457,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>354610000</v>
+        <v>392600000</v>
       </c>
       <c r="C152" t="n">
-        <v>1366.1288</v>
+        <v>1331.5554</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.25">
@@ -2468,10 +2468,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>268370000</v>
+        <v>478160000</v>
       </c>
       <c r="C153" t="n">
-        <v>1424.0941</v>
+        <v>1341.6771</v>
       </c>
     </row>
     <row r="154" x14ac:dyDescent="0.25">
@@ -2479,10 +2479,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>217230000</v>
+        <v>496829980</v>
       </c>
       <c r="C154" t="n">
-        <v>1419.2301</v>
+        <v>1374.025</v>
       </c>
     </row>
     <row r="155" x14ac:dyDescent="0.25">
@@ -2490,10 +2490,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>202800000</v>
+        <v>295170020</v>
       </c>
       <c r="C155" t="n">
-        <v>1418.7997</v>
+        <v>1424.7794</v>
       </c>
     </row>
     <row r="156" x14ac:dyDescent="0.25">
@@ -2501,10 +2501,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>182600000</v>
+        <v>169440000</v>
       </c>
       <c r="C156" t="n">
-        <v>1428.8804</v>
+        <v>1424.6221</v>
       </c>
     </row>
     <row r="157" x14ac:dyDescent="0.25">
@@ -2512,10 +2512,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>186830000</v>
+        <v>215520000</v>
       </c>
       <c r="C157" t="n">
-        <v>1450.185</v>
+        <v>1424.9015</v>
       </c>
     </row>
     <row r="158" x14ac:dyDescent="0.25">
@@ -2523,10 +2523,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>256060000</v>
+        <v>262840000</v>
       </c>
       <c r="C158" t="n">
-        <v>1463.845</v>
+        <v>1429.9982</v>
       </c>
     </row>
     <row r="159" x14ac:dyDescent="0.25">
@@ -2534,10 +2534,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>181350000</v>
+        <v>315000000</v>
       </c>
       <c r="C159" t="n">
-        <v>1464.3728</v>
+        <v>1430.0143</v>
       </c>
     </row>
     <row r="160" x14ac:dyDescent="0.25">
@@ -2545,10 +2545,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>175400000</v>
+        <v>338970020</v>
       </c>
       <c r="C160" t="n">
-        <v>1473.9847</v>
+        <v>1430.0298</v>
       </c>
     </row>
     <row r="161" x14ac:dyDescent="0.25">
@@ -2556,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>231000000</v>
+        <v>260880000</v>
       </c>
       <c r="C161" t="n">
-        <v>1474.4945</v>
+        <v>1445.8451</v>
       </c>
     </row>
     <row r="162" x14ac:dyDescent="0.25">
@@ -2567,10 +2567,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>286250020</v>
+        <v>346149980</v>
       </c>
       <c r="C162" t="n">
-        <v>1475.4567</v>
+        <v>1360.5026</v>
       </c>
     </row>
     <row r="163" x14ac:dyDescent="0.25">
@@ -2578,10 +2578,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>202930000</v>
+        <v>431149980</v>
       </c>
       <c r="C163" t="n">
-        <v>1432.3635</v>
+        <v>1374.594</v>
       </c>
     </row>
     <row r="164" x14ac:dyDescent="0.25">
@@ -2589,10 +2589,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>275320000</v>
+        <v>279500000</v>
       </c>
       <c r="C164" t="n">
-        <v>1355.8541</v>
+        <v>1391.4231</v>
       </c>
     </row>
     <row r="165" x14ac:dyDescent="0.25">
@@ -2600,10 +2600,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>480600000</v>
+        <v>357400000</v>
       </c>
       <c r="C165" t="n">
-        <v>1349.3301</v>
+        <v>1451.0302</v>
       </c>
     </row>
     <row r="166" x14ac:dyDescent="0.25">
@@ -2611,10 +2611,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>589150000</v>
+        <v>254070000</v>
       </c>
       <c r="C166" t="n">
-        <v>1328.1084</v>
+        <v>1468.6167</v>
       </c>
     </row>
     <row r="167" x14ac:dyDescent="0.25">
@@ -2622,10 +2622,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>392600000</v>
+        <v>405740000</v>
       </c>
       <c r="C167" t="n">
-        <v>1331.5554</v>
+        <v>1487.8336</v>
       </c>
     </row>
     <row r="168" x14ac:dyDescent="0.25">
@@ -2633,10 +2633,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>478160000</v>
+        <v>521350000</v>
       </c>
       <c r="C168" t="n">
-        <v>1341.6771</v>
+        <v>1487.5168</v>
       </c>
     </row>
     <row r="169" x14ac:dyDescent="0.25">
@@ -2644,10 +2644,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>496829980</v>
+        <v>393340030</v>
       </c>
       <c r="C169" t="n">
-        <v>1374.025</v>
+        <v>1484.1284</v>
       </c>
     </row>
     <row r="170" x14ac:dyDescent="0.25">
@@ -2655,10 +2655,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>295170020</v>
+        <v>423890020</v>
       </c>
       <c r="C170" t="n">
-        <v>1424.7794</v>
+        <v>1487.86</v>
       </c>
     </row>
     <row r="171" x14ac:dyDescent="0.25">
@@ -2666,10 +2666,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>169440000</v>
+        <v>176000000</v>
       </c>
       <c r="C171" t="n">
-        <v>1424.6221</v>
+        <v>1399.3921</v>
       </c>
     </row>
     <row r="172" x14ac:dyDescent="0.25">
@@ -2677,10 +2677,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>215520000</v>
+        <v>334980000</v>
       </c>
       <c r="C172" t="n">
-        <v>1424.9015</v>
+        <v>1470.8683</v>
       </c>
     </row>
     <row r="173" x14ac:dyDescent="0.25">
@@ -2688,10 +2688,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>262840000</v>
+        <v>139200000</v>
       </c>
       <c r="C173" t="n">
-        <v>1429.9982</v>
+        <v>1451.923</v>
       </c>
     </row>
     <row r="174" x14ac:dyDescent="0.25">
@@ -2699,10 +2699,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>315000000</v>
+        <v>127040000</v>
       </c>
       <c r="C174" t="n">
-        <v>1430.0143</v>
+        <v>1434.8594</v>
       </c>
     </row>
     <row r="175" x14ac:dyDescent="0.25">
@@ -2710,10 +2710,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>338970020</v>
+        <v>189260000</v>
       </c>
       <c r="C175" t="n">
-        <v>1430.0298</v>
+        <v>1445.9563</v>
       </c>
     </row>
     <row r="176" x14ac:dyDescent="0.25">
@@ -2721,10 +2721,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>260880000</v>
+        <v>275010000</v>
       </c>
       <c r="C176" t="n">
-        <v>1445.8451</v>
+        <v>1464.5646</v>
       </c>
     </row>
     <row r="177" x14ac:dyDescent="0.25">
@@ -2732,10 +2732,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>346149980</v>
+        <v>194450000</v>
       </c>
       <c r="C177" t="n">
-        <v>1360.5026</v>
+        <v>1471.4487</v>
       </c>
     </row>
     <row r="178" x14ac:dyDescent="0.25">
@@ -2743,10 +2743,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>431149980</v>
+        <v>196250000</v>
       </c>
       <c r="C178" t="n">
-        <v>1374.594</v>
+        <v>1447.6355</v>
       </c>
     </row>
     <row r="179" x14ac:dyDescent="0.25">
@@ -2754,10 +2754,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>279500000</v>
+        <v>208000000</v>
       </c>
       <c r="C179" t="n">
-        <v>1391.4231</v>
+        <v>1434.8132</v>
       </c>
     </row>
     <row r="180" x14ac:dyDescent="0.25">
@@ -2765,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>357400000</v>
+        <v>209360000</v>
       </c>
       <c r="C180" t="n">
-        <v>1451.0302</v>
+        <v>1420.3748</v>
       </c>
     </row>
     <row r="181" x14ac:dyDescent="0.25">
@@ -2776,10 +2776,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>254070000</v>
+        <v>212720000</v>
       </c>
       <c r="C181" t="n">
-        <v>1468.6167</v>
+        <v>1403.0524</v>
       </c>
     </row>
     <row r="182" x14ac:dyDescent="0.25">
@@ -2787,10 +2787,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>405740000</v>
+        <v>241830000</v>
       </c>
       <c r="C182" t="n">
-        <v>1487.8336</v>
+        <v>1407.8024</v>
       </c>
     </row>
     <row r="183" x14ac:dyDescent="0.25">
@@ -2798,10 +2798,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>521350000</v>
+        <v>312580000</v>
       </c>
       <c r="C183" t="n">
-        <v>1487.5168</v>
+        <v>1404.9287</v>
       </c>
     </row>
     <row r="184" x14ac:dyDescent="0.25">
@@ -2809,10 +2809,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>393340030</v>
+        <v>179500000</v>
       </c>
       <c r="C184" t="n">
-        <v>1484.1284</v>
+        <v>1401.7639</v>
       </c>
     </row>
     <row r="185" x14ac:dyDescent="0.25">
@@ -2820,10 +2820,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>423890020</v>
+        <v>107500000</v>
       </c>
       <c r="C185" t="n">
-        <v>1487.86</v>
+        <v>1392.025</v>
       </c>
     </row>
     <row r="186" x14ac:dyDescent="0.25">
@@ -2831,10 +2831,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>176000000</v>
+        <v>242990000</v>
       </c>
       <c r="C186" t="n">
-        <v>1399.3921</v>
+        <v>1402.779</v>
       </c>
     </row>
     <row r="187" x14ac:dyDescent="0.25">
@@ -2842,10 +2842,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>334980000</v>
+        <v>254470000</v>
       </c>
       <c r="C187" t="n">
-        <v>1470.8683</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="188" x14ac:dyDescent="0.25">
@@ -2853,10 +2853,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>139200000</v>
+        <v>331130000</v>
       </c>
       <c r="C188" t="n">
-        <v>1451.923</v>
+        <v>1446.06</v>
       </c>
     </row>
     <row r="189" x14ac:dyDescent="0.25">
@@ -2864,10 +2864,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>127040000</v>
+        <v>237200000</v>
       </c>
       <c r="C189" t="n">
-        <v>1434.8594</v>
+        <v>1450.5885</v>
       </c>
     </row>
     <row r="190" x14ac:dyDescent="0.25">
@@ -2875,10 +2875,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>189260000</v>
+        <v>268310000</v>
       </c>
       <c r="C190" t="n">
-        <v>1445.9563</v>
+        <v>1450.6201</v>
       </c>
     </row>
     <row r="191" x14ac:dyDescent="0.25">
@@ -2886,10 +2886,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>275010000</v>
+        <v>293410020</v>
       </c>
       <c r="C191" t="n">
-        <v>1464.5646</v>
+        <v>1449.9003</v>
       </c>
     </row>
     <row r="192" x14ac:dyDescent="0.25">
@@ -2897,10 +2897,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>194450000</v>
+        <v>190400000</v>
       </c>
       <c r="C192" t="n">
-        <v>1471.4487</v>
+        <v>1454.6627</v>
       </c>
     </row>
     <row r="193" x14ac:dyDescent="0.25">
@@ -2908,10 +2908,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>196250000</v>
+        <v>147700000</v>
       </c>
       <c r="C193" t="n">
-        <v>1447.6355</v>
+        <v>1453.8477</v>
       </c>
     </row>
     <row r="194" x14ac:dyDescent="0.25">
@@ -2919,10 +2919,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>208000000</v>
+        <v>152560000</v>
       </c>
       <c r="C194" t="n">
-        <v>1434.8132</v>
+        <v>1447.5896</v>
       </c>
     </row>
     <row r="195" x14ac:dyDescent="0.25">
@@ -2930,10 +2930,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>209360000</v>
+        <v>195400000</v>
       </c>
       <c r="C195" t="n">
-        <v>1420.3748</v>
+        <v>1440.0085</v>
       </c>
     </row>
     <row r="196" x14ac:dyDescent="0.25">
@@ -2941,10 +2941,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>212720000</v>
+        <v>185680000</v>
       </c>
       <c r="C196" t="n">
-        <v>1403.0524</v>
+        <v>1439.3232</v>
       </c>
     </row>
     <row r="197" x14ac:dyDescent="0.25">
@@ -2952,10 +2952,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>241830000</v>
+        <v>158700000</v>
       </c>
       <c r="C197" t="n">
-        <v>1407.8024</v>
+        <v>1438.0428</v>
       </c>
     </row>
     <row r="198" x14ac:dyDescent="0.25">
@@ -2963,10 +2963,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>312580000</v>
+        <v>250300000</v>
       </c>
       <c r="C198" t="n">
-        <v>1404.9287</v>
+        <v>1437.9939</v>
       </c>
     </row>
     <row r="199" x14ac:dyDescent="0.25">
@@ -2974,10 +2974,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>179500000</v>
+        <v>192580000</v>
       </c>
       <c r="C199" t="n">
-        <v>1401.7639</v>
+        <v>1439.1218</v>
       </c>
     </row>
     <row r="200" x14ac:dyDescent="0.25">
@@ -2985,10 +2985,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>107500000</v>
+        <v>244040000</v>
       </c>
       <c r="C200" t="n">
-        <v>1392.025</v>
+        <v>1440.4795</v>
       </c>
     </row>
     <row r="201" x14ac:dyDescent="0.25">
@@ -2996,10 +2996,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>242990000</v>
+        <v>298200000</v>
       </c>
       <c r="C201" t="n">
-        <v>1402.779</v>
+        <v>1452.0646</v>
       </c>
     </row>
     <row r="202" x14ac:dyDescent="0.25">
@@ -3007,10 +3007,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>254470000</v>
+        <v>182310000</v>
       </c>
       <c r="C202" t="n">
-        <v>1418.6</v>
+        <v>1449.3583</v>
       </c>
     </row>
     <row r="203" x14ac:dyDescent="0.25">
@@ -3018,10 +3018,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>331130000</v>
+        <v>349300000</v>
       </c>
       <c r="C203" t="n">
-        <v>1446.06</v>
+        <v>1453.4788</v>
       </c>
     </row>
     <row r="204" x14ac:dyDescent="0.25">
@@ -3029,10 +3029,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>237200000</v>
+        <v>247100000</v>
       </c>
       <c r="C204" t="n">
-        <v>1450.5885</v>
+        <v>1452.151</v>
       </c>
     </row>
     <row r="205" x14ac:dyDescent="0.25">
@@ -3040,10 +3040,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>268310000</v>
+        <v>245750000</v>
       </c>
       <c r="C205" t="n">
-        <v>1450.6201</v>
+        <v>1451.3027</v>
       </c>
     </row>
     <row r="206" x14ac:dyDescent="0.25">
@@ -3051,10 +3051,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>293410020</v>
+        <v>335240030</v>
       </c>
       <c r="C206" t="n">
-        <v>1449.9003</v>
+        <v>1450.3435</v>
       </c>
     </row>
     <row r="207" x14ac:dyDescent="0.25">
@@ -3062,10 +3062,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>190400000</v>
+        <v>275000000</v>
       </c>
       <c r="C207" t="n">
-        <v>1454.6627</v>
+        <v>1451.9496</v>
       </c>
     </row>
     <row r="208" x14ac:dyDescent="0.25">
@@ -3073,10 +3073,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>147700000</v>
+        <v>451869980</v>
       </c>
       <c r="C208" t="n">
-        <v>1453.8477</v>
+        <v>1455.7809</v>
       </c>
     </row>
     <row r="209" x14ac:dyDescent="0.25">
@@ -3084,10 +3084,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>152560000</v>
+        <v>216460000</v>
       </c>
       <c r="C209" t="n">
-        <v>1447.5896</v>
+        <v>1459.2133</v>
       </c>
     </row>
     <row r="210" x14ac:dyDescent="0.25">
@@ -3095,10 +3095,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>195400000</v>
+        <v>257600000</v>
       </c>
       <c r="C210" t="n">
-        <v>1440.0085</v>
+        <v>1469.6405</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.25">
@@ -3106,10 +3106,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>185680000</v>
+        <v>188200000</v>
       </c>
       <c r="C211" t="n">
-        <v>1439.3232</v>
+        <v>1473.0568</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.25">
@@ -3117,10 +3117,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>158700000</v>
+        <v>130800000</v>
       </c>
       <c r="C212" t="n">
-        <v>1438.0428</v>
+        <v>1467.733</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>250300000</v>
+        <v>156300000</v>
       </c>
       <c r="C213" t="n">
-        <v>1437.9939</v>
+        <v>1466.4419</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.25">
@@ -3139,10 +3139,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>192580000</v>
+        <v>222610000</v>
       </c>
       <c r="C214" t="n">
-        <v>1439.1218</v>
+        <v>1459.4448</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.25">
@@ -3150,10 +3150,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>244040000</v>
+        <v>225200000</v>
       </c>
       <c r="C215" t="n">
-        <v>1440.4795</v>
+        <v>1466.5925</v>
       </c>
     </row>
     <row r="216" x14ac:dyDescent="0.25">
@@ -3161,10 +3161,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>298200000</v>
+        <v>120370000</v>
       </c>
       <c r="C216" t="n">
-        <v>1452.0646</v>
+        <v>1466.7234</v>
       </c>
     </row>
     <row r="217" x14ac:dyDescent="0.25">
@@ -3172,10 +3172,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>182310000</v>
+        <v>280909980</v>
       </c>
       <c r="C217" t="n">
-        <v>1449.3583</v>
+        <v>1463.5974</v>
       </c>
     </row>
     <row r="218" x14ac:dyDescent="0.25">
@@ -3183,10 +3183,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>349300000</v>
+        <v>152620000</v>
       </c>
       <c r="C218" t="n">
-        <v>1453.4788</v>
+        <v>1454.3422</v>
       </c>
     </row>
     <row r="219" x14ac:dyDescent="0.25">
@@ -3194,10 +3194,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>247100000</v>
+        <v>226710000</v>
       </c>
       <c r="C219" t="n">
-        <v>1452.151</v>
+        <v>1444.1166</v>
       </c>
     </row>
     <row r="220" x14ac:dyDescent="0.25">
@@ -3205,10 +3205,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>245750000</v>
+        <v>198520000</v>
       </c>
       <c r="C220" t="n">
-        <v>1451.3027</v>
+        <v>1430.8835</v>
       </c>
     </row>
     <row r="221" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>335240030</v>
+        <v>169850000</v>
       </c>
       <c r="C221" t="n">
-        <v>1450.3435</v>
+        <v>1435.7379</v>
       </c>
     </row>
     <row r="222" x14ac:dyDescent="0.25">
@@ -3227,10 +3227,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>275000000</v>
+        <v>192350000</v>
       </c>
       <c r="C222" t="n">
-        <v>1451.9496</v>
+        <v>1429.8312</v>
       </c>
     </row>
     <row r="223" x14ac:dyDescent="0.25">
@@ -3238,10 +3238,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>451869980</v>
+        <v>203400000</v>
       </c>
       <c r="C223" t="n">
-        <v>1455.7809</v>
+        <v>1427.0317</v>
       </c>
     </row>
     <row r="224" x14ac:dyDescent="0.25">
@@ -3249,10 +3249,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>216460000</v>
+        <v>230700000</v>
       </c>
       <c r="C224" t="n">
-        <v>1459.2133</v>
+        <v>1432.9178</v>
       </c>
     </row>
     <row r="225" x14ac:dyDescent="0.25">
@@ -3260,10 +3260,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>257600000</v>
+        <v>201940000</v>
       </c>
       <c r="C225" t="n">
-        <v>1469.6405</v>
+        <v>1438.5153</v>
       </c>
     </row>
     <row r="226" x14ac:dyDescent="0.25">
@@ -3271,10 +3271,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>188200000</v>
+        <v>246000000</v>
       </c>
       <c r="C226" t="n">
-        <v>1473.0568</v>
+        <v>1441.2004</v>
       </c>
     </row>
     <row r="227" x14ac:dyDescent="0.25">
@@ -3282,10 +3282,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>130800000</v>
+        <v>184740000</v>
       </c>
       <c r="C227" t="n">
-        <v>1467.733</v>
+        <v>1442.5574</v>
       </c>
     </row>
     <row r="228" x14ac:dyDescent="0.25">
@@ -3293,10 +3293,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>156300000</v>
+        <v>213660000</v>
       </c>
       <c r="C228" t="n">
-        <v>1466.4419</v>
+        <v>1446.1775</v>
       </c>
     </row>
     <row r="229" x14ac:dyDescent="0.25">
@@ -3304,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>222610000</v>
+        <v>173170000</v>
       </c>
       <c r="C229" t="n">
-        <v>1459.4448</v>
+        <v>1447.7574</v>
       </c>
     </row>
     <row r="230" x14ac:dyDescent="0.25">
@@ -3315,10 +3315,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>225200000</v>
+        <v>140570000</v>
       </c>
       <c r="C230" t="n">
-        <v>1466.5925</v>
+        <v>1451.5089</v>
       </c>
     </row>
     <row r="231" x14ac:dyDescent="0.25">
@@ -3326,10 +3326,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>120370000</v>
+        <v>211040000</v>
       </c>
       <c r="C231" t="n">
-        <v>1466.7234</v>
+        <v>1447.9523</v>
       </c>
     </row>
     <row r="232" x14ac:dyDescent="0.25">
@@ -3337,10 +3337,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>280909980</v>
+        <v>231130000</v>
       </c>
       <c r="C232" t="n">
-        <v>1463.5974</v>
+        <v>1447.759</v>
       </c>
     </row>
     <row r="233" x14ac:dyDescent="0.25">
@@ -3348,10 +3348,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>305240000</v>
+        <v>459440000</v>
       </c>
       <c r="C233" t="n">
-        <v>1454.3422</v>
+        <v>1445.5366</v>
       </c>
     </row>
   </sheetData>
